--- a/logs/massive_topology_search/massive_topology_search.xlsx
+++ b/logs/massive_topology_search/massive_topology_search.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgep-my.sharepoint.com/personal/uxue_ballarin_alumni_mondragon_edu/Documents/Semestre 8-Erasmus/Simula/ship_qnn/logs/massive_topology_search/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="111" documentId="11_AD4D2F04E46CFB4ACB3E20D455D6CCDA693EDF1F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{71CB5A8F-76DC-4FDD-888F-3689BCF5ACFD}"/>
+  <xr:revisionPtr revIDLastSave="115" documentId="11_AD4D2F04E46CFB4ACB3E20D455D6CCDA693EDF1F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BDD347DC-735D-447B-8EA7-BC170726EA95}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="8" r:id="rId3"/>
+    <pivotCache cacheId="3" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2403" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2369" uniqueCount="268">
   <si>
     <t>date</t>
   </si>
@@ -890,7 +890,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -905,13 +905,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="3"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="4"/>
-    </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
@@ -9953,8 +9947,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2D21AEEF-8491-4048-847C-B48B541C6815}" name="TablaDinámica1" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A2:L67" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2D21AEEF-8491-4048-847C-B48B541C6815}" name="TablaDinámica1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A2:L30" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="75">
     <pivotField numFmtId="164" showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
@@ -9991,10 +9985,10 @@
     <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
       <items count="5">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="2"/>
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -10082,7 +10076,7 @@
     <field x="21"/>
     <field x="2"/>
   </rowFields>
-  <rowItems count="65">
+  <rowItems count="28">
     <i>
       <x/>
     </i>
@@ -10092,32 +10086,11 @@
     <i r="2">
       <x v="1"/>
     </i>
-    <i r="3">
-      <x/>
-    </i>
-    <i r="3">
-      <x v="4"/>
-    </i>
-    <i r="3">
-      <x v="6"/>
-    </i>
     <i r="2">
       <x v="2"/>
     </i>
-    <i r="3">
-      <x v="4"/>
-    </i>
-    <i r="3">
-      <x v="6"/>
-    </i>
     <i r="2">
       <x v="3"/>
-    </i>
-    <i r="3">
-      <x v="4"/>
-    </i>
-    <i r="3">
-      <x v="6"/>
     </i>
     <i r="1">
       <x v="1"/>
@@ -10125,35 +10098,11 @@
     <i r="2">
       <x v="1"/>
     </i>
-    <i r="3">
-      <x v="4"/>
-    </i>
-    <i r="3">
-      <x v="6"/>
-    </i>
     <i r="2">
-      <x v="2"/>
-    </i>
-    <i r="3">
-      <x v="4"/>
-    </i>
-    <i r="3">
-      <x v="6"/>
-    </i>
-    <i r="3">
-      <x v="7"/>
-    </i>
-    <i r="4">
       <x v="2"/>
     </i>
     <i r="2">
       <x v="3"/>
-    </i>
-    <i r="3">
-      <x v="4"/>
-    </i>
-    <i r="3">
-      <x v="6"/>
     </i>
     <i r="1">
       <x v="2"/>
@@ -10161,29 +10110,11 @@
     <i r="2">
       <x v="1"/>
     </i>
-    <i r="3">
-      <x v="4"/>
-    </i>
-    <i r="3">
-      <x v="6"/>
-    </i>
     <i r="2">
       <x v="2"/>
     </i>
-    <i r="3">
-      <x v="4"/>
-    </i>
-    <i r="3">
-      <x v="6"/>
-    </i>
     <i r="2">
       <x v="3"/>
-    </i>
-    <i r="3">
-      <x v="4"/>
-    </i>
-    <i r="3">
-      <x v="6"/>
     </i>
     <i>
       <x v="1"/>
@@ -10194,29 +10125,14 @@
     <i r="2">
       <x/>
     </i>
-    <i r="3">
-      <x v="2"/>
-    </i>
     <i r="2">
       <x v="1"/>
-    </i>
-    <i r="3">
-      <x v="2"/>
-    </i>
-    <i r="3">
-      <x v="3"/>
     </i>
     <i r="2">
       <x v="2"/>
     </i>
-    <i r="3">
-      <x v="2"/>
-    </i>
     <i r="2">
       <x v="3"/>
-    </i>
-    <i r="3">
-      <x v="2"/>
     </i>
     <i r="1">
       <x v="1"/>
@@ -10224,35 +10140,14 @@
     <i r="2">
       <x/>
     </i>
-    <i r="3">
-      <x v="1"/>
-    </i>
-    <i r="3">
-      <x v="2"/>
-    </i>
-    <i r="3">
-      <x v="3"/>
-    </i>
-    <i r="3">
-      <x v="5"/>
-    </i>
     <i r="2">
       <x v="1"/>
-    </i>
-    <i r="3">
-      <x v="2"/>
     </i>
     <i r="1">
       <x v="2"/>
     </i>
     <i r="2">
       <x/>
-    </i>
-    <i r="3">
-      <x v="2"/>
-    </i>
-    <i r="3">
-      <x v="5"/>
     </i>
     <i>
       <x v="2"/>
@@ -10262,18 +10157,6 @@
     </i>
     <i r="2">
       <x v="1"/>
-    </i>
-    <i r="3">
-      <x v="4"/>
-    </i>
-    <i r="3">
-      <x v="5"/>
-    </i>
-    <i r="3">
-      <x v="8"/>
-    </i>
-    <i r="3">
-      <x v="9"/>
     </i>
     <i t="grand">
       <x/>
@@ -10929,7 +10812,7 @@
       <c r="B2" t="s">
         <v>150</v>
       </c>
-      <c r="C2" s="9">
+      <c r="C2" s="7">
         <v>2</v>
       </c>
       <c r="D2" t="s">
@@ -10950,10 +10833,10 @@
       <c r="I2" t="s">
         <v>79</v>
       </c>
-      <c r="J2" s="9">
+      <c r="J2" s="7">
         <v>5</v>
       </c>
-      <c r="K2" s="9">
+      <c r="K2" s="7">
         <v>5</v>
       </c>
       <c r="L2" t="s">
@@ -10974,7 +10857,7 @@
       <c r="Q2" t="s">
         <v>146</v>
       </c>
-      <c r="R2" s="9">
+      <c r="R2" s="7">
         <v>3</v>
       </c>
       <c r="S2" t="s">
@@ -11153,7 +11036,7 @@
       <c r="B3" t="s">
         <v>120</v>
       </c>
-      <c r="C3" s="9">
+      <c r="C3" s="7">
         <v>1</v>
       </c>
       <c r="D3" t="s">
@@ -11174,10 +11057,10 @@
       <c r="I3" t="s">
         <v>79</v>
       </c>
-      <c r="J3" s="9">
+      <c r="J3" s="7">
         <v>5</v>
       </c>
-      <c r="K3" s="9">
+      <c r="K3" s="7">
         <v>5</v>
       </c>
       <c r="L3" t="s">
@@ -11198,7 +11081,7 @@
       <c r="Q3" t="s">
         <v>121</v>
       </c>
-      <c r="R3" s="9">
+      <c r="R3" s="7">
         <v>3</v>
       </c>
       <c r="S3" t="s">
@@ -11377,7 +11260,7 @@
       <c r="B4" t="s">
         <v>152</v>
       </c>
-      <c r="C4" s="9">
+      <c r="C4" s="7">
         <v>3</v>
       </c>
       <c r="D4" t="s">
@@ -11398,10 +11281,10 @@
       <c r="I4" t="s">
         <v>79</v>
       </c>
-      <c r="J4" s="9">
+      <c r="J4" s="7">
         <v>5</v>
       </c>
-      <c r="K4" s="9">
+      <c r="K4" s="7">
         <v>5</v>
       </c>
       <c r="L4" t="s">
@@ -11422,7 +11305,7 @@
       <c r="Q4" t="s">
         <v>146</v>
       </c>
-      <c r="R4" s="9">
+      <c r="R4" s="7">
         <v>3</v>
       </c>
       <c r="S4" t="s">
@@ -11601,7 +11484,7 @@
       <c r="B5" t="s">
         <v>145</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="7">
         <v>1</v>
       </c>
       <c r="D5" t="s">
@@ -11622,10 +11505,10 @@
       <c r="I5" t="s">
         <v>79</v>
       </c>
-      <c r="J5" s="9">
+      <c r="J5" s="7">
         <v>5</v>
       </c>
-      <c r="K5" s="9">
+      <c r="K5" s="7">
         <v>5</v>
       </c>
       <c r="L5" t="s">
@@ -11646,7 +11529,7 @@
       <c r="Q5" t="s">
         <v>146</v>
       </c>
-      <c r="R5" s="9">
+      <c r="R5" s="7">
         <v>3</v>
       </c>
       <c r="S5" t="s">
@@ -11825,7 +11708,7 @@
       <c r="B6" t="s">
         <v>209</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C6" s="7">
         <v>2</v>
       </c>
       <c r="D6" t="s">
@@ -11846,10 +11729,10 @@
       <c r="I6" t="s">
         <v>79</v>
       </c>
-      <c r="J6" s="9">
+      <c r="J6" s="7">
         <v>5</v>
       </c>
-      <c r="K6" s="9">
+      <c r="K6" s="7">
         <v>5</v>
       </c>
       <c r="L6" t="s">
@@ -11870,7 +11753,7 @@
       <c r="Q6" t="s">
         <v>203</v>
       </c>
-      <c r="R6" s="9">
+      <c r="R6" s="7">
         <v>4</v>
       </c>
       <c r="S6" t="s">
@@ -12049,7 +11932,7 @@
       <c r="B7" t="s">
         <v>211</v>
       </c>
-      <c r="C7" s="9">
+      <c r="C7" s="7">
         <v>1</v>
       </c>
       <c r="D7" t="s">
@@ -12070,10 +11953,10 @@
       <c r="I7" t="s">
         <v>79</v>
       </c>
-      <c r="J7" s="9">
+      <c r="J7" s="7">
         <v>5</v>
       </c>
-      <c r="K7" s="9">
+      <c r="K7" s="7">
         <v>5</v>
       </c>
       <c r="L7" t="s">
@@ -12094,7 +11977,7 @@
       <c r="Q7" t="s">
         <v>212</v>
       </c>
-      <c r="R7" s="9">
+      <c r="R7" s="7">
         <v>3</v>
       </c>
       <c r="S7" t="s">
@@ -12273,7 +12156,7 @@
       <c r="B8" t="s">
         <v>185</v>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="7">
         <v>2</v>
       </c>
       <c r="D8" t="s">
@@ -12294,10 +12177,10 @@
       <c r="I8" t="s">
         <v>79</v>
       </c>
-      <c r="J8" s="9">
+      <c r="J8" s="7">
         <v>5</v>
       </c>
-      <c r="K8" s="9">
+      <c r="K8" s="7">
         <v>5</v>
       </c>
       <c r="L8" t="s">
@@ -12318,7 +12201,7 @@
       <c r="Q8" t="s">
         <v>180</v>
       </c>
-      <c r="R8" s="9">
+      <c r="R8" s="7">
         <v>3</v>
       </c>
       <c r="S8" t="s">
@@ -12497,7 +12380,7 @@
       <c r="B9" t="s">
         <v>219</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="7">
         <v>3</v>
       </c>
       <c r="D9" t="s">
@@ -12518,10 +12401,10 @@
       <c r="I9" t="s">
         <v>79</v>
       </c>
-      <c r="J9" s="9">
+      <c r="J9" s="7">
         <v>5</v>
       </c>
-      <c r="K9" s="9">
+      <c r="K9" s="7">
         <v>5</v>
       </c>
       <c r="L9" t="s">
@@ -12542,7 +12425,7 @@
       <c r="Q9" t="s">
         <v>212</v>
       </c>
-      <c r="R9" s="9">
+      <c r="R9" s="7">
         <v>3</v>
       </c>
       <c r="S9" t="s">
@@ -12721,7 +12604,7 @@
       <c r="B10" t="s">
         <v>124</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C10" s="7">
         <v>2</v>
       </c>
       <c r="D10" t="s">
@@ -12742,10 +12625,10 @@
       <c r="I10" t="s">
         <v>79</v>
       </c>
-      <c r="J10" s="9">
+      <c r="J10" s="7">
         <v>5</v>
       </c>
-      <c r="K10" s="9">
+      <c r="K10" s="7">
         <v>5</v>
       </c>
       <c r="L10" t="s">
@@ -12766,7 +12649,7 @@
       <c r="Q10" t="s">
         <v>121</v>
       </c>
-      <c r="R10" s="9">
+      <c r="R10" s="7">
         <v>3</v>
       </c>
       <c r="S10" t="s">
@@ -12945,7 +12828,7 @@
       <c r="B11" t="s">
         <v>101</v>
       </c>
-      <c r="C11" s="9">
+      <c r="C11" s="7">
         <v>2</v>
       </c>
       <c r="D11" t="s">
@@ -12966,10 +12849,10 @@
       <c r="I11" t="s">
         <v>79</v>
       </c>
-      <c r="J11" s="9">
+      <c r="J11" s="7">
         <v>5</v>
       </c>
-      <c r="K11" s="9">
+      <c r="K11" s="7">
         <v>5</v>
       </c>
       <c r="L11" t="s">
@@ -12990,7 +12873,7 @@
       <c r="Q11" t="s">
         <v>95</v>
       </c>
-      <c r="R11" s="9">
+      <c r="R11" s="7">
         <v>3</v>
       </c>
       <c r="S11" t="s">
@@ -13169,7 +13052,7 @@
       <c r="B12" t="s">
         <v>117</v>
       </c>
-      <c r="C12" s="9">
+      <c r="C12" s="7">
         <v>3</v>
       </c>
       <c r="D12" t="s">
@@ -13190,10 +13073,10 @@
       <c r="I12" t="s">
         <v>79</v>
       </c>
-      <c r="J12" s="9">
+      <c r="J12" s="7">
         <v>5</v>
       </c>
-      <c r="K12" s="9">
+      <c r="K12" s="7">
         <v>5</v>
       </c>
       <c r="L12" t="s">
@@ -13214,7 +13097,7 @@
       <c r="Q12" t="s">
         <v>109</v>
       </c>
-      <c r="R12" s="9">
+      <c r="R12" s="7">
         <v>3</v>
       </c>
       <c r="S12" t="s">
@@ -13393,7 +13276,7 @@
       <c r="B13" t="s">
         <v>126</v>
       </c>
-      <c r="C13" s="9">
+      <c r="C13" s="7">
         <v>3</v>
       </c>
       <c r="D13" t="s">
@@ -13414,10 +13297,10 @@
       <c r="I13" t="s">
         <v>79</v>
       </c>
-      <c r="J13" s="9">
+      <c r="J13" s="7">
         <v>5</v>
       </c>
-      <c r="K13" s="9">
+      <c r="K13" s="7">
         <v>5</v>
       </c>
       <c r="L13" t="s">
@@ -13438,7 +13321,7 @@
       <c r="Q13" t="s">
         <v>121</v>
       </c>
-      <c r="R13" s="9">
+      <c r="R13" s="7">
         <v>3</v>
       </c>
       <c r="S13" t="s">
@@ -14065,7 +13948,7 @@
       <c r="B16" t="s">
         <v>218</v>
       </c>
-      <c r="C16" s="9">
+      <c r="C16" s="7">
         <v>3</v>
       </c>
       <c r="D16" t="s">
@@ -14086,10 +13969,10 @@
       <c r="I16" t="s">
         <v>79</v>
       </c>
-      <c r="J16" s="9">
+      <c r="J16" s="7">
         <v>5</v>
       </c>
-      <c r="K16" s="9">
+      <c r="K16" s="7">
         <v>5</v>
       </c>
       <c r="L16" t="s">
@@ -14110,7 +13993,7 @@
       <c r="Q16" t="s">
         <v>203</v>
       </c>
-      <c r="R16" s="9">
+      <c r="R16" s="7">
         <v>4</v>
       </c>
       <c r="S16" t="s">
@@ -14289,7 +14172,7 @@
       <c r="B17" t="s">
         <v>114</v>
       </c>
-      <c r="C17" s="9">
+      <c r="C17" s="7">
         <v>2</v>
       </c>
       <c r="D17" t="s">
@@ -14310,10 +14193,10 @@
       <c r="I17" t="s">
         <v>79</v>
       </c>
-      <c r="J17" s="9">
+      <c r="J17" s="7">
         <v>5</v>
       </c>
-      <c r="K17" s="9">
+      <c r="K17" s="7">
         <v>5</v>
       </c>
       <c r="L17" t="s">
@@ -14334,7 +14217,7 @@
       <c r="Q17" t="s">
         <v>109</v>
       </c>
-      <c r="R17" s="9">
+      <c r="R17" s="7">
         <v>3</v>
       </c>
       <c r="S17" t="s">
@@ -14513,7 +14396,7 @@
       <c r="B18" t="s">
         <v>108</v>
       </c>
-      <c r="C18" s="9">
+      <c r="C18" s="7">
         <v>1</v>
       </c>
       <c r="D18" t="s">
@@ -14534,10 +14417,10 @@
       <c r="I18" t="s">
         <v>79</v>
       </c>
-      <c r="J18" s="9">
+      <c r="J18" s="7">
         <v>5</v>
       </c>
-      <c r="K18" s="9">
+      <c r="K18" s="7">
         <v>5</v>
       </c>
       <c r="L18" t="s">
@@ -14558,7 +14441,7 @@
       <c r="Q18" t="s">
         <v>109</v>
       </c>
-      <c r="R18" s="9">
+      <c r="R18" s="7">
         <v>3</v>
       </c>
       <c r="S18" t="s">
@@ -14737,7 +14620,7 @@
       <c r="B19" t="s">
         <v>188</v>
       </c>
-      <c r="C19" s="9">
+      <c r="C19" s="7">
         <v>3</v>
       </c>
       <c r="D19" t="s">
@@ -14758,10 +14641,10 @@
       <c r="I19" t="s">
         <v>79</v>
       </c>
-      <c r="J19" s="9">
+      <c r="J19" s="7">
         <v>5</v>
       </c>
-      <c r="K19" s="9">
+      <c r="K19" s="7">
         <v>5</v>
       </c>
       <c r="L19" t="s">
@@ -14782,7 +14665,7 @@
       <c r="Q19" t="s">
         <v>175</v>
       </c>
-      <c r="R19" s="9">
+      <c r="R19" s="7">
         <v>4</v>
       </c>
       <c r="S19" t="s">
@@ -15185,7 +15068,7 @@
       <c r="B21" t="s">
         <v>189</v>
       </c>
-      <c r="C21" s="9">
+      <c r="C21" s="7">
         <v>3</v>
       </c>
       <c r="D21" t="s">
@@ -15206,10 +15089,10 @@
       <c r="I21" t="s">
         <v>79</v>
       </c>
-      <c r="J21" s="9">
+      <c r="J21" s="7">
         <v>5</v>
       </c>
-      <c r="K21" s="9">
+      <c r="K21" s="7">
         <v>5</v>
       </c>
       <c r="L21" t="s">
@@ -15230,7 +15113,7 @@
       <c r="Q21" t="s">
         <v>180</v>
       </c>
-      <c r="R21" s="9">
+      <c r="R21" s="7">
         <v>3</v>
       </c>
       <c r="S21" t="s">
@@ -15633,7 +15516,7 @@
       <c r="B23" t="s">
         <v>199</v>
       </c>
-      <c r="C23" s="9">
+      <c r="C23" s="7">
         <v>1</v>
       </c>
       <c r="D23" t="s">
@@ -15654,10 +15537,10 @@
       <c r="I23" t="s">
         <v>79</v>
       </c>
-      <c r="J23" s="9">
+      <c r="J23" s="7">
         <v>5</v>
       </c>
-      <c r="K23" s="9">
+      <c r="K23" s="7">
         <v>5</v>
       </c>
       <c r="L23" t="s">
@@ -15678,7 +15561,7 @@
       <c r="Q23" t="s">
         <v>200</v>
       </c>
-      <c r="R23" s="9">
+      <c r="R23" s="7">
         <v>3</v>
       </c>
       <c r="S23" t="s">
@@ -15857,7 +15740,7 @@
       <c r="B24" t="s">
         <v>93</v>
       </c>
-      <c r="C24" s="9">
+      <c r="C24" s="7">
         <v>1</v>
       </c>
       <c r="D24" t="s">
@@ -15878,10 +15761,10 @@
       <c r="I24" t="s">
         <v>79</v>
       </c>
-      <c r="J24" s="9">
+      <c r="J24" s="7">
         <v>5</v>
       </c>
-      <c r="K24" s="9">
+      <c r="K24" s="7">
         <v>5</v>
       </c>
       <c r="L24" t="s">
@@ -15902,7 +15785,7 @@
       <c r="Q24" t="s">
         <v>95</v>
       </c>
-      <c r="R24" s="9">
+      <c r="R24" s="7">
         <v>3</v>
       </c>
       <c r="S24" t="s">
@@ -16081,7 +15964,7 @@
       <c r="B25" t="s">
         <v>184</v>
       </c>
-      <c r="C25" s="9">
+      <c r="C25" s="7">
         <v>2</v>
       </c>
       <c r="D25" t="s">
@@ -16102,10 +15985,10 @@
       <c r="I25" t="s">
         <v>79</v>
       </c>
-      <c r="J25" s="9">
+      <c r="J25" s="7">
         <v>5</v>
       </c>
-      <c r="K25" s="9">
+      <c r="K25" s="7">
         <v>5</v>
       </c>
       <c r="L25" t="s">
@@ -16126,7 +16009,7 @@
       <c r="Q25" t="s">
         <v>175</v>
       </c>
-      <c r="R25" s="9">
+      <c r="R25" s="7">
         <v>4</v>
       </c>
       <c r="S25" t="s">
@@ -16529,7 +16412,7 @@
       <c r="B27" t="s">
         <v>173</v>
       </c>
-      <c r="C27" s="9">
+      <c r="C27" s="7">
         <v>1</v>
       </c>
       <c r="D27" t="s">
@@ -16550,10 +16433,10 @@
       <c r="I27" t="s">
         <v>79</v>
       </c>
-      <c r="J27" s="9">
+      <c r="J27" s="7">
         <v>5</v>
       </c>
-      <c r="K27" s="9">
+      <c r="K27" s="7">
         <v>5</v>
       </c>
       <c r="L27" t="s">
@@ -16574,7 +16457,7 @@
       <c r="Q27" t="s">
         <v>175</v>
       </c>
-      <c r="R27" s="9">
+      <c r="R27" s="7">
         <v>4</v>
       </c>
       <c r="S27" t="s">
@@ -16753,7 +16636,7 @@
       <c r="B28" t="s">
         <v>106</v>
       </c>
-      <c r="C28" s="9">
+      <c r="C28" s="7">
         <v>3</v>
       </c>
       <c r="D28" t="s">
@@ -16774,10 +16657,10 @@
       <c r="I28" t="s">
         <v>79</v>
       </c>
-      <c r="J28" s="9">
+      <c r="J28" s="7">
         <v>5</v>
       </c>
-      <c r="K28" s="9">
+      <c r="K28" s="7">
         <v>5</v>
       </c>
       <c r="L28" t="s">
@@ -16798,7 +16681,7 @@
       <c r="Q28" t="s">
         <v>95</v>
       </c>
-      <c r="R28" s="9">
+      <c r="R28" s="7">
         <v>3</v>
       </c>
       <c r="S28" t="s">
@@ -16977,7 +16860,7 @@
       <c r="B29" t="s">
         <v>204</v>
       </c>
-      <c r="C29" s="9">
+      <c r="C29" s="7">
         <v>2</v>
       </c>
       <c r="D29" t="s">
@@ -16998,10 +16881,10 @@
       <c r="I29" t="s">
         <v>79</v>
       </c>
-      <c r="J29" s="9">
+      <c r="J29" s="7">
         <v>5</v>
       </c>
-      <c r="K29" s="9">
+      <c r="K29" s="7">
         <v>5</v>
       </c>
       <c r="L29" t="s">
@@ -17022,7 +16905,7 @@
       <c r="Q29" t="s">
         <v>200</v>
       </c>
-      <c r="R29" s="9">
+      <c r="R29" s="7">
         <v>3</v>
       </c>
       <c r="S29" t="s">
@@ -17425,7 +17308,7 @@
       <c r="B31" t="s">
         <v>231</v>
       </c>
-      <c r="C31" s="9">
+      <c r="C31" s="7">
         <v>2</v>
       </c>
       <c r="D31" t="s">
@@ -17446,10 +17329,10 @@
       <c r="I31" t="s">
         <v>79</v>
       </c>
-      <c r="J31" s="9">
+      <c r="J31" s="7">
         <v>5</v>
       </c>
-      <c r="K31" s="9">
+      <c r="K31" s="7">
         <v>5</v>
       </c>
       <c r="L31" t="s">
@@ -17470,7 +17353,7 @@
       <c r="Q31" t="s">
         <v>224</v>
       </c>
-      <c r="R31" s="9">
+      <c r="R31" s="7">
         <v>3</v>
       </c>
       <c r="S31" t="s">
@@ -17649,7 +17532,7 @@
       <c r="B32" t="s">
         <v>179</v>
       </c>
-      <c r="C32" s="9">
+      <c r="C32" s="7">
         <v>1</v>
       </c>
       <c r="D32" t="s">
@@ -17670,10 +17553,10 @@
       <c r="I32" t="s">
         <v>79</v>
       </c>
-      <c r="J32" s="9">
+      <c r="J32" s="7">
         <v>5</v>
       </c>
-      <c r="K32" s="9">
+      <c r="K32" s="7">
         <v>5</v>
       </c>
       <c r="L32" t="s">
@@ -17694,7 +17577,7 @@
       <c r="Q32" t="s">
         <v>180</v>
       </c>
-      <c r="R32" s="9">
+      <c r="R32" s="7">
         <v>3</v>
       </c>
       <c r="S32" t="s">
@@ -17873,7 +17756,7 @@
       <c r="B33" t="s">
         <v>170</v>
       </c>
-      <c r="C33" s="9">
+      <c r="C33" s="7">
         <v>3</v>
       </c>
       <c r="D33" t="s">
@@ -17894,10 +17777,10 @@
       <c r="I33" t="s">
         <v>79</v>
       </c>
-      <c r="J33" s="9">
+      <c r="J33" s="7">
         <v>5</v>
       </c>
-      <c r="K33" s="9">
+      <c r="K33" s="7">
         <v>5</v>
       </c>
       <c r="L33" t="s">
@@ -17918,7 +17801,7 @@
       <c r="Q33" t="s">
         <v>158</v>
       </c>
-      <c r="R33" s="9">
+      <c r="R33" s="7">
         <v>3</v>
       </c>
       <c r="S33" t="s">
@@ -18545,7 +18428,7 @@
       <c r="B36" t="s">
         <v>225</v>
       </c>
-      <c r="C36" s="9">
+      <c r="C36" s="7">
         <v>1</v>
       </c>
       <c r="D36" t="s">
@@ -18566,10 +18449,10 @@
       <c r="I36" t="s">
         <v>79</v>
       </c>
-      <c r="J36" s="9">
+      <c r="J36" s="7">
         <v>5</v>
       </c>
-      <c r="K36" s="9">
+      <c r="K36" s="7">
         <v>5</v>
       </c>
       <c r="L36" t="s">
@@ -18590,7 +18473,7 @@
       <c r="Q36" t="s">
         <v>226</v>
       </c>
-      <c r="R36" s="9">
+      <c r="R36" s="7">
         <v>4</v>
       </c>
       <c r="S36" t="s">
@@ -18993,7 +18876,7 @@
       <c r="B38" t="s">
         <v>202</v>
       </c>
-      <c r="C38" s="9">
+      <c r="C38" s="7">
         <v>1</v>
       </c>
       <c r="D38" t="s">
@@ -19014,10 +18897,10 @@
       <c r="I38" t="s">
         <v>79</v>
       </c>
-      <c r="J38" s="9">
+      <c r="J38" s="7">
         <v>5</v>
       </c>
-      <c r="K38" s="9">
+      <c r="K38" s="7">
         <v>5</v>
       </c>
       <c r="L38" t="s">
@@ -19038,7 +18921,7 @@
       <c r="Q38" t="s">
         <v>203</v>
       </c>
-      <c r="R38" s="9">
+      <c r="R38" s="7">
         <v>4</v>
       </c>
       <c r="S38" t="s">
@@ -19217,7 +19100,7 @@
       <c r="B39" t="s">
         <v>163</v>
       </c>
-      <c r="C39" s="9">
+      <c r="C39" s="7">
         <v>2</v>
       </c>
       <c r="D39" t="s">
@@ -19238,10 +19121,10 @@
       <c r="I39" t="s">
         <v>79</v>
       </c>
-      <c r="J39" s="9">
+      <c r="J39" s="7">
         <v>5</v>
       </c>
-      <c r="K39" s="9">
+      <c r="K39" s="7">
         <v>5</v>
       </c>
       <c r="L39" t="s">
@@ -19262,7 +19145,7 @@
       <c r="Q39" t="s">
         <v>158</v>
       </c>
-      <c r="R39" s="9">
+      <c r="R39" s="7">
         <v>3</v>
       </c>
       <c r="S39" t="s">
@@ -19441,7 +19324,7 @@
       <c r="B40" t="s">
         <v>223</v>
       </c>
-      <c r="C40" s="9">
+      <c r="C40" s="7">
         <v>1</v>
       </c>
       <c r="D40" t="s">
@@ -19462,10 +19345,10 @@
       <c r="I40" t="s">
         <v>79</v>
       </c>
-      <c r="J40" s="9">
+      <c r="J40" s="7">
         <v>5</v>
       </c>
-      <c r="K40" s="9">
+      <c r="K40" s="7">
         <v>5</v>
       </c>
       <c r="L40" t="s">
@@ -19486,7 +19369,7 @@
       <c r="Q40" t="s">
         <v>224</v>
       </c>
-      <c r="R40" s="9">
+      <c r="R40" s="7">
         <v>3</v>
       </c>
       <c r="S40" t="s">
@@ -19665,7 +19548,7 @@
       <c r="B41" t="s">
         <v>216</v>
       </c>
-      <c r="C41" s="9">
+      <c r="C41" s="7">
         <v>2</v>
       </c>
       <c r="D41" t="s">
@@ -19686,10 +19569,10 @@
       <c r="I41" t="s">
         <v>79</v>
       </c>
-      <c r="J41" s="9">
+      <c r="J41" s="7">
         <v>5</v>
       </c>
-      <c r="K41" s="9">
+      <c r="K41" s="7">
         <v>5</v>
       </c>
       <c r="L41" t="s">
@@ -19710,7 +19593,7 @@
       <c r="Q41" t="s">
         <v>212</v>
       </c>
-      <c r="R41" s="9">
+      <c r="R41" s="7">
         <v>3</v>
       </c>
       <c r="S41" t="s">
@@ -19889,7 +19772,7 @@
       <c r="B42" t="s">
         <v>157</v>
       </c>
-      <c r="C42" s="9">
+      <c r="C42" s="7">
         <v>1</v>
       </c>
       <c r="D42" t="s">
@@ -19910,10 +19793,10 @@
       <c r="I42" t="s">
         <v>79</v>
       </c>
-      <c r="J42" s="9">
+      <c r="J42" s="7">
         <v>5</v>
       </c>
-      <c r="K42" s="9">
+      <c r="K42" s="7">
         <v>5</v>
       </c>
       <c r="L42" t="s">
@@ -19934,7 +19817,7 @@
       <c r="Q42" t="s">
         <v>158</v>
       </c>
-      <c r="R42" s="9">
+      <c r="R42" s="7">
         <v>3</v>
       </c>
       <c r="S42" t="s">
@@ -20113,7 +19996,7 @@
       <c r="B43" t="s">
         <v>137</v>
       </c>
-      <c r="C43" s="9">
+      <c r="C43" s="7">
         <v>2</v>
       </c>
       <c r="D43" t="s">
@@ -20134,10 +20017,10 @@
       <c r="I43" t="s">
         <v>79</v>
       </c>
-      <c r="J43" s="9">
+      <c r="J43" s="7">
         <v>5</v>
       </c>
-      <c r="K43" s="9">
+      <c r="K43" s="7">
         <v>5</v>
       </c>
       <c r="L43" t="s">
@@ -20158,7 +20041,7 @@
       <c r="Q43" t="s">
         <v>132</v>
       </c>
-      <c r="R43" s="9">
+      <c r="R43" s="7">
         <v>3</v>
       </c>
       <c r="S43" t="s">
@@ -20337,7 +20220,7 @@
       <c r="B44" t="s">
         <v>207</v>
       </c>
-      <c r="C44" s="9">
+      <c r="C44" s="7">
         <v>3</v>
       </c>
       <c r="D44" t="s">
@@ -20358,10 +20241,10 @@
       <c r="I44" t="s">
         <v>79</v>
       </c>
-      <c r="J44" s="9">
+      <c r="J44" s="7">
         <v>5</v>
       </c>
-      <c r="K44" s="9">
+      <c r="K44" s="7">
         <v>5</v>
       </c>
       <c r="L44" t="s">
@@ -20382,7 +20265,7 @@
       <c r="Q44" t="s">
         <v>200</v>
       </c>
-      <c r="R44" s="9">
+      <c r="R44" s="7">
         <v>3</v>
       </c>
       <c r="S44" t="s">
@@ -20561,7 +20444,7 @@
       <c r="B45" t="s">
         <v>131</v>
       </c>
-      <c r="C45" s="9">
+      <c r="C45" s="7">
         <v>1</v>
       </c>
       <c r="D45" t="s">
@@ -20582,10 +20465,10 @@
       <c r="I45" t="s">
         <v>79</v>
       </c>
-      <c r="J45" s="9">
+      <c r="J45" s="7">
         <v>5</v>
       </c>
-      <c r="K45" s="9">
+      <c r="K45" s="7">
         <v>5</v>
       </c>
       <c r="L45" t="s">
@@ -20606,7 +20489,7 @@
       <c r="Q45" t="s">
         <v>132</v>
       </c>
-      <c r="R45" s="9">
+      <c r="R45" s="7">
         <v>3</v>
       </c>
       <c r="S45" t="s">
@@ -20785,7 +20668,7 @@
       <c r="B46" t="s">
         <v>142</v>
       </c>
-      <c r="C46" s="9">
+      <c r="C46" s="7">
         <v>3</v>
       </c>
       <c r="D46" t="s">
@@ -20806,10 +20689,10 @@
       <c r="I46" t="s">
         <v>79</v>
       </c>
-      <c r="J46" s="9">
+      <c r="J46" s="7">
         <v>5</v>
       </c>
-      <c r="K46" s="9">
+      <c r="K46" s="7">
         <v>5</v>
       </c>
       <c r="L46" t="s">
@@ -20830,7 +20713,7 @@
       <c r="Q46" t="s">
         <v>132</v>
       </c>
-      <c r="R46" s="9">
+      <c r="R46" s="7">
         <v>3</v>
       </c>
       <c r="S46" t="s">
@@ -21009,7 +20892,7 @@
       <c r="B47" t="s">
         <v>92</v>
       </c>
-      <c r="C47" s="9">
+      <c r="C47" s="7">
         <v>2</v>
       </c>
       <c r="D47" t="s">
@@ -21030,10 +20913,10 @@
       <c r="I47" t="s">
         <v>79</v>
       </c>
-      <c r="J47" s="9">
+      <c r="J47" s="7">
         <v>5</v>
       </c>
-      <c r="K47" s="9">
+      <c r="K47" s="7">
         <v>5</v>
       </c>
       <c r="L47" t="s">
@@ -21054,7 +20937,7 @@
       <c r="Q47" t="s">
         <v>84</v>
       </c>
-      <c r="R47" s="9">
+      <c r="R47" s="7">
         <v>1</v>
       </c>
       <c r="S47" t="s">
@@ -21233,7 +21116,7 @@
       <c r="B48" t="s">
         <v>222</v>
       </c>
-      <c r="C48" s="9">
+      <c r="C48" s="7">
         <v>2</v>
       </c>
       <c r="D48" t="s">
@@ -21254,10 +21137,10 @@
       <c r="I48" t="s">
         <v>79</v>
       </c>
-      <c r="J48" s="9">
+      <c r="J48" s="7">
         <v>5</v>
       </c>
-      <c r="K48" s="9">
+      <c r="K48" s="7">
         <v>5</v>
       </c>
       <c r="L48" t="s">
@@ -21278,7 +21161,7 @@
       <c r="Q48" t="s">
         <v>221</v>
       </c>
-      <c r="R48" s="9">
+      <c r="R48" s="7">
         <v>1</v>
       </c>
       <c r="S48" t="s">
@@ -21457,7 +21340,7 @@
       <c r="B49" t="s">
         <v>215</v>
       </c>
-      <c r="C49" s="9">
+      <c r="C49" s="7">
         <v>2</v>
       </c>
       <c r="D49" t="s">
@@ -21478,10 +21361,10 @@
       <c r="I49" t="s">
         <v>79</v>
       </c>
-      <c r="J49" s="9">
+      <c r="J49" s="7">
         <v>5</v>
       </c>
-      <c r="K49" s="9">
+      <c r="K49" s="7">
         <v>5</v>
       </c>
       <c r="L49" t="s">
@@ -21502,7 +21385,7 @@
       <c r="Q49" t="s">
         <v>214</v>
       </c>
-      <c r="R49" s="9">
+      <c r="R49" s="7">
         <v>1</v>
       </c>
       <c r="S49" t="s">
@@ -21681,7 +21564,7 @@
       <c r="B50" t="s">
         <v>232</v>
       </c>
-      <c r="C50" s="9">
+      <c r="C50" s="7">
         <v>3</v>
       </c>
       <c r="D50" t="s">
@@ -21702,10 +21585,10 @@
       <c r="I50" t="s">
         <v>79</v>
       </c>
-      <c r="J50" s="9">
+      <c r="J50" s="7">
         <v>5</v>
       </c>
-      <c r="K50" s="9">
+      <c r="K50" s="7">
         <v>5</v>
       </c>
       <c r="L50" t="s">
@@ -21726,7 +21609,7 @@
       <c r="Q50" t="s">
         <v>229</v>
       </c>
-      <c r="R50" s="9">
+      <c r="R50" s="7">
         <v>1</v>
       </c>
       <c r="S50" t="s">
@@ -21905,7 +21788,7 @@
       <c r="B51" t="s">
         <v>134</v>
       </c>
-      <c r="C51" s="9">
+      <c r="C51" s="7">
         <v>1</v>
       </c>
       <c r="D51" t="s">
@@ -21926,10 +21809,10 @@
       <c r="I51" t="s">
         <v>79</v>
       </c>
-      <c r="J51" s="9">
+      <c r="J51" s="7">
         <v>5</v>
       </c>
-      <c r="K51" s="9">
+      <c r="K51" s="7">
         <v>5</v>
       </c>
       <c r="L51" t="s">
@@ -21950,7 +21833,7 @@
       <c r="Q51" t="s">
         <v>135</v>
       </c>
-      <c r="R51" s="9">
+      <c r="R51" s="7">
         <v>1</v>
       </c>
       <c r="S51" t="s">
@@ -22129,7 +22012,7 @@
       <c r="B52" t="s">
         <v>201</v>
       </c>
-      <c r="C52" s="9">
+      <c r="C52" s="7">
         <v>3</v>
       </c>
       <c r="D52" t="s">
@@ -22150,10 +22033,10 @@
       <c r="I52" t="s">
         <v>79</v>
       </c>
-      <c r="J52" s="9">
+      <c r="J52" s="7">
         <v>5</v>
       </c>
-      <c r="K52" s="9">
+      <c r="K52" s="7">
         <v>5</v>
       </c>
       <c r="L52" t="s">
@@ -22174,7 +22057,7 @@
       <c r="Q52" t="s">
         <v>191</v>
       </c>
-      <c r="R52" s="9">
+      <c r="R52" s="7">
         <v>1</v>
       </c>
       <c r="S52" t="s">
@@ -22353,7 +22236,7 @@
       <c r="B53" t="s">
         <v>198</v>
       </c>
-      <c r="C53" s="9">
+      <c r="C53" s="7">
         <v>2</v>
       </c>
       <c r="D53" t="s">
@@ -22374,10 +22257,10 @@
       <c r="I53" t="s">
         <v>79</v>
       </c>
-      <c r="J53" s="9">
+      <c r="J53" s="7">
         <v>5</v>
       </c>
-      <c r="K53" s="9">
+      <c r="K53" s="7">
         <v>5</v>
       </c>
       <c r="L53" t="s">
@@ -22398,7 +22281,7 @@
       <c r="Q53" t="s">
         <v>191</v>
       </c>
-      <c r="R53" s="9">
+      <c r="R53" s="7">
         <v>1</v>
       </c>
       <c r="S53" t="s">
@@ -22577,7 +22460,7 @@
       <c r="B54" t="s">
         <v>136</v>
       </c>
-      <c r="C54" s="9">
+      <c r="C54" s="7">
         <v>2</v>
       </c>
       <c r="D54" t="s">
@@ -22598,10 +22481,10 @@
       <c r="I54" t="s">
         <v>79</v>
       </c>
-      <c r="J54" s="9">
+      <c r="J54" s="7">
         <v>5</v>
       </c>
-      <c r="K54" s="9">
+      <c r="K54" s="7">
         <v>5</v>
       </c>
       <c r="L54" t="s">
@@ -22622,7 +22505,7 @@
       <c r="Q54" t="s">
         <v>135</v>
       </c>
-      <c r="R54" s="9">
+      <c r="R54" s="7">
         <v>1</v>
       </c>
       <c r="S54" t="s">
@@ -22801,7 +22684,7 @@
       <c r="B55" t="s">
         <v>220</v>
       </c>
-      <c r="C55" s="9">
+      <c r="C55" s="7">
         <v>1</v>
       </c>
       <c r="D55" t="s">
@@ -22822,10 +22705,10 @@
       <c r="I55" t="s">
         <v>79</v>
       </c>
-      <c r="J55" s="9">
+      <c r="J55" s="7">
         <v>5</v>
       </c>
-      <c r="K55" s="9">
+      <c r="K55" s="7">
         <v>5</v>
       </c>
       <c r="L55" t="s">
@@ -22846,7 +22729,7 @@
       <c r="Q55" t="s">
         <v>221</v>
       </c>
-      <c r="R55" s="9">
+      <c r="R55" s="7">
         <v>1</v>
       </c>
       <c r="S55" t="s">
@@ -23025,7 +22908,7 @@
       <c r="B56" t="s">
         <v>118</v>
       </c>
-      <c r="C56" s="9">
+      <c r="C56" s="7">
         <v>1</v>
       </c>
       <c r="D56" t="s">
@@ -23046,10 +22929,10 @@
       <c r="I56" t="s">
         <v>79</v>
       </c>
-      <c r="J56" s="9">
+      <c r="J56" s="7">
         <v>5</v>
       </c>
-      <c r="K56" s="9">
+      <c r="K56" s="7">
         <v>5</v>
       </c>
       <c r="L56" t="s">
@@ -23070,7 +22953,7 @@
       <c r="Q56" t="s">
         <v>119</v>
       </c>
-      <c r="R56" s="9">
+      <c r="R56" s="7">
         <v>1</v>
       </c>
       <c r="S56" t="s">
@@ -23249,7 +23132,7 @@
       <c r="B57" t="s">
         <v>227</v>
       </c>
-      <c r="C57" s="9">
+      <c r="C57" s="7">
         <v>3</v>
       </c>
       <c r="D57" t="s">
@@ -23270,10 +23153,10 @@
       <c r="I57" t="s">
         <v>79</v>
       </c>
-      <c r="J57" s="9">
+      <c r="J57" s="7">
         <v>5</v>
       </c>
-      <c r="K57" s="9">
+      <c r="K57" s="7">
         <v>5</v>
       </c>
       <c r="L57" t="s">
@@ -23294,7 +23177,7 @@
       <c r="Q57" t="s">
         <v>221</v>
       </c>
-      <c r="R57" s="9">
+      <c r="R57" s="7">
         <v>1</v>
       </c>
       <c r="S57" t="s">
@@ -23473,7 +23356,7 @@
       <c r="B58" t="s">
         <v>190</v>
       </c>
-      <c r="C58" s="9">
+      <c r="C58" s="7">
         <v>1</v>
       </c>
       <c r="D58" t="s">
@@ -23494,10 +23377,10 @@
       <c r="I58" t="s">
         <v>79</v>
       </c>
-      <c r="J58" s="9">
+      <c r="J58" s="7">
         <v>5</v>
       </c>
-      <c r="K58" s="9">
+      <c r="K58" s="7">
         <v>5</v>
       </c>
       <c r="L58" t="s">
@@ -23518,7 +23401,7 @@
       <c r="Q58" t="s">
         <v>191</v>
       </c>
-      <c r="R58" s="9">
+      <c r="R58" s="7">
         <v>1</v>
       </c>
       <c r="S58" t="s">
@@ -23697,7 +23580,7 @@
       <c r="B59" t="s">
         <v>143</v>
       </c>
-      <c r="C59" s="9">
+      <c r="C59" s="7">
         <v>2</v>
       </c>
       <c r="D59" t="s">
@@ -23718,10 +23601,10 @@
       <c r="I59" t="s">
         <v>79</v>
       </c>
-      <c r="J59" s="9">
+      <c r="J59" s="7">
         <v>5</v>
       </c>
-      <c r="K59" s="9">
+      <c r="K59" s="7">
         <v>5</v>
       </c>
       <c r="L59" t="s">
@@ -23742,7 +23625,7 @@
       <c r="Q59" t="s">
         <v>140</v>
       </c>
-      <c r="R59" s="9">
+      <c r="R59" s="7">
         <v>1</v>
       </c>
       <c r="S59" t="s">
@@ -23921,7 +23804,7 @@
       <c r="B60" t="s">
         <v>213</v>
       </c>
-      <c r="C60" s="9">
+      <c r="C60" s="7">
         <v>1</v>
       </c>
       <c r="D60" t="s">
@@ -23942,10 +23825,10 @@
       <c r="I60" t="s">
         <v>79</v>
       </c>
-      <c r="J60" s="9">
+      <c r="J60" s="7">
         <v>5</v>
       </c>
-      <c r="K60" s="9">
+      <c r="K60" s="7">
         <v>5</v>
       </c>
       <c r="L60" t="s">
@@ -23966,7 +23849,7 @@
       <c r="Q60" t="s">
         <v>214</v>
       </c>
-      <c r="R60" s="9">
+      <c r="R60" s="7">
         <v>1</v>
       </c>
       <c r="S60" t="s">
@@ -24145,7 +24028,7 @@
       <c r="B61" t="s">
         <v>129</v>
       </c>
-      <c r="C61" s="9">
+      <c r="C61" s="7">
         <v>2</v>
       </c>
       <c r="D61" t="s">
@@ -24166,10 +24049,10 @@
       <c r="I61" t="s">
         <v>79</v>
       </c>
-      <c r="J61" s="9">
+      <c r="J61" s="7">
         <v>5</v>
       </c>
-      <c r="K61" s="9">
+      <c r="K61" s="7">
         <v>5</v>
       </c>
       <c r="L61" t="s">
@@ -24190,7 +24073,7 @@
       <c r="Q61" t="s">
         <v>128</v>
       </c>
-      <c r="R61" s="9">
+      <c r="R61" s="7">
         <v>1</v>
       </c>
       <c r="S61" t="s">
@@ -24369,7 +24252,7 @@
       <c r="B62" t="s">
         <v>103</v>
       </c>
-      <c r="C62" s="9">
+      <c r="C62" s="7">
         <v>1</v>
       </c>
       <c r="D62" t="s">
@@ -24390,10 +24273,10 @@
       <c r="I62" t="s">
         <v>79</v>
       </c>
-      <c r="J62" s="9">
+      <c r="J62" s="7">
         <v>5</v>
       </c>
-      <c r="K62" s="9">
+      <c r="K62" s="7">
         <v>5</v>
       </c>
       <c r="L62" t="s">
@@ -24414,7 +24297,7 @@
       <c r="Q62" t="s">
         <v>104</v>
       </c>
-      <c r="R62" s="9">
+      <c r="R62" s="7">
         <v>1</v>
       </c>
       <c r="S62" t="s">
@@ -24593,7 +24476,7 @@
       <c r="B63" t="s">
         <v>205</v>
       </c>
-      <c r="C63" s="9">
+      <c r="C63" s="7">
         <v>1</v>
       </c>
       <c r="D63" t="s">
@@ -24614,10 +24497,10 @@
       <c r="I63" t="s">
         <v>79</v>
       </c>
-      <c r="J63" s="9">
+      <c r="J63" s="7">
         <v>5</v>
       </c>
-      <c r="K63" s="9">
+      <c r="K63" s="7">
         <v>5</v>
       </c>
       <c r="L63" t="s">
@@ -24638,7 +24521,7 @@
       <c r="Q63" t="s">
         <v>206</v>
       </c>
-      <c r="R63" s="9">
+      <c r="R63" s="7">
         <v>1</v>
       </c>
       <c r="S63" t="s">
@@ -24817,7 +24700,7 @@
       <c r="B64" t="s">
         <v>228</v>
       </c>
-      <c r="C64" s="9">
+      <c r="C64" s="7">
         <v>1</v>
       </c>
       <c r="D64" t="s">
@@ -24838,10 +24721,10 @@
       <c r="I64" t="s">
         <v>79</v>
       </c>
-      <c r="J64" s="9">
+      <c r="J64" s="7">
         <v>5</v>
       </c>
-      <c r="K64" s="9">
+      <c r="K64" s="7">
         <v>5</v>
       </c>
       <c r="L64" t="s">
@@ -24862,7 +24745,7 @@
       <c r="Q64" t="s">
         <v>229</v>
       </c>
-      <c r="R64" s="9">
+      <c r="R64" s="7">
         <v>1</v>
       </c>
       <c r="S64" t="s">
@@ -25265,7 +25148,7 @@
       <c r="B66" t="s">
         <v>75</v>
       </c>
-      <c r="C66" s="9">
+      <c r="C66" s="7">
         <v>1</v>
       </c>
       <c r="D66" t="s">
@@ -25286,10 +25169,10 @@
       <c r="I66" t="s">
         <v>79</v>
       </c>
-      <c r="J66" s="9">
+      <c r="J66" s="7">
         <v>5</v>
       </c>
-      <c r="K66" s="9">
+      <c r="K66" s="7">
         <v>5</v>
       </c>
       <c r="L66" t="s">
@@ -25310,7 +25193,7 @@
       <c r="Q66" t="s">
         <v>84</v>
       </c>
-      <c r="R66" s="9">
+      <c r="R66" s="7">
         <v>1</v>
       </c>
       <c r="S66" t="s">
@@ -25713,7 +25596,7 @@
       <c r="B68" t="s">
         <v>116</v>
       </c>
-      <c r="C68" s="9">
+      <c r="C68" s="7">
         <v>3</v>
       </c>
       <c r="D68" t="s">
@@ -25734,10 +25617,10 @@
       <c r="I68" t="s">
         <v>79</v>
       </c>
-      <c r="J68" s="9">
+      <c r="J68" s="7">
         <v>5</v>
       </c>
-      <c r="K68" s="9">
+      <c r="K68" s="7">
         <v>5</v>
       </c>
       <c r="L68" t="s">
@@ -25758,7 +25641,7 @@
       <c r="Q68" t="s">
         <v>113</v>
       </c>
-      <c r="R68" s="9">
+      <c r="R68" s="7">
         <v>1</v>
       </c>
       <c r="S68" t="s">
@@ -25937,7 +25820,7 @@
       <c r="B69" t="s">
         <v>127</v>
       </c>
-      <c r="C69" s="9">
+      <c r="C69" s="7">
         <v>1</v>
       </c>
       <c r="D69" t="s">
@@ -25958,10 +25841,10 @@
       <c r="I69" t="s">
         <v>79</v>
       </c>
-      <c r="J69" s="9">
+      <c r="J69" s="7">
         <v>5</v>
       </c>
-      <c r="K69" s="9">
+      <c r="K69" s="7">
         <v>5</v>
       </c>
       <c r="L69" t="s">
@@ -25982,7 +25865,7 @@
       <c r="Q69" t="s">
         <v>128</v>
       </c>
-      <c r="R69" s="9">
+      <c r="R69" s="7">
         <v>1</v>
       </c>
       <c r="S69" t="s">
@@ -26161,7 +26044,7 @@
       <c r="B70" t="s">
         <v>230</v>
       </c>
-      <c r="C70" s="9">
+      <c r="C70" s="7">
         <v>2</v>
       </c>
       <c r="D70" t="s">
@@ -26182,10 +26065,10 @@
       <c r="I70" t="s">
         <v>79</v>
       </c>
-      <c r="J70" s="9">
+      <c r="J70" s="7">
         <v>5</v>
       </c>
-      <c r="K70" s="9">
+      <c r="K70" s="7">
         <v>5</v>
       </c>
       <c r="L70" t="s">
@@ -26206,7 +26089,7 @@
       <c r="Q70" t="s">
         <v>229</v>
       </c>
-      <c r="R70" s="9">
+      <c r="R70" s="7">
         <v>1</v>
       </c>
       <c r="S70" t="s">
@@ -26385,7 +26268,7 @@
       <c r="B71" t="s">
         <v>181</v>
       </c>
-      <c r="C71" s="9">
+      <c r="C71" s="7">
         <v>3</v>
       </c>
       <c r="D71" t="s">
@@ -26406,10 +26289,10 @@
       <c r="I71" t="s">
         <v>79</v>
       </c>
-      <c r="J71" s="9">
+      <c r="J71" s="7">
         <v>5</v>
       </c>
-      <c r="K71" s="9">
+      <c r="K71" s="7">
         <v>5</v>
       </c>
       <c r="L71" t="s">
@@ -26430,7 +26313,7 @@
       <c r="Q71" t="s">
         <v>172</v>
       </c>
-      <c r="R71" s="9">
+      <c r="R71" s="7">
         <v>1</v>
       </c>
       <c r="S71" t="s">
@@ -26609,7 +26492,7 @@
       <c r="B72" t="s">
         <v>217</v>
       </c>
-      <c r="C72" s="9">
+      <c r="C72" s="7">
         <v>3</v>
       </c>
       <c r="D72" t="s">
@@ -26630,10 +26513,10 @@
       <c r="I72" t="s">
         <v>79</v>
       </c>
-      <c r="J72" s="9">
+      <c r="J72" s="7">
         <v>5</v>
       </c>
-      <c r="K72" s="9">
+      <c r="K72" s="7">
         <v>5</v>
       </c>
       <c r="L72" t="s">
@@ -26654,7 +26537,7 @@
       <c r="Q72" t="s">
         <v>214</v>
       </c>
-      <c r="R72" s="9">
+      <c r="R72" s="7">
         <v>1</v>
       </c>
       <c r="S72" t="s">
@@ -26833,7 +26716,7 @@
       <c r="B73" t="s">
         <v>210</v>
       </c>
-      <c r="C73" s="9">
+      <c r="C73" s="7">
         <v>3</v>
       </c>
       <c r="D73" t="s">
@@ -26854,10 +26737,10 @@
       <c r="I73" t="s">
         <v>79</v>
       </c>
-      <c r="J73" s="9">
+      <c r="J73" s="7">
         <v>5</v>
       </c>
-      <c r="K73" s="9">
+      <c r="K73" s="7">
         <v>5</v>
       </c>
       <c r="L73" t="s">
@@ -26878,7 +26761,7 @@
       <c r="Q73" t="s">
         <v>206</v>
       </c>
-      <c r="R73" s="9">
+      <c r="R73" s="7">
         <v>1</v>
       </c>
       <c r="S73" t="s">
@@ -27057,7 +26940,7 @@
       <c r="B74" t="s">
         <v>182</v>
       </c>
-      <c r="C74" s="9">
+      <c r="C74" s="7">
         <v>1</v>
       </c>
       <c r="D74" t="s">
@@ -27078,10 +26961,10 @@
       <c r="I74" t="s">
         <v>79</v>
       </c>
-      <c r="J74" s="9">
+      <c r="J74" s="7">
         <v>5</v>
       </c>
-      <c r="K74" s="9">
+      <c r="K74" s="7">
         <v>5</v>
       </c>
       <c r="L74" t="s">
@@ -27102,7 +26985,7 @@
       <c r="Q74" t="s">
         <v>183</v>
       </c>
-      <c r="R74" s="9">
+      <c r="R74" s="7">
         <v>1</v>
       </c>
       <c r="S74" t="s">
@@ -27281,7 +27164,7 @@
       <c r="B75" t="s">
         <v>186</v>
       </c>
-      <c r="C75" s="9">
+      <c r="C75" s="7">
         <v>2</v>
       </c>
       <c r="D75" t="s">
@@ -27302,10 +27185,10 @@
       <c r="I75" t="s">
         <v>79</v>
       </c>
-      <c r="J75" s="9">
+      <c r="J75" s="7">
         <v>5</v>
       </c>
-      <c r="K75" s="9">
+      <c r="K75" s="7">
         <v>5</v>
       </c>
       <c r="L75" t="s">
@@ -27326,7 +27209,7 @@
       <c r="Q75" t="s">
         <v>183</v>
       </c>
-      <c r="R75" s="9">
+      <c r="R75" s="7">
         <v>1</v>
       </c>
       <c r="S75" t="s">
@@ -27505,7 +27388,7 @@
       <c r="B76" t="s">
         <v>161</v>
       </c>
-      <c r="C76" s="9">
+      <c r="C76" s="7">
         <v>1</v>
       </c>
       <c r="D76" t="s">
@@ -27526,10 +27409,10 @@
       <c r="I76" t="s">
         <v>79</v>
       </c>
-      <c r="J76" s="9">
+      <c r="J76" s="7">
         <v>5</v>
       </c>
-      <c r="K76" s="9">
+      <c r="K76" s="7">
         <v>5</v>
       </c>
       <c r="L76" t="s">
@@ -27550,7 +27433,7 @@
       <c r="Q76" t="s">
         <v>162</v>
       </c>
-      <c r="R76" s="9">
+      <c r="R76" s="7">
         <v>1</v>
       </c>
       <c r="S76" t="s">
@@ -27729,7 +27612,7 @@
       <c r="B77" t="s">
         <v>208</v>
       </c>
-      <c r="C77" s="9">
+      <c r="C77" s="7">
         <v>2</v>
       </c>
       <c r="D77" t="s">
@@ -27750,10 +27633,10 @@
       <c r="I77" t="s">
         <v>79</v>
       </c>
-      <c r="J77" s="9">
+      <c r="J77" s="7">
         <v>5</v>
       </c>
-      <c r="K77" s="9">
+      <c r="K77" s="7">
         <v>5</v>
       </c>
       <c r="L77" t="s">
@@ -27774,7 +27657,7 @@
       <c r="Q77" t="s">
         <v>206</v>
       </c>
-      <c r="R77" s="9">
+      <c r="R77" s="7">
         <v>1</v>
       </c>
       <c r="S77" t="s">
@@ -27953,7 +27836,7 @@
       <c r="B78" t="s">
         <v>112</v>
       </c>
-      <c r="C78" s="9">
+      <c r="C78" s="7">
         <v>1</v>
       </c>
       <c r="D78" t="s">
@@ -27974,10 +27857,10 @@
       <c r="I78" t="s">
         <v>79</v>
       </c>
-      <c r="J78" s="9">
+      <c r="J78" s="7">
         <v>5</v>
       </c>
-      <c r="K78" s="9">
+      <c r="K78" s="7">
         <v>5</v>
       </c>
       <c r="L78" t="s">
@@ -27998,7 +27881,7 @@
       <c r="Q78" t="s">
         <v>113</v>
       </c>
-      <c r="R78" s="9">
+      <c r="R78" s="7">
         <v>1</v>
       </c>
       <c r="S78" t="s">
@@ -28177,7 +28060,7 @@
       <c r="B79" t="s">
         <v>111</v>
       </c>
-      <c r="C79" s="9">
+      <c r="C79" s="7">
         <v>3</v>
       </c>
       <c r="D79" t="s">
@@ -28198,10 +28081,10 @@
       <c r="I79" t="s">
         <v>79</v>
       </c>
-      <c r="J79" s="9">
+      <c r="J79" s="7">
         <v>5</v>
       </c>
-      <c r="K79" s="9">
+      <c r="K79" s="7">
         <v>5</v>
       </c>
       <c r="L79" t="s">
@@ -28222,7 +28105,7 @@
       <c r="Q79" t="s">
         <v>104</v>
       </c>
-      <c r="R79" s="9">
+      <c r="R79" s="7">
         <v>1</v>
       </c>
       <c r="S79" t="s">
@@ -28401,7 +28284,7 @@
       <c r="B80" t="s">
         <v>187</v>
       </c>
-      <c r="C80" s="9">
+      <c r="C80" s="7">
         <v>3</v>
       </c>
       <c r="D80" t="s">
@@ -28422,10 +28305,10 @@
       <c r="I80" t="s">
         <v>79</v>
       </c>
-      <c r="J80" s="9">
+      <c r="J80" s="7">
         <v>5</v>
       </c>
-      <c r="K80" s="9">
+      <c r="K80" s="7">
         <v>5</v>
       </c>
       <c r="L80" t="s">
@@ -28446,7 +28329,7 @@
       <c r="Q80" t="s">
         <v>183</v>
       </c>
-      <c r="R80" s="9">
+      <c r="R80" s="7">
         <v>1</v>
       </c>
       <c r="S80" t="s">
@@ -28625,7 +28508,7 @@
       <c r="B81" t="s">
         <v>125</v>
       </c>
-      <c r="C81" s="9">
+      <c r="C81" s="7">
         <v>3</v>
       </c>
       <c r="D81" t="s">
@@ -28646,10 +28529,10 @@
       <c r="I81" t="s">
         <v>79</v>
       </c>
-      <c r="J81" s="9">
+      <c r="J81" s="7">
         <v>5</v>
       </c>
-      <c r="K81" s="9">
+      <c r="K81" s="7">
         <v>5</v>
       </c>
       <c r="L81" t="s">
@@ -28670,7 +28553,7 @@
       <c r="Q81" t="s">
         <v>119</v>
       </c>
-      <c r="R81" s="9">
+      <c r="R81" s="7">
         <v>1</v>
       </c>
       <c r="S81" t="s">
@@ -28849,7 +28732,7 @@
       <c r="B82" t="s">
         <v>115</v>
       </c>
-      <c r="C82" s="9">
+      <c r="C82" s="7">
         <v>2</v>
       </c>
       <c r="D82" t="s">
@@ -28870,10 +28753,10 @@
       <c r="I82" t="s">
         <v>79</v>
       </c>
-      <c r="J82" s="9">
+      <c r="J82" s="7">
         <v>5</v>
       </c>
-      <c r="K82" s="9">
+      <c r="K82" s="7">
         <v>5</v>
       </c>
       <c r="L82" t="s">
@@ -28894,7 +28777,7 @@
       <c r="Q82" t="s">
         <v>113</v>
       </c>
-      <c r="R82" s="9">
+      <c r="R82" s="7">
         <v>1</v>
       </c>
       <c r="S82" t="s">
@@ -29073,7 +28956,7 @@
       <c r="B83" t="s">
         <v>171</v>
       </c>
-      <c r="C83" s="9">
+      <c r="C83" s="7">
         <v>1</v>
       </c>
       <c r="D83" t="s">
@@ -29094,10 +28977,10 @@
       <c r="I83" t="s">
         <v>79</v>
       </c>
-      <c r="J83" s="9">
+      <c r="J83" s="7">
         <v>5</v>
       </c>
-      <c r="K83" s="9">
+      <c r="K83" s="7">
         <v>5</v>
       </c>
       <c r="L83" t="s">
@@ -29118,7 +29001,7 @@
       <c r="Q83" t="s">
         <v>172</v>
       </c>
-      <c r="R83" s="9">
+      <c r="R83" s="7">
         <v>1</v>
       </c>
       <c r="S83" t="s">
@@ -29297,7 +29180,7 @@
       <c r="B84" t="s">
         <v>164</v>
       </c>
-      <c r="C84" s="9">
+      <c r="C84" s="7">
         <v>2</v>
       </c>
       <c r="D84" t="s">
@@ -29318,10 +29201,10 @@
       <c r="I84" t="s">
         <v>79</v>
       </c>
-      <c r="J84" s="9">
+      <c r="J84" s="7">
         <v>5</v>
       </c>
-      <c r="K84" s="9">
+      <c r="K84" s="7">
         <v>5</v>
       </c>
       <c r="L84" t="s">
@@ -29342,7 +29225,7 @@
       <c r="Q84" t="s">
         <v>162</v>
       </c>
-      <c r="R84" s="9">
+      <c r="R84" s="7">
         <v>1</v>
       </c>
       <c r="S84" t="s">
@@ -29521,7 +29404,7 @@
       <c r="B85" t="s">
         <v>99</v>
       </c>
-      <c r="C85" s="9">
+      <c r="C85" s="7">
         <v>3</v>
       </c>
       <c r="D85" t="s">
@@ -29542,10 +29425,10 @@
       <c r="I85" t="s">
         <v>79</v>
       </c>
-      <c r="J85" s="9">
+      <c r="J85" s="7">
         <v>5</v>
       </c>
-      <c r="K85" s="9">
+      <c r="K85" s="7">
         <v>5</v>
       </c>
       <c r="L85" t="s">
@@ -29566,7 +29449,7 @@
       <c r="Q85" t="s">
         <v>84</v>
       </c>
-      <c r="R85" s="9">
+      <c r="R85" s="7">
         <v>1</v>
       </c>
       <c r="S85" t="s">
@@ -29745,7 +29628,7 @@
       <c r="B86" t="s">
         <v>178</v>
       </c>
-      <c r="C86" s="9">
+      <c r="C86" s="7">
         <v>2</v>
       </c>
       <c r="D86" t="s">
@@ -29766,10 +29649,10 @@
       <c r="I86" t="s">
         <v>79</v>
       </c>
-      <c r="J86" s="9">
+      <c r="J86" s="7">
         <v>5</v>
       </c>
-      <c r="K86" s="9">
+      <c r="K86" s="7">
         <v>5</v>
       </c>
       <c r="L86" t="s">
@@ -29790,7 +29673,7 @@
       <c r="Q86" t="s">
         <v>172</v>
       </c>
-      <c r="R86" s="9">
+      <c r="R86" s="7">
         <v>1</v>
       </c>
       <c r="S86" t="s">
@@ -30193,7 +30076,7 @@
       <c r="B88" t="s">
         <v>138</v>
       </c>
-      <c r="C88" s="9">
+      <c r="C88" s="7">
         <v>3</v>
       </c>
       <c r="D88" t="s">
@@ -30214,10 +30097,10 @@
       <c r="I88" t="s">
         <v>79</v>
       </c>
-      <c r="J88" s="9">
+      <c r="J88" s="7">
         <v>5</v>
       </c>
-      <c r="K88" s="9">
+      <c r="K88" s="7">
         <v>5</v>
       </c>
       <c r="L88" t="s">
@@ -30238,7 +30121,7 @@
       <c r="Q88" t="s">
         <v>135</v>
       </c>
-      <c r="R88" s="9">
+      <c r="R88" s="7">
         <v>1</v>
       </c>
       <c r="S88" t="s">
@@ -30417,7 +30300,7 @@
       <c r="B89" t="s">
         <v>123</v>
       </c>
-      <c r="C89" s="9">
+      <c r="C89" s="7">
         <v>2</v>
       </c>
       <c r="D89" t="s">
@@ -30438,10 +30321,10 @@
       <c r="I89" t="s">
         <v>79</v>
       </c>
-      <c r="J89" s="9">
+      <c r="J89" s="7">
         <v>5</v>
       </c>
-      <c r="K89" s="9">
+      <c r="K89" s="7">
         <v>5</v>
       </c>
       <c r="L89" t="s">
@@ -30462,7 +30345,7 @@
       <c r="Q89" t="s">
         <v>119</v>
       </c>
-      <c r="R89" s="9">
+      <c r="R89" s="7">
         <v>1</v>
       </c>
       <c r="S89" t="s">
@@ -30641,7 +30524,7 @@
       <c r="B90" t="s">
         <v>144</v>
       </c>
-      <c r="C90" s="9">
+      <c r="C90" s="7">
         <v>3</v>
       </c>
       <c r="D90" t="s">
@@ -30662,10 +30545,10 @@
       <c r="I90" t="s">
         <v>79</v>
       </c>
-      <c r="J90" s="9">
+      <c r="J90" s="7">
         <v>5</v>
       </c>
-      <c r="K90" s="9">
+      <c r="K90" s="7">
         <v>5</v>
       </c>
       <c r="L90" t="s">
@@ -30686,7 +30569,7 @@
       <c r="Q90" t="s">
         <v>140</v>
       </c>
-      <c r="R90" s="9">
+      <c r="R90" s="7">
         <v>1</v>
       </c>
       <c r="S90" t="s">
@@ -30865,7 +30748,7 @@
       <c r="B91" t="s">
         <v>153</v>
       </c>
-      <c r="C91" s="9">
+      <c r="C91" s="7">
         <v>3</v>
       </c>
       <c r="D91" t="s">
@@ -30886,10 +30769,10 @@
       <c r="I91" t="s">
         <v>79</v>
       </c>
-      <c r="J91" s="9">
+      <c r="J91" s="7">
         <v>5</v>
       </c>
-      <c r="K91" s="9">
+      <c r="K91" s="7">
         <v>5</v>
       </c>
       <c r="L91" t="s">
@@ -30910,7 +30793,7 @@
       <c r="Q91" t="s">
         <v>149</v>
       </c>
-      <c r="R91" s="9">
+      <c r="R91" s="7">
         <v>1</v>
       </c>
       <c r="S91" t="s">
@@ -31089,7 +30972,7 @@
       <c r="B92" t="s">
         <v>130</v>
       </c>
-      <c r="C92" s="9">
+      <c r="C92" s="7">
         <v>3</v>
       </c>
       <c r="D92" t="s">
@@ -31110,10 +30993,10 @@
       <c r="I92" t="s">
         <v>79</v>
       </c>
-      <c r="J92" s="9">
+      <c r="J92" s="7">
         <v>5</v>
       </c>
-      <c r="K92" s="9">
+      <c r="K92" s="7">
         <v>5</v>
       </c>
       <c r="L92" t="s">
@@ -31134,7 +31017,7 @@
       <c r="Q92" t="s">
         <v>128</v>
       </c>
-      <c r="R92" s="9">
+      <c r="R92" s="7">
         <v>1</v>
       </c>
       <c r="S92" t="s">
@@ -31313,7 +31196,7 @@
       <c r="B93" t="s">
         <v>151</v>
       </c>
-      <c r="C93" s="9">
+      <c r="C93" s="7">
         <v>2</v>
       </c>
       <c r="D93" t="s">
@@ -31334,10 +31217,10 @@
       <c r="I93" t="s">
         <v>79</v>
       </c>
-      <c r="J93" s="9">
+      <c r="J93" s="7">
         <v>5</v>
       </c>
-      <c r="K93" s="9">
+      <c r="K93" s="7">
         <v>5</v>
       </c>
       <c r="L93" t="s">
@@ -31358,7 +31241,7 @@
       <c r="Q93" t="s">
         <v>149</v>
       </c>
-      <c r="R93" s="9">
+      <c r="R93" s="7">
         <v>1</v>
       </c>
       <c r="S93" t="s">
@@ -31537,7 +31420,7 @@
       <c r="B94" t="s">
         <v>154</v>
       </c>
-      <c r="C94" s="9">
+      <c r="C94" s="7">
         <v>1</v>
       </c>
       <c r="D94" t="s">
@@ -31558,10 +31441,10 @@
       <c r="I94" t="s">
         <v>79</v>
       </c>
-      <c r="J94" s="9">
+      <c r="J94" s="7">
         <v>5</v>
       </c>
-      <c r="K94" s="9">
+      <c r="K94" s="7">
         <v>5</v>
       </c>
       <c r="L94" t="s">
@@ -31582,7 +31465,7 @@
       <c r="Q94" t="s">
         <v>155</v>
       </c>
-      <c r="R94" s="9">
+      <c r="R94" s="7">
         <v>1</v>
       </c>
       <c r="S94" t="s">
@@ -31761,7 +31644,7 @@
       <c r="B95" t="s">
         <v>139</v>
       </c>
-      <c r="C95" s="9">
+      <c r="C95" s="7">
         <v>1</v>
       </c>
       <c r="D95" t="s">
@@ -31782,10 +31665,10 @@
       <c r="I95" t="s">
         <v>79</v>
       </c>
-      <c r="J95" s="9">
+      <c r="J95" s="7">
         <v>5</v>
       </c>
-      <c r="K95" s="9">
+      <c r="K95" s="7">
         <v>5</v>
       </c>
       <c r="L95" t="s">
@@ -31806,7 +31689,7 @@
       <c r="Q95" t="s">
         <v>140</v>
       </c>
-      <c r="R95" s="9">
+      <c r="R95" s="7">
         <v>1</v>
       </c>
       <c r="S95" t="s">
@@ -31985,7 +31868,7 @@
       <c r="B96" t="s">
         <v>160</v>
       </c>
-      <c r="C96" s="9">
+      <c r="C96" s="7">
         <v>3</v>
       </c>
       <c r="D96" t="s">
@@ -32006,10 +31889,10 @@
       <c r="I96" t="s">
         <v>79</v>
       </c>
-      <c r="J96" s="9">
+      <c r="J96" s="7">
         <v>5</v>
       </c>
-      <c r="K96" s="9">
+      <c r="K96" s="7">
         <v>5</v>
       </c>
       <c r="L96" t="s">
@@ -32030,7 +31913,7 @@
       <c r="Q96" t="s">
         <v>155</v>
       </c>
-      <c r="R96" s="9">
+      <c r="R96" s="7">
         <v>1</v>
       </c>
       <c r="S96" t="s">
@@ -32209,7 +32092,7 @@
       <c r="B97" t="s">
         <v>156</v>
       </c>
-      <c r="C97" s="9">
+      <c r="C97" s="7">
         <v>2</v>
       </c>
       <c r="D97" t="s">
@@ -32230,10 +32113,10 @@
       <c r="I97" t="s">
         <v>79</v>
       </c>
-      <c r="J97" s="9">
+      <c r="J97" s="7">
         <v>5</v>
       </c>
-      <c r="K97" s="9">
+      <c r="K97" s="7">
         <v>5</v>
       </c>
       <c r="L97" t="s">
@@ -32254,7 +32137,7 @@
       <c r="Q97" t="s">
         <v>155</v>
       </c>
-      <c r="R97" s="9">
+      <c r="R97" s="7">
         <v>1</v>
       </c>
       <c r="S97" t="s">
@@ -32433,7 +32316,7 @@
       <c r="B98" t="s">
         <v>148</v>
       </c>
-      <c r="C98" s="9">
+      <c r="C98" s="7">
         <v>1</v>
       </c>
       <c r="D98" t="s">
@@ -32454,10 +32337,10 @@
       <c r="I98" t="s">
         <v>79</v>
       </c>
-      <c r="J98" s="9">
+      <c r="J98" s="7">
         <v>5</v>
       </c>
-      <c r="K98" s="9">
+      <c r="K98" s="7">
         <v>5</v>
       </c>
       <c r="L98" t="s">
@@ -32478,7 +32361,7 @@
       <c r="Q98" t="s">
         <v>149</v>
       </c>
-      <c r="R98" s="9">
+      <c r="R98" s="7">
         <v>1</v>
       </c>
       <c r="S98" t="s">
@@ -32657,7 +32540,7 @@
       <c r="B99" t="s">
         <v>169</v>
       </c>
-      <c r="C99" s="9">
+      <c r="C99" s="7">
         <v>3</v>
       </c>
       <c r="D99" t="s">
@@ -32678,10 +32561,10 @@
       <c r="I99" t="s">
         <v>79</v>
       </c>
-      <c r="J99" s="9">
+      <c r="J99" s="7">
         <v>5</v>
       </c>
-      <c r="K99" s="9">
+      <c r="K99" s="7">
         <v>5</v>
       </c>
       <c r="L99" t="s">
@@ -32702,7 +32585,7 @@
       <c r="Q99" t="s">
         <v>162</v>
       </c>
-      <c r="R99" s="9">
+      <c r="R99" s="7">
         <v>1</v>
       </c>
       <c r="S99" t="s">
@@ -32881,7 +32764,7 @@
       <c r="B100" t="s">
         <v>107</v>
       </c>
-      <c r="C100" s="9">
+      <c r="C100" s="7">
         <v>2</v>
       </c>
       <c r="D100" t="s">
@@ -32902,10 +32785,10 @@
       <c r="I100" t="s">
         <v>79</v>
       </c>
-      <c r="J100" s="9">
+      <c r="J100" s="7">
         <v>5</v>
       </c>
-      <c r="K100" s="9">
+      <c r="K100" s="7">
         <v>5</v>
       </c>
       <c r="L100" t="s">
@@ -32926,7 +32809,7 @@
       <c r="Q100" t="s">
         <v>104</v>
       </c>
-      <c r="R100" s="9">
+      <c r="R100" s="7">
         <v>1</v>
       </c>
       <c r="S100" t="s">
@@ -36208,25 +36091,25 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC2417C5-69B1-40A5-8AFE-A835A2C478FA}">
-  <dimension ref="A2:L67"/>
+  <dimension ref="A2:L30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="36.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="31.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="39.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="39.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="35.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="36.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="40.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="40.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="36.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="37.44140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="41.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="41.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="54.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="53.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="47.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="49.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="56.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="55.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="49.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="51.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="25.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>165</v>
       </c>
       <c r="B2" t="s">
@@ -36267,37 +36150,37 @@
       <c r="A3" s="3">
         <v>1</v>
       </c>
-      <c r="B3" s="10">
-        <v>0.41636891498814876</v>
-      </c>
-      <c r="C3" s="10">
-        <v>-5.2726532349204547E-2</v>
-      </c>
-      <c r="D3" s="10">
+      <c r="B3" s="8">
+        <v>0.41636891498814882</v>
+      </c>
+      <c r="C3" s="8">
+        <v>-5.272653234920454E-2</v>
+      </c>
+      <c r="D3" s="8">
         <v>0.18015706416464142</v>
       </c>
-      <c r="E3" s="10">
+      <c r="E3" s="8">
         <v>0.39770216490801458</v>
       </c>
-      <c r="F3" s="10">
+      <c r="F3" s="8">
         <v>0.27050245309932736</v>
       </c>
-      <c r="G3" s="10">
+      <c r="G3" s="8">
         <v>0.58589066284319624</v>
       </c>
-      <c r="H3" s="10">
-        <v>-5.9397282790308946E-2</v>
-      </c>
-      <c r="I3" s="10">
-        <v>-2.0128387168623776E-2</v>
-      </c>
-      <c r="J3" s="10">
+      <c r="H3" s="8">
+        <v>-5.9397282790308953E-2</v>
+      </c>
+      <c r="I3" s="8">
+        <v>-2.0128387168623769E-2</v>
+      </c>
+      <c r="J3" s="8">
         <v>6.0134525364982656E-2</v>
       </c>
-      <c r="K3" s="10">
+      <c r="K3" s="8">
         <v>-0.15529802652982733</v>
       </c>
-      <c r="L3" s="10">
+      <c r="L3" s="8">
         <v>54</v>
       </c>
     </row>
@@ -36305,37 +36188,37 @@
       <c r="A4" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B4" s="10">
+      <c r="B4" s="8">
         <v>0.41481218833745293</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4" s="8">
         <v>2.7485134246625505E-3</v>
       </c>
-      <c r="D4" s="10">
+      <c r="D4" s="8">
         <v>0.12836449764766242</v>
       </c>
-      <c r="E4" s="10">
+      <c r="E4" s="8">
         <v>0.44885661891141937</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="8">
         <v>0.34588739321598294</v>
       </c>
-      <c r="G4" s="10">
-        <v>0.59600951150530634</v>
-      </c>
-      <c r="H4" s="10">
+      <c r="G4" s="8">
+        <v>0.59600951150530657</v>
+      </c>
+      <c r="H4" s="8">
         <v>-1.0467147533235115E-2</v>
       </c>
-      <c r="I4" s="10">
+      <c r="I4" s="8">
         <v>5.6986366157070471E-2</v>
       </c>
-      <c r="J4" s="10">
+      <c r="J4" s="8">
         <v>0.12384536268397991</v>
       </c>
-      <c r="K4" s="10">
+      <c r="K4" s="8">
         <v>-9.9265108601490723E-2</v>
       </c>
-      <c r="L4" s="10">
+      <c r="L4" s="8">
         <v>18</v>
       </c>
     </row>
@@ -36343,2393 +36226,987 @@
       <c r="A5" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="8">
         <v>0.41649572933414869</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="8">
         <v>1.2066273030157596E-2</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="8">
         <v>0.16610034031306109</v>
       </c>
-      <c r="E5" s="10">
+      <c r="E5" s="8">
         <v>0.44178139565759728</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="8">
         <v>0.33979311200200152</v>
       </c>
-      <c r="G5" s="10">
-        <v>0.58010958014022562</v>
-      </c>
-      <c r="H5" s="10">
+      <c r="G5" s="8">
+        <v>0.58010958014022573</v>
+      </c>
+      <c r="H5" s="8">
         <v>-7.6266129743784661E-2</v>
       </c>
-      <c r="I5" s="10">
-        <v>6.125421901736209E-2</v>
-      </c>
-      <c r="J5" s="10">
-        <v>0.13613175724654594</v>
-      </c>
-      <c r="K5" s="10">
+      <c r="I5" s="8">
+        <v>6.1254219017362103E-2</v>
+      </c>
+      <c r="J5" s="8">
+        <v>0.13613175724654591</v>
+      </c>
+      <c r="K5" s="8">
         <v>-8.9593429933529659E-2</v>
       </c>
-      <c r="L5" s="10">
+      <c r="L5" s="8">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="6">
-        <v>3</v>
-      </c>
-      <c r="B6" s="10">
-        <v>0.47184446816461212</v>
-      </c>
-      <c r="C6" s="10">
-        <v>3.5960151491591E-2</v>
-      </c>
-      <c r="D6" s="10">
-        <v>0.17648860174996456</v>
-      </c>
-      <c r="E6" s="10">
-        <v>0.47550373743033236</v>
-      </c>
-      <c r="F6" s="10">
-        <v>0.40908119558991163</v>
-      </c>
-      <c r="G6" s="10">
-        <v>0.67242764984964942</v>
-      </c>
-      <c r="H6" s="10">
-        <v>-0.1436146917061637</v>
-      </c>
-      <c r="I6" s="10">
-        <v>9.1237588749383133E-2</v>
-      </c>
-      <c r="J6" s="10">
-        <v>0.17179153429669744</v>
-      </c>
-      <c r="K6" s="10">
-        <v>-1.4780330309766889E-2</v>
-      </c>
-      <c r="L6" s="10">
-        <v>2</v>
+      <c r="A6" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="B6" s="8">
+        <v>0.38672315257077411</v>
+      </c>
+      <c r="C6" s="8">
+        <v>-3.2556582344845229E-2</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.10541859566651481</v>
+      </c>
+      <c r="E6" s="8">
+        <v>0.40550074549709153</v>
+      </c>
+      <c r="F6" s="8">
+        <v>0.29002648090086042</v>
+      </c>
+      <c r="G6" s="8">
+        <v>0.5926496797445735</v>
+      </c>
+      <c r="H6" s="8">
+        <v>1.6988611410332349E-2</v>
+      </c>
+      <c r="I6" s="8">
+        <v>8.3177979665681554E-3</v>
+      </c>
+      <c r="J6" s="8">
+        <v>4.0232345970101079E-2</v>
+      </c>
+      <c r="K6" s="8">
+        <v>-0.11841892781575065</v>
+      </c>
+      <c r="L6" s="8">
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="B7" s="10">
-        <v>0.39046343029180341</v>
-      </c>
-      <c r="C7" s="10">
-        <v>9.8991824297170933E-2</v>
-      </c>
-      <c r="D7" s="10">
-        <v>4.6395674545872463E-2</v>
-      </c>
-      <c r="E7" s="10">
-        <v>0.44821410493209313</v>
-      </c>
-      <c r="F7" s="10">
-        <v>0.33483561530921102</v>
-      </c>
-      <c r="G7" s="10">
-        <v>0.63480069405060913</v>
-      </c>
-      <c r="H7" s="10">
-        <v>-2.890165219812757E-2</v>
-      </c>
-      <c r="I7" s="10">
-        <v>0.1238787722065056</v>
-      </c>
-      <c r="J7" s="10">
-        <v>0.2217829262804607</v>
-      </c>
-      <c r="K7" s="10">
-        <v>-4.8849639677409178E-2</v>
-      </c>
-      <c r="L7" s="10">
-        <v>1</v>
+      <c r="A7" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="B7" s="8">
+        <v>0.44121768310743587</v>
+      </c>
+      <c r="C7" s="8">
+        <v>2.8735849588675286E-2</v>
+      </c>
+      <c r="D7" s="8">
+        <v>0.11357455696341133</v>
+      </c>
+      <c r="E7" s="8">
+        <v>0.49928771557956936</v>
+      </c>
+      <c r="F7" s="8">
+        <v>0.40784258674508694</v>
+      </c>
+      <c r="G7" s="8">
+        <v>0.6152692746311198</v>
+      </c>
+      <c r="H7" s="8">
+        <v>2.7876075733746966E-2</v>
+      </c>
+      <c r="I7" s="8">
+        <v>0.10138708148728116</v>
+      </c>
+      <c r="J7" s="8">
+        <v>0.19517198483529286</v>
+      </c>
+      <c r="K7" s="8">
+        <v>-8.978296805519187E-2</v>
+      </c>
+      <c r="L7" s="8">
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="B8" s="10">
-        <v>0.38827400312795485</v>
-      </c>
-      <c r="C8" s="10">
-        <v>-3.2838163033135782E-2</v>
-      </c>
-      <c r="D8" s="10">
-        <v>0.19907638794418836</v>
-      </c>
-      <c r="E8" s="10">
-        <v>0.41715559805094199</v>
-      </c>
-      <c r="F8" s="10">
-        <v>0.29525355517432489</v>
-      </c>
-      <c r="G8" s="10">
-        <v>0.50033382903048207</v>
-      </c>
-      <c r="H8" s="10">
-        <v>-4.7155247617417663E-2</v>
-      </c>
-      <c r="I8" s="10">
-        <v>2.0390454799633563E-2</v>
-      </c>
-      <c r="J8" s="10">
-        <v>8.3808182868473316E-2</v>
-      </c>
-      <c r="K8" s="10">
-        <v>-0.15305009310141168</v>
-      </c>
-      <c r="L8" s="10">
-        <v>3</v>
+      <c r="A8" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B8" s="8">
+        <v>0.41514304183391088</v>
+      </c>
+      <c r="C8" s="8">
+        <v>-1.3309368869829273E-2</v>
+      </c>
+      <c r="D8" s="8">
+        <v>0.18087050506977617</v>
+      </c>
+      <c r="E8" s="8">
+        <v>0.34319191631776508</v>
+      </c>
+      <c r="F8" s="8">
+        <v>0.25505830774410582</v>
+      </c>
+      <c r="G8" s="8">
+        <v>0.61359345475197558</v>
+      </c>
+      <c r="H8" s="8">
+        <v>-7.0487854964432009E-2</v>
+      </c>
+      <c r="I8" s="8">
+        <v>5.1538494592396976E-2</v>
+      </c>
+      <c r="J8" s="8">
+        <v>0.11345906601594417</v>
+      </c>
+      <c r="K8" s="8">
+        <v>-0.14237180323666387</v>
+      </c>
+      <c r="L8" s="8">
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="B9" s="10">
-        <v>0.38672315257077411</v>
-      </c>
-      <c r="C9" s="10">
-        <v>-3.2556582344845229E-2</v>
-      </c>
-      <c r="D9" s="10">
-        <v>0.10541859566651481</v>
-      </c>
-      <c r="E9" s="10">
-        <v>0.40550074549709153</v>
-      </c>
-      <c r="F9" s="10">
-        <v>0.29002648090086042</v>
-      </c>
-      <c r="G9" s="10">
-        <v>0.59264967974457339</v>
-      </c>
-      <c r="H9" s="10">
-        <v>1.6988611410332349E-2</v>
-      </c>
-      <c r="I9" s="10">
-        <v>8.3177979665681554E-3</v>
-      </c>
-      <c r="J9" s="10">
-        <v>4.0232345970101079E-2</v>
-      </c>
-      <c r="K9" s="10">
-        <v>-0.11841892781575065</v>
-      </c>
-      <c r="L9" s="10">
+        <v>86</v>
+      </c>
+      <c r="B9" s="8">
+        <v>0.41182962081908397</v>
+      </c>
+      <c r="C9" s="8">
+        <v>2.8868953353709489E-3</v>
+      </c>
+      <c r="D9" s="8">
+        <v>0.18356206683142173</v>
+      </c>
+      <c r="E9" s="8">
+        <v>0.33108753411922043</v>
+      </c>
+      <c r="F9" s="8">
+        <v>0.23829953150931393</v>
+      </c>
+      <c r="G9" s="8">
+        <v>0.62683178238177029</v>
+      </c>
+      <c r="H9" s="8">
+        <v>-8.6399609628571516E-2</v>
+      </c>
+      <c r="I9" s="8">
+        <v>0.10692234480096187</v>
+      </c>
+      <c r="J9" s="8">
+        <v>0.1434344393334463</v>
+      </c>
+      <c r="K9" s="8">
+        <v>-0.11977287839214608</v>
+      </c>
+      <c r="L9" s="8">
         <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="B10" s="10">
-        <v>0.40047572939952353</v>
-      </c>
-      <c r="C10" s="10">
-        <v>-3.1238386257275458E-2</v>
-      </c>
-      <c r="D10" s="10">
-        <v>9.2706312374016497E-2</v>
-      </c>
-      <c r="E10" s="10">
-        <v>0.42170822636846755</v>
-      </c>
-      <c r="F10" s="10">
-        <v>0.3243314803467397</v>
-      </c>
-      <c r="G10" s="10">
-        <v>0.66934569217607365</v>
-      </c>
-      <c r="H10" s="10">
-        <v>3.6749231259990557E-2</v>
-      </c>
-      <c r="I10" s="10">
-        <v>5.8069671563123482E-3</v>
-      </c>
-      <c r="J10" s="10">
-        <v>2.3708990672343184E-2</v>
-      </c>
-      <c r="K10" s="10">
-        <v>-7.2782307123181303E-2</v>
-      </c>
-      <c r="L10" s="10">
-        <v>3</v>
+      <c r="A10" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="B10" s="8">
+        <v>0.37666064411971895</v>
+      </c>
+      <c r="C10" s="8">
+        <v>-4.3011863077717129E-2</v>
+      </c>
+      <c r="D10" s="8">
+        <v>0.18414608943486688</v>
+      </c>
+      <c r="E10" s="8">
+        <v>0.26379717263170044</v>
+      </c>
+      <c r="F10" s="8">
+        <v>0.18152218228216588</v>
+      </c>
+      <c r="G10" s="8">
+        <v>0.61743888448858353</v>
+      </c>
+      <c r="H10" s="8">
+        <v>-3.0795728287285554E-2</v>
+      </c>
+      <c r="I10" s="8">
+        <v>-2.1532625919085464E-2</v>
+      </c>
+      <c r="J10" s="8">
+        <v>2.3922849331387181E-2</v>
+      </c>
+      <c r="K10" s="8">
+        <v>-0.12237274885407616</v>
+      </c>
+      <c r="L10" s="8">
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="B11" s="10">
-        <v>0.37297057574202475</v>
-      </c>
-      <c r="C11" s="10">
-        <v>-3.3874778432415008E-2</v>
-      </c>
-      <c r="D11" s="10">
-        <v>0.1181308789590131</v>
-      </c>
-      <c r="E11" s="10">
-        <v>0.3892932646257154</v>
-      </c>
-      <c r="F11" s="10">
-        <v>0.25572148145498108</v>
-      </c>
-      <c r="G11" s="10">
-        <v>0.51595366731307324</v>
-      </c>
-      <c r="H11" s="10">
-        <v>-2.772008439325862E-3</v>
-      </c>
-      <c r="I11" s="10">
-        <v>1.0828628776823964E-2</v>
-      </c>
-      <c r="J11" s="10">
-        <v>5.675570126785897E-2</v>
-      </c>
-      <c r="K11" s="10">
-        <v>-0.16405554850832002</v>
-      </c>
-      <c r="L11" s="10">
-        <v>3</v>
+      <c r="A11" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="B11" s="8">
+        <v>0.45693886056292982</v>
+      </c>
+      <c r="C11" s="8">
+        <v>1.968611328583674E-4</v>
+      </c>
+      <c r="D11" s="8">
+        <v>0.17490335894303996</v>
+      </c>
+      <c r="E11" s="8">
+        <v>0.43469104220237426</v>
+      </c>
+      <c r="F11" s="8">
+        <v>0.34535320944083764</v>
+      </c>
+      <c r="G11" s="8">
+        <v>0.5965096973855728</v>
+      </c>
+      <c r="H11" s="8">
+        <v>-9.426822697743896E-2</v>
+      </c>
+      <c r="I11" s="8">
+        <v>6.9225764895314512E-2</v>
+      </c>
+      <c r="J11" s="8">
+        <v>0.17301990938299905</v>
+      </c>
+      <c r="K11" s="8">
+        <v>-0.18496978246376938</v>
+      </c>
+      <c r="L11" s="8">
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="B12" s="10">
-        <v>0.44121768310743587</v>
-      </c>
-      <c r="C12" s="10">
-        <v>2.8735849588675286E-2</v>
-      </c>
-      <c r="D12" s="10">
-        <v>0.11357455696341133</v>
-      </c>
-      <c r="E12" s="10">
-        <v>0.49928771557956936</v>
-      </c>
-      <c r="F12" s="10">
-        <v>0.40784258674508694</v>
-      </c>
-      <c r="G12" s="10">
-        <v>0.6152692746311198</v>
-      </c>
-      <c r="H12" s="10">
-        <v>2.7876075733746966E-2</v>
-      </c>
-      <c r="I12" s="10">
-        <v>0.10138708148728116</v>
-      </c>
-      <c r="J12" s="10">
-        <v>0.19517198483529286</v>
-      </c>
-      <c r="K12" s="10">
-        <v>-8.978296805519187E-2</v>
-      </c>
-      <c r="L12" s="10">
-        <v>6</v>
+      <c r="A12" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B12" s="8">
+        <v>0.41915151479308266</v>
+      </c>
+      <c r="C12" s="8">
+        <v>-0.14761874160244692</v>
+      </c>
+      <c r="D12" s="8">
+        <v>0.23123618977648558</v>
+      </c>
+      <c r="E12" s="8">
+        <v>0.40105795949485912</v>
+      </c>
+      <c r="F12" s="8">
+        <v>0.2105616583378932</v>
+      </c>
+      <c r="G12" s="8">
+        <v>0.54806902227230669</v>
+      </c>
+      <c r="H12" s="8">
+        <v>-9.7236845873259703E-2</v>
+      </c>
+      <c r="I12" s="8">
+        <v>-0.1689100222553388</v>
+      </c>
+      <c r="J12" s="8">
+        <v>-5.6900852604976161E-2</v>
+      </c>
+      <c r="K12" s="8">
+        <v>-0.2242571677513274</v>
+      </c>
+      <c r="L12" s="8">
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="B13" s="10">
-        <v>0.46372286403370772</v>
-      </c>
-      <c r="C13" s="10">
-        <v>5.6919814061659718E-2</v>
-      </c>
-      <c r="D13" s="10">
-        <v>7.6065350276800489E-2</v>
-      </c>
-      <c r="E13" s="10">
-        <v>0.50276036398987001</v>
-      </c>
-      <c r="F13" s="10">
-        <v>0.42982665598362496</v>
-      </c>
-      <c r="G13" s="10">
-        <v>0.67863082049742129</v>
-      </c>
-      <c r="H13" s="10">
-        <v>4.275859424213861E-3</v>
-      </c>
-      <c r="I13" s="10">
-        <v>0.14888104537273122</v>
-      </c>
-      <c r="J13" s="10">
-        <v>0.26800522020676615</v>
-      </c>
-      <c r="K13" s="10">
-        <v>-5.888533259630719E-2</v>
-      </c>
-      <c r="L13" s="10">
-        <v>3</v>
+      <c r="A13" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B13" s="8">
+        <v>0.42548911236649428</v>
+      </c>
+      <c r="C13" s="8">
+        <v>-0.20632971320460988</v>
+      </c>
+      <c r="D13" s="8">
+        <v>0.25787034083173238</v>
+      </c>
+      <c r="E13" s="8">
+        <v>0.40720273127239709</v>
+      </c>
+      <c r="F13" s="8">
+        <v>0.20751021325172336</v>
+      </c>
+      <c r="G13" s="8">
+        <v>0.54728899238591511</v>
+      </c>
+      <c r="H13" s="8">
+        <v>-0.12632652051710611</v>
+      </c>
+      <c r="I13" s="8">
+        <v>-0.22420653742029029</v>
+      </c>
+      <c r="J13" s="8">
+        <v>-7.8063006656392944E-2</v>
+      </c>
+      <c r="K13" s="8">
+        <v>-0.26099065481730394</v>
+      </c>
+      <c r="L13" s="8">
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="B14" s="10">
-        <v>0.41871250218116413</v>
-      </c>
-      <c r="C14" s="10">
-        <v>5.5188511569085469E-4</v>
-      </c>
-      <c r="D14" s="10">
-        <v>0.15108376365002216</v>
-      </c>
-      <c r="E14" s="10">
-        <v>0.49581506716926871</v>
-      </c>
-      <c r="F14" s="10">
-        <v>0.38585851750654893</v>
-      </c>
-      <c r="G14" s="10">
-        <v>0.5519077287648182</v>
-      </c>
-      <c r="H14" s="10">
-        <v>5.1476292043280074E-2</v>
-      </c>
-      <c r="I14" s="10">
-        <v>5.3893117601831096E-2</v>
-      </c>
-      <c r="J14" s="10">
-        <v>0.12233874946381947</v>
-      </c>
-      <c r="K14" s="10">
-        <v>-0.12068060351407656</v>
-      </c>
-      <c r="L14" s="10">
-        <v>3</v>
+      <c r="A14" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="B14" s="8">
+        <v>0.40427970707371425</v>
+      </c>
+      <c r="C14" s="8">
+        <v>-0.16993700818121141</v>
+      </c>
+      <c r="D14" s="8">
+        <v>0.23951087992853468</v>
+      </c>
+      <c r="E14" s="8">
+        <v>0.35924752504481594</v>
+      </c>
+      <c r="F14" s="8">
+        <v>0.17429066191796852</v>
+      </c>
+      <c r="G14" s="8">
+        <v>0.55601434457194709</v>
+      </c>
+      <c r="H14" s="8">
+        <v>-0.13562971319638648</v>
+      </c>
+      <c r="I14" s="8">
+        <v>-0.18534483978469618</v>
+      </c>
+      <c r="J14" s="8">
+        <v>-9.851058646422918E-2</v>
+      </c>
+      <c r="K14" s="8">
+        <v>-0.16282907381050207</v>
+      </c>
+      <c r="L14" s="8">
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B15" s="10">
-        <v>0.41514304183391088</v>
-      </c>
-      <c r="C15" s="10">
-        <v>-1.3309368869829277E-2</v>
-      </c>
-      <c r="D15" s="10">
-        <v>0.18087050506977614</v>
-      </c>
-      <c r="E15" s="10">
-        <v>0.34319191631776502</v>
-      </c>
-      <c r="F15" s="10">
-        <v>0.25505830774410587</v>
-      </c>
-      <c r="G15" s="10">
-        <v>0.61359345475197546</v>
-      </c>
-      <c r="H15" s="10">
-        <v>-7.0487854964432009E-2</v>
-      </c>
-      <c r="I15" s="10">
-        <v>5.1538494592396976E-2</v>
-      </c>
-      <c r="J15" s="10">
-        <v>0.11345906601594419</v>
-      </c>
-      <c r="K15" s="10">
-        <v>-0.14237180323666387</v>
-      </c>
-      <c r="L15" s="10">
-        <v>18</v>
+      <c r="A15" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="B15" s="8">
+        <v>0.42768572493903956</v>
+      </c>
+      <c r="C15" s="8">
+        <v>-6.6589503421519425E-2</v>
+      </c>
+      <c r="D15" s="8">
+        <v>0.19632734856918968</v>
+      </c>
+      <c r="E15" s="8">
+        <v>0.43672362216736432</v>
+      </c>
+      <c r="F15" s="8">
+        <v>0.24988409984398782</v>
+      </c>
+      <c r="G15" s="8">
+        <v>0.54090372985905788</v>
+      </c>
+      <c r="H15" s="8">
+        <v>-2.9754303906286538E-2</v>
+      </c>
+      <c r="I15" s="8">
+        <v>-9.717868956102993E-2</v>
+      </c>
+      <c r="J15" s="8">
+        <v>5.8710353056936199E-3</v>
+      </c>
+      <c r="K15" s="8">
+        <v>-0.24895177462617601</v>
+      </c>
+      <c r="L15" s="8">
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="B16" s="10">
-        <v>0.41182962081908409</v>
-      </c>
-      <c r="C16" s="10">
-        <v>2.8868953353709467E-3</v>
-      </c>
-      <c r="D16" s="10">
-        <v>0.18356206683142173</v>
-      </c>
-      <c r="E16" s="10">
-        <v>0.33108753411922043</v>
-      </c>
-      <c r="F16" s="10">
-        <v>0.23829953150931393</v>
-      </c>
-      <c r="G16" s="10">
-        <v>0.62683178238177018</v>
-      </c>
-      <c r="H16" s="10">
-        <v>-8.6399609628571516E-2</v>
-      </c>
-      <c r="I16" s="10">
-        <v>0.10692234480096187</v>
-      </c>
-      <c r="J16" s="10">
-        <v>0.1434344393334463</v>
-      </c>
-      <c r="K16" s="10">
-        <v>-0.11977287839214608</v>
-      </c>
-      <c r="L16" s="10">
-        <v>6</v>
+      <c r="A16" s="3">
+        <v>3</v>
+      </c>
+      <c r="B16" s="8">
+        <v>0.76087828113810352</v>
+      </c>
+      <c r="C16" s="8">
+        <v>-0.14511575584386829</v>
+      </c>
+      <c r="D16" s="8">
+        <v>0.66053579039432575</v>
+      </c>
+      <c r="E16" s="8">
+        <v>0.86841575859085907</v>
+      </c>
+      <c r="F16" s="8">
+        <v>0.73785816343202759</v>
+      </c>
+      <c r="G16" s="8">
+        <v>0.81834930750205226</v>
+      </c>
+      <c r="H16" s="8">
+        <v>-0.23775439422524527</v>
+      </c>
+      <c r="I16" s="8">
+        <v>0.17944895217935697</v>
+      </c>
+      <c r="J16" s="8">
+        <v>0.18486664398519548</v>
+      </c>
+      <c r="K16" s="8">
+        <v>-0.30634882864767998</v>
+      </c>
+      <c r="L16" s="8">
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="B17" s="10">
-        <v>0.40930685987611942</v>
-      </c>
-      <c r="C17" s="10">
-        <v>7.0685636651660375E-2</v>
-      </c>
-      <c r="D17" s="10">
-        <v>0.10528884960468789</v>
-      </c>
-      <c r="E17" s="10">
-        <v>0.27630379368723895</v>
-      </c>
-      <c r="F17" s="10">
-        <v>0.21533332743841824</v>
-      </c>
-      <c r="G17" s="10">
-        <v>0.69792463265646687</v>
-      </c>
-      <c r="H17" s="10">
-        <v>3.3967091022774065E-4</v>
-      </c>
-      <c r="I17" s="10">
-        <v>0.18002045280963111</v>
-      </c>
-      <c r="J17" s="10">
-        <v>0.20680719154600113</v>
-      </c>
-      <c r="K17" s="10">
-        <v>-8.1868244357839723E-2</v>
-      </c>
-      <c r="L17" s="10">
-        <v>3</v>
+      <c r="A17" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B17" s="8">
+        <v>0.76460608963809717</v>
+      </c>
+      <c r="C17" s="8">
+        <v>-5.959830236770667E-2</v>
+      </c>
+      <c r="D17" s="8">
+        <v>0.64437256785837838</v>
+      </c>
+      <c r="E17" s="8">
+        <v>0.84537286988362603</v>
+      </c>
+      <c r="F17" s="8">
+        <v>0.70591895971299601</v>
+      </c>
+      <c r="G17" s="8">
+        <v>0.85187607237024821</v>
+      </c>
+      <c r="H17" s="8">
+        <v>-0.18247486557212841</v>
+      </c>
+      <c r="I17" s="8">
+        <v>0.13740250350105895</v>
+      </c>
+      <c r="J17" s="8">
+        <v>0.12151224117308593</v>
+      </c>
+      <c r="K17" s="8">
+        <v>-0.15375529979127775</v>
+      </c>
+      <c r="L17" s="8">
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="B18" s="10">
-        <v>0.41435238176204864</v>
-      </c>
-      <c r="C18" s="10">
-        <v>-6.4911845980918481E-2</v>
-      </c>
-      <c r="D18" s="10">
-        <v>0.26183528405815554</v>
-      </c>
-      <c r="E18" s="10">
-        <v>0.3858712745512019</v>
-      </c>
-      <c r="F18" s="10">
-        <v>0.26126573558020955</v>
-      </c>
-      <c r="G18" s="10">
-        <v>0.55573893210707359</v>
-      </c>
-      <c r="H18" s="10">
-        <v>-0.1731388901673708</v>
-      </c>
-      <c r="I18" s="10">
-        <v>3.3824236792292628E-2</v>
-      </c>
-      <c r="J18" s="10">
-        <v>8.006168712089147E-2</v>
-      </c>
-      <c r="K18" s="10">
-        <v>-0.15767751242645248</v>
-      </c>
-      <c r="L18" s="10">
+      <c r="A18" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B18" s="8">
+        <v>0.76953124209829904</v>
+      </c>
+      <c r="C18" s="8">
+        <v>-0.10384564706225352</v>
+      </c>
+      <c r="D18" s="8">
+        <v>0.63968835263477863</v>
+      </c>
+      <c r="E18" s="8">
+        <v>0.86375823967965637</v>
+      </c>
+      <c r="F18" s="8">
+        <v>0.75279545775576595</v>
+      </c>
+      <c r="G18" s="8">
+        <v>0.8391541811013522</v>
+      </c>
+      <c r="H18" s="8">
+        <v>-0.39568612698807698</v>
+      </c>
+      <c r="I18" s="8">
+        <v>0.27518835113514223</v>
+      </c>
+      <c r="J18" s="8">
+        <v>0.25117807788184437</v>
+      </c>
+      <c r="K18" s="8">
+        <v>-8.036524787550732E-2</v>
+      </c>
+      <c r="L18" s="8">
         <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="B19" s="10">
-        <v>0.37666064411971895</v>
-      </c>
-      <c r="C19" s="10">
-        <v>-4.3011863077717143E-2</v>
-      </c>
-      <c r="D19" s="10">
-        <v>0.18414608943486688</v>
-      </c>
-      <c r="E19" s="10">
-        <v>0.26379717263170044</v>
-      </c>
-      <c r="F19" s="10">
-        <v>0.18152218228216588</v>
-      </c>
-      <c r="G19" s="10">
-        <v>0.61743888448858353</v>
-      </c>
-      <c r="H19" s="10">
-        <v>-3.0795728287285551E-2</v>
-      </c>
-      <c r="I19" s="10">
-        <v>-2.1532625919085464E-2</v>
-      </c>
-      <c r="J19" s="10">
-        <v>2.3922849331387181E-2</v>
-      </c>
-      <c r="K19" s="10">
-        <v>-0.12237274885407616</v>
-      </c>
-      <c r="L19" s="10">
+        <v>86</v>
+      </c>
+      <c r="B19" s="8">
+        <v>0.77175196202239327</v>
+      </c>
+      <c r="C19" s="8">
+        <v>-7.6206852635060676E-2</v>
+      </c>
+      <c r="D19" s="8">
+        <v>0.72083365014854195</v>
+      </c>
+      <c r="E19" s="8">
+        <v>0.82853598507324133</v>
+      </c>
+      <c r="F19" s="8">
+        <v>0.66602935126990681</v>
+      </c>
+      <c r="G19" s="8">
+        <v>0.85077545148807543</v>
+      </c>
+      <c r="H19" s="8">
+        <v>-7.7962647850242456E-2</v>
+      </c>
+      <c r="I19" s="8">
+        <v>6.6477440414106845E-2</v>
+      </c>
+      <c r="J19" s="8">
+        <v>0.10113278354238121</v>
+      </c>
+      <c r="K19" s="8">
+        <v>-0.25194720890554312</v>
+      </c>
+      <c r="L19" s="8">
         <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="B20" s="10">
-        <v>0.36853048848934661</v>
-      </c>
-      <c r="C20" s="10">
-        <v>1.3270285236931844E-2</v>
-      </c>
-      <c r="D20" s="10">
-        <v>0.13262533239484198</v>
-      </c>
-      <c r="E20" s="10">
-        <v>0.16722071933191349</v>
-      </c>
-      <c r="F20" s="10">
-        <v>0.1203457025719078</v>
-      </c>
-      <c r="G20" s="10">
-        <v>0.71808192528813597</v>
-      </c>
-      <c r="H20" s="10">
-        <v>0.10327339453880596</v>
-      </c>
-      <c r="I20" s="10">
-        <v>-4.797604656881207E-3</v>
-      </c>
-      <c r="J20" s="10">
-        <v>5.661637847764589E-2</v>
-      </c>
-      <c r="K20" s="10">
-        <v>-9.5023233908335669E-2</v>
-      </c>
-      <c r="L20" s="10">
+      <c r="A20" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="B20" s="8">
+        <v>0.73149509996953055</v>
+      </c>
+      <c r="C20" s="8">
+        <v>-2.8586423182114341E-2</v>
+      </c>
+      <c r="D20" s="8">
+        <v>0.52255892204669263</v>
+      </c>
+      <c r="E20" s="8">
+        <v>0.82320125797833932</v>
+      </c>
+      <c r="F20" s="8">
+        <v>0.72122640791496284</v>
+      </c>
+      <c r="G20" s="8">
+        <v>0.8558440209459891</v>
+      </c>
+      <c r="H20" s="8">
+        <v>7.5927219566325532E-2</v>
+      </c>
+      <c r="I20" s="8">
+        <v>3.766670982291765E-2</v>
+      </c>
+      <c r="J20" s="8">
+        <v>-7.2006954760897954E-2</v>
+      </c>
+      <c r="K20" s="8">
+        <v>-0.12393476061016166</v>
+      </c>
+      <c r="L20" s="8">
         <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="B21" s="10">
-        <v>0.40170382758983558</v>
-      </c>
-      <c r="C21" s="10">
-        <v>-0.12597331203293771</v>
-      </c>
-      <c r="D21" s="10">
-        <v>0.24188393538789074</v>
-      </c>
-      <c r="E21" s="10">
-        <v>0.37151572925556914</v>
-      </c>
-      <c r="F21" s="10">
-        <v>0.26768386660276705</v>
-      </c>
-      <c r="G21" s="10">
-        <v>0.50084264843404147</v>
-      </c>
-      <c r="H21" s="10">
-        <v>-0.15474096322677511</v>
-      </c>
-      <c r="I21" s="10">
-        <v>-5.5351558408839319E-2</v>
-      </c>
-      <c r="J21" s="10">
-        <v>-2.2047659999371916E-2</v>
-      </c>
-      <c r="K21" s="10">
-        <v>-0.15775347308385801</v>
-      </c>
-      <c r="L21" s="10">
-        <v>2</v>
+      <c r="A21" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="B21" s="8">
+        <v>0.77850018207787042</v>
+      </c>
+      <c r="C21" s="8">
+        <v>-1.3145736324044107E-2</v>
+      </c>
+      <c r="D21" s="8">
+        <v>0.61794826431333727</v>
+      </c>
+      <c r="E21" s="8">
+        <v>0.88283288161365192</v>
+      </c>
+      <c r="F21" s="8">
+        <v>0.72351423035443763</v>
+      </c>
+      <c r="G21" s="8">
+        <v>0.86283125682774919</v>
+      </c>
+      <c r="H21" s="8">
+        <v>-0.43669012473840579</v>
+      </c>
+      <c r="I21" s="8">
+        <v>0.24120257571902134</v>
+      </c>
+      <c r="J21" s="8">
+        <v>0.22612451565972078</v>
+      </c>
+      <c r="K21" s="8">
+        <v>-6.0582072659633411E-2</v>
+      </c>
+      <c r="L21" s="8">
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" s="6">
-        <v>6</v>
-      </c>
-      <c r="B22" s="10">
-        <v>0.35096474407060257</v>
-      </c>
-      <c r="C22" s="10">
-        <v>-4.593541011122293E-2</v>
-      </c>
-      <c r="D22" s="10">
-        <v>0.22323266864889399</v>
-      </c>
-      <c r="E22" s="10">
-        <v>0.33808941928332392</v>
-      </c>
-      <c r="F22" s="10">
-        <v>0.1927282527717378</v>
-      </c>
-      <c r="G22" s="10">
-        <v>0.54870223419900976</v>
-      </c>
-      <c r="H22" s="10">
-        <v>-0.18511262688658101</v>
-      </c>
-      <c r="I22" s="10">
-        <v>-4.0998247261905263E-3</v>
-      </c>
-      <c r="J22" s="10">
-        <v>1.7783280554129251E-2</v>
-      </c>
-      <c r="K22" s="10">
-        <v>-0.13365984523173391</v>
-      </c>
-      <c r="L22" s="10">
-        <v>1</v>
+      <c r="A22" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B22" s="8">
+        <v>0.75613362183755173</v>
+      </c>
+      <c r="C22" s="8">
+        <v>-9.7176188239614977E-2</v>
+      </c>
+      <c r="D22" s="8">
+        <v>0.6696598228763615</v>
+      </c>
+      <c r="E22" s="8">
+        <v>0.87612473347389841</v>
+      </c>
+      <c r="F22" s="8">
+        <v>0.74350830904792964</v>
+      </c>
+      <c r="G22" s="8">
+        <v>0.80470206510809461</v>
+      </c>
+      <c r="H22" s="8">
+        <v>-0.23870858198575715</v>
+      </c>
+      <c r="I22" s="8">
+        <v>0.31735826477875656</v>
+      </c>
+      <c r="J22" s="8">
+        <v>0.27942577414939918</v>
+      </c>
+      <c r="K22" s="8">
+        <v>-0.32933327641170074</v>
+      </c>
+      <c r="L22" s="8">
+        <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A23" s="8">
-        <v>3</v>
-      </c>
-      <c r="B23" s="10">
-        <v>0.35096474407060257</v>
-      </c>
-      <c r="C23" s="10">
-        <v>-4.593541011122293E-2</v>
-      </c>
-      <c r="D23" s="10">
-        <v>0.22323266864889399</v>
-      </c>
-      <c r="E23" s="10">
-        <v>0.33808941928332392</v>
-      </c>
-      <c r="F23" s="10">
-        <v>0.1927282527717378</v>
-      </c>
-      <c r="G23" s="10">
-        <v>0.54870223419900976</v>
-      </c>
-      <c r="H23" s="10">
-        <v>-0.18511262688658101</v>
-      </c>
-      <c r="I23" s="10">
-        <v>-4.0998247261905263E-3</v>
-      </c>
-      <c r="J23" s="10">
-        <v>1.7783280554129251E-2</v>
-      </c>
-      <c r="K23" s="10">
-        <v>-0.13365984523173391</v>
-      </c>
-      <c r="L23" s="10">
-        <v>1</v>
+      <c r="A23" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B23" s="8">
+        <v>0.7536399090977578</v>
+      </c>
+      <c r="C23" s="8">
+        <v>-0.24726427831233375</v>
+      </c>
+      <c r="D23" s="8">
+        <v>0.70221452214844893</v>
+      </c>
+      <c r="E23" s="8">
+        <v>0.85892770409869035</v>
+      </c>
+      <c r="F23" s="8">
+        <v>0.73221991076598691</v>
+      </c>
+      <c r="G23" s="8">
+        <v>0.76700556984874346</v>
+      </c>
+      <c r="H23" s="8">
+        <v>-0.44328190876545043</v>
+      </c>
+      <c r="I23" s="8">
+        <v>0.25396316828080889</v>
+      </c>
+      <c r="J23" s="8">
+        <v>0.22576187319871766</v>
+      </c>
+      <c r="K23" s="8">
+        <v>-0.40601788305720882</v>
+      </c>
+      <c r="L23" s="8">
+        <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="B24" s="10">
-        <v>0.45693886056292982</v>
-      </c>
-      <c r="C24" s="10">
-        <v>1.9686113285836507E-4</v>
-      </c>
-      <c r="D24" s="10">
-        <v>0.17490335894303999</v>
-      </c>
-      <c r="E24" s="10">
-        <v>0.43469104220237426</v>
-      </c>
-      <c r="F24" s="10">
-        <v>0.34535320944083764</v>
-      </c>
-      <c r="G24" s="10">
-        <v>0.59650969738557269</v>
-      </c>
-      <c r="H24" s="10">
-        <v>-9.426822697743896E-2</v>
-      </c>
-      <c r="I24" s="10">
-        <v>6.9225764895314512E-2</v>
-      </c>
-      <c r="J24" s="10">
-        <v>0.17301990938299905</v>
-      </c>
-      <c r="K24" s="10">
-        <v>-0.18496978246376938</v>
-      </c>
-      <c r="L24" s="10">
-        <v>6</v>
+        <v>86</v>
+      </c>
+      <c r="B24" s="8">
+        <v>0.75812859202938665</v>
+      </c>
+      <c r="C24" s="8">
+        <v>2.2894283818560068E-2</v>
+      </c>
+      <c r="D24" s="8">
+        <v>0.64361606345869171</v>
+      </c>
+      <c r="E24" s="8">
+        <v>0.88988235697406459</v>
+      </c>
+      <c r="F24" s="8">
+        <v>0.7525390276734838</v>
+      </c>
+      <c r="G24" s="8">
+        <v>0.83485926131557564</v>
+      </c>
+      <c r="H24" s="8">
+        <v>-7.5049920562002631E-2</v>
+      </c>
+      <c r="I24" s="8">
+        <v>0.36807434197711481</v>
+      </c>
+      <c r="J24" s="8">
+        <v>0.32235689490994418</v>
+      </c>
+      <c r="K24" s="8">
+        <v>-0.26798559109529424</v>
+      </c>
+      <c r="L24" s="8">
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A25" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="B25" s="10">
-        <v>0.44785197150671113</v>
-      </c>
-      <c r="C25" s="10">
-        <v>5.8039209100705556E-2</v>
-      </c>
-      <c r="D25" s="10">
-        <v>9.7433752940038379E-2</v>
-      </c>
-      <c r="E25" s="10">
-        <v>0.41282823543555924</v>
-      </c>
-      <c r="F25" s="10">
-        <v>0.31645460431820599</v>
-      </c>
-      <c r="G25" s="10">
-        <v>0.67502711668757653</v>
-      </c>
-      <c r="H25" s="10">
-        <v>-4.4082801433359825E-3</v>
-      </c>
-      <c r="I25" s="10">
-        <v>9.3801387451844007E-2</v>
-      </c>
-      <c r="J25" s="10">
-        <v>0.22613713727566806</v>
-      </c>
-      <c r="K25" s="10">
-        <v>-0.19353642674786678</v>
-      </c>
-      <c r="L25" s="10">
-        <v>3</v>
+      <c r="A25" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B25" s="8">
+        <v>0.77290972674060299</v>
+      </c>
+      <c r="C25" s="8">
+        <v>-0.57463744375341264</v>
+      </c>
+      <c r="D25" s="8">
+        <v>0.65988570056503359</v>
+      </c>
+      <c r="E25" s="8">
+        <v>0.89133259338526638</v>
+      </c>
+      <c r="F25" s="8">
+        <v>0.79228051745805061</v>
+      </c>
+      <c r="G25" s="8">
+        <v>0.79594498610437314</v>
+      </c>
+      <c r="H25" s="8">
+        <v>-0.37165937093573492</v>
+      </c>
+      <c r="I25" s="8">
+        <v>-0.33602683282219598</v>
+      </c>
+      <c r="J25" s="8">
+        <v>-8.226343472344666E-2</v>
+      </c>
+      <c r="K25" s="8">
+        <v>-0.58440263585059204</v>
+      </c>
+      <c r="L25" s="8">
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A26" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="B26" s="10">
-        <v>0.46602574961914839</v>
-      </c>
-      <c r="C26" s="10">
-        <v>-5.7645486834988824E-2</v>
-      </c>
-      <c r="D26" s="10">
-        <v>0.2523729649460415</v>
-      </c>
-      <c r="E26" s="10">
-        <v>0.45655384896918932</v>
-      </c>
-      <c r="F26" s="10">
-        <v>0.3742518145634694</v>
-      </c>
-      <c r="G26" s="10">
-        <v>0.51799227808356896</v>
-      </c>
-      <c r="H26" s="10">
-        <v>-0.18412817381154192</v>
-      </c>
-      <c r="I26" s="10">
-        <v>4.4650142338785011E-2</v>
-      </c>
-      <c r="J26" s="10">
-        <v>0.11990268149033008</v>
-      </c>
-      <c r="K26" s="10">
-        <v>-0.17640313817967201</v>
-      </c>
-      <c r="L26" s="10">
-        <v>3</v>
+      <c r="A26" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B26" s="8">
+        <v>0.77290972674060299</v>
+      </c>
+      <c r="C26" s="8">
+        <v>-0.57463744375341264</v>
+      </c>
+      <c r="D26" s="8">
+        <v>0.65988570056503359</v>
+      </c>
+      <c r="E26" s="8">
+        <v>0.89133259338526638</v>
+      </c>
+      <c r="F26" s="8">
+        <v>0.79228051745805061</v>
+      </c>
+      <c r="G26" s="8">
+        <v>0.79594498610437314</v>
+      </c>
+      <c r="H26" s="8">
+        <v>-0.37165937093573492</v>
+      </c>
+      <c r="I26" s="8">
+        <v>-0.33602683282219598</v>
+      </c>
+      <c r="J26" s="8">
+        <v>-8.226343472344666E-2</v>
+      </c>
+      <c r="K26" s="8">
+        <v>-0.58440263585059204</v>
+      </c>
+      <c r="L26" s="8">
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A27" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="B27" s="10">
-        <v>0.41915151479308266</v>
-      </c>
-      <c r="C27" s="10">
-        <v>-0.14761874160244692</v>
-      </c>
-      <c r="D27" s="10">
-        <v>0.23123618977648558</v>
-      </c>
-      <c r="E27" s="10">
-        <v>0.40105795949485912</v>
-      </c>
-      <c r="F27" s="10">
-        <v>0.21056165833789323</v>
-      </c>
-      <c r="G27" s="10">
-        <v>0.54806902227230681</v>
-      </c>
-      <c r="H27" s="10">
-        <v>-9.7236845873259703E-2</v>
-      </c>
-      <c r="I27" s="10">
-        <v>-0.1689100222553388</v>
-      </c>
-      <c r="J27" s="10">
-        <v>-5.6900852604976161E-2</v>
-      </c>
-      <c r="K27" s="10">
-        <v>-0.22425716775132734</v>
-      </c>
-      <c r="L27" s="10">
-        <v>18</v>
+      <c r="A27" s="3">
+        <v>4</v>
+      </c>
+      <c r="B27" s="8">
+        <v>0.75370487808515341</v>
+      </c>
+      <c r="C27" s="8">
+        <v>8.0478240048969182E-2</v>
+      </c>
+      <c r="D27" s="8">
+        <v>0.6659976436875108</v>
+      </c>
+      <c r="E27" s="8">
+        <v>0.76875805815376164</v>
+      </c>
+      <c r="F27" s="8">
+        <v>0.76400211090040837</v>
+      </c>
+      <c r="G27" s="8">
+        <v>0.7501128556589165</v>
+      </c>
+      <c r="H27" s="8">
+        <v>3.9048256169417178E-2</v>
+      </c>
+      <c r="I27" s="8">
+        <v>0.1100805924114598</v>
+      </c>
+      <c r="J27" s="8">
+        <v>0.31337908697498446</v>
+      </c>
+      <c r="K27" s="8">
+        <v>-3.7131629291725643E-2</v>
+      </c>
+      <c r="L27" s="8">
+        <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A28" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="B28" s="10">
-        <v>0.42548911236649428</v>
-      </c>
-      <c r="C28" s="10">
-        <v>-0.20632971320460991</v>
-      </c>
-      <c r="D28" s="10">
-        <v>0.25787034083173238</v>
-      </c>
-      <c r="E28" s="10">
-        <v>0.40720273127239709</v>
-      </c>
-      <c r="F28" s="10">
-        <v>0.20751021325172339</v>
-      </c>
-      <c r="G28" s="10">
-        <v>0.54728899238591522</v>
-      </c>
-      <c r="H28" s="10">
-        <v>-0.12632652051710611</v>
-      </c>
-      <c r="I28" s="10">
-        <v>-0.22420653742029029</v>
-      </c>
-      <c r="J28" s="10">
-        <v>-7.8063006656392944E-2</v>
-      </c>
-      <c r="K28" s="10">
-        <v>-0.26099065481730394</v>
-      </c>
-      <c r="L28" s="10">
-        <v>6</v>
+      <c r="A28" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B28" s="8">
+        <v>0.75370487808515341</v>
+      </c>
+      <c r="C28" s="8">
+        <v>8.0478240048969182E-2</v>
+      </c>
+      <c r="D28" s="8">
+        <v>0.6659976436875108</v>
+      </c>
+      <c r="E28" s="8">
+        <v>0.76875805815376164</v>
+      </c>
+      <c r="F28" s="8">
+        <v>0.76400211090040837</v>
+      </c>
+      <c r="G28" s="8">
+        <v>0.7501128556589165</v>
+      </c>
+      <c r="H28" s="8">
+        <v>3.9048256169417178E-2</v>
+      </c>
+      <c r="I28" s="8">
+        <v>0.1100805924114598</v>
+      </c>
+      <c r="J28" s="8">
+        <v>0.31337908697498446</v>
+      </c>
+      <c r="K28" s="8">
+        <v>-3.7131629291725643E-2</v>
+      </c>
+      <c r="L28" s="8">
+        <v>11</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A29" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="B29" s="10">
-        <v>0.41185885806808625</v>
-      </c>
-      <c r="C29" s="10">
-        <v>-0.36099267023131992</v>
-      </c>
-      <c r="D29" s="10">
-        <v>0.1666430787480627</v>
-      </c>
-      <c r="E29" s="10">
-        <v>0.34458964402747744</v>
-      </c>
-      <c r="F29" s="10">
-        <v>0.14884857957504036</v>
-      </c>
-      <c r="G29" s="10">
-        <v>0.64713978394937666</v>
-      </c>
-      <c r="H29" s="10">
-        <v>-0.16220100554077543</v>
-      </c>
-      <c r="I29" s="10">
-        <v>-0.32336564766302217</v>
-      </c>
-      <c r="J29" s="10">
-        <v>-0.1436686837559519</v>
-      </c>
-      <c r="K29" s="10">
-        <v>-0.22928799948759729</v>
-      </c>
-      <c r="L29" s="10">
-        <v>3</v>
+      <c r="A29" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B29" s="8">
+        <v>0.75370487808515341</v>
+      </c>
+      <c r="C29" s="8">
+        <v>8.0478240048969182E-2</v>
+      </c>
+      <c r="D29" s="8">
+        <v>0.6659976436875108</v>
+      </c>
+      <c r="E29" s="8">
+        <v>0.76875805815376164</v>
+      </c>
+      <c r="F29" s="8">
+        <v>0.76400211090040837</v>
+      </c>
+      <c r="G29" s="8">
+        <v>0.7501128556589165</v>
+      </c>
+      <c r="H29" s="8">
+        <v>3.9048256169417178E-2</v>
+      </c>
+      <c r="I29" s="8">
+        <v>0.1100805924114598</v>
+      </c>
+      <c r="J29" s="8">
+        <v>0.31337908697498446</v>
+      </c>
+      <c r="K29" s="8">
+        <v>-3.7131629291725643E-2</v>
+      </c>
+      <c r="L29" s="8">
+        <v>11</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A30" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="B30" s="10">
-        <v>0.43911936666490231</v>
-      </c>
-      <c r="C30" s="10">
-        <v>-5.1666756177899953E-2</v>
-      </c>
-      <c r="D30" s="10">
-        <v>0.34909760291540204</v>
-      </c>
-      <c r="E30" s="10">
-        <v>0.46981581851731669</v>
-      </c>
-      <c r="F30" s="10">
-        <v>0.2661718469284064</v>
-      </c>
-      <c r="G30" s="10">
-        <v>0.44743820082245378</v>
-      </c>
-      <c r="H30" s="10">
-        <v>-9.0452035493436764E-2</v>
-      </c>
-      <c r="I30" s="10">
-        <v>-0.1250474271775584</v>
-      </c>
-      <c r="J30" s="10">
-        <v>-1.2457329556833983E-2</v>
-      </c>
-      <c r="K30" s="10">
-        <v>-0.29269331014701061</v>
-      </c>
-      <c r="L30" s="10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A31" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="B31" s="10">
-        <v>0.40427970707371425</v>
-      </c>
-      <c r="C31" s="10">
-        <v>-0.16993700818121141</v>
-      </c>
-      <c r="D31" s="10">
-        <v>0.23951087992853468</v>
-      </c>
-      <c r="E31" s="10">
-        <v>0.35924752504481594</v>
-      </c>
-      <c r="F31" s="10">
-        <v>0.17429066191796849</v>
-      </c>
-      <c r="G31" s="10">
-        <v>0.55601434457194709</v>
-      </c>
-      <c r="H31" s="10">
-        <v>-0.13562971319638648</v>
-      </c>
-      <c r="I31" s="10">
-        <v>-0.18534483978469618</v>
-      </c>
-      <c r="J31" s="10">
-        <v>-9.851058646422918E-2</v>
-      </c>
-      <c r="K31" s="10">
-        <v>-0.16282907381050207</v>
-      </c>
-      <c r="L31" s="10">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A32" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="B32" s="10">
-        <v>0.39954696172779797</v>
-      </c>
-      <c r="C32" s="10">
-        <v>-0.21149148966020517</v>
-      </c>
-      <c r="D32" s="10">
-        <v>0.13390195047901154</v>
-      </c>
-      <c r="E32" s="10">
-        <v>0.33983572504555465</v>
-      </c>
-      <c r="F32" s="10">
-        <v>0.16067253388758851</v>
-      </c>
-      <c r="G32" s="10">
-        <v>0.63491664361051658</v>
-      </c>
-      <c r="H32" s="10">
-        <v>-6.0981454735038389E-2</v>
-      </c>
-      <c r="I32" s="10">
-        <v>-0.33809065221772161</v>
-      </c>
-      <c r="J32" s="10">
-        <v>-0.23123394543046283</v>
-      </c>
-      <c r="K32" s="10">
-        <v>-0.19525652551542852</v>
-      </c>
-      <c r="L32" s="10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A33" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="B33" s="10">
-        <v>0.40901245241963052</v>
-      </c>
-      <c r="C33" s="10">
-        <v>-0.12838252670221764</v>
-      </c>
-      <c r="D33" s="10">
-        <v>0.3451198093780577</v>
-      </c>
-      <c r="E33" s="10">
-        <v>0.37865932504407723</v>
-      </c>
-      <c r="F33" s="10">
-        <v>0.18790878994834848</v>
-      </c>
-      <c r="G33" s="10">
-        <v>0.47711204553337744</v>
-      </c>
-      <c r="H33" s="10">
-        <v>-0.21027797165773454</v>
-      </c>
-      <c r="I33" s="10">
-        <v>-3.2599027351670751E-2</v>
-      </c>
-      <c r="J33" s="10">
-        <v>3.4212772502004461E-2</v>
-      </c>
-      <c r="K33" s="10">
-        <v>-0.13040162210557563</v>
-      </c>
-      <c r="L33" s="10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A34" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="B34" s="10">
-        <v>0.4276857249390395</v>
-      </c>
-      <c r="C34" s="10">
-        <v>-6.6589503421519425E-2</v>
-      </c>
-      <c r="D34" s="10">
-        <v>0.19632734856918968</v>
-      </c>
-      <c r="E34" s="10">
-        <v>0.43672362216736432</v>
-      </c>
-      <c r="F34" s="10">
-        <v>0.24988409984398782</v>
-      </c>
-      <c r="G34" s="10">
-        <v>0.54090372985905788</v>
-      </c>
-      <c r="H34" s="10">
-        <v>-2.9754303906286538E-2</v>
-      </c>
-      <c r="I34" s="10">
-        <v>-9.717868956102993E-2</v>
-      </c>
-      <c r="J34" s="10">
-        <v>5.8710353056936199E-3</v>
-      </c>
-      <c r="K34" s="10">
-        <v>-0.24895177462617601</v>
-      </c>
-      <c r="L34" s="10">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A35" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="B35" s="10">
-        <v>0.44112458346239897</v>
-      </c>
-      <c r="C35" s="10">
-        <v>-7.4224026722955416E-2</v>
-      </c>
-      <c r="D35" s="10">
-        <v>0.10653846144681367</v>
-      </c>
-      <c r="E35" s="10">
-        <v>0.40397786057157931</v>
-      </c>
-      <c r="F35" s="10">
-        <v>0.24644133986357639</v>
-      </c>
-      <c r="G35" s="10">
-        <v>0.64469477801939234</v>
-      </c>
-      <c r="H35" s="10">
-        <v>-2.2789921924410095E-2</v>
-      </c>
-      <c r="I35" s="10">
-        <v>-0.11821452641829193</v>
-      </c>
-      <c r="J35" s="10">
-        <v>4.758862268505905E-3</v>
-      </c>
-      <c r="K35" s="10">
-        <v>-0.14870864813219306</v>
-      </c>
-      <c r="L35" s="10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A36" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="B36" s="10">
-        <v>0.41424686641567993</v>
-      </c>
-      <c r="C36" s="10">
-        <v>-5.8954980120083413E-2</v>
-      </c>
-      <c r="D36" s="10">
-        <v>0.28611623569156569</v>
-      </c>
-      <c r="E36" s="10">
-        <v>0.46946938376314945</v>
-      </c>
-      <c r="F36" s="10">
-        <v>0.25332685982439929</v>
-      </c>
-      <c r="G36" s="10">
-        <v>0.43711268169872336</v>
-      </c>
-      <c r="H36" s="10">
-        <v>-3.6718685888162982E-2</v>
-      </c>
-      <c r="I36" s="10">
-        <v>-7.614285270376793E-2</v>
-      </c>
-      <c r="J36" s="10">
-        <v>6.9832083428813347E-3</v>
-      </c>
-      <c r="K36" s="10">
-        <v>-0.34919490112015894</v>
-      </c>
-      <c r="L36" s="10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A37" s="3">
-        <v>3</v>
-      </c>
-      <c r="B37" s="10">
-        <v>0.76087828113810352</v>
-      </c>
-      <c r="C37" s="10">
-        <v>-0.14511575584386829</v>
-      </c>
-      <c r="D37" s="10">
-        <v>0.66053579039432575</v>
-      </c>
-      <c r="E37" s="10">
-        <v>0.86841575859085907</v>
-      </c>
-      <c r="F37" s="10">
-        <v>0.73785816343202759</v>
-      </c>
-      <c r="G37" s="10">
-        <v>0.81834930750205226</v>
-      </c>
-      <c r="H37" s="10">
-        <v>-0.23775439422524527</v>
-      </c>
-      <c r="I37" s="10">
-        <v>0.17944895217935697</v>
-      </c>
-      <c r="J37" s="10">
-        <v>0.18486664398519548</v>
-      </c>
-      <c r="K37" s="10">
-        <v>-0.30634882864767998</v>
-      </c>
-      <c r="L37" s="10">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A38" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B38" s="10">
-        <v>0.76460608963809717</v>
-      </c>
-      <c r="C38" s="10">
-        <v>-5.959830236770667E-2</v>
-      </c>
-      <c r="D38" s="10">
-        <v>0.64437256785837838</v>
-      </c>
-      <c r="E38" s="10">
-        <v>0.84537286988362603</v>
-      </c>
-      <c r="F38" s="10">
-        <v>0.70591895971299601</v>
-      </c>
-      <c r="G38" s="10">
-        <v>0.85187607237024809</v>
-      </c>
-      <c r="H38" s="10">
-        <v>-0.18247486557212841</v>
-      </c>
-      <c r="I38" s="10">
-        <v>0.13740250350105895</v>
-      </c>
-      <c r="J38" s="10">
-        <v>0.12151224117308591</v>
-      </c>
-      <c r="K38" s="10">
-        <v>-0.15375529979127775</v>
-      </c>
-      <c r="L38" s="10">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A39" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="B39" s="10">
-        <v>0.76953124209829904</v>
-      </c>
-      <c r="C39" s="10">
-        <v>-0.10384564706225352</v>
-      </c>
-      <c r="D39" s="10">
-        <v>0.63968835263477863</v>
-      </c>
-      <c r="E39" s="10">
-        <v>0.86375823967965637</v>
-      </c>
-      <c r="F39" s="10">
-        <v>0.75279545775576595</v>
-      </c>
-      <c r="G39" s="10">
-        <v>0.8391541811013522</v>
-      </c>
-      <c r="H39" s="10">
-        <v>-0.39568612698807698</v>
-      </c>
-      <c r="I39" s="10">
-        <v>0.27518835113514223</v>
-      </c>
-      <c r="J39" s="10">
-        <v>0.25117807788184437</v>
-      </c>
-      <c r="K39" s="10">
-        <v>-8.036524787550732E-2</v>
-      </c>
-      <c r="L39" s="10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A40" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="B40" s="10">
-        <v>0.76953124209829904</v>
-      </c>
-      <c r="C40" s="10">
-        <v>-0.10384564706225352</v>
-      </c>
-      <c r="D40" s="10">
-        <v>0.63968835263477863</v>
-      </c>
-      <c r="E40" s="10">
-        <v>0.86375823967965637</v>
-      </c>
-      <c r="F40" s="10">
-        <v>0.75279545775576595</v>
-      </c>
-      <c r="G40" s="10">
-        <v>0.8391541811013522</v>
-      </c>
-      <c r="H40" s="10">
-        <v>-0.39568612698807698</v>
-      </c>
-      <c r="I40" s="10">
-        <v>0.27518835113514223</v>
-      </c>
-      <c r="J40" s="10">
-        <v>0.25117807788184437</v>
-      </c>
-      <c r="K40" s="10">
-        <v>-8.036524787550732E-2</v>
-      </c>
-      <c r="L40" s="10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A41" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="B41" s="10">
-        <v>0.77175196202239305</v>
-      </c>
-      <c r="C41" s="10">
-        <v>-7.6206852635060676E-2</v>
-      </c>
-      <c r="D41" s="10">
-        <v>0.72083365014854184</v>
-      </c>
-      <c r="E41" s="10">
-        <v>0.82853598507324133</v>
-      </c>
-      <c r="F41" s="10">
-        <v>0.66602935126990681</v>
-      </c>
-      <c r="G41" s="10">
-        <v>0.85077545148807532</v>
-      </c>
-      <c r="H41" s="10">
-        <v>-7.796264785024247E-2</v>
-      </c>
-      <c r="I41" s="10">
-        <v>6.6477440414106859E-2</v>
-      </c>
-      <c r="J41" s="10">
-        <v>0.10113278354238121</v>
-      </c>
-      <c r="K41" s="10">
-        <v>-0.25194720890554312</v>
-      </c>
-      <c r="L41" s="10">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A42" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="B42" s="10">
-        <v>0.7711531847331724</v>
-      </c>
-      <c r="C42" s="10">
-        <v>-5.7194655199862367E-2</v>
-      </c>
-      <c r="D42" s="10">
-        <v>0.66149383121950844</v>
-      </c>
-      <c r="E42" s="10">
-        <v>0.86450428222818732</v>
-      </c>
-      <c r="F42" s="10">
-        <v>0.70031502240607491</v>
-      </c>
-      <c r="G42" s="10">
-        <v>0.84813635649902686</v>
-      </c>
-      <c r="H42" s="10">
-        <v>-0.15444220710000864</v>
-      </c>
-      <c r="I42" s="10">
-        <v>0.20892572023781208</v>
-      </c>
-      <c r="J42" s="10">
-        <v>0.24519790403769959</v>
-      </c>
-      <c r="K42" s="10">
-        <v>-0.28536916583910016</v>
-      </c>
-      <c r="L42" s="10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A43" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="B43" s="10">
-        <v>0.77235073931161391</v>
-      </c>
-      <c r="C43" s="10">
-        <v>-9.5219050070258993E-2</v>
-      </c>
-      <c r="D43" s="10">
-        <v>0.78017346907757534</v>
-      </c>
-      <c r="E43" s="10">
-        <v>0.79256768791829535</v>
-      </c>
-      <c r="F43" s="10">
-        <v>0.63174368013373872</v>
-      </c>
-      <c r="G43" s="10">
-        <v>0.85341454647712389</v>
-      </c>
-      <c r="H43" s="10">
-        <v>-1.4830886004762618E-3</v>
-      </c>
-      <c r="I43" s="10">
-        <v>-7.5970839409598367E-2</v>
-      </c>
-      <c r="J43" s="10">
-        <v>-4.2932336952937154E-2</v>
-      </c>
-      <c r="K43" s="10">
-        <v>-0.21852525197198605</v>
-      </c>
-      <c r="L43" s="10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A44" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="B44" s="10">
-        <v>0.73149509996953055</v>
-      </c>
-      <c r="C44" s="10">
-        <v>-2.8586423182114341E-2</v>
-      </c>
-      <c r="D44" s="10">
-        <v>0.52255892204669263</v>
-      </c>
-      <c r="E44" s="10">
-        <v>0.82320125797833932</v>
-      </c>
-      <c r="F44" s="10">
-        <v>0.72122640791496284</v>
-      </c>
-      <c r="G44" s="10">
-        <v>0.8558440209459891</v>
-      </c>
-      <c r="H44" s="10">
-        <v>7.5927219566325532E-2</v>
-      </c>
-      <c r="I44" s="10">
-        <v>3.766670982291765E-2</v>
-      </c>
-      <c r="J44" s="10">
-        <v>-7.2006954760897954E-2</v>
-      </c>
-      <c r="K44" s="10">
-        <v>-0.12393476061016166</v>
-      </c>
-      <c r="L44" s="10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A45" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="B45" s="10">
-        <v>0.73149509996953055</v>
-      </c>
-      <c r="C45" s="10">
-        <v>-2.8586423182114341E-2</v>
-      </c>
-      <c r="D45" s="10">
-        <v>0.52255892204669263</v>
-      </c>
-      <c r="E45" s="10">
-        <v>0.82320125797833932</v>
-      </c>
-      <c r="F45" s="10">
-        <v>0.72122640791496284</v>
-      </c>
-      <c r="G45" s="10">
-        <v>0.8558440209459891</v>
-      </c>
-      <c r="H45" s="10">
-        <v>7.5927219566325532E-2</v>
-      </c>
-      <c r="I45" s="10">
-        <v>3.766670982291765E-2</v>
-      </c>
-      <c r="J45" s="10">
-        <v>-7.2006954760897954E-2</v>
-      </c>
-      <c r="K45" s="10">
-        <v>-0.12393476061016166</v>
-      </c>
-      <c r="L45" s="10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A46" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="B46" s="10">
-        <v>0.77850018207787042</v>
-      </c>
-      <c r="C46" s="10">
-        <v>-1.3145736324044107E-2</v>
-      </c>
-      <c r="D46" s="10">
-        <v>0.61794826431333727</v>
-      </c>
-      <c r="E46" s="10">
-        <v>0.88283288161365192</v>
-      </c>
-      <c r="F46" s="10">
-        <v>0.72351423035443763</v>
-      </c>
-      <c r="G46" s="10">
-        <v>0.86283125682774919</v>
-      </c>
-      <c r="H46" s="10">
-        <v>-0.43669012473840579</v>
-      </c>
-      <c r="I46" s="10">
-        <v>0.24120257571902134</v>
-      </c>
-      <c r="J46" s="10">
-        <v>0.22612451565972078</v>
-      </c>
-      <c r="K46" s="10">
-        <v>-6.0582072659633411E-2</v>
-      </c>
-      <c r="L46" s="10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A47" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="B47" s="10">
-        <v>0.77850018207787042</v>
-      </c>
-      <c r="C47" s="10">
-        <v>-1.3145736324044107E-2</v>
-      </c>
-      <c r="D47" s="10">
-        <v>0.61794826431333727</v>
-      </c>
-      <c r="E47" s="10">
-        <v>0.88283288161365192</v>
-      </c>
-      <c r="F47" s="10">
-        <v>0.72351423035443763</v>
-      </c>
-      <c r="G47" s="10">
-        <v>0.86283125682774919</v>
-      </c>
-      <c r="H47" s="10">
-        <v>-0.43669012473840579</v>
-      </c>
-      <c r="I47" s="10">
-        <v>0.24120257571902134</v>
-      </c>
-      <c r="J47" s="10">
-        <v>0.22612451565972078</v>
-      </c>
-      <c r="K47" s="10">
-        <v>-6.0582072659633411E-2</v>
-      </c>
-      <c r="L47" s="10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A48" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B48" s="10">
-        <v>0.75613362183755173</v>
-      </c>
-      <c r="C48" s="10">
-        <v>-9.7176188239614977E-2</v>
-      </c>
-      <c r="D48" s="10">
-        <v>0.6696598228763615</v>
-      </c>
-      <c r="E48" s="10">
-        <v>0.87612473347389841</v>
-      </c>
-      <c r="F48" s="10">
-        <v>0.74350830904792964</v>
-      </c>
-      <c r="G48" s="10">
-        <v>0.80470206510809461</v>
-      </c>
-      <c r="H48" s="10">
-        <v>-0.23870858198575715</v>
-      </c>
-      <c r="I48" s="10">
-        <v>0.31735826477875656</v>
-      </c>
-      <c r="J48" s="10">
-        <v>0.27942577414939918</v>
-      </c>
-      <c r="K48" s="10">
-        <v>-0.32933327641170074</v>
-      </c>
-      <c r="L48" s="10">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A49" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="B49" s="10">
-        <v>0.7536399090977578</v>
-      </c>
-      <c r="C49" s="10">
-        <v>-0.24726427831233375</v>
-      </c>
-      <c r="D49" s="10">
-        <v>0.70221452214844893</v>
-      </c>
-      <c r="E49" s="10">
-        <v>0.85892770409869035</v>
-      </c>
-      <c r="F49" s="10">
-        <v>0.73221991076598691</v>
-      </c>
-      <c r="G49" s="10">
-        <v>0.76700556984874346</v>
-      </c>
-      <c r="H49" s="10">
-        <v>-0.44328190876545043</v>
-      </c>
-      <c r="I49" s="10">
-        <v>0.25396316828080889</v>
-      </c>
-      <c r="J49" s="10">
-        <v>0.22576187319871766</v>
-      </c>
-      <c r="K49" s="10">
-        <v>-0.40601788305720882</v>
-      </c>
-      <c r="L49" s="10">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A50" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="B50" s="10">
-        <v>0.84418831267468697</v>
-      </c>
-      <c r="C50" s="10">
-        <v>-0.98928012875441951</v>
-      </c>
-      <c r="D50" s="10">
-        <v>0.88766983293904234</v>
-      </c>
-      <c r="E50" s="10">
-        <v>0.88908502337218565</v>
-      </c>
-      <c r="F50" s="10">
-        <v>0.76904052415305191</v>
-      </c>
-      <c r="G50" s="10">
-        <v>0.8351531315824966</v>
-      </c>
-      <c r="H50" s="10">
-        <v>-1.7336709085962372</v>
-      </c>
-      <c r="I50" s="10">
-        <v>0.56000994841475915</v>
-      </c>
-      <c r="J50" s="10">
-        <v>0.47570200274960556</v>
-      </c>
-      <c r="K50" s="10">
-        <v>-1.1814644095181581</v>
-      </c>
-      <c r="L50" s="10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A51" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="B51" s="10">
-        <v>0.78080432727161619</v>
-      </c>
-      <c r="C51" s="10">
-        <v>0.12331756212205791</v>
-      </c>
-      <c r="D51" s="10">
-        <v>0.73191045657243492</v>
-      </c>
-      <c r="E51" s="10">
-        <v>0.88730455851755796</v>
-      </c>
-      <c r="F51" s="10">
-        <v>0.77520481488547233</v>
-      </c>
-      <c r="G51" s="10">
-        <v>0.79118414822180938</v>
-      </c>
-      <c r="H51" s="10">
-        <v>0.12491851781939363</v>
-      </c>
-      <c r="I51" s="10">
-        <v>0.27137939560030622</v>
-      </c>
-      <c r="J51" s="10">
-        <v>0.2082691310338621</v>
-      </c>
-      <c r="K51" s="10">
-        <v>8.5201340042552351E-2</v>
-      </c>
-      <c r="L51" s="10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A52" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="B52" s="10">
-        <v>0.72296968447116239</v>
-      </c>
-      <c r="C52" s="10">
-        <v>-0.21274331483584544</v>
-      </c>
-      <c r="D52" s="10">
-        <v>0.70622315004840208</v>
-      </c>
-      <c r="E52" s="10">
-        <v>0.82263817965584984</v>
-      </c>
-      <c r="F52" s="10">
-        <v>0.68217882702790256</v>
-      </c>
-      <c r="G52" s="10">
-        <v>0.77337754359623201</v>
-      </c>
-      <c r="H52" s="10">
-        <v>-0.13582572781821278</v>
-      </c>
-      <c r="I52" s="10">
-        <v>-7.0542367600500575E-2</v>
-      </c>
-      <c r="J52" s="10">
-        <v>-4.958466065450795E-2</v>
-      </c>
-      <c r="K52" s="10">
-        <v>-0.43177132716531447</v>
-      </c>
-      <c r="L52" s="10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A53" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="B53" s="10">
-        <v>0.66659731197356553</v>
-      </c>
-      <c r="C53" s="10">
-        <v>8.9648768218872188E-2</v>
-      </c>
-      <c r="D53" s="10">
-        <v>0.48305464903391676</v>
-      </c>
-      <c r="E53" s="10">
-        <v>0.83668305484916772</v>
-      </c>
-      <c r="F53" s="10">
-        <v>0.70245547699752076</v>
-      </c>
-      <c r="G53" s="10">
-        <v>0.66830745599443586</v>
-      </c>
-      <c r="H53" s="10">
-        <v>-2.854951646674515E-2</v>
-      </c>
-      <c r="I53" s="10">
-        <v>0.25500569670867074</v>
-      </c>
-      <c r="J53" s="10">
-        <v>0.26866101966591088</v>
-      </c>
-      <c r="K53" s="10">
-        <v>-9.6037135587915004E-2</v>
-      </c>
-      <c r="L53" s="10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A54" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="B54" s="10">
-        <v>0.75812859202938665</v>
-      </c>
-      <c r="C54" s="10">
-        <v>2.2894283818560068E-2</v>
-      </c>
-      <c r="D54" s="10">
-        <v>0.64361606345869171</v>
-      </c>
-      <c r="E54" s="10">
-        <v>0.88988235697406459</v>
-      </c>
-      <c r="F54" s="10">
-        <v>0.7525390276734838</v>
-      </c>
-      <c r="G54" s="10">
-        <v>0.83485926131557564</v>
-      </c>
-      <c r="H54" s="10">
-        <v>-7.5049920562002631E-2</v>
-      </c>
-      <c r="I54" s="10">
-        <v>0.36807434197711481</v>
-      </c>
-      <c r="J54" s="10">
-        <v>0.32235689490994418</v>
-      </c>
-      <c r="K54" s="10">
-        <v>-0.26798559109529424</v>
-      </c>
-      <c r="L54" s="10">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A55" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="B55" s="10">
-        <v>0.75812859202938665</v>
-      </c>
-      <c r="C55" s="10">
-        <v>2.2894283818560068E-2</v>
-      </c>
-      <c r="D55" s="10">
-        <v>0.64361606345869171</v>
-      </c>
-      <c r="E55" s="10">
-        <v>0.88988235697406459</v>
-      </c>
-      <c r="F55" s="10">
-        <v>0.7525390276734838</v>
-      </c>
-      <c r="G55" s="10">
-        <v>0.83485926131557564</v>
-      </c>
-      <c r="H55" s="10">
-        <v>-7.5049920562002631E-2</v>
-      </c>
-      <c r="I55" s="10">
-        <v>0.36807434197711481</v>
-      </c>
-      <c r="J55" s="10">
-        <v>0.32235689490994418</v>
-      </c>
-      <c r="K55" s="10">
-        <v>-0.26798559109529424</v>
-      </c>
-      <c r="L55" s="10">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A56" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="B56" s="10">
-        <v>0.77290972674060299</v>
-      </c>
-      <c r="C56" s="10">
-        <v>-0.57463744375341264</v>
-      </c>
-      <c r="D56" s="10">
-        <v>0.65988570056503359</v>
-      </c>
-      <c r="E56" s="10">
-        <v>0.89133259338526638</v>
-      </c>
-      <c r="F56" s="10">
-        <v>0.79228051745805061</v>
-      </c>
-      <c r="G56" s="10">
-        <v>0.79594498610437314</v>
-      </c>
-      <c r="H56" s="10">
-        <v>-0.37165937093573492</v>
-      </c>
-      <c r="I56" s="10">
-        <v>-0.33602683282219598</v>
-      </c>
-      <c r="J56" s="10">
-        <v>-8.226343472344666E-2</v>
-      </c>
-      <c r="K56" s="10">
-        <v>-0.58440263585059204</v>
-      </c>
-      <c r="L56" s="10">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A57" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="B57" s="10">
-        <v>0.77290972674060299</v>
-      </c>
-      <c r="C57" s="10">
-        <v>-0.57463744375341264</v>
-      </c>
-      <c r="D57" s="10">
-        <v>0.65988570056503359</v>
-      </c>
-      <c r="E57" s="10">
-        <v>0.89133259338526638</v>
-      </c>
-      <c r="F57" s="10">
-        <v>0.79228051745805061</v>
-      </c>
-      <c r="G57" s="10">
-        <v>0.79594498610437314</v>
-      </c>
-      <c r="H57" s="10">
-        <v>-0.37165937093573492</v>
-      </c>
-      <c r="I57" s="10">
-        <v>-0.33602683282219598</v>
-      </c>
-      <c r="J57" s="10">
-        <v>-8.226343472344666E-2</v>
-      </c>
-      <c r="K57" s="10">
-        <v>-0.58440263585059204</v>
-      </c>
-      <c r="L57" s="10">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A58" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="B58" s="10">
-        <v>0.80931506626641969</v>
-      </c>
-      <c r="C58" s="10">
-        <v>-0.64915569865115053</v>
-      </c>
-      <c r="D58" s="10">
-        <v>0.75813851603485183</v>
-      </c>
-      <c r="E58" s="10">
-        <v>0.90650875160174349</v>
-      </c>
-      <c r="F58" s="10">
-        <v>0.8322243475299923</v>
-      </c>
-      <c r="G58" s="10">
-        <v>0.80944090108791833</v>
-      </c>
-      <c r="H58" s="10">
-        <v>-0.809589803684994</v>
-      </c>
-      <c r="I58" s="10">
-        <v>-0.4443799481502933</v>
-      </c>
-      <c r="J58" s="10">
-        <v>-1.5470004649048352E-2</v>
-      </c>
-      <c r="K58" s="10">
-        <v>-1.0184116845780429</v>
-      </c>
-      <c r="L58" s="10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A59" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="B59" s="10">
-        <v>0.73650438721478639</v>
-      </c>
-      <c r="C59" s="10">
-        <v>-0.50011918885567475</v>
-      </c>
-      <c r="D59" s="10">
-        <v>0.56163288509521536</v>
-      </c>
-      <c r="E59" s="10">
-        <v>0.87615643516878927</v>
-      </c>
-      <c r="F59" s="10">
-        <v>0.75233668738610904</v>
-      </c>
-      <c r="G59" s="10">
-        <v>0.78244907112082795</v>
-      </c>
-      <c r="H59" s="10">
-        <v>6.627106181352431E-2</v>
-      </c>
-      <c r="I59" s="10">
-        <v>-0.22767371749409857</v>
-      </c>
-      <c r="J59" s="10">
-        <v>-0.14905686479784497</v>
-      </c>
-      <c r="K59" s="10">
-        <v>-0.15039358712314113</v>
-      </c>
-      <c r="L59" s="10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A60" s="3">
-        <v>4</v>
-      </c>
-      <c r="B60" s="10">
-        <v>0.75370487808515341</v>
-      </c>
-      <c r="C60" s="10">
-        <v>8.0478240048969182E-2</v>
-      </c>
-      <c r="D60" s="10">
-        <v>0.66599764368751091</v>
-      </c>
-      <c r="E60" s="10">
-        <v>0.76875805815376175</v>
-      </c>
-      <c r="F60" s="10">
-        <v>0.76400211090040848</v>
-      </c>
-      <c r="G60" s="10">
-        <v>0.7501128556589165</v>
-      </c>
-      <c r="H60" s="10">
-        <v>3.9048256169417178E-2</v>
-      </c>
-      <c r="I60" s="10">
-        <v>0.11008059241145979</v>
-      </c>
-      <c r="J60" s="10">
-        <v>0.31337908697498446</v>
-      </c>
-      <c r="K60" s="10">
-        <v>-3.7131629291725643E-2</v>
-      </c>
-      <c r="L60" s="10">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A61" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B61" s="10">
-        <v>0.75370487808515341</v>
-      </c>
-      <c r="C61" s="10">
-        <v>8.0478240048969182E-2</v>
-      </c>
-      <c r="D61" s="10">
-        <v>0.66599764368751091</v>
-      </c>
-      <c r="E61" s="10">
-        <v>0.76875805815376175</v>
-      </c>
-      <c r="F61" s="10">
-        <v>0.76400211090040848</v>
-      </c>
-      <c r="G61" s="10">
-        <v>0.7501128556589165</v>
-      </c>
-      <c r="H61" s="10">
-        <v>3.9048256169417178E-2</v>
-      </c>
-      <c r="I61" s="10">
-        <v>0.11008059241145979</v>
-      </c>
-      <c r="J61" s="10">
-        <v>0.31337908697498446</v>
-      </c>
-      <c r="K61" s="10">
-        <v>-3.7131629291725643E-2</v>
-      </c>
-      <c r="L61" s="10">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A62" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="B62" s="10">
-        <v>0.75370487808515341</v>
-      </c>
-      <c r="C62" s="10">
-        <v>8.0478240048969182E-2</v>
-      </c>
-      <c r="D62" s="10">
-        <v>0.66599764368751091</v>
-      </c>
-      <c r="E62" s="10">
-        <v>0.76875805815376175</v>
-      </c>
-      <c r="F62" s="10">
-        <v>0.76400211090040848</v>
-      </c>
-      <c r="G62" s="10">
-        <v>0.7501128556589165</v>
-      </c>
-      <c r="H62" s="10">
-        <v>3.9048256169417178E-2</v>
-      </c>
-      <c r="I62" s="10">
-        <v>0.11008059241145979</v>
-      </c>
-      <c r="J62" s="10">
-        <v>0.31337908697498446</v>
-      </c>
-      <c r="K62" s="10">
-        <v>-3.7131629291725643E-2</v>
-      </c>
-      <c r="L62" s="10">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A63" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="B63" s="10">
-        <v>0.77524258853677475</v>
-      </c>
-      <c r="C63" s="10">
-        <v>3.7976877322300019E-2</v>
-      </c>
-      <c r="D63" s="10">
-        <v>0.77304646220539042</v>
-      </c>
-      <c r="E63" s="10">
-        <v>0.83177234289534863</v>
-      </c>
-      <c r="F63" s="10">
-        <v>0.74282838012189456</v>
-      </c>
-      <c r="G63" s="10">
-        <v>0.75810211585266796</v>
-      </c>
-      <c r="H63" s="10">
-        <v>-9.7437493651897841E-2</v>
-      </c>
-      <c r="I63" s="10">
-        <v>0.3747397838373574</v>
-      </c>
-      <c r="J63" s="10">
-        <v>0.16805161558230722</v>
-      </c>
-      <c r="K63" s="10">
-        <v>-8.4463535577716645E-2</v>
-      </c>
-      <c r="L63" s="10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A64" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="B64" s="10">
-        <v>0.74512525706482646</v>
-      </c>
-      <c r="C64" s="10">
-        <v>0.16261700879737989</v>
-      </c>
-      <c r="D64" s="10">
-        <v>0.67087482805852294</v>
-      </c>
-      <c r="E64" s="10">
-        <v>0.72737613112787558</v>
-      </c>
-      <c r="F64" s="10">
-        <v>0.74416452627284846</v>
-      </c>
-      <c r="G64" s="10">
-        <v>0.72533037757646479</v>
-      </c>
-      <c r="H64" s="10">
-        <v>0.19510051965839367</v>
-      </c>
-      <c r="I64" s="10">
-        <v>0.19404735033338219</v>
-      </c>
-      <c r="J64" s="10">
-        <v>0.32301046130768984</v>
-      </c>
-      <c r="K64" s="10">
-        <v>-5.7590260174745785E-2</v>
-      </c>
-      <c r="L64" s="10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A65" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="B65" s="10">
-        <v>0.76411536818040482</v>
-      </c>
-      <c r="C65" s="10">
-        <v>0.11354503967076053</v>
-      </c>
-      <c r="D65" s="10">
-        <v>0.58110006489703736</v>
-      </c>
-      <c r="E65" s="10">
-        <v>0.84297227909773664</v>
-      </c>
-      <c r="F65" s="10">
-        <v>0.81321685060025128</v>
-      </c>
-      <c r="G65" s="10">
-        <v>0.83941846687770683</v>
-      </c>
-      <c r="H65" s="10">
-        <v>-3.2580287222685356E-2</v>
-      </c>
-      <c r="I65" s="10">
-        <v>-0.14749592269400455</v>
-      </c>
-      <c r="J65" s="10">
-        <v>0.58746193494830778</v>
-      </c>
-      <c r="K65" s="10">
-        <v>0.20230466481130646</v>
-      </c>
-      <c r="L65" s="10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A66" s="6" t="s">
-        <v>250</v>
-      </c>
-      <c r="B66" s="10">
-        <v>0.71865200879533409</v>
-      </c>
-      <c r="C66" s="10">
-        <v>-2.8578068416330229E-2</v>
-      </c>
-      <c r="D66" s="10">
-        <v>0.62545500753988414</v>
-      </c>
-      <c r="E66" s="10">
-        <v>0.624988190164248</v>
-      </c>
-      <c r="F66" s="10">
-        <v>0.75169697445975481</v>
-      </c>
-      <c r="G66" s="10">
-        <v>0.64134426566378111</v>
-      </c>
-      <c r="H66" s="10">
-        <v>0.11714130075607876</v>
-      </c>
-      <c r="I66" s="10">
-        <v>-2.6493558952073837E-2</v>
-      </c>
-      <c r="J66" s="10">
-        <v>0.10579896060495737</v>
-      </c>
-      <c r="K66" s="10">
-        <v>-0.29460026469275707</v>
-      </c>
-      <c r="L66" s="10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A67" s="3" t="s">
+      <c r="A30" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="B67" s="10">
+      <c r="B30" s="8">
         <v>0.59554719082235108</v>
       </c>
-      <c r="C67" s="10">
+      <c r="C30" s="8">
         <v>-7.9004675989593529E-2</v>
       </c>
-      <c r="D67" s="10">
+      <c r="D30" s="8">
         <v>0.43150596003876884</v>
       </c>
-      <c r="E67" s="10">
+      <c r="E30" s="8">
         <v>0.63377178723084393</v>
       </c>
-      <c r="F67" s="10">
+      <c r="F30" s="8">
         <v>0.51706502240712848</v>
       </c>
-      <c r="G67" s="10">
+      <c r="G30" s="8">
         <v>0.70062038907857715</v>
       </c>
-      <c r="H67" s="10">
-        <v>-0.12557640155420233</v>
-      </c>
-      <c r="I67" s="10">
-        <v>7.7323038177252307E-2</v>
-      </c>
-      <c r="J67" s="10">
+      <c r="H30" s="8">
+        <v>-0.12557640155420235</v>
+      </c>
+      <c r="I30" s="8">
+        <v>7.7323038177252265E-2</v>
+      </c>
+      <c r="J30" s="8">
         <v>0.13777020564356879</v>
       </c>
-      <c r="K67" s="10">
+      <c r="K30" s="8">
         <v>-0.20795827548591406</v>
       </c>
-      <c r="L67" s="10">
+      <c r="L30" s="8">
         <v>113</v>
       </c>
     </row>

--- a/logs/massive_topology_search/massive_topology_search.xlsx
+++ b/logs/massive_topology_search/massive_topology_search.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgep-my.sharepoint.com/personal/uxue_ballarin_alumni_mondragon_edu/Documents/Semestre 8-Erasmus/Simula/ship_qnn/logs/massive_topology_search/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="115" documentId="11_AD4D2F04E46CFB4ACB3E20D455D6CCDA693EDF1F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BDD347DC-735D-447B-8EA7-BC170726EA95}"/>
+  <xr:revisionPtr revIDLastSave="117" documentId="11_AD4D2F04E46CFB4ACB3E20D455D6CCDA693EDF1F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D88CC4BE-41F3-4A72-B6A6-3ED046CC684E}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-5580" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="3" r:id="rId3"/>
+    <pivotCache cacheId="8" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2369" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2411" uniqueCount="271">
   <si>
     <t>date</t>
   </si>
@@ -834,6 +834,15 @@
   <si>
     <t>03-01_04-07-53_multihead_spsa_compact_f5_w5_h5_effsu2_full_r8.pkl</t>
   </si>
+  <si>
+    <t>03-02_02-42-04_multihead_spsa_compact_f5_w5_h5_effsu2_full_r8.pkl</t>
+  </si>
+  <si>
+    <t>03-03_01-19-26_multihead_spsa_compact_f5_w5_h5_effsu2_lin_r2.pkl</t>
+  </si>
+  <si>
+    <t>[{'features': ['wv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1]}, {'features': ['sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1]}, {'features': ['yr', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1]}]</t>
+  </si>
 </sst>
 </file>
 
@@ -973,13 +982,13 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Uxue Ballarin" refreshedDate="46083.423559722221" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="113" xr:uid="{74ED0919-17AD-467A-B408-AADD8AC7697B}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Uxue Ballarin" refreshedDate="46084.434332523146" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="115" xr:uid="{74ED0919-17AD-467A-B408-AADD8AC7697B}">
   <cacheSource type="worksheet">
     <worksheetSource name="Tabla1"/>
   </cacheSource>
   <cacheFields count="75">
     <cacheField name="date" numFmtId="164">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-02-17T13:56:47" maxDate="2026-03-01T18:04:55"/>
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-02-17T13:56:47" maxDate="2026-03-03T01:19:26"/>
     </cacheField>
     <cacheField name="model_id" numFmtId="0">
       <sharedItems/>
@@ -1163,10 +1172,10 @@
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="3.9944439159358747E-2" maxValue="0.89998691909115858"/>
     </cacheField>
     <cacheField name="Surge Velocity Global closed MSE" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="8.2940032548061926E-2" maxValue="0.53968232144899331"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="5.4442523907353178E-2" maxValue="0.53968232144899331"/>
     </cacheField>
     <cacheField name="Surge Velocity Global closed R2" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-2.9187914405837958" maxValue="0.39774812567803308"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-2.9187914405837958" maxValue="0.60467688450662282"/>
     </cacheField>
     <cacheField name="Sway Velocity Step MSE" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="2.0382786963712471E-2" maxValue="0.24723604900886939"/>
@@ -1241,7 +1250,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="113">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="115">
   <r>
     <d v="2026-02-22T09:16:08"/>
     <s v="02-22_09-16-08_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_lin_r1_3_1.pkl"/>
@@ -9943,12 +9952,166 @@
     <n v="456.71390585834598"/>
     <n v="-0.29988828543455243"/>
   </r>
+  <r>
+    <d v="2026-03-02T02:42:04"/>
+    <s v="03-02_02-42-04_multihead_spsa_compact_f5_w5_h5_effsu2_full_r8.pkl"/>
+    <x v="2"/>
+    <s v="Final (Last Iteration)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <s v="[['wv', 'rarad'], ['sv', 'rarad'], ['yr', 'rarad'], ['ya', 'yr']]"/>
+    <s v="['Surge Velocity', 'Sway Velocity', 'Yaw Rate', 'Yaw Angle']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="motion"/>
+    <s v="true"/>
+    <s v="false"/>
+    <s v="false"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['wv', 'rarad'], 'output_dim': 1, 'reps': 8, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, -1]}, {'features': ['sv', 'rarad'], 'output_dim': 1, 'reps': 8, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, -1]}, {'features': ['yr', 'rarad'], 'output_dim': 1, 'reps': 8, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, -1]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 8, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, -1]}]"/>
+    <x v="1"/>
+    <s v="compact"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="6"/>
+    <s v="[0, 1, -1]"/>
+    <s v="false"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="512"/>
+    <s v="[0.05, 0.001]"/>
+    <n v="0.1"/>
+    <n v="440"/>
+    <n v="320"/>
+    <n v="120"/>
+    <n v="9.5111517238954488E-2"/>
+    <n v="21.706679439530909"/>
+    <n v="0.71007696714144486"/>
+    <n v="0.13777218883326059"/>
+    <n v="35.893629939937632"/>
+    <n v="0.63361233190299326"/>
+    <n v="35.893629939937632"/>
+    <n v="35.893629939937632"/>
+    <n v="0.63361233190299326"/>
+    <n v="105.5871357883788"/>
+    <n v="4.3215620281502581E-2"/>
+    <n v="0.8"/>
+    <s v="identity"/>
+    <n v="6.4836666614307592E-2"/>
+    <n v="0.52920196925859919"/>
+    <n v="6.4836666614307592E-2"/>
+    <n v="6.4836666614307592E-2"/>
+    <n v="0.52920196925859919"/>
+    <n v="9.6276211969363631E-2"/>
+    <n v="0.30091021995236578"/>
+    <n v="0.1093327358302809"/>
+    <n v="0.62118542185364456"/>
+    <n v="0.1093327358302809"/>
+    <n v="0.1093327358302809"/>
+    <n v="0.62118542185364456"/>
+    <n v="0.33048954534042052"/>
+    <n v="-0.14507568798290599"/>
+    <n v="5.1795564175187443E-2"/>
+    <n v="0.79205719287223342"/>
+    <n v="5.1795564175187443E-2"/>
+    <n v="5.1795564175187443E-2"/>
+    <n v="0.79205719287223342"/>
+    <n v="0.19495014239808961"/>
+    <n v="0.21733684137305981"/>
+    <n v="143.348554793131"/>
+    <n v="0.59200474362749489"/>
+    <n v="143.348554793131"/>
+    <n v="143.348554793131"/>
+    <n v="0.59200474362749489"/>
+    <n v="421.72682725380753"/>
+    <n v="-0.2003088922165073"/>
+  </r>
+  <r>
+    <d v="2026-03-03T01:19:26"/>
+    <s v="03-03_01-19-26_multihead_spsa_compact_f5_w5_h5_effsu2_lin_r2.pkl"/>
+    <x v="1"/>
+    <s v="Final (Last Iteration)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <s v="[['wv', 'rarad'], ['sv', 'rarad'], ['yr', 'rarad'], ['ya', 'yr']]"/>
+    <s v="['Surge Velocity', 'Sway Velocity', 'Yaw Rate', 'Yaw Angle']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="motion"/>
+    <s v="true"/>
+    <s v="false"/>
+    <s v="false"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['wv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1]}, {'features': ['sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1]}, {'features': ['yr', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1]}]"/>
+    <x v="1"/>
+    <s v="compact"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="5"/>
+    <s v="[0, 1, -1]"/>
+    <s v="false"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="512"/>
+    <s v="[0.05, 0.001]"/>
+    <n v="0.1"/>
+    <n v="200"/>
+    <n v="80"/>
+    <n v="120"/>
+    <n v="7.2955293197742244E-2"/>
+    <n v="12.689402052466789"/>
+    <n v="0.78974256903254514"/>
+    <n v="-5.0314965514804633E-2"/>
+    <n v="14.796927003355609"/>
+    <n v="0.7960035020959586"/>
+    <n v="14.796927003355609"/>
+    <n v="14.796927003355609"/>
+    <n v="0.7960035020959586"/>
+    <n v="228.4102505292411"/>
+    <n v="-6.1352646996310767E-2"/>
+    <n v="0.8"/>
+    <s v="identity"/>
+    <n v="2.1566851671586621E-2"/>
+    <n v="0.84339677181932338"/>
+    <n v="2.1566851671586621E-2"/>
+    <n v="2.1566851671586621E-2"/>
+    <n v="0.84339677181932338"/>
+    <n v="5.4442523907353178E-2"/>
+    <n v="0.60467688450662282"/>
+    <n v="8.860763825186993E-2"/>
+    <n v="0.69299345845482319"/>
+    <n v="8.860763825186993E-2"/>
+    <n v="8.860763825186993E-2"/>
+    <n v="0.69299345845482319"/>
+    <n v="0.25936558978461888"/>
+    <n v="0.10135362722050111"/>
+    <n v="4.5921886495760761E-2"/>
+    <n v="0.81563815089969305"/>
+    <n v="4.5921886495760761E-2"/>
+    <n v="4.5921886495760761E-2"/>
+    <n v="0.81563815089969305"/>
+    <n v="8.7728105308024246E-2"/>
+    <n v="0.64779940575509976"/>
+    <n v="59.031611637003209"/>
+    <n v="0.83198562720999703"/>
+    <n v="59.031611637003209"/>
+    <n v="59.031611637003209"/>
+    <n v="0.83198562720999703"/>
+    <n v="913.23946589796401"/>
+    <n v="-1.5992405054674721"/>
+  </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2D21AEEF-8491-4048-847C-B48B541C6815}" name="TablaDinámica1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A2:L30" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2D21AEEF-8491-4048-847C-B48B541C6815}" name="TablaDinámica1" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A2:L32" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="75">
     <pivotField numFmtId="164" showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
@@ -10076,7 +10239,7 @@
     <field x="21"/>
     <field x="2"/>
   </rowFields>
-  <rowItems count="28">
+  <rowItems count="30">
     <i>
       <x/>
     </i>
@@ -10158,6 +10321,12 @@
     <i r="2">
       <x v="1"/>
     </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="2">
+      <x v="1"/>
+    </i>
     <i t="grand">
       <x/>
     </i>
@@ -10226,8 +10395,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3111F1FF-B489-4444-B033-EAAA6A990F8A}" name="Tabla1" displayName="Tabla1" ref="A1:BW114" totalsRowShown="0" headerRowDxfId="3" headerRowBorderDxfId="2" tableBorderDxfId="1">
-  <autoFilter ref="A1:BW114" xr:uid="{3111F1FF-B489-4444-B033-EAAA6A990F8A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3111F1FF-B489-4444-B033-EAAA6A990F8A}" name="Tabla1" displayName="Tabla1" ref="A1:BW116" totalsRowShown="0" headerRowDxfId="3" headerRowBorderDxfId="2" tableBorderDxfId="1">
+  <autoFilter ref="A1:BW116" xr:uid="{3111F1FF-B489-4444-B033-EAAA6A990F8A}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:BW100">
     <sortCondition descending="1" ref="AK1:AK100"/>
   </sortState>
@@ -10575,7 +10744,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BW114"/>
+  <dimension ref="A1:BW116"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:75" x14ac:dyDescent="0.3">
@@ -36079,6 +36248,454 @@
       </c>
       <c r="BW114">
         <v>-0.29988828543455243</v>
+      </c>
+    </row>
+    <row r="115" spans="1:75" x14ac:dyDescent="0.3">
+      <c r="A115" s="2">
+        <v>46083.112546296303</v>
+      </c>
+      <c r="B115" t="s">
+        <v>268</v>
+      </c>
+      <c r="C115">
+        <v>3</v>
+      </c>
+      <c r="D115" t="s">
+        <v>76</v>
+      </c>
+      <c r="E115" t="s">
+        <v>77</v>
+      </c>
+      <c r="F115">
+        <v>16590</v>
+      </c>
+      <c r="G115">
+        <v>4.5</v>
+      </c>
+      <c r="H115" t="s">
+        <v>174</v>
+      </c>
+      <c r="I115" t="s">
+        <v>79</v>
+      </c>
+      <c r="J115">
+        <v>5</v>
+      </c>
+      <c r="K115">
+        <v>5</v>
+      </c>
+      <c r="L115" t="s">
+        <v>80</v>
+      </c>
+      <c r="M115" t="s">
+        <v>81</v>
+      </c>
+      <c r="N115" t="s">
+        <v>82</v>
+      </c>
+      <c r="O115" t="s">
+        <v>82</v>
+      </c>
+      <c r="P115" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q115" t="s">
+        <v>249</v>
+      </c>
+      <c r="R115">
+        <v>4</v>
+      </c>
+      <c r="S115" t="s">
+        <v>85</v>
+      </c>
+      <c r="T115" t="s">
+        <v>86</v>
+      </c>
+      <c r="U115" t="s">
+        <v>87</v>
+      </c>
+      <c r="V115" t="s">
+        <v>250</v>
+      </c>
+      <c r="W115" t="s">
+        <v>177</v>
+      </c>
+      <c r="X115" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y115" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z115">
+        <v>4000</v>
+      </c>
+      <c r="AA115">
+        <v>4000</v>
+      </c>
+      <c r="AC115">
+        <v>512</v>
+      </c>
+      <c r="AD115" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE115">
+        <v>0.1</v>
+      </c>
+      <c r="AF115">
+        <v>440</v>
+      </c>
+      <c r="AG115">
+        <v>320</v>
+      </c>
+      <c r="AH115">
+        <v>120</v>
+      </c>
+      <c r="AI115">
+        <v>9.5111517238954488E-2</v>
+      </c>
+      <c r="AJ115">
+        <v>21.706679439530909</v>
+      </c>
+      <c r="AK115">
+        <v>0.71007696714144486</v>
+      </c>
+      <c r="AL115">
+        <v>0.13777218883326059</v>
+      </c>
+      <c r="AM115">
+        <v>35.893629939937632</v>
+      </c>
+      <c r="AN115">
+        <v>0.63361233190299326</v>
+      </c>
+      <c r="AO115">
+        <v>35.893629939937632</v>
+      </c>
+      <c r="AP115">
+        <v>35.893629939937632</v>
+      </c>
+      <c r="AQ115">
+        <v>0.63361233190299326</v>
+      </c>
+      <c r="AR115">
+        <v>105.5871357883788</v>
+      </c>
+      <c r="AS115">
+        <v>4.3215620281502581E-2</v>
+      </c>
+      <c r="AT115">
+        <v>0.8</v>
+      </c>
+      <c r="AU115" t="s">
+        <v>91</v>
+      </c>
+      <c r="AV115">
+        <v>6.4836666614307592E-2</v>
+      </c>
+      <c r="AW115">
+        <v>0.52920196925859919</v>
+      </c>
+      <c r="AX115">
+        <v>6.4836666614307592E-2</v>
+      </c>
+      <c r="AY115">
+        <v>6.4836666614307592E-2</v>
+      </c>
+      <c r="AZ115">
+        <v>0.52920196925859919</v>
+      </c>
+      <c r="BA115">
+        <v>9.6276211969363631E-2</v>
+      </c>
+      <c r="BB115">
+        <v>0.30091021995236578</v>
+      </c>
+      <c r="BC115">
+        <v>0.1093327358302809</v>
+      </c>
+      <c r="BD115">
+        <v>0.62118542185364456</v>
+      </c>
+      <c r="BE115">
+        <v>0.1093327358302809</v>
+      </c>
+      <c r="BF115">
+        <v>0.1093327358302809</v>
+      </c>
+      <c r="BG115">
+        <v>0.62118542185364456</v>
+      </c>
+      <c r="BH115">
+        <v>0.33048954534042052</v>
+      </c>
+      <c r="BI115">
+        <v>-0.14507568798290599</v>
+      </c>
+      <c r="BJ115">
+        <v>5.1795564175187443E-2</v>
+      </c>
+      <c r="BK115">
+        <v>0.79205719287223342</v>
+      </c>
+      <c r="BL115">
+        <v>5.1795564175187443E-2</v>
+      </c>
+      <c r="BM115">
+        <v>5.1795564175187443E-2</v>
+      </c>
+      <c r="BN115">
+        <v>0.79205719287223342</v>
+      </c>
+      <c r="BO115">
+        <v>0.19495014239808961</v>
+      </c>
+      <c r="BP115">
+        <v>0.21733684137305981</v>
+      </c>
+      <c r="BQ115">
+        <v>143.348554793131</v>
+      </c>
+      <c r="BR115">
+        <v>0.59200474362749489</v>
+      </c>
+      <c r="BS115">
+        <v>143.348554793131</v>
+      </c>
+      <c r="BT115">
+        <v>143.348554793131</v>
+      </c>
+      <c r="BU115">
+        <v>0.59200474362749489</v>
+      </c>
+      <c r="BV115">
+        <v>421.72682725380753</v>
+      </c>
+      <c r="BW115">
+        <v>-0.2003088922165073</v>
+      </c>
+    </row>
+    <row r="116" spans="1:75" x14ac:dyDescent="0.3">
+      <c r="A116" s="2">
+        <v>46084.055162037039</v>
+      </c>
+      <c r="B116" t="s">
+        <v>269</v>
+      </c>
+      <c r="C116">
+        <v>1</v>
+      </c>
+      <c r="D116" t="s">
+        <v>76</v>
+      </c>
+      <c r="E116" t="s">
+        <v>77</v>
+      </c>
+      <c r="F116">
+        <v>16590</v>
+      </c>
+      <c r="G116">
+        <v>4.5</v>
+      </c>
+      <c r="H116" t="s">
+        <v>174</v>
+      </c>
+      <c r="I116" t="s">
+        <v>79</v>
+      </c>
+      <c r="J116">
+        <v>5</v>
+      </c>
+      <c r="K116">
+        <v>5</v>
+      </c>
+      <c r="L116" t="s">
+        <v>80</v>
+      </c>
+      <c r="M116" t="s">
+        <v>81</v>
+      </c>
+      <c r="N116" t="s">
+        <v>82</v>
+      </c>
+      <c r="O116" t="s">
+        <v>82</v>
+      </c>
+      <c r="P116" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q116" t="s">
+        <v>270</v>
+      </c>
+      <c r="R116">
+        <v>4</v>
+      </c>
+      <c r="S116" t="s">
+        <v>85</v>
+      </c>
+      <c r="T116" t="s">
+        <v>86</v>
+      </c>
+      <c r="U116" t="s">
+        <v>110</v>
+      </c>
+      <c r="V116" t="s">
+        <v>176</v>
+      </c>
+      <c r="W116" t="s">
+        <v>177</v>
+      </c>
+      <c r="X116" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y116" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z116">
+        <v>4000</v>
+      </c>
+      <c r="AA116">
+        <v>4000</v>
+      </c>
+      <c r="AC116">
+        <v>512</v>
+      </c>
+      <c r="AD116" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE116">
+        <v>0.1</v>
+      </c>
+      <c r="AF116">
+        <v>200</v>
+      </c>
+      <c r="AG116">
+        <v>80</v>
+      </c>
+      <c r="AH116">
+        <v>120</v>
+      </c>
+      <c r="AI116">
+        <v>7.2955293197742244E-2</v>
+      </c>
+      <c r="AJ116">
+        <v>12.689402052466789</v>
+      </c>
+      <c r="AK116">
+        <v>0.78974256903254514</v>
+      </c>
+      <c r="AL116">
+        <v>-5.0314965514804633E-2</v>
+      </c>
+      <c r="AM116">
+        <v>14.796927003355609</v>
+      </c>
+      <c r="AN116">
+        <v>0.7960035020959586</v>
+      </c>
+      <c r="AO116">
+        <v>14.796927003355609</v>
+      </c>
+      <c r="AP116">
+        <v>14.796927003355609</v>
+      </c>
+      <c r="AQ116">
+        <v>0.7960035020959586</v>
+      </c>
+      <c r="AR116">
+        <v>228.4102505292411</v>
+      </c>
+      <c r="AS116">
+        <v>-6.1352646996310767E-2</v>
+      </c>
+      <c r="AT116">
+        <v>0.8</v>
+      </c>
+      <c r="AU116" t="s">
+        <v>91</v>
+      </c>
+      <c r="AV116">
+        <v>2.1566851671586621E-2</v>
+      </c>
+      <c r="AW116">
+        <v>0.84339677181932338</v>
+      </c>
+      <c r="AX116">
+        <v>2.1566851671586621E-2</v>
+      </c>
+      <c r="AY116">
+        <v>2.1566851671586621E-2</v>
+      </c>
+      <c r="AZ116">
+        <v>0.84339677181932338</v>
+      </c>
+      <c r="BA116">
+        <v>5.4442523907353178E-2</v>
+      </c>
+      <c r="BB116">
+        <v>0.60467688450662282</v>
+      </c>
+      <c r="BC116">
+        <v>8.860763825186993E-2</v>
+      </c>
+      <c r="BD116">
+        <v>0.69299345845482319</v>
+      </c>
+      <c r="BE116">
+        <v>8.860763825186993E-2</v>
+      </c>
+      <c r="BF116">
+        <v>8.860763825186993E-2</v>
+      </c>
+      <c r="BG116">
+        <v>0.69299345845482319</v>
+      </c>
+      <c r="BH116">
+        <v>0.25936558978461888</v>
+      </c>
+      <c r="BI116">
+        <v>0.10135362722050111</v>
+      </c>
+      <c r="BJ116">
+        <v>4.5921886495760761E-2</v>
+      </c>
+      <c r="BK116">
+        <v>0.81563815089969305</v>
+      </c>
+      <c r="BL116">
+        <v>4.5921886495760761E-2</v>
+      </c>
+      <c r="BM116">
+        <v>4.5921886495760761E-2</v>
+      </c>
+      <c r="BN116">
+        <v>0.81563815089969305</v>
+      </c>
+      <c r="BO116">
+        <v>8.7728105308024246E-2</v>
+      </c>
+      <c r="BP116">
+        <v>0.64779940575509976</v>
+      </c>
+      <c r="BQ116">
+        <v>59.031611637003209</v>
+      </c>
+      <c r="BR116">
+        <v>0.83198562720999703</v>
+      </c>
+      <c r="BS116">
+        <v>59.031611637003209</v>
+      </c>
+      <c r="BT116">
+        <v>59.031611637003209</v>
+      </c>
+      <c r="BU116">
+        <v>0.83198562720999703</v>
+      </c>
+      <c r="BV116">
+        <v>913.23946589796401</v>
+      </c>
+      <c r="BW116">
+        <v>-1.5992405054674721</v>
       </c>
     </row>
   </sheetData>
@@ -36091,21 +36708,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC2417C5-69B1-40A5-8AFE-A835A2C478FA}">
-  <dimension ref="A2:L30"/>
+  <dimension ref="A2:L32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="41.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="41.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="54.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="53.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="47.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="49.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="56.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="55.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="49.77734375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="51.44140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="25.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="41.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="56.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="55.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="50.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="51.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="59" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="58" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="52.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="53.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="26.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
@@ -37063,37 +37680,37 @@
         <v>4</v>
       </c>
       <c r="B27" s="8">
-        <v>0.75370487808515341</v>
+        <v>0.75312101500851369</v>
       </c>
       <c r="C27" s="8">
-        <v>8.0478240048969182E-2</v>
+        <v>7.4824451065932066E-2</v>
       </c>
       <c r="D27" s="8">
-        <v>0.6659976436875108</v>
+        <v>0.6691209862800418</v>
       </c>
       <c r="E27" s="8">
-        <v>0.76875805815376164</v>
+        <v>0.7515782707692189</v>
       </c>
       <c r="F27" s="8">
-        <v>0.76400211090040837</v>
+        <v>0.77013219720587833</v>
       </c>
       <c r="G27" s="8">
-        <v>0.7501128556589165</v>
+        <v>0.74424859869889026</v>
       </c>
       <c r="H27" s="8">
-        <v>3.9048256169417178E-2</v>
+        <v>0.10270137864019827</v>
       </c>
       <c r="I27" s="8">
-        <v>0.1100805924114598</v>
+        <v>8.9781881212588691E-2</v>
       </c>
       <c r="J27" s="8">
-        <v>0.31337908697498446</v>
+        <v>0.33171586183484525</v>
       </c>
       <c r="K27" s="8">
-        <v>-3.7131629291725643E-2</v>
+        <v>-0.16984594768407396</v>
       </c>
       <c r="L27" s="8">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
@@ -37101,37 +37718,37 @@
         <v>87</v>
       </c>
       <c r="B28" s="8">
-        <v>0.75370487808515341</v>
+        <v>0.75006921883984434</v>
       </c>
       <c r="C28" s="8">
-        <v>8.0478240048969182E-2</v>
+        <v>8.5252735780993461E-2</v>
       </c>
       <c r="D28" s="8">
-        <v>0.6659976436875108</v>
+        <v>0.65459800415176816</v>
       </c>
       <c r="E28" s="8">
-        <v>0.76875805815376164</v>
+        <v>0.75646033846208516</v>
       </c>
       <c r="F28" s="8">
-        <v>0.76400211090040837</v>
+        <v>0.76634003439806042</v>
       </c>
       <c r="G28" s="8">
-        <v>0.7501128556589165</v>
+        <v>0.73693717965629801</v>
       </c>
       <c r="H28" s="8">
-        <v>3.9048256169417178E-2</v>
+        <v>6.087008648466289E-2</v>
       </c>
       <c r="I28" s="8">
-        <v>0.1100805924114598</v>
+        <v>8.8817569045262654E-2</v>
       </c>
       <c r="J28" s="8">
-        <v>0.31337908697498446</v>
+        <v>0.30537556650815739</v>
       </c>
       <c r="K28" s="8">
-        <v>-3.7131629291725643E-2</v>
+        <v>-5.0729734535457448E-2</v>
       </c>
       <c r="L28" s="8">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
@@ -37139,75 +37756,151 @@
         <v>86</v>
       </c>
       <c r="B29" s="8">
-        <v>0.75370487808515341</v>
+        <v>0.75006921883984434</v>
       </c>
       <c r="C29" s="8">
-        <v>8.0478240048969182E-2</v>
+        <v>8.5252735780993461E-2</v>
       </c>
       <c r="D29" s="8">
-        <v>0.6659976436875108</v>
+        <v>0.65459800415176816</v>
       </c>
       <c r="E29" s="8">
-        <v>0.76875805815376164</v>
+        <v>0.75646033846208516</v>
       </c>
       <c r="F29" s="8">
-        <v>0.76400211090040837</v>
+        <v>0.76634003439806042</v>
       </c>
       <c r="G29" s="8">
-        <v>0.7501128556589165</v>
+        <v>0.73693717965629801</v>
       </c>
       <c r="H29" s="8">
-        <v>3.9048256169417178E-2</v>
+        <v>6.087008648466289E-2</v>
       </c>
       <c r="I29" s="8">
-        <v>0.1100805924114598</v>
+        <v>8.8817569045262654E-2</v>
       </c>
       <c r="J29" s="8">
-        <v>0.31337908697498446</v>
+        <v>0.30537556650815739</v>
       </c>
       <c r="K29" s="8">
-        <v>-3.7131629291725643E-2</v>
+        <v>-5.0729734535457448E-2</v>
       </c>
       <c r="L29" s="8">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B30" s="8">
+        <v>0.78974256903254514</v>
+      </c>
+      <c r="C30" s="8">
+        <v>-5.0314965514804633E-2</v>
+      </c>
+      <c r="D30" s="8">
+        <v>0.84339677181932338</v>
+      </c>
+      <c r="E30" s="8">
+        <v>0.69299345845482319</v>
+      </c>
+      <c r="F30" s="8">
+        <v>0.81563815089969305</v>
+      </c>
+      <c r="G30" s="8">
+        <v>0.83198562720999703</v>
+      </c>
+      <c r="H30" s="8">
+        <v>0.60467688450662282</v>
+      </c>
+      <c r="I30" s="8">
+        <v>0.10135362722050111</v>
+      </c>
+      <c r="J30" s="8">
+        <v>0.64779940575509976</v>
+      </c>
+      <c r="K30" s="8">
+        <v>-1.5992405054674721</v>
+      </c>
+      <c r="L30" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A31" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B31" s="8">
+        <v>0.78974256903254514</v>
+      </c>
+      <c r="C31" s="8">
+        <v>-5.0314965514804633E-2</v>
+      </c>
+      <c r="D31" s="8">
+        <v>0.84339677181932338</v>
+      </c>
+      <c r="E31" s="8">
+        <v>0.69299345845482319</v>
+      </c>
+      <c r="F31" s="8">
+        <v>0.81563815089969305</v>
+      </c>
+      <c r="G31" s="8">
+        <v>0.83198562720999703</v>
+      </c>
+      <c r="H31" s="8">
+        <v>0.60467688450662282</v>
+      </c>
+      <c r="I31" s="8">
+        <v>0.10135362722050111</v>
+      </c>
+      <c r="J31" s="8">
+        <v>0.64779940575509976</v>
+      </c>
+      <c r="K31" s="8">
+        <v>-1.5992405054674721</v>
+      </c>
+      <c r="L31" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A32" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="B30" s="8">
-        <v>0.59554719082235108</v>
-      </c>
-      <c r="C30" s="8">
-        <v>-7.9004675989593529E-2</v>
-      </c>
-      <c r="D30" s="8">
-        <v>0.43150596003876884</v>
-      </c>
-      <c r="E30" s="8">
-        <v>0.63377178723084393</v>
-      </c>
-      <c r="F30" s="8">
-        <v>0.51706502240712848</v>
-      </c>
-      <c r="G30" s="8">
-        <v>0.70062038907857715</v>
-      </c>
-      <c r="H30" s="8">
-        <v>-0.12557640155420235</v>
-      </c>
-      <c r="I30" s="8">
-        <v>7.7323038177252265E-2</v>
-      </c>
-      <c r="J30" s="8">
-        <v>0.13777020564356879</v>
-      </c>
-      <c r="K30" s="8">
-        <v>-0.20795827548591406</v>
-      </c>
-      <c r="L30" s="8">
-        <v>113</v>
+      <c r="B32" s="8">
+        <v>0.59823175738347534</v>
+      </c>
+      <c r="C32" s="8">
+        <v>-7.6870184030483582E-2</v>
+      </c>
+      <c r="D32" s="8">
+        <v>0.43593714978659825</v>
+      </c>
+      <c r="E32" s="8">
+        <v>0.63417731162951152</v>
+      </c>
+      <c r="F32" s="8">
+        <v>0.52205254674589086</v>
+      </c>
+      <c r="G32" s="8">
+        <v>0.70081821162362368</v>
+      </c>
+      <c r="H32" s="8">
+        <v>-0.115517793662312</v>
+      </c>
+      <c r="I32" s="8">
+        <v>7.5598097854496532E-2</v>
+      </c>
+      <c r="J32" s="8">
+        <v>0.14289712595522985</v>
+      </c>
+      <c r="K32" s="8">
+        <v>-0.21998986545732405</v>
+      </c>
+      <c r="L32" s="8">
+        <v>115</v>
       </c>
     </row>
   </sheetData>

--- a/logs/massive_topology_search/massive_topology_search.xlsx
+++ b/logs/massive_topology_search/massive_topology_search.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgep-my.sharepoint.com/personal/uxue_ballarin_alumni_mondragon_edu/Documents/Semestre 8-Erasmus/Simula/ship_qnn/logs/massive_topology_search/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="117" documentId="11_AD4D2F04E46CFB4ACB3E20D455D6CCDA693EDF1F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D88CC4BE-41F3-4A72-B6A6-3ED046CC684E}"/>
+  <xr:revisionPtr revIDLastSave="219" documentId="11_AD4D2F04E46CFB4ACB3E20D455D6CCDA693EDF1F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EC38DEB0-993A-4CB1-89CD-BFFD4B9E3197}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-5580" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="8" r:id="rId3"/>
+    <pivotCache cacheId="24" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2411" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2370" uniqueCount="267">
   <si>
     <t>date</t>
   </si>
@@ -331,9 +331,6 @@
     <t>02-17_21-39-23_multihead_spsa_compact_f5_w5_h5_effsu2_full_r3.pkl</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
     <t>02-17_22-08-54_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
   </si>
   <si>
@@ -344,9 +341,6 @@
   </si>
   <si>
     <t>[{'features': ['wv', 'sv', 'yr', 'ya', 'rarad'], 'output_dim': 4, 'reps': 6, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, 2, 3, 4, -1]}]</t>
-  </si>
-  <si>
-    <t>6</t>
   </si>
   <si>
     <t>02-18_06-18-37_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_full_r2_3_2.pkl</t>
@@ -428,9 +422,6 @@
   </si>
   <si>
     <t>[{'features': ['wv', 'sv', 'rarad'], 'output_dim': 1, 'reps': 5, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}, {'features': ['sv', 'yr', 'rarad'], 'output_dim': 2, 'reps': 5, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 5, 'encoding': 'compact', 'ansatz': 'realamplitudes', 'entangle': 'lin', 'map': [0, 1, -1]}]</t>
-  </si>
-  <si>
-    <t>5</t>
   </si>
   <si>
     <t>02-21_02-27-30_multihead_spsa_compact_f5_w5_h5_effsu2_rev_r6.pkl</t>
@@ -557,9 +548,6 @@
   </si>
   <si>
     <t>[{'features': ['wv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, -1]}, {'features': ['sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, -1]}, {'features': ['yr', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, -1]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, -1]}]</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
   <si>
     <t>[0, 1, -1]</t>
@@ -781,9 +769,6 @@
     <t>[{'features': ['wv', 'rarad'], 'output_dim': 1, 'reps': 8, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, -1]}, {'features': ['sv', 'rarad'], 'output_dim': 1, 'reps': 8, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, -1]}, {'features': ['yr', 'rarad'], 'output_dim': 1, 'reps': 8, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, -1]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 8, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'full', 'map': [0, 1, -1]}]</t>
   </si>
   <si>
-    <t>8</t>
-  </si>
-  <si>
     <t>02-28_23-48-45_multihead_spsa_compact_f5_w5_h5_effsu2_lin_r2_3_2.pkl</t>
   </si>
   <si>
@@ -843,6 +828,9 @@
   <si>
     <t>[{'features': ['wv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1]}, {'features': ['sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1]}, {'features': ['yr', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1]}]</t>
   </si>
+  <si>
+    <t>03-03_07-18-06_multihead_spsa_compact_f5_w5_h5_effsu2_lin_r2.pkl</t>
+  </si>
 </sst>
 </file>
 
@@ -899,7 +887,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -916,6 +904,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="3"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -982,13 +973,13 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Uxue Ballarin" refreshedDate="46084.434332523146" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="115" xr:uid="{74ED0919-17AD-467A-B408-AADD8AC7697B}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Uxue Ballarin" refreshedDate="46084.590416203704" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="116" xr:uid="{74ED0919-17AD-467A-B408-AADD8AC7697B}">
   <cacheSource type="worksheet">
     <worksheetSource name="Tabla1"/>
   </cacheSource>
   <cacheFields count="75">
     <cacheField name="date" numFmtId="164">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-02-17T13:56:47" maxDate="2026-03-03T01:19:26"/>
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-02-17T13:56:47" maxDate="2026-03-03T07:18:06"/>
     </cacheField>
     <cacheField name="model_id" numFmtId="0">
       <sharedItems/>
@@ -1053,31 +1044,31 @@
       <sharedItems/>
     </cacheField>
     <cacheField name="ansatz" numFmtId="0">
-      <sharedItems count="4">
+      <sharedItems count="5">
         <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
         <s v="effsu2"/>
         <s v="ugates"/>
         <s v="realamplitudes"/>
+        <s v="lin" u="1"/>
       </sharedItems>
     </cacheField>
     <cacheField name="entangle" numFmtId="0">
-      <sharedItems count="3">
+      <sharedItems count="4">
         <s v="lin"/>
         <s v="rev"/>
         <s v="full"/>
+        <s v="2" u="1"/>
       </sharedItems>
     </cacheField>
     <cacheField name="reps" numFmtId="0">
-      <sharedItems containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="3" maxValue="6" count="10">
+      <sharedItems containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="2" maxValue="8" count="8">
         <s v="[1, 3, 1]"/>
         <s v="[2, 3, 2]"/>
-        <s v="3"/>
+        <n v="3"/>
         <s v="[3, 5, 2]"/>
-        <s v="5"/>
-        <s v="2"/>
-        <s v="8"/>
-        <n v="3"/>
-        <s v="6"/>
+        <n v="5"/>
+        <n v="2"/>
+        <n v="8"/>
         <n v="6"/>
       </sharedItems>
     </cacheField>
@@ -1250,7 +1241,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="115">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="116">
   <r>
     <d v="2026-02-22T09:16:08"/>
     <s v="02-22_09-16-08_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_lin_r1_3_1.pkl"/>
@@ -4738,7 +4729,7 @@
     <s v="compact"/>
     <x v="1"/>
     <x v="2"/>
-    <x v="7"/>
+    <x v="2"/>
     <s v="[0, 1, 2, 3, 4, -1]"/>
     <s v="false"/>
     <s v="spsa"/>
@@ -4815,7 +4806,7 @@
     <s v="compact"/>
     <x v="2"/>
     <x v="0"/>
-    <x v="8"/>
+    <x v="7"/>
     <s v="[0, 1, 2, 3, 4, -1]"/>
     <s v="false"/>
     <s v="spsa"/>
@@ -5046,7 +5037,7 @@
     <s v="compact"/>
     <x v="1"/>
     <x v="1"/>
-    <x v="8"/>
+    <x v="7"/>
     <s v="[0, 1, 2, 3, 4, -1]"/>
     <s v="false"/>
     <s v="spsa"/>
@@ -5277,7 +5268,7 @@
     <s v="compact"/>
     <x v="1"/>
     <x v="1"/>
-    <x v="8"/>
+    <x v="7"/>
     <s v="[0, 1, 2, 3, 4, -1]"/>
     <s v="false"/>
     <s v="spsa"/>
@@ -5354,7 +5345,7 @@
     <s v="compact"/>
     <x v="2"/>
     <x v="0"/>
-    <x v="8"/>
+    <x v="7"/>
     <s v="[0, 1, 2, 3, 4, -1]"/>
     <s v="false"/>
     <s v="spsa"/>
@@ -5431,7 +5422,7 @@
     <s v="compact"/>
     <x v="1"/>
     <x v="0"/>
-    <x v="8"/>
+    <x v="7"/>
     <s v="[0, 1, 2, 3, 4, -1]"/>
     <s v="false"/>
     <s v="spsa"/>
@@ -5508,7 +5499,7 @@
     <s v="compact"/>
     <x v="2"/>
     <x v="0"/>
-    <x v="8"/>
+    <x v="7"/>
     <s v="[0, 1, 2, 3, 4, -1]"/>
     <s v="false"/>
     <s v="spsa"/>
@@ -5893,7 +5884,7 @@
     <s v="compact"/>
     <x v="1"/>
     <x v="2"/>
-    <x v="8"/>
+    <x v="7"/>
     <s v="[0, 1, 2, 3, 4, -1]"/>
     <s v="false"/>
     <s v="spsa"/>
@@ -5970,7 +5961,7 @@
     <s v="compact"/>
     <x v="2"/>
     <x v="2"/>
-    <x v="8"/>
+    <x v="7"/>
     <s v="[0, 1, 2, 3, 4, -1]"/>
     <s v="false"/>
     <s v="spsa"/>
@@ -6124,7 +6115,7 @@
     <s v="compact"/>
     <x v="2"/>
     <x v="1"/>
-    <x v="8"/>
+    <x v="7"/>
     <s v="[0, 1, 2, 3, 4, -1]"/>
     <s v="false"/>
     <s v="spsa"/>
@@ -6201,7 +6192,7 @@
     <s v="compact"/>
     <x v="1"/>
     <x v="2"/>
-    <x v="7"/>
+    <x v="2"/>
     <s v="[0, 1, 2, 3, 4, -1]"/>
     <s v="false"/>
     <s v="spsa"/>
@@ -6278,7 +6269,7 @@
     <s v="compact"/>
     <x v="2"/>
     <x v="1"/>
-    <x v="8"/>
+    <x v="7"/>
     <s v="[0, 1, 2, 3, 4, -1]"/>
     <s v="false"/>
     <s v="spsa"/>
@@ -6740,7 +6731,7 @@
     <s v="compact"/>
     <x v="2"/>
     <x v="2"/>
-    <x v="8"/>
+    <x v="7"/>
     <s v="[0, 1, 2, 3, 4, -1]"/>
     <s v="false"/>
     <s v="spsa"/>
@@ -6817,7 +6808,7 @@
     <s v="compact"/>
     <x v="3"/>
     <x v="1"/>
-    <x v="8"/>
+    <x v="7"/>
     <s v="[0, 1, 2, 3, 4, -1]"/>
     <s v="false"/>
     <s v="spsa"/>
@@ -6894,7 +6885,7 @@
     <s v="compact"/>
     <x v="3"/>
     <x v="1"/>
-    <x v="8"/>
+    <x v="7"/>
     <s v="[0, 1, 2, 3, 4, -1]"/>
     <s v="false"/>
     <s v="spsa"/>
@@ -6971,7 +6962,7 @@
     <s v="compact"/>
     <x v="3"/>
     <x v="0"/>
-    <x v="8"/>
+    <x v="7"/>
     <s v="[0, 1, 2, 3, 4, -1]"/>
     <s v="false"/>
     <s v="spsa"/>
@@ -7048,7 +7039,7 @@
     <s v="compact"/>
     <x v="2"/>
     <x v="2"/>
-    <x v="8"/>
+    <x v="7"/>
     <s v="[0, 1, 2, 3, 4, -1]"/>
     <s v="false"/>
     <s v="spsa"/>
@@ -7202,7 +7193,7 @@
     <s v="compact"/>
     <x v="1"/>
     <x v="2"/>
-    <x v="8"/>
+    <x v="7"/>
     <s v="[0, 1, 2, 3, 4, -1]"/>
     <s v="false"/>
     <s v="spsa"/>
@@ -7279,7 +7270,7 @@
     <s v="compact"/>
     <x v="3"/>
     <x v="1"/>
-    <x v="8"/>
+    <x v="7"/>
     <s v="[0, 1, 2, 3, 4, -1]"/>
     <s v="false"/>
     <s v="spsa"/>
@@ -7356,7 +7347,7 @@
     <s v="compact"/>
     <x v="1"/>
     <x v="0"/>
-    <x v="8"/>
+    <x v="7"/>
     <s v="[0, 1, 2, 3, 4, -1]"/>
     <s v="false"/>
     <s v="spsa"/>
@@ -7587,7 +7578,7 @@
     <s v="compact"/>
     <x v="3"/>
     <x v="0"/>
-    <x v="8"/>
+    <x v="7"/>
     <s v="[0, 1, 2, 3, 4, -1]"/>
     <s v="false"/>
     <s v="spsa"/>
@@ -7818,7 +7809,7 @@
     <s v="compact"/>
     <x v="2"/>
     <x v="1"/>
-    <x v="8"/>
+    <x v="7"/>
     <s v="[0, 1, 2, 3, 4, -1]"/>
     <s v="false"/>
     <s v="spsa"/>
@@ -7895,7 +7886,7 @@
     <s v="compact"/>
     <x v="1"/>
     <x v="1"/>
-    <x v="8"/>
+    <x v="7"/>
     <s v="[0, 1, 2, 3, 4, -1]"/>
     <s v="false"/>
     <s v="spsa"/>
@@ -7972,7 +7963,7 @@
     <s v="compact"/>
     <x v="1"/>
     <x v="0"/>
-    <x v="8"/>
+    <x v="7"/>
     <s v="[0, 1, 2, 3, 4, -1]"/>
     <s v="false"/>
     <s v="spsa"/>
@@ -8126,7 +8117,7 @@
     <s v="compact"/>
     <x v="3"/>
     <x v="2"/>
-    <x v="8"/>
+    <x v="7"/>
     <s v="[0, 1, 2, 3, 4, -1]"/>
     <s v="false"/>
     <s v="spsa"/>
@@ -8280,7 +8271,7 @@
     <s v="compact"/>
     <x v="3"/>
     <x v="2"/>
-    <x v="8"/>
+    <x v="7"/>
     <s v="[0, 1, 2, 3, 4, -1]"/>
     <s v="false"/>
     <s v="spsa"/>
@@ -8665,7 +8656,7 @@
     <s v="compact"/>
     <x v="3"/>
     <x v="2"/>
-    <x v="8"/>
+    <x v="7"/>
     <s v="[0, 1, 2, 3, 4, -1]"/>
     <s v="false"/>
     <s v="spsa"/>
@@ -8742,7 +8733,7 @@
     <s v="compact"/>
     <x v="3"/>
     <x v="0"/>
-    <x v="9"/>
+    <x v="7"/>
     <s v="[0, 1, 2, 3, 4, -1]"/>
     <s v="false"/>
     <s v="spsa"/>
@@ -8819,7 +8810,7 @@
     <s v="compact"/>
     <x v="1"/>
     <x v="2"/>
-    <x v="8"/>
+    <x v="7"/>
     <s v="[0, 1, 2, 3, 4, -1]"/>
     <s v="false"/>
     <s v="spsa"/>
@@ -10106,12 +10097,89 @@
     <n v="913.23946589796401"/>
     <n v="-1.5992405054674721"/>
   </r>
+  <r>
+    <d v="2026-03-03T07:18:06"/>
+    <s v="03-03_07-18-06_multihead_spsa_compact_f5_w5_h5_effsu2_lin_r2.pkl"/>
+    <x v="0"/>
+    <s v="Best (Lowest Val Loss)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <s v="[['wv', 'rarad'], ['sv', 'rarad'], ['yr', 'rarad'], ['ya', 'yr']]"/>
+    <s v="['Surge Velocity', 'Sway Velocity', 'Yaw Rate', 'Yaw Angle']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="motion"/>
+    <s v="true"/>
+    <s v="false"/>
+    <s v="false"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['wv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1]}, {'features': ['sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1]}, {'features': ['yr', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1]}]"/>
+    <x v="1"/>
+    <s v="compact"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="5"/>
+    <s v="[0, 1, -1]"/>
+    <s v="false"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="512"/>
+    <s v="[0.05, 0.001]"/>
+    <n v="0.1"/>
+    <n v="200"/>
+    <n v="80"/>
+    <n v="120"/>
+    <n v="7.1990638112177832E-2"/>
+    <n v="16.583762115825699"/>
+    <n v="0.80999601350231554"/>
+    <n v="0.29228831132759953"/>
+    <n v="17.715144406576162"/>
+    <n v="0.8042748584903836"/>
+    <n v="17.715144406576162"/>
+    <n v="17.715144406576162"/>
+    <n v="0.8042748584903836"/>
+    <n v="87.719550229630585"/>
+    <n v="0.23691904110060119"/>
+    <n v="0.8"/>
+    <s v="identity"/>
+    <n v="2.0018159176767719E-2"/>
+    <n v="0.85464228172688905"/>
+    <n v="2.0018159176767719E-2"/>
+    <n v="2.0018159176767719E-2"/>
+    <n v="0.85464228172688905"/>
+    <n v="6.2099186902190011E-2"/>
+    <n v="0.54907961141633299"/>
+    <n v="5.5449924405327859E-2"/>
+    <n v="0.80787785504189369"/>
+    <n v="5.5449924405327859E-2"/>
+    <n v="5.5449924405327859E-2"/>
+    <n v="0.80787785504189369"/>
+    <n v="0.26617355534639658"/>
+    <n v="7.776548060791566E-2"/>
+    <n v="6.0808495296395107E-2"/>
+    <n v="0.75587312522786643"/>
+    <n v="6.0808495296395107E-2"/>
+    <n v="6.0808495296395107E-2"/>
+    <n v="0.75587312522786643"/>
+    <n v="0.1698578353466268"/>
+    <n v="0.3180745174401659"/>
+    <n v="70.724301047426437"/>
+    <n v="0.79870617196488358"/>
+    <n v="70.724301047426437"/>
+    <n v="70.724301047426437"/>
+    <n v="0.79870617196488358"/>
+    <n v="350.38007034092919"/>
+    <n v="2.75655493797955E-3"/>
+  </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2D21AEEF-8491-4048-847C-B48B541C6815}" name="TablaDinámica1" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A2:L32" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2D21AEEF-8491-4048-847C-B48B541C6815}" name="TablaDinámica1" cacheId="24" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A2:L67" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="75">
     <pivotField numFmtId="164" showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
@@ -10147,32 +10215,32 @@
     </pivotField>
     <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
-      <items count="5">
-        <item sd="0" x="0"/>
-        <item sd="0" x="1"/>
-        <item sd="0" x="3"/>
-        <item sd="0" x="2"/>
+      <items count="6">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item m="1" x="4"/>
         <item t="default"/>
       </items>
     </pivotField>
     <pivotField axis="axisRow" showAll="0">
-      <items count="4">
+      <items count="5">
         <item x="2"/>
         <item x="0"/>
         <item x="1"/>
+        <item m="1" x="3"/>
         <item t="default"/>
       </items>
     </pivotField>
     <pivotField axis="axisRow" showAll="0">
-      <items count="11">
-        <item sd="0" x="7"/>
+      <items count="9">
+        <item sd="0" x="2"/>
         <item sd="0" x="0"/>
         <item sd="0" x="1"/>
         <item sd="0" x="3"/>
-        <item sd="0" x="2"/>
+        <item sd="0" x="7"/>
         <item sd="0" x="4"/>
-        <item sd="0" x="8"/>
-        <item x="9"/>
         <item sd="0" x="5"/>
         <item sd="0" x="6"/>
         <item t="default"/>
@@ -10239,7 +10307,7 @@
     <field x="21"/>
     <field x="2"/>
   </rowFields>
-  <rowItems count="30">
+  <rowItems count="65">
     <i>
       <x/>
     </i>
@@ -10249,11 +10317,29 @@
     <i r="2">
       <x v="1"/>
     </i>
+    <i r="3">
+      <x/>
+    </i>
+    <i r="3">
+      <x v="4"/>
+    </i>
     <i r="2">
       <x v="2"/>
     </i>
+    <i r="3">
+      <x/>
+    </i>
+    <i r="3">
+      <x v="4"/>
+    </i>
     <i r="2">
       <x v="3"/>
+    </i>
+    <i r="3">
+      <x/>
+    </i>
+    <i r="3">
+      <x v="4"/>
     </i>
     <i r="1">
       <x v="1"/>
@@ -10261,11 +10347,29 @@
     <i r="2">
       <x v="1"/>
     </i>
+    <i r="3">
+      <x/>
+    </i>
+    <i r="3">
+      <x v="4"/>
+    </i>
     <i r="2">
       <x v="2"/>
     </i>
+    <i r="3">
+      <x/>
+    </i>
+    <i r="3">
+      <x v="4"/>
+    </i>
     <i r="2">
       <x v="3"/>
+    </i>
+    <i r="3">
+      <x/>
+    </i>
+    <i r="3">
+      <x v="4"/>
     </i>
     <i r="1">
       <x v="2"/>
@@ -10273,11 +10377,29 @@
     <i r="2">
       <x v="1"/>
     </i>
+    <i r="3">
+      <x/>
+    </i>
+    <i r="3">
+      <x v="4"/>
+    </i>
     <i r="2">
       <x v="2"/>
     </i>
+    <i r="3">
+      <x/>
+    </i>
+    <i r="3">
+      <x v="4"/>
+    </i>
     <i r="2">
       <x v="3"/>
+    </i>
+    <i r="3">
+      <x/>
+    </i>
+    <i r="3">
+      <x v="4"/>
     </i>
     <i>
       <x v="1"/>
@@ -10288,14 +10410,29 @@
     <i r="2">
       <x/>
     </i>
+    <i r="3">
+      <x v="2"/>
+    </i>
     <i r="2">
       <x v="1"/>
+    </i>
+    <i r="3">
+      <x v="2"/>
+    </i>
+    <i r="3">
+      <x v="3"/>
     </i>
     <i r="2">
       <x v="2"/>
     </i>
+    <i r="3">
+      <x v="2"/>
+    </i>
     <i r="2">
       <x v="3"/>
+    </i>
+    <i r="3">
+      <x v="2"/>
     </i>
     <i r="1">
       <x v="1"/>
@@ -10303,14 +10440,35 @@
     <i r="2">
       <x/>
     </i>
+    <i r="3">
+      <x v="1"/>
+    </i>
+    <i r="3">
+      <x v="2"/>
+    </i>
+    <i r="3">
+      <x v="3"/>
+    </i>
+    <i r="3">
+      <x v="5"/>
+    </i>
     <i r="2">
       <x v="1"/>
+    </i>
+    <i r="3">
+      <x v="2"/>
     </i>
     <i r="1">
       <x v="2"/>
     </i>
     <i r="2">
       <x/>
+    </i>
+    <i r="3">
+      <x v="2"/>
+    </i>
+    <i r="3">
+      <x v="5"/>
     </i>
     <i>
       <x v="2"/>
@@ -10321,11 +10479,26 @@
     <i r="2">
       <x v="1"/>
     </i>
+    <i r="3">
+      <x/>
+    </i>
+    <i r="3">
+      <x v="5"/>
+    </i>
+    <i r="3">
+      <x v="6"/>
+    </i>
+    <i r="3">
+      <x v="7"/>
+    </i>
     <i r="1">
       <x v="1"/>
     </i>
     <i r="2">
       <x v="1"/>
+    </i>
+    <i r="3">
+      <x v="6"/>
     </i>
     <i t="grand">
       <x/>
@@ -10395,8 +10568,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3111F1FF-B489-4444-B033-EAAA6A990F8A}" name="Tabla1" displayName="Tabla1" ref="A1:BW116" totalsRowShown="0" headerRowDxfId="3" headerRowBorderDxfId="2" tableBorderDxfId="1">
-  <autoFilter ref="A1:BW116" xr:uid="{3111F1FF-B489-4444-B033-EAAA6A990F8A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3111F1FF-B489-4444-B033-EAAA6A990F8A}" name="Tabla1" displayName="Tabla1" ref="A1:BW117" totalsRowShown="0" headerRowDxfId="3" headerRowBorderDxfId="2" tableBorderDxfId="1">
+  <autoFilter ref="A1:BW117" xr:uid="{3111F1FF-B489-4444-B033-EAAA6A990F8A}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:BW100">
     <sortCondition descending="1" ref="AK1:AK100"/>
   </sortState>
@@ -10744,7 +10917,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BW116"/>
+  <dimension ref="A1:BW117"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:75" x14ac:dyDescent="0.3">
@@ -10979,13 +11152,13 @@
         <v>46075.386203703703</v>
       </c>
       <c r="B2" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C2" s="7">
         <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E2" t="s">
         <v>77</v>
@@ -11024,7 +11197,7 @@
         <v>83</v>
       </c>
       <c r="Q2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="R2" s="7">
         <v>3</v>
@@ -11036,10 +11209,10 @@
         <v>96</v>
       </c>
       <c r="U2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V2" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="W2" t="s">
         <v>98</v>
@@ -11203,7 +11376,7 @@
         <v>46072.802384259259</v>
       </c>
       <c r="B3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C3" s="7">
         <v>1</v>
@@ -11248,7 +11421,7 @@
         <v>83</v>
       </c>
       <c r="Q3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="R3" s="7">
         <v>3</v>
@@ -11260,7 +11433,7 @@
         <v>96</v>
       </c>
       <c r="U3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="V3" t="s">
         <v>97</v>
@@ -11427,7 +11600,7 @@
         <v>46075.613553240742</v>
       </c>
       <c r="B4" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C4" s="7">
         <v>3</v>
@@ -11472,7 +11645,7 @@
         <v>83</v>
       </c>
       <c r="Q4" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="R4" s="7">
         <v>3</v>
@@ -11484,10 +11657,10 @@
         <v>96</v>
       </c>
       <c r="U4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V4" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="W4" t="s">
         <v>98</v>
@@ -11651,13 +11824,13 @@
         <v>46075.16302083333</v>
       </c>
       <c r="B5" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C5" s="7">
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E5" t="s">
         <v>77</v>
@@ -11696,7 +11869,7 @@
         <v>83</v>
       </c>
       <c r="Q5" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="R5" s="7">
         <v>3</v>
@@ -11708,10 +11881,10 @@
         <v>96</v>
       </c>
       <c r="U5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V5" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="W5" t="s">
         <v>98</v>
@@ -11875,13 +12048,13 @@
         <v>46078.031365740739</v>
       </c>
       <c r="B6" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C6" s="7">
         <v>2</v>
       </c>
       <c r="D6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E6" t="s">
         <v>77</v>
@@ -11893,7 +12066,7 @@
         <v>4.5</v>
       </c>
       <c r="H6" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="I6" t="s">
         <v>79</v>
@@ -11920,7 +12093,7 @@
         <v>83</v>
       </c>
       <c r="Q6" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="R6" s="7">
         <v>4</v>
@@ -11934,11 +12107,11 @@
       <c r="U6" t="s">
         <v>87</v>
       </c>
-      <c r="V6" t="s">
-        <v>100</v>
+      <c r="V6">
+        <v>3</v>
       </c>
       <c r="W6" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="X6" t="s">
         <v>82</v>
@@ -12099,7 +12272,7 @@
         <v>46078.356712962966</v>
       </c>
       <c r="B7" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="C7" s="7">
         <v>1</v>
@@ -12144,7 +12317,7 @@
         <v>83</v>
       </c>
       <c r="Q7" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="R7" s="7">
         <v>3</v>
@@ -12153,7 +12326,7 @@
         <v>85</v>
       </c>
       <c r="T7" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="U7" t="s">
         <v>87</v>
@@ -12323,13 +12496,13 @@
         <v>46077.074745370373</v>
       </c>
       <c r="B8" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C8" s="7">
         <v>2</v>
       </c>
       <c r="D8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E8" t="s">
         <v>77</v>
@@ -12368,7 +12541,7 @@
         <v>83</v>
       </c>
       <c r="Q8" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="R8" s="7">
         <v>3</v>
@@ -12547,7 +12720,7 @@
         <v>46078.945914351847</v>
       </c>
       <c r="B9" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C9" s="7">
         <v>3</v>
@@ -12592,7 +12765,7 @@
         <v>83</v>
       </c>
       <c r="Q9" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="R9" s="7">
         <v>3</v>
@@ -12601,7 +12774,7 @@
         <v>85</v>
       </c>
       <c r="T9" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="U9" t="s">
         <v>87</v>
@@ -12771,7 +12944,7 @@
         <v>46073.117384259262</v>
       </c>
       <c r="B10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C10" s="7">
         <v>2</v>
@@ -12816,7 +12989,7 @@
         <v>83</v>
       </c>
       <c r="Q10" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="R10" s="7">
         <v>3</v>
@@ -12828,7 +13001,7 @@
         <v>96</v>
       </c>
       <c r="U10" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="V10" t="s">
         <v>97</v>
@@ -12995,13 +13168,13 @@
         <v>46070.922847222217</v>
       </c>
       <c r="B11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C11" s="7">
         <v>2</v>
       </c>
       <c r="D11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E11" t="s">
         <v>77</v>
@@ -13219,13 +13392,13 @@
         <v>46072.486967592587</v>
       </c>
       <c r="B12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C12" s="7">
         <v>3</v>
       </c>
       <c r="D12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E12" t="s">
         <v>77</v>
@@ -13264,7 +13437,7 @@
         <v>83</v>
       </c>
       <c r="Q12" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="R12" s="7">
         <v>3</v>
@@ -13276,7 +13449,7 @@
         <v>96</v>
       </c>
       <c r="U12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V12" t="s">
         <v>97</v>
@@ -13443,7 +13616,7 @@
         <v>46073.433611111112</v>
       </c>
       <c r="B13" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C13" s="7">
         <v>3</v>
@@ -13488,7 +13661,7 @@
         <v>83</v>
       </c>
       <c r="Q13" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="R13" s="7">
         <v>3</v>
@@ -13500,7 +13673,7 @@
         <v>96</v>
       </c>
       <c r="U13" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="V13" t="s">
         <v>97</v>
@@ -13667,7 +13840,7 @@
         <v>46081.688692129632</v>
       </c>
       <c r="B14" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C14">
         <v>3</v>
@@ -13712,7 +13885,7 @@
         <v>83</v>
       </c>
       <c r="Q14" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="R14">
         <v>3</v>
@@ -13727,7 +13900,7 @@
         <v>87</v>
       </c>
       <c r="V14" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="W14" t="s">
         <v>98</v>
@@ -13891,7 +14064,7 @@
         <v>46079.914155092592</v>
       </c>
       <c r="B15" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C15">
         <v>2</v>
@@ -13909,7 +14082,7 @@
         <v>4.5</v>
       </c>
       <c r="H15" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="I15" t="s">
         <v>79</v>
@@ -13936,7 +14109,7 @@
         <v>83</v>
       </c>
       <c r="Q15" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="R15">
         <v>4</v>
@@ -13950,11 +14123,11 @@
       <c r="U15" t="s">
         <v>87</v>
       </c>
-      <c r="V15" t="s">
-        <v>133</v>
+      <c r="V15">
+        <v>5</v>
       </c>
       <c r="W15" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="X15" t="s">
         <v>82</v>
@@ -14115,13 +14288,13 @@
         <v>46078.613888888889</v>
       </c>
       <c r="B16" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="C16" s="7">
         <v>3</v>
       </c>
       <c r="D16" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E16" t="s">
         <v>77</v>
@@ -14133,7 +14306,7 @@
         <v>4.5</v>
       </c>
       <c r="H16" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="I16" t="s">
         <v>79</v>
@@ -14160,7 +14333,7 @@
         <v>83</v>
       </c>
       <c r="Q16" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="R16" s="7">
         <v>4</v>
@@ -14174,11 +14347,11 @@
       <c r="U16" t="s">
         <v>87</v>
       </c>
-      <c r="V16" t="s">
-        <v>100</v>
+      <c r="V16">
+        <v>3</v>
       </c>
       <c r="W16" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="X16" t="s">
         <v>82</v>
@@ -14339,13 +14512,13 @@
         <v>46072.063067129631</v>
       </c>
       <c r="B17" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C17" s="7">
         <v>2</v>
       </c>
       <c r="D17" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E17" t="s">
         <v>77</v>
@@ -14384,7 +14557,7 @@
         <v>83</v>
       </c>
       <c r="Q17" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="R17" s="7">
         <v>3</v>
@@ -14396,7 +14569,7 @@
         <v>96</v>
       </c>
       <c r="U17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V17" t="s">
         <v>97</v>
@@ -14563,13 +14736,13 @@
         <v>46071.632303240738</v>
       </c>
       <c r="B18" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C18" s="7">
         <v>1</v>
       </c>
       <c r="D18" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E18" t="s">
         <v>77</v>
@@ -14608,7 +14781,7 @@
         <v>83</v>
       </c>
       <c r="Q18" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="R18" s="7">
         <v>3</v>
@@ -14620,7 +14793,7 @@
         <v>96</v>
       </c>
       <c r="U18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V18" t="s">
         <v>97</v>
@@ -14787,13 +14960,13 @@
         <v>46077.271053240736</v>
       </c>
       <c r="B19" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C19" s="7">
         <v>3</v>
       </c>
       <c r="D19" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E19" t="s">
         <v>77</v>
@@ -14805,7 +14978,7 @@
         <v>4.5</v>
       </c>
       <c r="H19" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="I19" t="s">
         <v>79</v>
@@ -14832,7 +15005,7 @@
         <v>83</v>
       </c>
       <c r="Q19" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="R19" s="7">
         <v>4</v>
@@ -14846,11 +15019,11 @@
       <c r="U19" t="s">
         <v>87</v>
       </c>
-      <c r="V19" t="s">
-        <v>176</v>
+      <c r="V19">
+        <v>2</v>
       </c>
       <c r="W19" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="X19" t="s">
         <v>82</v>
@@ -15011,7 +15184,7 @@
         <v>46080.917175925933</v>
       </c>
       <c r="B20" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -15056,7 +15229,7 @@
         <v>83</v>
       </c>
       <c r="Q20" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="R20">
         <v>3</v>
@@ -15071,7 +15244,7 @@
         <v>87</v>
       </c>
       <c r="V20" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="W20" t="s">
         <v>98</v>
@@ -15235,7 +15408,7 @@
         <v>46077.341770833344</v>
       </c>
       <c r="B21" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C21" s="7">
         <v>3</v>
@@ -15280,7 +15453,7 @@
         <v>83</v>
       </c>
       <c r="Q21" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="R21" s="7">
         <v>3</v>
@@ -15459,13 +15632,13 @@
         <v>46081.9921875</v>
       </c>
       <c r="B22" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="C22">
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E22" t="s">
         <v>77</v>
@@ -15504,7 +15677,7 @@
         <v>83</v>
       </c>
       <c r="Q22" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="R22">
         <v>3</v>
@@ -15516,7 +15689,7 @@
         <v>86</v>
       </c>
       <c r="U22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V22" t="s">
         <v>97</v>
@@ -15683,7 +15856,7 @@
         <v>46077.646620370368</v>
       </c>
       <c r="B23" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C23" s="7">
         <v>1</v>
@@ -15728,7 +15901,7 @@
         <v>83</v>
       </c>
       <c r="Q23" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="R23" s="7">
         <v>3</v>
@@ -15737,7 +15910,7 @@
         <v>85</v>
       </c>
       <c r="T23" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="U23" t="s">
         <v>87</v>
@@ -16131,13 +16304,13 @@
         <v>46076.957627314812</v>
       </c>
       <c r="B25" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C25" s="7">
         <v>2</v>
       </c>
       <c r="D25" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E25" t="s">
         <v>77</v>
@@ -16149,7 +16322,7 @@
         <v>4.5</v>
       </c>
       <c r="H25" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="I25" t="s">
         <v>79</v>
@@ -16176,7 +16349,7 @@
         <v>83</v>
       </c>
       <c r="Q25" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="R25" s="7">
         <v>4</v>
@@ -16190,11 +16363,11 @@
       <c r="U25" t="s">
         <v>87</v>
       </c>
-      <c r="V25" t="s">
-        <v>176</v>
+      <c r="V25">
+        <v>2</v>
       </c>
       <c r="W25" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="X25" t="s">
         <v>82</v>
@@ -16355,13 +16528,13 @@
         <v>46081.372372685182</v>
       </c>
       <c r="B26" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="C26">
         <v>2</v>
       </c>
       <c r="D26" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E26" t="s">
         <v>77</v>
@@ -16400,7 +16573,7 @@
         <v>83</v>
       </c>
       <c r="Q26" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="R26">
         <v>3</v>
@@ -16415,7 +16588,7 @@
         <v>87</v>
       </c>
       <c r="V26" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="W26" t="s">
         <v>98</v>
@@ -16579,13 +16752,13 @@
         <v>46076.577847222223</v>
       </c>
       <c r="B27" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C27" s="7">
         <v>1</v>
       </c>
       <c r="D27" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E27" t="s">
         <v>77</v>
@@ -16597,7 +16770,7 @@
         <v>4.5</v>
       </c>
       <c r="H27" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="I27" t="s">
         <v>79</v>
@@ -16624,7 +16797,7 @@
         <v>83</v>
       </c>
       <c r="Q27" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="R27" s="7">
         <v>4</v>
@@ -16638,11 +16811,11 @@
       <c r="U27" t="s">
         <v>87</v>
       </c>
-      <c r="V27" t="s">
-        <v>176</v>
+      <c r="V27">
+        <v>2</v>
       </c>
       <c r="W27" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="X27" t="s">
         <v>82</v>
@@ -16803,7 +16976,7 @@
         <v>46071.262928240743</v>
       </c>
       <c r="B28" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C28" s="7">
         <v>3</v>
@@ -17027,13 +17200,13 @@
         <v>46077.904328703713</v>
       </c>
       <c r="B29" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C29" s="7">
         <v>2</v>
       </c>
       <c r="D29" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E29" t="s">
         <v>77</v>
@@ -17072,7 +17245,7 @@
         <v>83</v>
       </c>
       <c r="Q29" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="R29" s="7">
         <v>3</v>
@@ -17081,7 +17254,7 @@
         <v>85</v>
       </c>
       <c r="T29" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="U29" t="s">
         <v>87</v>
@@ -17251,7 +17424,7 @@
         <v>46080.332430555558</v>
       </c>
       <c r="B30" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="C30">
         <v>3</v>
@@ -17296,7 +17469,7 @@
         <v>83</v>
       </c>
       <c r="Q30" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="R30">
         <v>3</v>
@@ -17308,10 +17481,10 @@
         <v>96</v>
       </c>
       <c r="U30" t="s">
-        <v>122</v>
-      </c>
-      <c r="V30" t="s">
-        <v>133</v>
+        <v>120</v>
+      </c>
+      <c r="V30">
+        <v>5</v>
       </c>
       <c r="W30" t="s">
         <v>98</v>
@@ -17475,7 +17648,7 @@
         <v>46079.848599537043</v>
       </c>
       <c r="B31" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C31" s="7">
         <v>2</v>
@@ -17520,7 +17693,7 @@
         <v>83</v>
       </c>
       <c r="Q31" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="R31" s="7">
         <v>3</v>
@@ -17532,10 +17705,10 @@
         <v>96</v>
       </c>
       <c r="U31" t="s">
-        <v>122</v>
-      </c>
-      <c r="V31" t="s">
-        <v>133</v>
+        <v>120</v>
+      </c>
+      <c r="V31">
+        <v>5</v>
       </c>
       <c r="W31" t="s">
         <v>98</v>
@@ -17699,7 +17872,7 @@
         <v>46076.812847222223</v>
       </c>
       <c r="B32" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C32" s="7">
         <v>1</v>
@@ -17744,7 +17917,7 @@
         <v>83</v>
       </c>
       <c r="Q32" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="R32" s="7">
         <v>3</v>
@@ -17923,13 +18096,13 @@
         <v>46076.455104166656</v>
       </c>
       <c r="B33" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C33" s="7">
         <v>3</v>
       </c>
       <c r="D33" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E33" t="s">
         <v>77</v>
@@ -17968,7 +18141,7 @@
         <v>83</v>
       </c>
       <c r="Q33" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="R33" s="7">
         <v>3</v>
@@ -17980,10 +18153,10 @@
         <v>96</v>
       </c>
       <c r="U33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V33" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="W33" t="s">
         <v>98</v>
@@ -18147,13 +18320,13 @@
         <v>46082.20722222222</v>
       </c>
       <c r="B34" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="C34">
         <v>2</v>
       </c>
       <c r="D34" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E34" t="s">
         <v>77</v>
@@ -18192,7 +18365,7 @@
         <v>83</v>
       </c>
       <c r="Q34" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="R34">
         <v>3</v>
@@ -18204,7 +18377,7 @@
         <v>86</v>
       </c>
       <c r="U34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V34" t="s">
         <v>97</v>
@@ -18371,7 +18544,7 @@
         <v>46080.75403935185</v>
       </c>
       <c r="B35" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C35">
         <v>3</v>
@@ -18389,7 +18562,7 @@
         <v>4.5</v>
       </c>
       <c r="H35" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="I35" t="s">
         <v>79</v>
@@ -18416,7 +18589,7 @@
         <v>83</v>
       </c>
       <c r="Q35" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="R35">
         <v>4</v>
@@ -18430,11 +18603,11 @@
       <c r="U35" t="s">
         <v>87</v>
       </c>
-      <c r="V35" t="s">
-        <v>133</v>
+      <c r="V35">
+        <v>5</v>
       </c>
       <c r="W35" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="X35" t="s">
         <v>82</v>
@@ -18595,7 +18768,7 @@
         <v>46079.057916666658</v>
       </c>
       <c r="B36" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C36" s="7">
         <v>1</v>
@@ -18613,7 +18786,7 @@
         <v>4.5</v>
       </c>
       <c r="H36" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="I36" t="s">
         <v>79</v>
@@ -18640,7 +18813,7 @@
         <v>83</v>
       </c>
       <c r="Q36" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="R36" s="7">
         <v>4</v>
@@ -18654,11 +18827,11 @@
       <c r="U36" t="s">
         <v>87</v>
       </c>
-      <c r="V36" t="s">
-        <v>133</v>
+      <c r="V36">
+        <v>5</v>
       </c>
       <c r="W36" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="X36" t="s">
         <v>82</v>
@@ -18819,7 +18992,7 @@
         <v>46081.488726851851</v>
       </c>
       <c r="B37" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="C37">
         <v>1</v>
@@ -18837,7 +19010,7 @@
         <v>4.5</v>
       </c>
       <c r="H37" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="I37" t="s">
         <v>79</v>
@@ -18864,7 +19037,7 @@
         <v>83</v>
       </c>
       <c r="Q37" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="R37">
         <v>4</v>
@@ -18878,11 +19051,11 @@
       <c r="U37" t="s">
         <v>87</v>
       </c>
-      <c r="V37" t="s">
-        <v>250</v>
+      <c r="V37">
+        <v>8</v>
       </c>
       <c r="W37" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="X37" t="s">
         <v>82</v>
@@ -19043,7 +19216,7 @@
         <v>46077.623784722222</v>
       </c>
       <c r="B38" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C38" s="7">
         <v>1</v>
@@ -19061,7 +19234,7 @@
         <v>4.5</v>
       </c>
       <c r="H38" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="I38" t="s">
         <v>79</v>
@@ -19088,7 +19261,7 @@
         <v>83</v>
       </c>
       <c r="Q38" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="R38" s="7">
         <v>4</v>
@@ -19102,11 +19275,11 @@
       <c r="U38" t="s">
         <v>87</v>
       </c>
-      <c r="V38" t="s">
-        <v>100</v>
+      <c r="V38">
+        <v>3</v>
       </c>
       <c r="W38" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="X38" t="s">
         <v>82</v>
@@ -19267,13 +19440,13 @@
         <v>46076.144560185188</v>
       </c>
       <c r="B39" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C39" s="7">
         <v>2</v>
       </c>
       <c r="D39" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E39" t="s">
         <v>77</v>
@@ -19312,7 +19485,7 @@
         <v>83</v>
       </c>
       <c r="Q39" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="R39" s="7">
         <v>3</v>
@@ -19324,10 +19497,10 @@
         <v>96</v>
       </c>
       <c r="U39" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V39" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="W39" t="s">
         <v>98</v>
@@ -19491,13 +19664,13 @@
         <v>46079.243622685193</v>
       </c>
       <c r="B40" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C40" s="7">
         <v>1</v>
       </c>
       <c r="D40" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E40" t="s">
         <v>77</v>
@@ -19536,7 +19709,7 @@
         <v>83</v>
       </c>
       <c r="Q40" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="R40" s="7">
         <v>3</v>
@@ -19548,10 +19721,10 @@
         <v>96</v>
       </c>
       <c r="U40" t="s">
-        <v>122</v>
-      </c>
-      <c r="V40" t="s">
-        <v>133</v>
+        <v>120</v>
+      </c>
+      <c r="V40">
+        <v>5</v>
       </c>
       <c r="W40" t="s">
         <v>98</v>
@@ -19715,7 +19888,7 @@
         <v>46078.660567129627</v>
       </c>
       <c r="B41" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C41" s="7">
         <v>2</v>
@@ -19760,7 +19933,7 @@
         <v>83</v>
       </c>
       <c r="Q41" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="R41" s="7">
         <v>3</v>
@@ -19769,7 +19942,7 @@
         <v>85</v>
       </c>
       <c r="T41" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="U41" t="s">
         <v>87</v>
@@ -19939,13 +20112,13 @@
         <v>46075.840243055558</v>
       </c>
       <c r="B42" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C42" s="7">
         <v>1</v>
       </c>
       <c r="D42" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E42" t="s">
         <v>77</v>
@@ -19984,7 +20157,7 @@
         <v>83</v>
       </c>
       <c r="Q42" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="R42" s="7">
         <v>3</v>
@@ -19996,10 +20169,10 @@
         <v>96</v>
       </c>
       <c r="U42" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V42" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="W42" t="s">
         <v>98</v>
@@ -20163,7 +20336,7 @@
         <v>46074.249907407408</v>
       </c>
       <c r="B43" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C43" s="7">
         <v>2</v>
@@ -20208,7 +20381,7 @@
         <v>83</v>
       </c>
       <c r="Q43" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="R43" s="7">
         <v>3</v>
@@ -20220,10 +20393,10 @@
         <v>96</v>
       </c>
       <c r="U43" t="s">
-        <v>110</v>
-      </c>
-      <c r="V43" t="s">
-        <v>133</v>
+        <v>108</v>
+      </c>
+      <c r="V43">
+        <v>5</v>
       </c>
       <c r="W43" t="s">
         <v>98</v>
@@ -20387,13 +20560,13 @@
         <v>46078.133113425924</v>
       </c>
       <c r="B44" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="C44" s="7">
         <v>3</v>
       </c>
       <c r="D44" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E44" t="s">
         <v>77</v>
@@ -20432,7 +20605,7 @@
         <v>83</v>
       </c>
       <c r="Q44" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="R44" s="7">
         <v>3</v>
@@ -20441,7 +20614,7 @@
         <v>85</v>
       </c>
       <c r="T44" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="U44" t="s">
         <v>87</v>
@@ -20611,13 +20784,13 @@
         <v>46073.748981481483</v>
       </c>
       <c r="B45" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C45" s="7">
         <v>1</v>
       </c>
       <c r="D45" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E45" t="s">
         <v>77</v>
@@ -20656,7 +20829,7 @@
         <v>83</v>
       </c>
       <c r="Q45" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="R45" s="7">
         <v>3</v>
@@ -20668,10 +20841,10 @@
         <v>96</v>
       </c>
       <c r="U45" t="s">
-        <v>110</v>
-      </c>
-      <c r="V45" t="s">
-        <v>133</v>
+        <v>108</v>
+      </c>
+      <c r="V45">
+        <v>5</v>
       </c>
       <c r="W45" t="s">
         <v>98</v>
@@ -20835,7 +21008,7 @@
         <v>46074.751967592587</v>
       </c>
       <c r="B46" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C46" s="7">
         <v>3</v>
@@ -20880,7 +21053,7 @@
         <v>83</v>
       </c>
       <c r="Q46" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="R46" s="7">
         <v>3</v>
@@ -20892,10 +21065,10 @@
         <v>96</v>
       </c>
       <c r="U46" t="s">
-        <v>110</v>
-      </c>
-      <c r="V46" t="s">
-        <v>133</v>
+        <v>108</v>
+      </c>
+      <c r="V46">
+        <v>5</v>
       </c>
       <c r="W46" t="s">
         <v>98</v>
@@ -21283,13 +21456,13 @@
         <v>46079.267881944441</v>
       </c>
       <c r="B48" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C48" s="7">
         <v>2</v>
       </c>
       <c r="D48" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E48" t="s">
         <v>77</v>
@@ -21328,7 +21501,7 @@
         <v>83</v>
       </c>
       <c r="Q48" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="R48" s="7">
         <v>1</v>
@@ -21337,13 +21510,13 @@
         <v>85</v>
       </c>
       <c r="T48" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="U48" t="s">
-        <v>110</v>
-      </c>
-      <c r="V48" t="s">
-        <v>105</v>
+        <v>108</v>
+      </c>
+      <c r="V48">
+        <v>6</v>
       </c>
       <c r="W48" t="s">
         <v>88</v>
@@ -21507,7 +21680,7 @@
         <v>46078.776493055557</v>
       </c>
       <c r="B49" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="C49" s="7">
         <v>2</v>
@@ -21552,7 +21725,7 @@
         <v>83</v>
       </c>
       <c r="Q49" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="R49" s="7">
         <v>1</v>
@@ -21561,13 +21734,13 @@
         <v>85</v>
       </c>
       <c r="T49" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="U49" t="s">
-        <v>110</v>
-      </c>
-      <c r="V49" t="s">
-        <v>100</v>
+        <v>108</v>
+      </c>
+      <c r="V49">
+        <v>3</v>
       </c>
       <c r="W49" t="s">
         <v>88</v>
@@ -21731,13 +21904,13 @@
         <v>46080.227384259262</v>
       </c>
       <c r="B50" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C50" s="7">
         <v>3</v>
       </c>
       <c r="D50" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E50" t="s">
         <v>77</v>
@@ -21776,7 +21949,7 @@
         <v>83</v>
       </c>
       <c r="Q50" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="R50" s="7">
         <v>1</v>
@@ -21785,13 +21958,13 @@
         <v>85</v>
       </c>
       <c r="T50" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="U50" t="s">
-        <v>122</v>
-      </c>
-      <c r="V50" t="s">
-        <v>100</v>
+        <v>120</v>
+      </c>
+      <c r="V50">
+        <v>3</v>
       </c>
       <c r="W50" t="s">
         <v>88</v>
@@ -21955,7 +22128,7 @@
         <v>46074.102430555547</v>
       </c>
       <c r="B51" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C51" s="7">
         <v>1</v>
@@ -22000,7 +22173,7 @@
         <v>83</v>
       </c>
       <c r="Q51" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="R51" s="7">
         <v>1</v>
@@ -22012,10 +22185,10 @@
         <v>86</v>
       </c>
       <c r="U51" t="s">
-        <v>122</v>
-      </c>
-      <c r="V51" t="s">
-        <v>105</v>
+        <v>120</v>
+      </c>
+      <c r="V51">
+        <v>6</v>
       </c>
       <c r="W51" t="s">
         <v>88</v>
@@ -22179,7 +22352,7 @@
         <v>46077.872754629629</v>
       </c>
       <c r="B52" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C52" s="7">
         <v>3</v>
@@ -22224,7 +22397,7 @@
         <v>83</v>
       </c>
       <c r="Q52" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="R52" s="7">
         <v>1</v>
@@ -22233,13 +22406,13 @@
         <v>85</v>
       </c>
       <c r="T52" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="U52" t="s">
         <v>87</v>
       </c>
-      <c r="V52" t="s">
-        <v>100</v>
+      <c r="V52">
+        <v>3</v>
       </c>
       <c r="W52" t="s">
         <v>88</v>
@@ -22403,13 +22576,13 @@
         <v>46077.734409722223</v>
       </c>
       <c r="B53" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C53" s="7">
         <v>2</v>
       </c>
       <c r="D53" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E53" t="s">
         <v>77</v>
@@ -22448,7 +22621,7 @@
         <v>83</v>
       </c>
       <c r="Q53" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="R53" s="7">
         <v>1</v>
@@ -22457,13 +22630,13 @@
         <v>85</v>
       </c>
       <c r="T53" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="U53" t="s">
         <v>87</v>
       </c>
-      <c r="V53" t="s">
-        <v>100</v>
+      <c r="V53">
+        <v>3</v>
       </c>
       <c r="W53" t="s">
         <v>88</v>
@@ -22627,7 +22800,7 @@
         <v>46074.407372685193</v>
       </c>
       <c r="B54" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C54" s="7">
         <v>2</v>
@@ -22672,7 +22845,7 @@
         <v>83</v>
       </c>
       <c r="Q54" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="R54" s="7">
         <v>1</v>
@@ -22684,10 +22857,10 @@
         <v>86</v>
       </c>
       <c r="U54" t="s">
-        <v>122</v>
-      </c>
-      <c r="V54" t="s">
-        <v>105</v>
+        <v>120</v>
+      </c>
+      <c r="V54">
+        <v>6</v>
       </c>
       <c r="W54" t="s">
         <v>88</v>
@@ -22851,7 +23024,7 @@
         <v>46079.020370370366</v>
       </c>
       <c r="B55" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C55" s="7">
         <v>1</v>
@@ -22896,7 +23069,7 @@
         <v>83</v>
       </c>
       <c r="Q55" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="R55" s="7">
         <v>1</v>
@@ -22905,13 +23078,13 @@
         <v>85</v>
       </c>
       <c r="T55" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="U55" t="s">
-        <v>110</v>
-      </c>
-      <c r="V55" t="s">
-        <v>105</v>
+        <v>108</v>
+      </c>
+      <c r="V55">
+        <v>6</v>
       </c>
       <c r="W55" t="s">
         <v>88</v>
@@ -23075,13 +23248,13 @@
         <v>46072.781273148154</v>
       </c>
       <c r="B56" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C56" s="7">
         <v>1</v>
       </c>
       <c r="D56" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E56" t="s">
         <v>77</v>
@@ -23120,7 +23293,7 @@
         <v>83</v>
       </c>
       <c r="Q56" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="R56" s="7">
         <v>1</v>
@@ -23132,10 +23305,10 @@
         <v>86</v>
       </c>
       <c r="U56" t="s">
-        <v>110</v>
-      </c>
-      <c r="V56" t="s">
-        <v>105</v>
+        <v>108</v>
+      </c>
+      <c r="V56">
+        <v>6</v>
       </c>
       <c r="W56" t="s">
         <v>88</v>
@@ -23299,13 +23472,13 @@
         <v>46079.586597222216</v>
       </c>
       <c r="B57" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C57" s="7">
         <v>3</v>
       </c>
       <c r="D57" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E57" t="s">
         <v>77</v>
@@ -23344,7 +23517,7 @@
         <v>83</v>
       </c>
       <c r="Q57" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="R57" s="7">
         <v>1</v>
@@ -23353,13 +23526,13 @@
         <v>85</v>
       </c>
       <c r="T57" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="U57" t="s">
-        <v>110</v>
-      </c>
-      <c r="V57" t="s">
-        <v>105</v>
+        <v>108</v>
+      </c>
+      <c r="V57">
+        <v>6</v>
       </c>
       <c r="W57" t="s">
         <v>88</v>
@@ -23523,13 +23696,13 @@
         <v>46077.610729166663</v>
       </c>
       <c r="B58" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C58" s="7">
         <v>1</v>
       </c>
       <c r="D58" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E58" t="s">
         <v>77</v>
@@ -23568,7 +23741,7 @@
         <v>83</v>
       </c>
       <c r="Q58" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="R58" s="7">
         <v>1</v>
@@ -23577,13 +23750,13 @@
         <v>85</v>
       </c>
       <c r="T58" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="U58" t="s">
         <v>87</v>
       </c>
-      <c r="V58" t="s">
-        <v>100</v>
+      <c r="V58">
+        <v>3</v>
       </c>
       <c r="W58" t="s">
         <v>88</v>
@@ -23747,13 +23920,13 @@
         <v>46075.071423611109</v>
       </c>
       <c r="B59" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C59" s="7">
         <v>2</v>
       </c>
       <c r="D59" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E59" t="s">
         <v>77</v>
@@ -23792,7 +23965,7 @@
         <v>83</v>
       </c>
       <c r="Q59" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="R59" s="7">
         <v>1</v>
@@ -23801,13 +23974,13 @@
         <v>85</v>
       </c>
       <c r="T59" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="U59" t="s">
         <v>87</v>
       </c>
-      <c r="V59" t="s">
-        <v>100</v>
+      <c r="V59">
+        <v>3</v>
       </c>
       <c r="W59" t="s">
         <v>88</v>
@@ -23971,7 +24144,7 @@
         <v>46078.656041666669</v>
       </c>
       <c r="B60" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C60" s="7">
         <v>1</v>
@@ -24016,7 +24189,7 @@
         <v>83</v>
       </c>
       <c r="Q60" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="R60" s="7">
         <v>1</v>
@@ -24025,13 +24198,13 @@
         <v>85</v>
       </c>
       <c r="T60" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="U60" t="s">
-        <v>110</v>
-      </c>
-      <c r="V60" t="s">
-        <v>100</v>
+        <v>108</v>
+      </c>
+      <c r="V60">
+        <v>3</v>
       </c>
       <c r="W60" t="s">
         <v>88</v>
@@ -24195,7 +24368,7 @@
         <v>46073.797314814823</v>
       </c>
       <c r="B61" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C61" s="7">
         <v>2</v>
@@ -24240,7 +24413,7 @@
         <v>83</v>
       </c>
       <c r="Q61" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="R61" s="7">
         <v>1</v>
@@ -24252,10 +24425,10 @@
         <v>86</v>
       </c>
       <c r="U61" t="s">
-        <v>122</v>
-      </c>
-      <c r="V61" t="s">
-        <v>100</v>
+        <v>120</v>
+      </c>
+      <c r="V61">
+        <v>3</v>
       </c>
       <c r="W61" t="s">
         <v>88</v>
@@ -24419,13 +24592,13 @@
         <v>46071.056585648148</v>
       </c>
       <c r="B62" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C62" s="7">
         <v>1</v>
       </c>
       <c r="D62" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E62" t="s">
         <v>77</v>
@@ -24464,7 +24637,7 @@
         <v>83</v>
       </c>
       <c r="Q62" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="R62" s="7">
         <v>1</v>
@@ -24478,8 +24651,8 @@
       <c r="U62" t="s">
         <v>87</v>
       </c>
-      <c r="V62" t="s">
-        <v>105</v>
+      <c r="V62">
+        <v>6</v>
       </c>
       <c r="W62" t="s">
         <v>88</v>
@@ -24643,13 +24816,13 @@
         <v>46077.982627314806</v>
       </c>
       <c r="B63" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C63" s="7">
         <v>1</v>
       </c>
       <c r="D63" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E63" t="s">
         <v>77</v>
@@ -24688,7 +24861,7 @@
         <v>83</v>
       </c>
       <c r="Q63" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="R63" s="7">
         <v>1</v>
@@ -24697,13 +24870,13 @@
         <v>85</v>
       </c>
       <c r="T63" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="U63" t="s">
         <v>87</v>
       </c>
-      <c r="V63" t="s">
-        <v>105</v>
+      <c r="V63">
+        <v>6</v>
       </c>
       <c r="W63" t="s">
         <v>88</v>
@@ -24867,7 +25040,7 @@
         <v>46079.948807870373</v>
       </c>
       <c r="B64" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C64" s="7">
         <v>1</v>
@@ -24912,7 +25085,7 @@
         <v>83</v>
       </c>
       <c r="Q64" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="R64" s="7">
         <v>1</v>
@@ -24921,13 +25094,13 @@
         <v>85</v>
       </c>
       <c r="T64" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="U64" t="s">
-        <v>122</v>
-      </c>
-      <c r="V64" t="s">
-        <v>100</v>
+        <v>120</v>
+      </c>
+      <c r="V64">
+        <v>3</v>
       </c>
       <c r="W64" t="s">
         <v>88</v>
@@ -25091,7 +25264,7 @@
         <v>46080.735983796287</v>
       </c>
       <c r="B65" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C65">
         <v>2</v>
@@ -25136,7 +25309,7 @@
         <v>83</v>
       </c>
       <c r="Q65" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="R65">
         <v>1</v>
@@ -25145,13 +25318,13 @@
         <v>85</v>
       </c>
       <c r="T65" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="U65" t="s">
-        <v>122</v>
-      </c>
-      <c r="V65" t="s">
-        <v>105</v>
+        <v>120</v>
+      </c>
+      <c r="V65">
+        <v>6</v>
       </c>
       <c r="W65" t="s">
         <v>88</v>
@@ -25539,13 +25712,13 @@
         <v>46081.056493055563</v>
       </c>
       <c r="B67" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C67">
         <v>3</v>
       </c>
       <c r="D67" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E67" t="s">
         <v>77</v>
@@ -25584,7 +25757,7 @@
         <v>83</v>
       </c>
       <c r="Q67" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="R67">
         <v>1</v>
@@ -25593,13 +25766,13 @@
         <v>85</v>
       </c>
       <c r="T67" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="U67" t="s">
-        <v>122</v>
-      </c>
-      <c r="V67" t="s">
-        <v>105</v>
+        <v>120</v>
+      </c>
+      <c r="V67">
+        <v>6</v>
       </c>
       <c r="W67" t="s">
         <v>88</v>
@@ -25763,13 +25936,13 @@
         <v>46072.63616898148</v>
       </c>
       <c r="B68" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C68" s="7">
         <v>3</v>
       </c>
       <c r="D68" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E68" t="s">
         <v>77</v>
@@ -25808,7 +25981,7 @@
         <v>83</v>
       </c>
       <c r="Q68" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="R68" s="7">
         <v>1</v>
@@ -25820,10 +25993,10 @@
         <v>86</v>
       </c>
       <c r="U68" t="s">
-        <v>110</v>
-      </c>
-      <c r="V68" t="s">
-        <v>100</v>
+        <v>108</v>
+      </c>
+      <c r="V68">
+        <v>3</v>
       </c>
       <c r="W68" t="s">
         <v>88</v>
@@ -25987,7 +26160,7 @@
         <v>46073.648159722223</v>
       </c>
       <c r="B69" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C69" s="7">
         <v>1</v>
@@ -26032,7 +26205,7 @@
         <v>83</v>
       </c>
       <c r="Q69" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="R69" s="7">
         <v>1</v>
@@ -26044,10 +26217,10 @@
         <v>86</v>
       </c>
       <c r="U69" t="s">
-        <v>122</v>
-      </c>
-      <c r="V69" t="s">
-        <v>100</v>
+        <v>120</v>
+      </c>
+      <c r="V69">
+        <v>3</v>
       </c>
       <c r="W69" t="s">
         <v>88</v>
@@ -26211,7 +26384,7 @@
         <v>46080.08761574074</v>
       </c>
       <c r="B70" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C70" s="7">
         <v>2</v>
@@ -26256,7 +26429,7 @@
         <v>83</v>
       </c>
       <c r="Q70" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="R70" s="7">
         <v>1</v>
@@ -26265,13 +26438,13 @@
         <v>85</v>
       </c>
       <c r="T70" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="U70" t="s">
-        <v>122</v>
-      </c>
-      <c r="V70" t="s">
-        <v>100</v>
+        <v>120</v>
+      </c>
+      <c r="V70">
+        <v>3</v>
       </c>
       <c r="W70" t="s">
         <v>88</v>
@@ -26435,7 +26608,7 @@
         <v>46076.983113425929</v>
       </c>
       <c r="B71" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C71" s="7">
         <v>3</v>
@@ -26480,7 +26653,7 @@
         <v>83</v>
       </c>
       <c r="Q71" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="R71" s="7">
         <v>1</v>
@@ -26489,13 +26662,13 @@
         <v>85</v>
       </c>
       <c r="T71" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="U71" t="s">
-        <v>122</v>
-      </c>
-      <c r="V71" t="s">
-        <v>100</v>
+        <v>120</v>
+      </c>
+      <c r="V71">
+        <v>3</v>
       </c>
       <c r="W71" t="s">
         <v>88</v>
@@ -26659,7 +26832,7 @@
         <v>46078.8984837963</v>
       </c>
       <c r="B72" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="C72" s="7">
         <v>3</v>
@@ -26704,7 +26877,7 @@
         <v>83</v>
       </c>
       <c r="Q72" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="R72" s="7">
         <v>1</v>
@@ -26713,13 +26886,13 @@
         <v>85</v>
       </c>
       <c r="T72" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="U72" t="s">
-        <v>110</v>
-      </c>
-      <c r="V72" t="s">
-        <v>100</v>
+        <v>108</v>
+      </c>
+      <c r="V72">
+        <v>3</v>
       </c>
       <c r="W72" t="s">
         <v>88</v>
@@ -26883,13 +27056,13 @@
         <v>46078.398159722223</v>
       </c>
       <c r="B73" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C73" s="7">
         <v>3</v>
       </c>
       <c r="D73" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E73" t="s">
         <v>77</v>
@@ -26928,7 +27101,7 @@
         <v>83</v>
       </c>
       <c r="Q73" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="R73" s="7">
         <v>1</v>
@@ -26937,13 +27110,13 @@
         <v>85</v>
       </c>
       <c r="T73" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="U73" t="s">
         <v>87</v>
       </c>
-      <c r="V73" t="s">
-        <v>105</v>
+      <c r="V73">
+        <v>6</v>
       </c>
       <c r="W73" t="s">
         <v>88</v>
@@ -27107,7 +27280,7 @@
         <v>46077.076273148137</v>
       </c>
       <c r="B74" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C74" s="7">
         <v>1</v>
@@ -27152,7 +27325,7 @@
         <v>83</v>
       </c>
       <c r="Q74" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="R74" s="7">
         <v>1</v>
@@ -27161,13 +27334,13 @@
         <v>85</v>
       </c>
       <c r="T74" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="U74" t="s">
-        <v>122</v>
-      </c>
-      <c r="V74" t="s">
-        <v>105</v>
+        <v>120</v>
+      </c>
+      <c r="V74">
+        <v>6</v>
       </c>
       <c r="W74" t="s">
         <v>88</v>
@@ -27331,7 +27504,7 @@
         <v>46077.241851851853</v>
       </c>
       <c r="B75" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C75" s="7">
         <v>2</v>
@@ -27376,7 +27549,7 @@
         <v>83</v>
       </c>
       <c r="Q75" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="R75" s="7">
         <v>1</v>
@@ -27385,13 +27558,13 @@
         <v>85</v>
       </c>
       <c r="T75" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="U75" t="s">
-        <v>122</v>
-      </c>
-      <c r="V75" t="s">
-        <v>105</v>
+        <v>120</v>
+      </c>
+      <c r="V75">
+        <v>6</v>
       </c>
       <c r="W75" t="s">
         <v>88</v>
@@ -27555,13 +27728,13 @@
         <v>46076.203240740739</v>
       </c>
       <c r="B76" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C76" s="7">
         <v>1</v>
       </c>
       <c r="D76" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E76" t="s">
         <v>77</v>
@@ -27600,7 +27773,7 @@
         <v>83</v>
       </c>
       <c r="Q76" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="R76" s="7">
         <v>1</v>
@@ -27609,13 +27782,13 @@
         <v>85</v>
       </c>
       <c r="T76" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="U76" t="s">
-        <v>110</v>
-      </c>
-      <c r="V76" t="s">
-        <v>105</v>
+        <v>108</v>
+      </c>
+      <c r="V76">
+        <v>6</v>
       </c>
       <c r="W76" t="s">
         <v>88</v>
@@ -27779,7 +27952,7 @@
         <v>46078.186527777783</v>
       </c>
       <c r="B77" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C77" s="7">
         <v>2</v>
@@ -27824,7 +27997,7 @@
         <v>83</v>
       </c>
       <c r="Q77" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="R77" s="7">
         <v>1</v>
@@ -27833,13 +28006,13 @@
         <v>85</v>
       </c>
       <c r="T77" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="U77" t="s">
         <v>87</v>
       </c>
-      <c r="V77" t="s">
-        <v>105</v>
+      <c r="V77">
+        <v>6</v>
       </c>
       <c r="W77" t="s">
         <v>88</v>
@@ -28003,7 +28176,7 @@
         <v>46072.264560185176</v>
       </c>
       <c r="B78" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C78" s="7">
         <v>1</v>
@@ -28048,7 +28221,7 @@
         <v>83</v>
       </c>
       <c r="Q78" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="R78" s="7">
         <v>1</v>
@@ -28060,10 +28233,10 @@
         <v>86</v>
       </c>
       <c r="U78" t="s">
-        <v>110</v>
-      </c>
-      <c r="V78" t="s">
-        <v>100</v>
+        <v>108</v>
+      </c>
+      <c r="V78">
+        <v>3</v>
       </c>
       <c r="W78" t="s">
         <v>88</v>
@@ -28227,7 +28400,7 @@
         <v>46071.771157407413</v>
       </c>
       <c r="B79" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C79" s="7">
         <v>3</v>
@@ -28272,7 +28445,7 @@
         <v>83</v>
       </c>
       <c r="Q79" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="R79" s="7">
         <v>1</v>
@@ -28286,8 +28459,8 @@
       <c r="U79" t="s">
         <v>87</v>
       </c>
-      <c r="V79" t="s">
-        <v>105</v>
+      <c r="V79">
+        <v>6</v>
       </c>
       <c r="W79" t="s">
         <v>88</v>
@@ -28451,7 +28624,7 @@
         <v>46077.427199074067</v>
       </c>
       <c r="B80" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C80" s="7">
         <v>3</v>
@@ -28496,7 +28669,7 @@
         <v>83</v>
       </c>
       <c r="Q80" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="R80" s="7">
         <v>1</v>
@@ -28505,13 +28678,13 @@
         <v>85</v>
       </c>
       <c r="T80" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="U80" t="s">
-        <v>122</v>
-      </c>
-      <c r="V80" t="s">
-        <v>105</v>
+        <v>120</v>
+      </c>
+      <c r="V80">
+        <v>6</v>
       </c>
       <c r="W80" t="s">
         <v>88</v>
@@ -28675,7 +28848,7 @@
         <v>46073.355173611111</v>
       </c>
       <c r="B81" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C81" s="7">
         <v>3</v>
@@ -28720,7 +28893,7 @@
         <v>83</v>
       </c>
       <c r="Q81" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="R81" s="7">
         <v>1</v>
@@ -28732,10 +28905,10 @@
         <v>86</v>
       </c>
       <c r="U81" t="s">
-        <v>110</v>
-      </c>
-      <c r="V81" t="s">
-        <v>105</v>
+        <v>108</v>
+      </c>
+      <c r="V81">
+        <v>6</v>
       </c>
       <c r="W81" t="s">
         <v>88</v>
@@ -28899,13 +29072,13 @@
         <v>46072.475162037037</v>
       </c>
       <c r="B82" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C82" s="7">
         <v>2</v>
       </c>
       <c r="D82" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E82" t="s">
         <v>77</v>
@@ -28944,7 +29117,7 @@
         <v>83</v>
       </c>
       <c r="Q82" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="R82" s="7">
         <v>1</v>
@@ -28956,10 +29129,10 @@
         <v>86</v>
       </c>
       <c r="U82" t="s">
-        <v>110</v>
-      </c>
-      <c r="V82" t="s">
-        <v>100</v>
+        <v>108</v>
+      </c>
+      <c r="V82">
+        <v>3</v>
       </c>
       <c r="W82" t="s">
         <v>88</v>
@@ -29123,13 +29296,13 @@
         <v>46076.791238425933</v>
       </c>
       <c r="B83" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C83" s="7">
         <v>1</v>
       </c>
       <c r="D83" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E83" t="s">
         <v>77</v>
@@ -29168,7 +29341,7 @@
         <v>83</v>
       </c>
       <c r="Q83" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="R83" s="7">
         <v>1</v>
@@ -29177,13 +29350,13 @@
         <v>85</v>
       </c>
       <c r="T83" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="U83" t="s">
-        <v>122</v>
-      </c>
-      <c r="V83" t="s">
-        <v>100</v>
+        <v>120</v>
+      </c>
+      <c r="V83">
+        <v>3</v>
       </c>
       <c r="W83" t="s">
         <v>88</v>
@@ -29347,13 +29520,13 @@
         <v>46076.38616898148</v>
       </c>
       <c r="B84" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C84" s="7">
         <v>2</v>
       </c>
       <c r="D84" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E84" t="s">
         <v>77</v>
@@ -29392,7 +29565,7 @@
         <v>83</v>
       </c>
       <c r="Q84" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="R84" s="7">
         <v>1</v>
@@ -29401,13 +29574,13 @@
         <v>85</v>
       </c>
       <c r="T84" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="U84" t="s">
-        <v>110</v>
-      </c>
-      <c r="V84" t="s">
-        <v>105</v>
+        <v>108</v>
+      </c>
+      <c r="V84">
+        <v>6</v>
       </c>
       <c r="W84" t="s">
         <v>88</v>
@@ -29630,8 +29803,8 @@
       <c r="U85" t="s">
         <v>87</v>
       </c>
-      <c r="V85" t="s">
-        <v>100</v>
+      <c r="V85">
+        <v>3</v>
       </c>
       <c r="W85" t="s">
         <v>88</v>
@@ -29795,7 +29968,7 @@
         <v>46076.889351851853</v>
       </c>
       <c r="B86" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C86" s="7">
         <v>2</v>
@@ -29840,7 +30013,7 @@
         <v>83</v>
       </c>
       <c r="Q86" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="R86" s="7">
         <v>1</v>
@@ -29849,13 +30022,13 @@
         <v>85</v>
       </c>
       <c r="T86" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="U86" t="s">
-        <v>122</v>
-      </c>
-      <c r="V86" t="s">
-        <v>100</v>
+        <v>120</v>
+      </c>
+      <c r="V86">
+        <v>3</v>
       </c>
       <c r="W86" t="s">
         <v>88</v>
@@ -30019,7 +30192,7 @@
         <v>46080.367060185177</v>
       </c>
       <c r="B87" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="C87">
         <v>1</v>
@@ -30064,7 +30237,7 @@
         <v>83</v>
       </c>
       <c r="Q87" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="R87">
         <v>1</v>
@@ -30073,13 +30246,13 @@
         <v>85</v>
       </c>
       <c r="T87" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="U87" t="s">
-        <v>122</v>
-      </c>
-      <c r="V87" t="s">
-        <v>105</v>
+        <v>120</v>
+      </c>
+      <c r="V87">
+        <v>6</v>
       </c>
       <c r="W87" t="s">
         <v>88</v>
@@ -30243,7 +30416,7 @@
         <v>46074.70517361111</v>
       </c>
       <c r="B88" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C88" s="7">
         <v>3</v>
@@ -30288,7 +30461,7 @@
         <v>83</v>
       </c>
       <c r="Q88" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="R88" s="7">
         <v>1</v>
@@ -30300,10 +30473,10 @@
         <v>86</v>
       </c>
       <c r="U88" t="s">
-        <v>122</v>
-      </c>
-      <c r="V88" t="s">
-        <v>105</v>
+        <v>120</v>
+      </c>
+      <c r="V88">
+        <v>6</v>
       </c>
       <c r="W88" t="s">
         <v>88</v>
@@ -30467,7 +30640,7 @@
         <v>46073.068287037036</v>
       </c>
       <c r="B89" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C89" s="7">
         <v>2</v>
@@ -30512,7 +30685,7 @@
         <v>83</v>
       </c>
       <c r="Q89" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="R89" s="7">
         <v>1</v>
@@ -30524,10 +30697,10 @@
         <v>86</v>
       </c>
       <c r="U89" t="s">
-        <v>110</v>
-      </c>
-      <c r="V89" t="s">
-        <v>105</v>
+        <v>108</v>
+      </c>
+      <c r="V89">
+        <v>6</v>
       </c>
       <c r="W89" t="s">
         <v>88</v>
@@ -30691,7 +30864,7 @@
         <v>46075.184444444443</v>
       </c>
       <c r="B90" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C90" s="7">
         <v>3</v>
@@ -30736,7 +30909,7 @@
         <v>83</v>
       </c>
       <c r="Q90" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="R90" s="7">
         <v>1</v>
@@ -30745,13 +30918,13 @@
         <v>85</v>
       </c>
       <c r="T90" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="U90" t="s">
         <v>87</v>
       </c>
-      <c r="V90" t="s">
-        <v>100</v>
+      <c r="V90">
+        <v>3</v>
       </c>
       <c r="W90" t="s">
         <v>88</v>
@@ -30915,7 +31088,7 @@
         <v>46075.700752314813</v>
       </c>
       <c r="B91" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C91" s="7">
         <v>3</v>
@@ -30960,7 +31133,7 @@
         <v>83</v>
       </c>
       <c r="Q91" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="R91" s="7">
         <v>1</v>
@@ -30969,13 +31142,13 @@
         <v>85</v>
       </c>
       <c r="T91" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="U91" t="s">
         <v>87</v>
       </c>
-      <c r="V91" t="s">
-        <v>105</v>
+      <c r="V91">
+        <v>6</v>
       </c>
       <c r="W91" t="s">
         <v>88</v>
@@ -31139,13 +31312,13 @@
         <v>46073.949895833342</v>
       </c>
       <c r="B92" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C92" s="7">
         <v>3</v>
       </c>
       <c r="D92" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E92" t="s">
         <v>77</v>
@@ -31184,7 +31357,7 @@
         <v>83</v>
       </c>
       <c r="Q92" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="R92" s="7">
         <v>1</v>
@@ -31196,10 +31369,10 @@
         <v>86</v>
       </c>
       <c r="U92" t="s">
-        <v>122</v>
-      </c>
-      <c r="V92" t="s">
-        <v>100</v>
+        <v>120</v>
+      </c>
+      <c r="V92">
+        <v>3</v>
       </c>
       <c r="W92" t="s">
         <v>88</v>
@@ -31363,13 +31536,13 @@
         <v>46075.498645833337</v>
       </c>
       <c r="B93" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C93" s="7">
         <v>2</v>
       </c>
       <c r="D93" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E93" t="s">
         <v>77</v>
@@ -31408,7 +31581,7 @@
         <v>83</v>
       </c>
       <c r="Q93" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="R93" s="7">
         <v>1</v>
@@ -31417,13 +31590,13 @@
         <v>85</v>
       </c>
       <c r="T93" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="U93" t="s">
         <v>87</v>
       </c>
-      <c r="V93" t="s">
-        <v>105</v>
+      <c r="V93">
+        <v>6</v>
       </c>
       <c r="W93" t="s">
         <v>88</v>
@@ -31587,7 +31760,7 @@
         <v>46075.900717592587</v>
       </c>
       <c r="B94" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C94" s="7">
         <v>1</v>
@@ -31632,7 +31805,7 @@
         <v>83</v>
       </c>
       <c r="Q94" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="R94" s="7">
         <v>1</v>
@@ -31641,13 +31814,13 @@
         <v>85</v>
       </c>
       <c r="T94" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="U94" t="s">
-        <v>110</v>
-      </c>
-      <c r="V94" t="s">
-        <v>100</v>
+        <v>108</v>
+      </c>
+      <c r="V94">
+        <v>3</v>
       </c>
       <c r="W94" t="s">
         <v>88</v>
@@ -31811,13 +31984,13 @@
         <v>46074.957662037043</v>
       </c>
       <c r="B95" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C95" s="7">
         <v>1</v>
       </c>
       <c r="D95" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E95" t="s">
         <v>77</v>
@@ -31856,7 +32029,7 @@
         <v>83</v>
       </c>
       <c r="Q95" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="R95" s="7">
         <v>1</v>
@@ -31865,13 +32038,13 @@
         <v>85</v>
       </c>
       <c r="T95" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="U95" t="s">
         <v>87</v>
       </c>
-      <c r="V95" t="s">
-        <v>100</v>
+      <c r="V95">
+        <v>3</v>
       </c>
       <c r="W95" t="s">
         <v>88</v>
@@ -32035,7 +32208,7 @@
         <v>46076.102581018517</v>
       </c>
       <c r="B96" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C96" s="7">
         <v>3</v>
@@ -32080,7 +32253,7 @@
         <v>83</v>
       </c>
       <c r="Q96" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="R96" s="7">
         <v>1</v>
@@ -32089,13 +32262,13 @@
         <v>85</v>
       </c>
       <c r="T96" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="U96" t="s">
-        <v>110</v>
-      </c>
-      <c r="V96" t="s">
-        <v>100</v>
+        <v>108</v>
+      </c>
+      <c r="V96">
+        <v>3</v>
       </c>
       <c r="W96" t="s">
         <v>88</v>
@@ -32259,13 +32432,13 @@
         <v>46076.001608796287</v>
       </c>
       <c r="B97" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C97" s="7">
         <v>2</v>
       </c>
       <c r="D97" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E97" t="s">
         <v>77</v>
@@ -32304,7 +32477,7 @@
         <v>83</v>
       </c>
       <c r="Q97" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="R97" s="7">
         <v>1</v>
@@ -32313,13 +32486,13 @@
         <v>85</v>
       </c>
       <c r="T97" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="U97" t="s">
-        <v>110</v>
-      </c>
-      <c r="V97" t="s">
-        <v>100</v>
+        <v>108</v>
+      </c>
+      <c r="V97">
+        <v>3</v>
       </c>
       <c r="W97" t="s">
         <v>88</v>
@@ -32483,13 +32656,13 @@
         <v>46075.295891203707</v>
       </c>
       <c r="B98" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C98" s="7">
         <v>1</v>
       </c>
       <c r="D98" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E98" t="s">
         <v>77</v>
@@ -32528,7 +32701,7 @@
         <v>83</v>
       </c>
       <c r="Q98" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="R98" s="7">
         <v>1</v>
@@ -32537,13 +32710,13 @@
         <v>85</v>
       </c>
       <c r="T98" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="U98" t="s">
         <v>87</v>
       </c>
-      <c r="V98" t="s">
-        <v>105</v>
+      <c r="V98">
+        <v>6</v>
       </c>
       <c r="W98" t="s">
         <v>88</v>
@@ -32707,7 +32880,7 @@
         <v>46076.553194444437</v>
       </c>
       <c r="B99" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C99" s="7">
         <v>3</v>
@@ -32752,7 +32925,7 @@
         <v>83</v>
       </c>
       <c r="Q99" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="R99" s="7">
         <v>1</v>
@@ -32761,10 +32934,10 @@
         <v>85</v>
       </c>
       <c r="T99" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="U99" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V99">
         <v>6</v>
@@ -32931,13 +33104,13 @@
         <v>46071.36959490741</v>
       </c>
       <c r="B100" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C100" s="7">
         <v>2</v>
       </c>
       <c r="D100" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E100" t="s">
         <v>77</v>
@@ -32976,7 +33149,7 @@
         <v>83</v>
       </c>
       <c r="Q100" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="R100" s="7">
         <v>1</v>
@@ -32990,8 +33163,8 @@
       <c r="U100" t="s">
         <v>87</v>
       </c>
-      <c r="V100" t="s">
-        <v>105</v>
+      <c r="V100">
+        <v>6</v>
       </c>
       <c r="W100" t="s">
         <v>88</v>
@@ -33155,7 +33328,7 @@
         <v>46082.423425925917</v>
       </c>
       <c r="B101" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="C101">
         <v>3</v>
@@ -33200,7 +33373,7 @@
         <v>83</v>
       </c>
       <c r="Q101" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="R101">
         <v>3</v>
@@ -33212,7 +33385,7 @@
         <v>86</v>
       </c>
       <c r="U101" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V101" t="s">
         <v>97</v>
@@ -33379,13 +33552,13 @@
         <v>46082.752824074072</v>
       </c>
       <c r="B102" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="C102">
         <v>1</v>
       </c>
       <c r="D102" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E102" t="s">
         <v>77</v>
@@ -33421,7 +33594,7 @@
         <v>83</v>
       </c>
       <c r="Q102" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="R102">
         <v>3</v>
@@ -33433,7 +33606,7 @@
         <v>86</v>
       </c>
       <c r="U102" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V102" t="s">
         <v>97</v>
@@ -33600,13 +33773,13 @@
         <v>46082.752893518518</v>
       </c>
       <c r="B103" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="C103">
         <v>2</v>
       </c>
       <c r="D103" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E103" t="s">
         <v>77</v>
@@ -33642,7 +33815,7 @@
         <v>83</v>
       </c>
       <c r="Q103" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="R103">
         <v>3</v>
@@ -33654,7 +33827,7 @@
         <v>86</v>
       </c>
       <c r="U103" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V103" t="s">
         <v>97</v>
@@ -33821,7 +33994,7 @@
         <v>46082.752939814818</v>
       </c>
       <c r="B104" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="C104">
         <v>3</v>
@@ -33863,7 +34036,7 @@
         <v>83</v>
       </c>
       <c r="Q104" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="R104">
         <v>3</v>
@@ -33875,7 +34048,7 @@
         <v>86</v>
       </c>
       <c r="U104" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V104" t="s">
         <v>97</v>
@@ -34042,13 +34215,13 @@
         <v>46082.752997685187</v>
       </c>
       <c r="B105" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="C105">
         <v>1</v>
       </c>
       <c r="D105" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E105" t="s">
         <v>77</v>
@@ -34084,7 +34257,7 @@
         <v>83</v>
       </c>
       <c r="Q105" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="R105">
         <v>3</v>
@@ -34096,7 +34269,7 @@
         <v>86</v>
       </c>
       <c r="U105" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V105" t="s">
         <v>97</v>
@@ -34263,13 +34436,13 @@
         <v>46082.75304398148</v>
       </c>
       <c r="B106" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="C106">
         <v>2</v>
       </c>
       <c r="D106" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E106" t="s">
         <v>77</v>
@@ -34305,7 +34478,7 @@
         <v>83</v>
       </c>
       <c r="Q106" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="R106">
         <v>3</v>
@@ -34317,7 +34490,7 @@
         <v>86</v>
       </c>
       <c r="U106" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V106" t="s">
         <v>97</v>
@@ -34484,7 +34657,7 @@
         <v>46082.753101851849</v>
       </c>
       <c r="B107" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="C107">
         <v>3</v>
@@ -34526,7 +34699,7 @@
         <v>83</v>
       </c>
       <c r="Q107" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="R107">
         <v>3</v>
@@ -34538,7 +34711,7 @@
         <v>86</v>
       </c>
       <c r="U107" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V107" t="s">
         <v>97</v>
@@ -34705,13 +34878,13 @@
         <v>46082.753148148149</v>
       </c>
       <c r="B108" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="C108">
         <v>1</v>
       </c>
       <c r="D108" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E108" t="s">
         <v>77</v>
@@ -34747,7 +34920,7 @@
         <v>83</v>
       </c>
       <c r="Q108" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="R108">
         <v>3</v>
@@ -34759,7 +34932,7 @@
         <v>86</v>
       </c>
       <c r="U108" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V108" t="s">
         <v>97</v>
@@ -34926,13 +35099,13 @@
         <v>46082.753206018519</v>
       </c>
       <c r="B109" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="C109">
         <v>2</v>
       </c>
       <c r="D109" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E109" t="s">
         <v>77</v>
@@ -34968,7 +35141,7 @@
         <v>83</v>
       </c>
       <c r="Q109" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="R109">
         <v>3</v>
@@ -34980,7 +35153,7 @@
         <v>86</v>
       </c>
       <c r="U109" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V109" t="s">
         <v>97</v>
@@ -35147,7 +35320,7 @@
         <v>46082.753252314818</v>
       </c>
       <c r="B110" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="C110">
         <v>3</v>
@@ -35189,7 +35362,7 @@
         <v>83</v>
       </c>
       <c r="Q110" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="R110">
         <v>3</v>
@@ -35201,7 +35374,7 @@
         <v>86</v>
       </c>
       <c r="U110" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V110" t="s">
         <v>97</v>
@@ -35368,13 +35541,13 @@
         <v>46082.753310185188</v>
       </c>
       <c r="B111" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="C111">
         <v>1</v>
       </c>
       <c r="D111" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E111" t="s">
         <v>77</v>
@@ -35410,7 +35583,7 @@
         <v>83</v>
       </c>
       <c r="Q111" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="R111">
         <v>3</v>
@@ -35422,7 +35595,7 @@
         <v>86</v>
       </c>
       <c r="U111" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V111" t="s">
         <v>97</v>
@@ -35589,13 +35762,13 @@
         <v>46082.753368055557</v>
       </c>
       <c r="B112" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="C112">
         <v>2</v>
       </c>
       <c r="D112" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E112" t="s">
         <v>77</v>
@@ -35631,7 +35804,7 @@
         <v>83</v>
       </c>
       <c r="Q112" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="R112">
         <v>3</v>
@@ -35643,7 +35816,7 @@
         <v>86</v>
       </c>
       <c r="U112" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V112" t="s">
         <v>97</v>
@@ -35810,7 +35983,7 @@
         <v>46082.75341435185</v>
       </c>
       <c r="B113" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="C113">
         <v>3</v>
@@ -35852,7 +36025,7 @@
         <v>83</v>
       </c>
       <c r="Q113" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="R113">
         <v>3</v>
@@ -35864,7 +36037,7 @@
         <v>86</v>
       </c>
       <c r="U113" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V113" t="s">
         <v>97</v>
@@ -36031,7 +36204,7 @@
         <v>46082.1721412037</v>
       </c>
       <c r="B114" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="C114">
         <v>2</v>
@@ -36049,7 +36222,7 @@
         <v>4.5</v>
       </c>
       <c r="H114" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="I114" t="s">
         <v>79</v>
@@ -36076,7 +36249,7 @@
         <v>83</v>
       </c>
       <c r="Q114" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="R114">
         <v>4</v>
@@ -36090,11 +36263,11 @@
       <c r="U114" t="s">
         <v>87</v>
       </c>
-      <c r="V114" t="s">
-        <v>250</v>
+      <c r="V114">
+        <v>8</v>
       </c>
       <c r="W114" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="X114" t="s">
         <v>82</v>
@@ -36255,7 +36428,7 @@
         <v>46083.112546296303</v>
       </c>
       <c r="B115" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="C115">
         <v>3</v>
@@ -36273,7 +36446,7 @@
         <v>4.5</v>
       </c>
       <c r="H115" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="I115" t="s">
         <v>79</v>
@@ -36300,7 +36473,7 @@
         <v>83</v>
       </c>
       <c r="Q115" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="R115">
         <v>4</v>
@@ -36314,11 +36487,11 @@
       <c r="U115" t="s">
         <v>87</v>
       </c>
-      <c r="V115" t="s">
-        <v>250</v>
+      <c r="V115">
+        <v>8</v>
       </c>
       <c r="W115" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="X115" t="s">
         <v>82</v>
@@ -36479,7 +36652,7 @@
         <v>46084.055162037039</v>
       </c>
       <c r="B116" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="C116">
         <v>1</v>
@@ -36497,7 +36670,7 @@
         <v>4.5</v>
       </c>
       <c r="H116" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="I116" t="s">
         <v>79</v>
@@ -36524,7 +36697,7 @@
         <v>83</v>
       </c>
       <c r="Q116" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="R116">
         <v>4</v>
@@ -36536,13 +36709,13 @@
         <v>86</v>
       </c>
       <c r="U116" t="s">
-        <v>110</v>
-      </c>
-      <c r="V116" t="s">
-        <v>176</v>
+        <v>108</v>
+      </c>
+      <c r="V116">
+        <v>2</v>
       </c>
       <c r="W116" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="X116" t="s">
         <v>82</v>
@@ -36696,6 +36869,230 @@
       </c>
       <c r="BW116">
         <v>-1.5992405054674721</v>
+      </c>
+    </row>
+    <row r="117" spans="1:75" x14ac:dyDescent="0.3">
+      <c r="A117" s="2">
+        <v>46084.304236111107</v>
+      </c>
+      <c r="B117" t="s">
+        <v>266</v>
+      </c>
+      <c r="C117">
+        <v>2</v>
+      </c>
+      <c r="D117" t="s">
+        <v>101</v>
+      </c>
+      <c r="E117" t="s">
+        <v>77</v>
+      </c>
+      <c r="F117">
+        <v>16590</v>
+      </c>
+      <c r="G117">
+        <v>4.5</v>
+      </c>
+      <c r="H117" t="s">
+        <v>171</v>
+      </c>
+      <c r="I117" t="s">
+        <v>79</v>
+      </c>
+      <c r="J117">
+        <v>5</v>
+      </c>
+      <c r="K117">
+        <v>5</v>
+      </c>
+      <c r="L117" t="s">
+        <v>80</v>
+      </c>
+      <c r="M117" t="s">
+        <v>81</v>
+      </c>
+      <c r="N117" t="s">
+        <v>82</v>
+      </c>
+      <c r="O117" t="s">
+        <v>82</v>
+      </c>
+      <c r="P117" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q117" t="s">
+        <v>265</v>
+      </c>
+      <c r="R117">
+        <v>4</v>
+      </c>
+      <c r="S117" t="s">
+        <v>85</v>
+      </c>
+      <c r="T117" t="s">
+        <v>86</v>
+      </c>
+      <c r="U117" t="s">
+        <v>108</v>
+      </c>
+      <c r="V117">
+        <v>2</v>
+      </c>
+      <c r="W117" t="s">
+        <v>173</v>
+      </c>
+      <c r="X117" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y117" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z117">
+        <v>4000</v>
+      </c>
+      <c r="AA117">
+        <v>4000</v>
+      </c>
+      <c r="AC117">
+        <v>512</v>
+      </c>
+      <c r="AD117" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE117">
+        <v>0.1</v>
+      </c>
+      <c r="AF117">
+        <v>200</v>
+      </c>
+      <c r="AG117">
+        <v>80</v>
+      </c>
+      <c r="AH117">
+        <v>120</v>
+      </c>
+      <c r="AI117">
+        <v>7.1990638112177832E-2</v>
+      </c>
+      <c r="AJ117">
+        <v>16.583762115825699</v>
+      </c>
+      <c r="AK117">
+        <v>0.80999601350231554</v>
+      </c>
+      <c r="AL117">
+        <v>0.29228831132759953</v>
+      </c>
+      <c r="AM117">
+        <v>17.715144406576162</v>
+      </c>
+      <c r="AN117">
+        <v>0.8042748584903836</v>
+      </c>
+      <c r="AO117">
+        <v>17.715144406576162</v>
+      </c>
+      <c r="AP117">
+        <v>17.715144406576162</v>
+      </c>
+      <c r="AQ117">
+        <v>0.8042748584903836</v>
+      </c>
+      <c r="AR117">
+        <v>87.719550229630585</v>
+      </c>
+      <c r="AS117">
+        <v>0.23691904110060119</v>
+      </c>
+      <c r="AT117">
+        <v>0.8</v>
+      </c>
+      <c r="AU117" t="s">
+        <v>91</v>
+      </c>
+      <c r="AV117">
+        <v>2.0018159176767719E-2</v>
+      </c>
+      <c r="AW117">
+        <v>0.85464228172688905</v>
+      </c>
+      <c r="AX117">
+        <v>2.0018159176767719E-2</v>
+      </c>
+      <c r="AY117">
+        <v>2.0018159176767719E-2</v>
+      </c>
+      <c r="AZ117">
+        <v>0.85464228172688905</v>
+      </c>
+      <c r="BA117">
+        <v>6.2099186902190011E-2</v>
+      </c>
+      <c r="BB117">
+        <v>0.54907961141633299</v>
+      </c>
+      <c r="BC117">
+        <v>5.5449924405327859E-2</v>
+      </c>
+      <c r="BD117">
+        <v>0.80787785504189369</v>
+      </c>
+      <c r="BE117">
+        <v>5.5449924405327859E-2</v>
+      </c>
+      <c r="BF117">
+        <v>5.5449924405327859E-2</v>
+      </c>
+      <c r="BG117">
+        <v>0.80787785504189369</v>
+      </c>
+      <c r="BH117">
+        <v>0.26617355534639658</v>
+      </c>
+      <c r="BI117">
+        <v>7.776548060791566E-2</v>
+      </c>
+      <c r="BJ117">
+        <v>6.0808495296395107E-2</v>
+      </c>
+      <c r="BK117">
+        <v>0.75587312522786643</v>
+      </c>
+      <c r="BL117">
+        <v>6.0808495296395107E-2</v>
+      </c>
+      <c r="BM117">
+        <v>6.0808495296395107E-2</v>
+      </c>
+      <c r="BN117">
+        <v>0.75587312522786643</v>
+      </c>
+      <c r="BO117">
+        <v>0.1698578353466268</v>
+      </c>
+      <c r="BP117">
+        <v>0.3180745174401659</v>
+      </c>
+      <c r="BQ117">
+        <v>70.724301047426437</v>
+      </c>
+      <c r="BR117">
+        <v>0.79870617196488358</v>
+      </c>
+      <c r="BS117">
+        <v>70.724301047426437</v>
+      </c>
+      <c r="BT117">
+        <v>70.724301047426437</v>
+      </c>
+      <c r="BU117">
+        <v>0.79870617196488358</v>
+      </c>
+      <c r="BV117">
+        <v>350.38007034092919</v>
+      </c>
+      <c r="BW117">
+        <v>2.75655493797955E-3</v>
       </c>
     </row>
   </sheetData>
@@ -36708,96 +37105,96 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC2417C5-69B1-40A5-8AFE-A835A2C478FA}">
-  <dimension ref="A2:L32"/>
+  <dimension ref="A2:L67"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="41.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="42.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="45.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="56.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="55.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="50.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="51.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="59" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="58" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="52.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="53.77734375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="26.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="41.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="41.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="54.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="53.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="47.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="49.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="56.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="55.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="49.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="51.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="25.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B2" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C2" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D2" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="E2" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="F2" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="G2" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="H2" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="I2" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="J2" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="K2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="L2" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>1</v>
       </c>
-      <c r="B3" s="8">
-        <v>0.41636891498814882</v>
-      </c>
-      <c r="C3" s="8">
-        <v>-5.272653234920454E-2</v>
-      </c>
-      <c r="D3" s="8">
+      <c r="B3" s="9">
+        <v>0.41636891498814876</v>
+      </c>
+      <c r="C3" s="9">
+        <v>-5.2726532349204547E-2</v>
+      </c>
+      <c r="D3" s="9">
         <v>0.18015706416464142</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="9">
         <v>0.39770216490801458</v>
       </c>
-      <c r="F3" s="8">
+      <c r="F3" s="9">
         <v>0.27050245309932736</v>
       </c>
-      <c r="G3" s="8">
+      <c r="G3" s="9">
         <v>0.58589066284319624</v>
       </c>
-      <c r="H3" s="8">
-        <v>-5.9397282790308953E-2</v>
-      </c>
-      <c r="I3" s="8">
-        <v>-2.0128387168623769E-2</v>
-      </c>
-      <c r="J3" s="8">
+      <c r="H3" s="9">
+        <v>-5.9397282790308946E-2</v>
+      </c>
+      <c r="I3" s="9">
+        <v>-2.0128387168623776E-2</v>
+      </c>
+      <c r="J3" s="9">
         <v>6.0134525364982656E-2</v>
       </c>
-      <c r="K3" s="8">
+      <c r="K3" s="9">
         <v>-0.15529802652982733</v>
       </c>
-      <c r="L3" s="8">
+      <c r="L3" s="9">
         <v>54</v>
       </c>
     </row>
@@ -36805,37 +37202,37 @@
       <c r="A4" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="9">
         <v>0.41481218833745293</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="9">
         <v>2.7485134246625505E-3</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="9">
         <v>0.12836449764766242</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="9">
         <v>0.44885661891141937</v>
       </c>
-      <c r="F4" s="8">
+      <c r="F4" s="9">
         <v>0.34588739321598294</v>
       </c>
-      <c r="G4" s="8">
-        <v>0.59600951150530657</v>
-      </c>
-      <c r="H4" s="8">
+      <c r="G4" s="9">
+        <v>0.59600951150530634</v>
+      </c>
+      <c r="H4" s="9">
         <v>-1.0467147533235115E-2</v>
       </c>
-      <c r="I4" s="8">
+      <c r="I4" s="9">
         <v>5.6986366157070471E-2</v>
       </c>
-      <c r="J4" s="8">
+      <c r="J4" s="9">
         <v>0.12384536268397991</v>
       </c>
-      <c r="K4" s="8">
+      <c r="K4" s="9">
         <v>-9.9265108601490723E-2</v>
       </c>
-      <c r="L4" s="8">
+      <c r="L4" s="9">
         <v>18</v>
       </c>
     </row>
@@ -36843,1064 +37240,2394 @@
       <c r="A5" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="9">
         <v>0.41649572933414869</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="9">
         <v>1.2066273030157596E-2</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="9">
         <v>0.16610034031306109</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="9">
         <v>0.44178139565759728</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="9">
         <v>0.33979311200200152</v>
       </c>
-      <c r="G5" s="8">
-        <v>0.58010958014022573</v>
-      </c>
-      <c r="H5" s="8">
+      <c r="G5" s="9">
+        <v>0.58010958014022562</v>
+      </c>
+      <c r="H5" s="9">
         <v>-7.6266129743784661E-2</v>
       </c>
-      <c r="I5" s="8">
-        <v>6.1254219017362103E-2</v>
-      </c>
-      <c r="J5" s="8">
-        <v>0.13613175724654591</v>
-      </c>
-      <c r="K5" s="8">
+      <c r="I5" s="9">
+        <v>6.125421901736209E-2</v>
+      </c>
+      <c r="J5" s="9">
+        <v>0.13613175724654594</v>
+      </c>
+      <c r="K5" s="9">
         <v>-8.9593429933529659E-2</v>
       </c>
-      <c r="L5" s="8">
+      <c r="L5" s="9">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="B6" s="8">
-        <v>0.38672315257077411</v>
-      </c>
-      <c r="C6" s="8">
-        <v>-3.2556582344845229E-2</v>
-      </c>
-      <c r="D6" s="8">
-        <v>0.10541859566651481</v>
-      </c>
-      <c r="E6" s="8">
-        <v>0.40550074549709153</v>
-      </c>
-      <c r="F6" s="8">
-        <v>0.29002648090086042</v>
-      </c>
-      <c r="G6" s="8">
-        <v>0.5926496797445735</v>
-      </c>
-      <c r="H6" s="8">
-        <v>1.6988611410332349E-2</v>
-      </c>
-      <c r="I6" s="8">
-        <v>8.3177979665681554E-3</v>
-      </c>
-      <c r="J6" s="8">
-        <v>4.0232345970101079E-2</v>
-      </c>
-      <c r="K6" s="8">
-        <v>-0.11841892781575065</v>
-      </c>
-      <c r="L6" s="8">
-        <v>6</v>
+      <c r="A6" s="8">
+        <v>3</v>
+      </c>
+      <c r="B6" s="9">
+        <v>0.44471745554034259</v>
+      </c>
+      <c r="C6" s="9">
+        <v>5.6970709093450977E-2</v>
+      </c>
+      <c r="D6" s="9">
+        <v>0.13312429268193385</v>
+      </c>
+      <c r="E6" s="9">
+        <v>0.46640719326425262</v>
+      </c>
+      <c r="F6" s="9">
+        <v>0.38433266882967815</v>
+      </c>
+      <c r="G6" s="9">
+        <v>0.65988533124996929</v>
+      </c>
+      <c r="H6" s="9">
+        <v>-0.10537701187015165</v>
+      </c>
+      <c r="I6" s="9">
+        <v>0.10211798323509062</v>
+      </c>
+      <c r="J6" s="9">
+        <v>0.18845533162461856</v>
+      </c>
+      <c r="K6" s="9">
+        <v>-2.6136766765647652E-2</v>
+      </c>
+      <c r="L6" s="9">
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="B7" s="8">
-        <v>0.44121768310743587</v>
-      </c>
-      <c r="C7" s="8">
-        <v>2.8735849588675286E-2</v>
-      </c>
-      <c r="D7" s="8">
-        <v>0.11357455696341133</v>
-      </c>
-      <c r="E7" s="8">
-        <v>0.49928771557956936</v>
-      </c>
-      <c r="F7" s="8">
-        <v>0.40784258674508694</v>
-      </c>
-      <c r="G7" s="8">
-        <v>0.6152692746311198</v>
-      </c>
-      <c r="H7" s="8">
-        <v>2.7876075733746966E-2</v>
-      </c>
-      <c r="I7" s="8">
-        <v>0.10138708148728116</v>
-      </c>
-      <c r="J7" s="8">
-        <v>0.19517198483529286</v>
-      </c>
-      <c r="K7" s="8">
-        <v>-8.978296805519187E-2</v>
-      </c>
-      <c r="L7" s="8">
+      <c r="A7" s="8">
         <v>6</v>
+      </c>
+      <c r="B7" s="9">
+        <v>0.38827400312795485</v>
+      </c>
+      <c r="C7" s="9">
+        <v>-3.2838163033135782E-2</v>
+      </c>
+      <c r="D7" s="9">
+        <v>0.19907638794418836</v>
+      </c>
+      <c r="E7" s="9">
+        <v>0.41715559805094199</v>
+      </c>
+      <c r="F7" s="9">
+        <v>0.29525355517432489</v>
+      </c>
+      <c r="G7" s="9">
+        <v>0.50033382903048207</v>
+      </c>
+      <c r="H7" s="9">
+        <v>-4.7155247617417663E-2</v>
+      </c>
+      <c r="I7" s="9">
+        <v>2.0390454799633563E-2</v>
+      </c>
+      <c r="J7" s="9">
+        <v>8.3808182868473316E-2</v>
+      </c>
+      <c r="K7" s="9">
+        <v>-0.15305009310141168</v>
+      </c>
+      <c r="L7" s="9">
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B8" s="8">
-        <v>0.41514304183391088</v>
-      </c>
-      <c r="C8" s="8">
-        <v>-1.3309368869829273E-2</v>
-      </c>
-      <c r="D8" s="8">
-        <v>0.18087050506977617</v>
-      </c>
-      <c r="E8" s="8">
-        <v>0.34319191631776508</v>
-      </c>
-      <c r="F8" s="8">
-        <v>0.25505830774410582</v>
-      </c>
-      <c r="G8" s="8">
-        <v>0.61359345475197558</v>
-      </c>
-      <c r="H8" s="8">
-        <v>-7.0487854964432009E-2</v>
-      </c>
-      <c r="I8" s="8">
-        <v>5.1538494592396976E-2</v>
-      </c>
-      <c r="J8" s="8">
-        <v>0.11345906601594417</v>
-      </c>
-      <c r="K8" s="8">
-        <v>-0.14237180323666387</v>
-      </c>
-      <c r="L8" s="8">
-        <v>18</v>
+      <c r="A8" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="B8" s="9">
+        <v>0.38672315257077411</v>
+      </c>
+      <c r="C8" s="9">
+        <v>-3.2556582344845229E-2</v>
+      </c>
+      <c r="D8" s="9">
+        <v>0.10541859566651481</v>
+      </c>
+      <c r="E8" s="9">
+        <v>0.40550074549709153</v>
+      </c>
+      <c r="F8" s="9">
+        <v>0.29002648090086042</v>
+      </c>
+      <c r="G8" s="9">
+        <v>0.59264967974457339</v>
+      </c>
+      <c r="H8" s="9">
+        <v>1.6988611410332349E-2</v>
+      </c>
+      <c r="I8" s="9">
+        <v>8.3177979665681554E-3</v>
+      </c>
+      <c r="J8" s="9">
+        <v>4.0232345970101079E-2</v>
+      </c>
+      <c r="K8" s="9">
+        <v>-0.11841892781575065</v>
+      </c>
+      <c r="L8" s="9">
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="B9" s="8">
-        <v>0.41182962081908397</v>
-      </c>
-      <c r="C9" s="8">
-        <v>2.8868953353709489E-3</v>
-      </c>
-      <c r="D9" s="8">
-        <v>0.18356206683142173</v>
-      </c>
-      <c r="E9" s="8">
-        <v>0.33108753411922043</v>
-      </c>
-      <c r="F9" s="8">
-        <v>0.23829953150931393</v>
-      </c>
-      <c r="G9" s="8">
-        <v>0.62683178238177029</v>
-      </c>
-      <c r="H9" s="8">
-        <v>-8.6399609628571516E-2</v>
-      </c>
-      <c r="I9" s="8">
-        <v>0.10692234480096187</v>
-      </c>
-      <c r="J9" s="8">
-        <v>0.1434344393334463</v>
-      </c>
-      <c r="K9" s="8">
-        <v>-0.11977287839214608</v>
-      </c>
-      <c r="L9" s="8">
-        <v>6</v>
+      <c r="A9" s="8">
+        <v>3</v>
+      </c>
+      <c r="B9" s="9">
+        <v>0.40047572939952353</v>
+      </c>
+      <c r="C9" s="9">
+        <v>-3.1238386257275458E-2</v>
+      </c>
+      <c r="D9" s="9">
+        <v>9.2706312374016497E-2</v>
+      </c>
+      <c r="E9" s="9">
+        <v>0.42170822636846755</v>
+      </c>
+      <c r="F9" s="9">
+        <v>0.3243314803467397</v>
+      </c>
+      <c r="G9" s="9">
+        <v>0.66934569217607365</v>
+      </c>
+      <c r="H9" s="9">
+        <v>3.6749231259990557E-2</v>
+      </c>
+      <c r="I9" s="9">
+        <v>5.8069671563123482E-3</v>
+      </c>
+      <c r="J9" s="9">
+        <v>2.3708990672343184E-2</v>
+      </c>
+      <c r="K9" s="9">
+        <v>-7.2782307123181303E-2</v>
+      </c>
+      <c r="L9" s="9">
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="B10" s="8">
-        <v>0.37666064411971895</v>
-      </c>
-      <c r="C10" s="8">
-        <v>-4.3011863077717129E-2</v>
-      </c>
-      <c r="D10" s="8">
-        <v>0.18414608943486688</v>
-      </c>
-      <c r="E10" s="8">
-        <v>0.26379717263170044</v>
-      </c>
-      <c r="F10" s="8">
-        <v>0.18152218228216588</v>
-      </c>
-      <c r="G10" s="8">
-        <v>0.61743888448858353</v>
-      </c>
-      <c r="H10" s="8">
-        <v>-3.0795728287285554E-2</v>
-      </c>
-      <c r="I10" s="8">
-        <v>-2.1532625919085464E-2</v>
-      </c>
-      <c r="J10" s="8">
-        <v>2.3922849331387181E-2</v>
-      </c>
-      <c r="K10" s="8">
-        <v>-0.12237274885407616</v>
-      </c>
-      <c r="L10" s="8">
+      <c r="A10" s="8">
         <v>6</v>
+      </c>
+      <c r="B10" s="9">
+        <v>0.37297057574202475</v>
+      </c>
+      <c r="C10" s="9">
+        <v>-3.3874778432415008E-2</v>
+      </c>
+      <c r="D10" s="9">
+        <v>0.1181308789590131</v>
+      </c>
+      <c r="E10" s="9">
+        <v>0.3892932646257154</v>
+      </c>
+      <c r="F10" s="9">
+        <v>0.25572148145498108</v>
+      </c>
+      <c r="G10" s="9">
+        <v>0.51595366731307324</v>
+      </c>
+      <c r="H10" s="9">
+        <v>-2.772008439325862E-3</v>
+      </c>
+      <c r="I10" s="9">
+        <v>1.0828628776823964E-2</v>
+      </c>
+      <c r="J10" s="9">
+        <v>5.675570126785897E-2</v>
+      </c>
+      <c r="K10" s="9">
+        <v>-0.16405554850832002</v>
+      </c>
+      <c r="L10" s="9">
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="B11" s="8">
-        <v>0.45693886056292982</v>
-      </c>
-      <c r="C11" s="8">
-        <v>1.968611328583674E-4</v>
-      </c>
-      <c r="D11" s="8">
-        <v>0.17490335894303996</v>
-      </c>
-      <c r="E11" s="8">
-        <v>0.43469104220237426</v>
-      </c>
-      <c r="F11" s="8">
-        <v>0.34535320944083764</v>
-      </c>
-      <c r="G11" s="8">
-        <v>0.5965096973855728</v>
-      </c>
-      <c r="H11" s="8">
-        <v>-9.426822697743896E-2</v>
-      </c>
-      <c r="I11" s="8">
-        <v>6.9225764895314512E-2</v>
-      </c>
-      <c r="J11" s="8">
-        <v>0.17301990938299905</v>
-      </c>
-      <c r="K11" s="8">
-        <v>-0.18496978246376938</v>
-      </c>
-      <c r="L11" s="8">
+        <v>188</v>
+      </c>
+      <c r="B11" s="9">
+        <v>0.44121768310743587</v>
+      </c>
+      <c r="C11" s="9">
+        <v>2.8735849588675286E-2</v>
+      </c>
+      <c r="D11" s="9">
+        <v>0.11357455696341133</v>
+      </c>
+      <c r="E11" s="9">
+        <v>0.49928771557956936</v>
+      </c>
+      <c r="F11" s="9">
+        <v>0.40784258674508694</v>
+      </c>
+      <c r="G11" s="9">
+        <v>0.6152692746311198</v>
+      </c>
+      <c r="H11" s="9">
+        <v>2.7876075733746966E-2</v>
+      </c>
+      <c r="I11" s="9">
+        <v>0.10138708148728116</v>
+      </c>
+      <c r="J11" s="9">
+        <v>0.19517198483529286</v>
+      </c>
+      <c r="K11" s="9">
+        <v>-8.978296805519187E-2</v>
+      </c>
+      <c r="L11" s="9">
         <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="B12" s="8">
-        <v>0.41915151479308266</v>
-      </c>
-      <c r="C12" s="8">
-        <v>-0.14761874160244692</v>
-      </c>
-      <c r="D12" s="8">
-        <v>0.23123618977648558</v>
-      </c>
-      <c r="E12" s="8">
-        <v>0.40105795949485912</v>
-      </c>
-      <c r="F12" s="8">
-        <v>0.2105616583378932</v>
-      </c>
-      <c r="G12" s="8">
-        <v>0.54806902227230669</v>
-      </c>
-      <c r="H12" s="8">
-        <v>-9.7236845873259703E-2</v>
-      </c>
-      <c r="I12" s="8">
-        <v>-0.1689100222553388</v>
-      </c>
-      <c r="J12" s="8">
-        <v>-5.6900852604976161E-2</v>
-      </c>
-      <c r="K12" s="8">
-        <v>-0.2242571677513274</v>
-      </c>
-      <c r="L12" s="8">
-        <v>18</v>
+      <c r="A12" s="8">
+        <v>3</v>
+      </c>
+      <c r="B12" s="9">
+        <v>0.46372286403370772</v>
+      </c>
+      <c r="C12" s="9">
+        <v>5.6919814061659718E-2</v>
+      </c>
+      <c r="D12" s="9">
+        <v>7.6065350276800489E-2</v>
+      </c>
+      <c r="E12" s="9">
+        <v>0.50276036398987001</v>
+      </c>
+      <c r="F12" s="9">
+        <v>0.42982665598362496</v>
+      </c>
+      <c r="G12" s="9">
+        <v>0.67863082049742129</v>
+      </c>
+      <c r="H12" s="9">
+        <v>4.275859424213861E-3</v>
+      </c>
+      <c r="I12" s="9">
+        <v>0.14888104537273122</v>
+      </c>
+      <c r="J12" s="9">
+        <v>0.26800522020676615</v>
+      </c>
+      <c r="K12" s="9">
+        <v>-5.888533259630719E-2</v>
+      </c>
+      <c r="L12" s="9">
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="B13" s="8">
-        <v>0.42548911236649428</v>
-      </c>
-      <c r="C13" s="8">
-        <v>-0.20632971320460988</v>
-      </c>
-      <c r="D13" s="8">
-        <v>0.25787034083173238</v>
-      </c>
-      <c r="E13" s="8">
-        <v>0.40720273127239709</v>
-      </c>
-      <c r="F13" s="8">
-        <v>0.20751021325172336</v>
-      </c>
-      <c r="G13" s="8">
-        <v>0.54728899238591511</v>
-      </c>
-      <c r="H13" s="8">
-        <v>-0.12632652051710611</v>
-      </c>
-      <c r="I13" s="8">
-        <v>-0.22420653742029029</v>
-      </c>
-      <c r="J13" s="8">
-        <v>-7.8063006656392944E-2</v>
-      </c>
-      <c r="K13" s="8">
-        <v>-0.26099065481730394</v>
-      </c>
-      <c r="L13" s="8">
+      <c r="A13" s="8">
         <v>6</v>
+      </c>
+      <c r="B13" s="9">
+        <v>0.41871250218116413</v>
+      </c>
+      <c r="C13" s="9">
+        <v>5.5188511569085469E-4</v>
+      </c>
+      <c r="D13" s="9">
+        <v>0.15108376365002216</v>
+      </c>
+      <c r="E13" s="9">
+        <v>0.49581506716926871</v>
+      </c>
+      <c r="F13" s="9">
+        <v>0.38585851750654893</v>
+      </c>
+      <c r="G13" s="9">
+        <v>0.5519077287648182</v>
+      </c>
+      <c r="H13" s="9">
+        <v>5.1476292043280074E-2</v>
+      </c>
+      <c r="I13" s="9">
+        <v>5.3893117601831096E-2</v>
+      </c>
+      <c r="J13" s="9">
+        <v>0.12233874946381947</v>
+      </c>
+      <c r="K13" s="9">
+        <v>-0.12068060351407656</v>
+      </c>
+      <c r="L13" s="9">
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="B14" s="8">
-        <v>0.40427970707371425</v>
-      </c>
-      <c r="C14" s="8">
-        <v>-0.16993700818121141</v>
-      </c>
-      <c r="D14" s="8">
-        <v>0.23951087992853468</v>
-      </c>
-      <c r="E14" s="8">
-        <v>0.35924752504481594</v>
-      </c>
-      <c r="F14" s="8">
-        <v>0.17429066191796852</v>
-      </c>
-      <c r="G14" s="8">
-        <v>0.55601434457194709</v>
-      </c>
-      <c r="H14" s="8">
-        <v>-0.13562971319638648</v>
-      </c>
-      <c r="I14" s="8">
-        <v>-0.18534483978469618</v>
-      </c>
-      <c r="J14" s="8">
-        <v>-9.851058646422918E-2</v>
-      </c>
-      <c r="K14" s="8">
-        <v>-0.16282907381050207</v>
-      </c>
-      <c r="L14" s="8">
-        <v>6</v>
+      <c r="A14" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B14" s="9">
+        <v>0.41514304183391088</v>
+      </c>
+      <c r="C14" s="9">
+        <v>-1.3309368869829277E-2</v>
+      </c>
+      <c r="D14" s="9">
+        <v>0.18087050506977614</v>
+      </c>
+      <c r="E14" s="9">
+        <v>0.34319191631776502</v>
+      </c>
+      <c r="F14" s="9">
+        <v>0.25505830774410587</v>
+      </c>
+      <c r="G14" s="9">
+        <v>0.61359345475197546</v>
+      </c>
+      <c r="H14" s="9">
+        <v>-7.0487854964432009E-2</v>
+      </c>
+      <c r="I14" s="9">
+        <v>5.1538494592396976E-2</v>
+      </c>
+      <c r="J14" s="9">
+        <v>0.11345906601594419</v>
+      </c>
+      <c r="K14" s="9">
+        <v>-0.14237180323666387</v>
+      </c>
+      <c r="L14" s="9">
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="B15" s="8">
-        <v>0.42768572493903956</v>
-      </c>
-      <c r="C15" s="8">
-        <v>-6.6589503421519425E-2</v>
-      </c>
-      <c r="D15" s="8">
-        <v>0.19632734856918968</v>
-      </c>
-      <c r="E15" s="8">
-        <v>0.43672362216736432</v>
-      </c>
-      <c r="F15" s="8">
-        <v>0.24988409984398782</v>
-      </c>
-      <c r="G15" s="8">
-        <v>0.54090372985905788</v>
-      </c>
-      <c r="H15" s="8">
-        <v>-2.9754303906286538E-2</v>
-      </c>
-      <c r="I15" s="8">
-        <v>-9.717868956102993E-2</v>
-      </c>
-      <c r="J15" s="8">
-        <v>5.8710353056936199E-3</v>
-      </c>
-      <c r="K15" s="8">
-        <v>-0.24895177462617601</v>
-      </c>
-      <c r="L15" s="8">
+        <v>86</v>
+      </c>
+      <c r="B15" s="9">
+        <v>0.41182962081908409</v>
+      </c>
+      <c r="C15" s="9">
+        <v>2.8868953353709467E-3</v>
+      </c>
+      <c r="D15" s="9">
+        <v>0.18356206683142173</v>
+      </c>
+      <c r="E15" s="9">
+        <v>0.33108753411922043</v>
+      </c>
+      <c r="F15" s="9">
+        <v>0.23829953150931393</v>
+      </c>
+      <c r="G15" s="9">
+        <v>0.62683178238177018</v>
+      </c>
+      <c r="H15" s="9">
+        <v>-8.6399609628571516E-2</v>
+      </c>
+      <c r="I15" s="9">
+        <v>0.10692234480096187</v>
+      </c>
+      <c r="J15" s="9">
+        <v>0.1434344393334463</v>
+      </c>
+      <c r="K15" s="9">
+        <v>-0.11977287839214608</v>
+      </c>
+      <c r="L15" s="9">
         <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="3">
+      <c r="A16" s="8">
         <v>3</v>
       </c>
-      <c r="B16" s="8">
-        <v>0.76087828113810352</v>
-      </c>
-      <c r="C16" s="8">
-        <v>-0.14511575584386829</v>
-      </c>
-      <c r="D16" s="8">
-        <v>0.66053579039432575</v>
-      </c>
-      <c r="E16" s="8">
-        <v>0.86841575859085907</v>
-      </c>
-      <c r="F16" s="8">
-        <v>0.73785816343202759</v>
-      </c>
-      <c r="G16" s="8">
-        <v>0.81834930750205226</v>
-      </c>
-      <c r="H16" s="8">
-        <v>-0.23775439422524527</v>
-      </c>
-      <c r="I16" s="8">
-        <v>0.17944895217935697</v>
-      </c>
-      <c r="J16" s="8">
-        <v>0.18486664398519548</v>
-      </c>
-      <c r="K16" s="8">
-        <v>-0.30634882864767998</v>
-      </c>
-      <c r="L16" s="8">
-        <v>48</v>
+      <c r="B16" s="9">
+        <v>0.40930685987611942</v>
+      </c>
+      <c r="C16" s="9">
+        <v>7.0685636651660375E-2</v>
+      </c>
+      <c r="D16" s="9">
+        <v>0.10528884960468789</v>
+      </c>
+      <c r="E16" s="9">
+        <v>0.27630379368723895</v>
+      </c>
+      <c r="F16" s="9">
+        <v>0.21533332743841824</v>
+      </c>
+      <c r="G16" s="9">
+        <v>0.69792463265646687</v>
+      </c>
+      <c r="H16" s="9">
+        <v>3.3967091022774065E-4</v>
+      </c>
+      <c r="I16" s="9">
+        <v>0.18002045280963111</v>
+      </c>
+      <c r="J16" s="9">
+        <v>0.20680719154600113</v>
+      </c>
+      <c r="K16" s="9">
+        <v>-8.1868244357839723E-2</v>
+      </c>
+      <c r="L16" s="9">
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B17" s="8">
-        <v>0.76460608963809717</v>
-      </c>
-      <c r="C17" s="8">
-        <v>-5.959830236770667E-2</v>
-      </c>
-      <c r="D17" s="8">
-        <v>0.64437256785837838</v>
-      </c>
-      <c r="E17" s="8">
-        <v>0.84537286988362603</v>
-      </c>
-      <c r="F17" s="8">
-        <v>0.70591895971299601</v>
-      </c>
-      <c r="G17" s="8">
-        <v>0.85187607237024821</v>
-      </c>
-      <c r="H17" s="8">
-        <v>-0.18247486557212841</v>
-      </c>
-      <c r="I17" s="8">
-        <v>0.13740250350105895</v>
-      </c>
-      <c r="J17" s="8">
-        <v>0.12151224117308593</v>
-      </c>
-      <c r="K17" s="8">
-        <v>-0.15375529979127775</v>
-      </c>
-      <c r="L17" s="8">
-        <v>15</v>
+      <c r="A17" s="8">
+        <v>6</v>
+      </c>
+      <c r="B17" s="9">
+        <v>0.41435238176204864</v>
+      </c>
+      <c r="C17" s="9">
+        <v>-6.4911845980918481E-2</v>
+      </c>
+      <c r="D17" s="9">
+        <v>0.26183528405815554</v>
+      </c>
+      <c r="E17" s="9">
+        <v>0.3858712745512019</v>
+      </c>
+      <c r="F17" s="9">
+        <v>0.26126573558020955</v>
+      </c>
+      <c r="G17" s="9">
+        <v>0.55573893210707359</v>
+      </c>
+      <c r="H17" s="9">
+        <v>-0.1731388901673708</v>
+      </c>
+      <c r="I17" s="9">
+        <v>3.3824236792292628E-2</v>
+      </c>
+      <c r="J17" s="9">
+        <v>8.006168712089147E-2</v>
+      </c>
+      <c r="K17" s="9">
+        <v>-0.15767751242645248</v>
+      </c>
+      <c r="L17" s="9">
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="B18" s="8">
-        <v>0.76953124209829904</v>
-      </c>
-      <c r="C18" s="8">
-        <v>-0.10384564706225352</v>
-      </c>
-      <c r="D18" s="8">
-        <v>0.63968835263477863</v>
-      </c>
-      <c r="E18" s="8">
-        <v>0.86375823967965637</v>
-      </c>
-      <c r="F18" s="8">
-        <v>0.75279545775576595</v>
-      </c>
-      <c r="G18" s="8">
-        <v>0.8391541811013522</v>
-      </c>
-      <c r="H18" s="8">
-        <v>-0.39568612698807698</v>
-      </c>
-      <c r="I18" s="8">
-        <v>0.27518835113514223</v>
-      </c>
-      <c r="J18" s="8">
-        <v>0.25117807788184437</v>
-      </c>
-      <c r="K18" s="8">
-        <v>-8.036524787550732E-2</v>
-      </c>
-      <c r="L18" s="8">
-        <v>3</v>
+        <v>138</v>
+      </c>
+      <c r="B18" s="9">
+        <v>0.37666064411971895</v>
+      </c>
+      <c r="C18" s="9">
+        <v>-4.3011863077717143E-2</v>
+      </c>
+      <c r="D18" s="9">
+        <v>0.18414608943486688</v>
+      </c>
+      <c r="E18" s="9">
+        <v>0.26379717263170044</v>
+      </c>
+      <c r="F18" s="9">
+        <v>0.18152218228216588</v>
+      </c>
+      <c r="G18" s="9">
+        <v>0.61743888448858353</v>
+      </c>
+      <c r="H18" s="9">
+        <v>-3.0795728287285551E-2</v>
+      </c>
+      <c r="I18" s="9">
+        <v>-2.1532625919085464E-2</v>
+      </c>
+      <c r="J18" s="9">
+        <v>2.3922849331387181E-2</v>
+      </c>
+      <c r="K18" s="9">
+        <v>-0.12237274885407616</v>
+      </c>
+      <c r="L18" s="9">
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="B19" s="8">
-        <v>0.77175196202239327</v>
-      </c>
-      <c r="C19" s="8">
-        <v>-7.6206852635060676E-2</v>
-      </c>
-      <c r="D19" s="8">
-        <v>0.72083365014854195</v>
-      </c>
-      <c r="E19" s="8">
-        <v>0.82853598507324133</v>
-      </c>
-      <c r="F19" s="8">
-        <v>0.66602935126990681</v>
-      </c>
-      <c r="G19" s="8">
-        <v>0.85077545148807543</v>
-      </c>
-      <c r="H19" s="8">
-        <v>-7.7962647850242456E-2</v>
-      </c>
-      <c r="I19" s="8">
-        <v>6.6477440414106845E-2</v>
-      </c>
-      <c r="J19" s="8">
-        <v>0.10113278354238121</v>
-      </c>
-      <c r="K19" s="8">
-        <v>-0.25194720890554312</v>
-      </c>
-      <c r="L19" s="8">
-        <v>6</v>
+      <c r="A19" s="8">
+        <v>3</v>
+      </c>
+      <c r="B19" s="9">
+        <v>0.36853048848934661</v>
+      </c>
+      <c r="C19" s="9">
+        <v>1.3270285236931844E-2</v>
+      </c>
+      <c r="D19" s="9">
+        <v>0.13262533239484198</v>
+      </c>
+      <c r="E19" s="9">
+        <v>0.16722071933191349</v>
+      </c>
+      <c r="F19" s="9">
+        <v>0.1203457025719078</v>
+      </c>
+      <c r="G19" s="9">
+        <v>0.71808192528813597</v>
+      </c>
+      <c r="H19" s="9">
+        <v>0.10327339453880596</v>
+      </c>
+      <c r="I19" s="9">
+        <v>-4.797604656881207E-3</v>
+      </c>
+      <c r="J19" s="9">
+        <v>5.661637847764589E-2</v>
+      </c>
+      <c r="K19" s="9">
+        <v>-9.5023233908335669E-2</v>
+      </c>
+      <c r="L19" s="9">
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="B20" s="8">
-        <v>0.73149509996953055</v>
-      </c>
-      <c r="C20" s="8">
-        <v>-2.8586423182114341E-2</v>
-      </c>
-      <c r="D20" s="8">
-        <v>0.52255892204669263</v>
-      </c>
-      <c r="E20" s="8">
-        <v>0.82320125797833932</v>
-      </c>
-      <c r="F20" s="8">
-        <v>0.72122640791496284</v>
-      </c>
-      <c r="G20" s="8">
-        <v>0.8558440209459891</v>
-      </c>
-      <c r="H20" s="8">
-        <v>7.5927219566325532E-2</v>
-      </c>
-      <c r="I20" s="8">
-        <v>3.766670982291765E-2</v>
-      </c>
-      <c r="J20" s="8">
-        <v>-7.2006954760897954E-2</v>
-      </c>
-      <c r="K20" s="8">
-        <v>-0.12393476061016166</v>
-      </c>
-      <c r="L20" s="8">
+      <c r="A20" s="8">
+        <v>6</v>
+      </c>
+      <c r="B20" s="9">
+        <v>0.38479079975009123</v>
+      </c>
+      <c r="C20" s="9">
+        <v>-9.9294011392366113E-2</v>
+      </c>
+      <c r="D20" s="9">
+        <v>0.23566684647489181</v>
+      </c>
+      <c r="E20" s="9">
+        <v>0.36037362593148742</v>
+      </c>
+      <c r="F20" s="9">
+        <v>0.24269866199242396</v>
+      </c>
+      <c r="G20" s="9">
+        <v>0.51679584368903086</v>
+      </c>
+      <c r="H20" s="9">
+        <v>-0.16486485111337709</v>
+      </c>
+      <c r="I20" s="9">
+        <v>-3.8267647181289721E-2</v>
+      </c>
+      <c r="J20" s="9">
+        <v>-8.7706798148715261E-3</v>
+      </c>
+      <c r="K20" s="9">
+        <v>-0.14972226379981665</v>
+      </c>
+      <c r="L20" s="9">
         <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="B21" s="8">
-        <v>0.77850018207787042</v>
-      </c>
-      <c r="C21" s="8">
-        <v>-1.3145736324044107E-2</v>
-      </c>
-      <c r="D21" s="8">
-        <v>0.61794826431333727</v>
-      </c>
-      <c r="E21" s="8">
-        <v>0.88283288161365192</v>
-      </c>
-      <c r="F21" s="8">
-        <v>0.72351423035443763</v>
-      </c>
-      <c r="G21" s="8">
-        <v>0.86283125682774919</v>
-      </c>
-      <c r="H21" s="8">
-        <v>-0.43669012473840579</v>
-      </c>
-      <c r="I21" s="8">
-        <v>0.24120257571902134</v>
-      </c>
-      <c r="J21" s="8">
-        <v>0.22612451565972078</v>
-      </c>
-      <c r="K21" s="8">
-        <v>-6.0582072659633411E-2</v>
-      </c>
-      <c r="L21" s="8">
-        <v>3</v>
+        <v>188</v>
+      </c>
+      <c r="B21" s="9">
+        <v>0.45693886056292982</v>
+      </c>
+      <c r="C21" s="9">
+        <v>1.9686113285836507E-4</v>
+      </c>
+      <c r="D21" s="9">
+        <v>0.17490335894303999</v>
+      </c>
+      <c r="E21" s="9">
+        <v>0.43469104220237426</v>
+      </c>
+      <c r="F21" s="9">
+        <v>0.34535320944083764</v>
+      </c>
+      <c r="G21" s="9">
+        <v>0.59650969738557269</v>
+      </c>
+      <c r="H21" s="9">
+        <v>-9.426822697743896E-2</v>
+      </c>
+      <c r="I21" s="9">
+        <v>6.9225764895314512E-2</v>
+      </c>
+      <c r="J21" s="9">
+        <v>0.17301990938299905</v>
+      </c>
+      <c r="K21" s="9">
+        <v>-0.18496978246376938</v>
+      </c>
+      <c r="L21" s="9">
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B22" s="8">
-        <v>0.75613362183755173</v>
-      </c>
-      <c r="C22" s="8">
-        <v>-9.7176188239614977E-2</v>
-      </c>
-      <c r="D22" s="8">
-        <v>0.6696598228763615</v>
-      </c>
-      <c r="E22" s="8">
-        <v>0.87612473347389841</v>
-      </c>
-      <c r="F22" s="8">
-        <v>0.74350830904792964</v>
-      </c>
-      <c r="G22" s="8">
-        <v>0.80470206510809461</v>
-      </c>
-      <c r="H22" s="8">
-        <v>-0.23870858198575715</v>
-      </c>
-      <c r="I22" s="8">
-        <v>0.31735826477875656</v>
-      </c>
-      <c r="J22" s="8">
-        <v>0.27942577414939918</v>
-      </c>
-      <c r="K22" s="8">
-        <v>-0.32933327641170074</v>
-      </c>
-      <c r="L22" s="8">
-        <v>27</v>
+      <c r="A22" s="8">
+        <v>3</v>
+      </c>
+      <c r="B22" s="9">
+        <v>0.44785197150671113</v>
+      </c>
+      <c r="C22" s="9">
+        <v>5.8039209100705556E-2</v>
+      </c>
+      <c r="D22" s="9">
+        <v>9.7433752940038379E-2</v>
+      </c>
+      <c r="E22" s="9">
+        <v>0.41282823543555924</v>
+      </c>
+      <c r="F22" s="9">
+        <v>0.31645460431820599</v>
+      </c>
+      <c r="G22" s="9">
+        <v>0.67502711668757653</v>
+      </c>
+      <c r="H22" s="9">
+        <v>-4.4082801433359825E-3</v>
+      </c>
+      <c r="I22" s="9">
+        <v>9.3801387451844007E-2</v>
+      </c>
+      <c r="J22" s="9">
+        <v>0.22613713727566806</v>
+      </c>
+      <c r="K22" s="9">
+        <v>-0.19353642674786678</v>
+      </c>
+      <c r="L22" s="9">
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A23" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="B23" s="8">
-        <v>0.7536399090977578</v>
-      </c>
-      <c r="C23" s="8">
-        <v>-0.24726427831233375</v>
-      </c>
-      <c r="D23" s="8">
-        <v>0.70221452214844893</v>
-      </c>
-      <c r="E23" s="8">
-        <v>0.85892770409869035</v>
-      </c>
-      <c r="F23" s="8">
-        <v>0.73221991076598691</v>
-      </c>
-      <c r="G23" s="8">
-        <v>0.76700556984874346</v>
-      </c>
-      <c r="H23" s="8">
-        <v>-0.44328190876545043</v>
-      </c>
-      <c r="I23" s="8">
-        <v>0.25396316828080889</v>
-      </c>
-      <c r="J23" s="8">
-        <v>0.22576187319871766</v>
-      </c>
-      <c r="K23" s="8">
-        <v>-0.40601788305720882</v>
-      </c>
-      <c r="L23" s="8">
-        <v>12</v>
+      <c r="A23" s="8">
+        <v>6</v>
+      </c>
+      <c r="B23" s="9">
+        <v>0.46602574961914839</v>
+      </c>
+      <c r="C23" s="9">
+        <v>-5.7645486834988824E-2</v>
+      </c>
+      <c r="D23" s="9">
+        <v>0.2523729649460415</v>
+      </c>
+      <c r="E23" s="9">
+        <v>0.45655384896918932</v>
+      </c>
+      <c r="F23" s="9">
+        <v>0.3742518145634694</v>
+      </c>
+      <c r="G23" s="9">
+        <v>0.51799227808356896</v>
+      </c>
+      <c r="H23" s="9">
+        <v>-0.18412817381154192</v>
+      </c>
+      <c r="I23" s="9">
+        <v>4.4650142338785011E-2</v>
+      </c>
+      <c r="J23" s="9">
+        <v>0.11990268149033008</v>
+      </c>
+      <c r="K23" s="9">
+        <v>-0.17640313817967201</v>
+      </c>
+      <c r="L23" s="9">
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A24" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="B24" s="8">
-        <v>0.75812859202938665</v>
-      </c>
-      <c r="C24" s="8">
-        <v>2.2894283818560068E-2</v>
-      </c>
-      <c r="D24" s="8">
-        <v>0.64361606345869171</v>
-      </c>
-      <c r="E24" s="8">
-        <v>0.88988235697406459</v>
-      </c>
-      <c r="F24" s="8">
-        <v>0.7525390276734838</v>
-      </c>
-      <c r="G24" s="8">
-        <v>0.83485926131557564</v>
-      </c>
-      <c r="H24" s="8">
-        <v>-7.5049920562002631E-2</v>
-      </c>
-      <c r="I24" s="8">
-        <v>0.36807434197711481</v>
-      </c>
-      <c r="J24" s="8">
-        <v>0.32235689490994418</v>
-      </c>
-      <c r="K24" s="8">
-        <v>-0.26798559109529424</v>
-      </c>
-      <c r="L24" s="8">
-        <v>15</v>
+      <c r="A24" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B24" s="9">
+        <v>0.41915151479308266</v>
+      </c>
+      <c r="C24" s="9">
+        <v>-0.14761874160244692</v>
+      </c>
+      <c r="D24" s="9">
+        <v>0.23123618977648558</v>
+      </c>
+      <c r="E24" s="9">
+        <v>0.40105795949485912</v>
+      </c>
+      <c r="F24" s="9">
+        <v>0.21056165833789323</v>
+      </c>
+      <c r="G24" s="9">
+        <v>0.54806902227230681</v>
+      </c>
+      <c r="H24" s="9">
+        <v>-9.7236845873259703E-2</v>
+      </c>
+      <c r="I24" s="9">
+        <v>-0.1689100222553388</v>
+      </c>
+      <c r="J24" s="9">
+        <v>-5.6900852604976161E-2</v>
+      </c>
+      <c r="K24" s="9">
+        <v>-0.22425716775132734</v>
+      </c>
+      <c r="L24" s="9">
+        <v>18</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A25" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="B25" s="8">
-        <v>0.77290972674060299</v>
-      </c>
-      <c r="C25" s="8">
-        <v>-0.57463744375341264</v>
-      </c>
-      <c r="D25" s="8">
-        <v>0.65988570056503359</v>
-      </c>
-      <c r="E25" s="8">
-        <v>0.89133259338526638</v>
-      </c>
-      <c r="F25" s="8">
-        <v>0.79228051745805061</v>
-      </c>
-      <c r="G25" s="8">
-        <v>0.79594498610437314</v>
-      </c>
-      <c r="H25" s="8">
-        <v>-0.37165937093573492</v>
-      </c>
-      <c r="I25" s="8">
-        <v>-0.33602683282219598</v>
-      </c>
-      <c r="J25" s="8">
-        <v>-8.226343472344666E-2</v>
-      </c>
-      <c r="K25" s="8">
-        <v>-0.58440263585059204</v>
-      </c>
-      <c r="L25" s="8">
+      <c r="A25" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B25" s="9">
+        <v>0.42548911236649428</v>
+      </c>
+      <c r="C25" s="9">
+        <v>-0.20632971320460991</v>
+      </c>
+      <c r="D25" s="9">
+        <v>0.25787034083173238</v>
+      </c>
+      <c r="E25" s="9">
+        <v>0.40720273127239709</v>
+      </c>
+      <c r="F25" s="9">
+        <v>0.20751021325172339</v>
+      </c>
+      <c r="G25" s="9">
+        <v>0.54728899238591522</v>
+      </c>
+      <c r="H25" s="9">
+        <v>-0.12632652051710611</v>
+      </c>
+      <c r="I25" s="9">
+        <v>-0.22420653742029029</v>
+      </c>
+      <c r="J25" s="9">
+        <v>-7.8063006656392944E-2</v>
+      </c>
+      <c r="K25" s="9">
+        <v>-0.26099065481730394</v>
+      </c>
+      <c r="L25" s="9">
         <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A26" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="B26" s="8">
-        <v>0.77290972674060299</v>
-      </c>
-      <c r="C26" s="8">
-        <v>-0.57463744375341264</v>
-      </c>
-      <c r="D26" s="8">
-        <v>0.65988570056503359</v>
-      </c>
-      <c r="E26" s="8">
-        <v>0.89133259338526638</v>
-      </c>
-      <c r="F26" s="8">
-        <v>0.79228051745805061</v>
-      </c>
-      <c r="G26" s="8">
-        <v>0.79594498610437314</v>
-      </c>
-      <c r="H26" s="8">
-        <v>-0.37165937093573492</v>
-      </c>
-      <c r="I26" s="8">
-        <v>-0.33602683282219598</v>
-      </c>
-      <c r="J26" s="8">
-        <v>-8.226343472344666E-2</v>
-      </c>
-      <c r="K26" s="8">
-        <v>-0.58440263585059204</v>
-      </c>
-      <c r="L26" s="8">
-        <v>6</v>
+      <c r="A26" s="8">
+        <v>3</v>
+      </c>
+      <c r="B26" s="9">
+        <v>0.41185885806808625</v>
+      </c>
+      <c r="C26" s="9">
+        <v>-0.36099267023131992</v>
+      </c>
+      <c r="D26" s="9">
+        <v>0.1666430787480627</v>
+      </c>
+      <c r="E26" s="9">
+        <v>0.34458964402747744</v>
+      </c>
+      <c r="F26" s="9">
+        <v>0.14884857957504036</v>
+      </c>
+      <c r="G26" s="9">
+        <v>0.64713978394937666</v>
+      </c>
+      <c r="H26" s="9">
+        <v>-0.16220100554077543</v>
+      </c>
+      <c r="I26" s="9">
+        <v>-0.32336564766302217</v>
+      </c>
+      <c r="J26" s="9">
+        <v>-0.1436686837559519</v>
+      </c>
+      <c r="K26" s="9">
+        <v>-0.22928799948759729</v>
+      </c>
+      <c r="L26" s="9">
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A27" s="3">
-        <v>4</v>
-      </c>
-      <c r="B27" s="8">
-        <v>0.75312101500851369</v>
-      </c>
-      <c r="C27" s="8">
-        <v>7.4824451065932066E-2</v>
-      </c>
-      <c r="D27" s="8">
-        <v>0.6691209862800418</v>
-      </c>
-      <c r="E27" s="8">
-        <v>0.7515782707692189</v>
-      </c>
-      <c r="F27" s="8">
-        <v>0.77013219720587833</v>
-      </c>
-      <c r="G27" s="8">
-        <v>0.74424859869889026</v>
-      </c>
-      <c r="H27" s="8">
-        <v>0.10270137864019827</v>
-      </c>
-      <c r="I27" s="8">
-        <v>8.9781881212588691E-2</v>
-      </c>
-      <c r="J27" s="8">
-        <v>0.33171586183484525</v>
-      </c>
-      <c r="K27" s="8">
-        <v>-0.16984594768407396</v>
-      </c>
-      <c r="L27" s="8">
-        <v>13</v>
+      <c r="A27" s="8">
+        <v>6</v>
+      </c>
+      <c r="B27" s="9">
+        <v>0.43911936666490231</v>
+      </c>
+      <c r="C27" s="9">
+        <v>-5.1666756177899953E-2</v>
+      </c>
+      <c r="D27" s="9">
+        <v>0.34909760291540204</v>
+      </c>
+      <c r="E27" s="9">
+        <v>0.46981581851731669</v>
+      </c>
+      <c r="F27" s="9">
+        <v>0.2661718469284064</v>
+      </c>
+      <c r="G27" s="9">
+        <v>0.44743820082245378</v>
+      </c>
+      <c r="H27" s="9">
+        <v>-9.0452035493436764E-2</v>
+      </c>
+      <c r="I27" s="9">
+        <v>-0.1250474271775584</v>
+      </c>
+      <c r="J27" s="9">
+        <v>-1.2457329556833983E-2</v>
+      </c>
+      <c r="K27" s="9">
+        <v>-0.29269331014701061</v>
+      </c>
+      <c r="L27" s="9">
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A28" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B28" s="8">
-        <v>0.75006921883984434</v>
-      </c>
-      <c r="C28" s="8">
-        <v>8.5252735780993461E-2</v>
-      </c>
-      <c r="D28" s="8">
-        <v>0.65459800415176816</v>
-      </c>
-      <c r="E28" s="8">
-        <v>0.75646033846208516</v>
-      </c>
-      <c r="F28" s="8">
-        <v>0.76634003439806042</v>
-      </c>
-      <c r="G28" s="8">
-        <v>0.73693717965629801</v>
-      </c>
-      <c r="H28" s="8">
-        <v>6.087008648466289E-2</v>
-      </c>
-      <c r="I28" s="8">
-        <v>8.8817569045262654E-2</v>
-      </c>
-      <c r="J28" s="8">
-        <v>0.30537556650815739</v>
-      </c>
-      <c r="K28" s="8">
-        <v>-5.0729734535457448E-2</v>
-      </c>
-      <c r="L28" s="8">
-        <v>12</v>
+      <c r="A28" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="B28" s="9">
+        <v>0.40427970707371425</v>
+      </c>
+      <c r="C28" s="9">
+        <v>-0.16993700818121141</v>
+      </c>
+      <c r="D28" s="9">
+        <v>0.23951087992853468</v>
+      </c>
+      <c r="E28" s="9">
+        <v>0.35924752504481594</v>
+      </c>
+      <c r="F28" s="9">
+        <v>0.17429066191796849</v>
+      </c>
+      <c r="G28" s="9">
+        <v>0.55601434457194709</v>
+      </c>
+      <c r="H28" s="9">
+        <v>-0.13562971319638648</v>
+      </c>
+      <c r="I28" s="9">
+        <v>-0.18534483978469618</v>
+      </c>
+      <c r="J28" s="9">
+        <v>-9.851058646422918E-2</v>
+      </c>
+      <c r="K28" s="9">
+        <v>-0.16282907381050207</v>
+      </c>
+      <c r="L28" s="9">
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A29" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="B29" s="8">
-        <v>0.75006921883984434</v>
-      </c>
-      <c r="C29" s="8">
-        <v>8.5252735780993461E-2</v>
-      </c>
-      <c r="D29" s="8">
-        <v>0.65459800415176816</v>
-      </c>
-      <c r="E29" s="8">
-        <v>0.75646033846208516</v>
-      </c>
-      <c r="F29" s="8">
-        <v>0.76634003439806042</v>
-      </c>
-      <c r="G29" s="8">
-        <v>0.73693717965629801</v>
-      </c>
-      <c r="H29" s="8">
-        <v>6.087008648466289E-2</v>
-      </c>
-      <c r="I29" s="8">
-        <v>8.8817569045262654E-2</v>
-      </c>
-      <c r="J29" s="8">
-        <v>0.30537556650815739</v>
-      </c>
-      <c r="K29" s="8">
-        <v>-5.0729734535457448E-2</v>
-      </c>
-      <c r="L29" s="8">
-        <v>12</v>
+      <c r="A29" s="8">
+        <v>3</v>
+      </c>
+      <c r="B29" s="9">
+        <v>0.39954696172779797</v>
+      </c>
+      <c r="C29" s="9">
+        <v>-0.21149148966020517</v>
+      </c>
+      <c r="D29" s="9">
+        <v>0.13390195047901154</v>
+      </c>
+      <c r="E29" s="9">
+        <v>0.33983572504555465</v>
+      </c>
+      <c r="F29" s="9">
+        <v>0.16067253388758851</v>
+      </c>
+      <c r="G29" s="9">
+        <v>0.63491664361051658</v>
+      </c>
+      <c r="H29" s="9">
+        <v>-6.0981454735038389E-2</v>
+      </c>
+      <c r="I29" s="9">
+        <v>-0.33809065221772161</v>
+      </c>
+      <c r="J29" s="9">
+        <v>-0.23123394543046283</v>
+      </c>
+      <c r="K29" s="9">
+        <v>-0.19525652551542852</v>
+      </c>
+      <c r="L29" s="9">
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A30" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B30" s="8">
-        <v>0.78974256903254514</v>
-      </c>
-      <c r="C30" s="8">
-        <v>-5.0314965514804633E-2</v>
-      </c>
-      <c r="D30" s="8">
-        <v>0.84339677181932338</v>
-      </c>
-      <c r="E30" s="8">
-        <v>0.69299345845482319</v>
-      </c>
-      <c r="F30" s="8">
-        <v>0.81563815089969305</v>
-      </c>
-      <c r="G30" s="8">
-        <v>0.83198562720999703</v>
-      </c>
-      <c r="H30" s="8">
-        <v>0.60467688450662282</v>
-      </c>
-      <c r="I30" s="8">
-        <v>0.10135362722050111</v>
-      </c>
-      <c r="J30" s="8">
-        <v>0.64779940575509976</v>
-      </c>
-      <c r="K30" s="8">
-        <v>-1.5992405054674721</v>
-      </c>
-      <c r="L30" s="8">
-        <v>1</v>
+      <c r="A30" s="8">
+        <v>6</v>
+      </c>
+      <c r="B30" s="9">
+        <v>0.40901245241963052</v>
+      </c>
+      <c r="C30" s="9">
+        <v>-0.12838252670221764</v>
+      </c>
+      <c r="D30" s="9">
+        <v>0.3451198093780577</v>
+      </c>
+      <c r="E30" s="9">
+        <v>0.37865932504407723</v>
+      </c>
+      <c r="F30" s="9">
+        <v>0.18790878994834848</v>
+      </c>
+      <c r="G30" s="9">
+        <v>0.47711204553337744</v>
+      </c>
+      <c r="H30" s="9">
+        <v>-0.21027797165773454</v>
+      </c>
+      <c r="I30" s="9">
+        <v>-3.2599027351670751E-2</v>
+      </c>
+      <c r="J30" s="9">
+        <v>3.4212772502004461E-2</v>
+      </c>
+      <c r="K30" s="9">
+        <v>-0.13040162210557563</v>
+      </c>
+      <c r="L30" s="9">
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="B31" s="8">
-        <v>0.78974256903254514</v>
-      </c>
-      <c r="C31" s="8">
-        <v>-5.0314965514804633E-2</v>
-      </c>
-      <c r="D31" s="8">
-        <v>0.84339677181932338</v>
-      </c>
-      <c r="E31" s="8">
-        <v>0.69299345845482319</v>
-      </c>
-      <c r="F31" s="8">
-        <v>0.81563815089969305</v>
-      </c>
-      <c r="G31" s="8">
-        <v>0.83198562720999703</v>
-      </c>
-      <c r="H31" s="8">
-        <v>0.60467688450662282</v>
-      </c>
-      <c r="I31" s="8">
-        <v>0.10135362722050111</v>
-      </c>
-      <c r="J31" s="8">
-        <v>0.64779940575509976</v>
-      </c>
-      <c r="K31" s="8">
-        <v>-1.5992405054674721</v>
-      </c>
-      <c r="L31" s="8">
-        <v>1</v>
+        <v>188</v>
+      </c>
+      <c r="B31" s="9">
+        <v>0.4276857249390395</v>
+      </c>
+      <c r="C31" s="9">
+        <v>-6.6589503421519425E-2</v>
+      </c>
+      <c r="D31" s="9">
+        <v>0.19632734856918968</v>
+      </c>
+      <c r="E31" s="9">
+        <v>0.43672362216736432</v>
+      </c>
+      <c r="F31" s="9">
+        <v>0.24988409984398782</v>
+      </c>
+      <c r="G31" s="9">
+        <v>0.54090372985905788</v>
+      </c>
+      <c r="H31" s="9">
+        <v>-2.9754303906286538E-2</v>
+      </c>
+      <c r="I31" s="9">
+        <v>-9.717868956102993E-2</v>
+      </c>
+      <c r="J31" s="9">
+        <v>5.8710353056936199E-3</v>
+      </c>
+      <c r="K31" s="9">
+        <v>-0.24895177462617601</v>
+      </c>
+      <c r="L31" s="9">
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A32" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="B32" s="8">
-        <v>0.59823175738347534</v>
-      </c>
-      <c r="C32" s="8">
-        <v>-7.6870184030483582E-2</v>
-      </c>
-      <c r="D32" s="8">
-        <v>0.43593714978659825</v>
-      </c>
-      <c r="E32" s="8">
-        <v>0.63417731162951152</v>
-      </c>
-      <c r="F32" s="8">
-        <v>0.52205254674589086</v>
-      </c>
-      <c r="G32" s="8">
-        <v>0.70081821162362368</v>
-      </c>
-      <c r="H32" s="8">
-        <v>-0.115517793662312</v>
-      </c>
-      <c r="I32" s="8">
-        <v>7.5598097854496532E-2</v>
-      </c>
-      <c r="J32" s="8">
-        <v>0.14289712595522985</v>
-      </c>
-      <c r="K32" s="8">
-        <v>-0.21998986545732405</v>
-      </c>
-      <c r="L32" s="8">
-        <v>115</v>
+      <c r="A32" s="8">
+        <v>3</v>
+      </c>
+      <c r="B32" s="9">
+        <v>0.44112458346239897</v>
+      </c>
+      <c r="C32" s="9">
+        <v>-7.4224026722955416E-2</v>
+      </c>
+      <c r="D32" s="9">
+        <v>0.10653846144681367</v>
+      </c>
+      <c r="E32" s="9">
+        <v>0.40397786057157931</v>
+      </c>
+      <c r="F32" s="9">
+        <v>0.24644133986357639</v>
+      </c>
+      <c r="G32" s="9">
+        <v>0.64469477801939234</v>
+      </c>
+      <c r="H32" s="9">
+        <v>-2.2789921924410095E-2</v>
+      </c>
+      <c r="I32" s="9">
+        <v>-0.11821452641829193</v>
+      </c>
+      <c r="J32" s="9">
+        <v>4.758862268505905E-3</v>
+      </c>
+      <c r="K32" s="9">
+        <v>-0.14870864813219306</v>
+      </c>
+      <c r="L32" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A33" s="8">
+        <v>6</v>
+      </c>
+      <c r="B33" s="9">
+        <v>0.41424686641567993</v>
+      </c>
+      <c r="C33" s="9">
+        <v>-5.8954980120083413E-2</v>
+      </c>
+      <c r="D33" s="9">
+        <v>0.28611623569156569</v>
+      </c>
+      <c r="E33" s="9">
+        <v>0.46946938376314945</v>
+      </c>
+      <c r="F33" s="9">
+        <v>0.25332685982439929</v>
+      </c>
+      <c r="G33" s="9">
+        <v>0.43711268169872336</v>
+      </c>
+      <c r="H33" s="9">
+        <v>-3.6718685888162982E-2</v>
+      </c>
+      <c r="I33" s="9">
+        <v>-7.614285270376793E-2</v>
+      </c>
+      <c r="J33" s="9">
+        <v>6.9832083428813347E-3</v>
+      </c>
+      <c r="K33" s="9">
+        <v>-0.34919490112015894</v>
+      </c>
+      <c r="L33" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A34" s="3">
+        <v>3</v>
+      </c>
+      <c r="B34" s="9">
+        <v>0.76087828113810352</v>
+      </c>
+      <c r="C34" s="9">
+        <v>-0.14511575584386829</v>
+      </c>
+      <c r="D34" s="9">
+        <v>0.66053579039432575</v>
+      </c>
+      <c r="E34" s="9">
+        <v>0.86841575859085907</v>
+      </c>
+      <c r="F34" s="9">
+        <v>0.73785816343202759</v>
+      </c>
+      <c r="G34" s="9">
+        <v>0.81834930750205226</v>
+      </c>
+      <c r="H34" s="9">
+        <v>-0.23775439422524527</v>
+      </c>
+      <c r="I34" s="9">
+        <v>0.17944895217935697</v>
+      </c>
+      <c r="J34" s="9">
+        <v>0.18486664398519548</v>
+      </c>
+      <c r="K34" s="9">
+        <v>-0.30634882864767998</v>
+      </c>
+      <c r="L34" s="9">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A35" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B35" s="9">
+        <v>0.76460608963809717</v>
+      </c>
+      <c r="C35" s="9">
+        <v>-5.959830236770667E-2</v>
+      </c>
+      <c r="D35" s="9">
+        <v>0.64437256785837838</v>
+      </c>
+      <c r="E35" s="9">
+        <v>0.84537286988362603</v>
+      </c>
+      <c r="F35" s="9">
+        <v>0.70591895971299601</v>
+      </c>
+      <c r="G35" s="9">
+        <v>0.85187607237024809</v>
+      </c>
+      <c r="H35" s="9">
+        <v>-0.18247486557212841</v>
+      </c>
+      <c r="I35" s="9">
+        <v>0.13740250350105895</v>
+      </c>
+      <c r="J35" s="9">
+        <v>0.12151224117308591</v>
+      </c>
+      <c r="K35" s="9">
+        <v>-0.15375529979127775</v>
+      </c>
+      <c r="L35" s="9">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A36" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B36" s="9">
+        <v>0.76953124209829904</v>
+      </c>
+      <c r="C36" s="9">
+        <v>-0.10384564706225352</v>
+      </c>
+      <c r="D36" s="9">
+        <v>0.63968835263477863</v>
+      </c>
+      <c r="E36" s="9">
+        <v>0.86375823967965637</v>
+      </c>
+      <c r="F36" s="9">
+        <v>0.75279545775576595</v>
+      </c>
+      <c r="G36" s="9">
+        <v>0.8391541811013522</v>
+      </c>
+      <c r="H36" s="9">
+        <v>-0.39568612698807698</v>
+      </c>
+      <c r="I36" s="9">
+        <v>0.27518835113514223</v>
+      </c>
+      <c r="J36" s="9">
+        <v>0.25117807788184437</v>
+      </c>
+      <c r="K36" s="9">
+        <v>-8.036524787550732E-2</v>
+      </c>
+      <c r="L36" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A37" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="B37" s="9">
+        <v>0.76953124209829904</v>
+      </c>
+      <c r="C37" s="9">
+        <v>-0.10384564706225352</v>
+      </c>
+      <c r="D37" s="9">
+        <v>0.63968835263477863</v>
+      </c>
+      <c r="E37" s="9">
+        <v>0.86375823967965637</v>
+      </c>
+      <c r="F37" s="9">
+        <v>0.75279545775576595</v>
+      </c>
+      <c r="G37" s="9">
+        <v>0.8391541811013522</v>
+      </c>
+      <c r="H37" s="9">
+        <v>-0.39568612698807698</v>
+      </c>
+      <c r="I37" s="9">
+        <v>0.27518835113514223</v>
+      </c>
+      <c r="J37" s="9">
+        <v>0.25117807788184437</v>
+      </c>
+      <c r="K37" s="9">
+        <v>-8.036524787550732E-2</v>
+      </c>
+      <c r="L37" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A38" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B38" s="9">
+        <v>0.77175196202239305</v>
+      </c>
+      <c r="C38" s="9">
+        <v>-7.6206852635060676E-2</v>
+      </c>
+      <c r="D38" s="9">
+        <v>0.72083365014854184</v>
+      </c>
+      <c r="E38" s="9">
+        <v>0.82853598507324133</v>
+      </c>
+      <c r="F38" s="9">
+        <v>0.66602935126990681</v>
+      </c>
+      <c r="G38" s="9">
+        <v>0.85077545148807532</v>
+      </c>
+      <c r="H38" s="9">
+        <v>-7.796264785024247E-2</v>
+      </c>
+      <c r="I38" s="9">
+        <v>6.6477440414106859E-2</v>
+      </c>
+      <c r="J38" s="9">
+        <v>0.10113278354238121</v>
+      </c>
+      <c r="K38" s="9">
+        <v>-0.25194720890554312</v>
+      </c>
+      <c r="L38" s="9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A39" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="B39" s="9">
+        <v>0.7711531847331724</v>
+      </c>
+      <c r="C39" s="9">
+        <v>-5.7194655199862367E-2</v>
+      </c>
+      <c r="D39" s="9">
+        <v>0.66149383121950844</v>
+      </c>
+      <c r="E39" s="9">
+        <v>0.86450428222818732</v>
+      </c>
+      <c r="F39" s="9">
+        <v>0.70031502240607491</v>
+      </c>
+      <c r="G39" s="9">
+        <v>0.84813635649902686</v>
+      </c>
+      <c r="H39" s="9">
+        <v>-0.15444220710000864</v>
+      </c>
+      <c r="I39" s="9">
+        <v>0.20892572023781208</v>
+      </c>
+      <c r="J39" s="9">
+        <v>0.24519790403769959</v>
+      </c>
+      <c r="K39" s="9">
+        <v>-0.28536916583910016</v>
+      </c>
+      <c r="L39" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A40" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="B40" s="9">
+        <v>0.77235073931161391</v>
+      </c>
+      <c r="C40" s="9">
+        <v>-9.5219050070258993E-2</v>
+      </c>
+      <c r="D40" s="9">
+        <v>0.78017346907757534</v>
+      </c>
+      <c r="E40" s="9">
+        <v>0.79256768791829535</v>
+      </c>
+      <c r="F40" s="9">
+        <v>0.63174368013373872</v>
+      </c>
+      <c r="G40" s="9">
+        <v>0.85341454647712389</v>
+      </c>
+      <c r="H40" s="9">
+        <v>-1.4830886004762618E-3</v>
+      </c>
+      <c r="I40" s="9">
+        <v>-7.5970839409598367E-2</v>
+      </c>
+      <c r="J40" s="9">
+        <v>-4.2932336952937154E-2</v>
+      </c>
+      <c r="K40" s="9">
+        <v>-0.21852525197198605</v>
+      </c>
+      <c r="L40" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A41" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="B41" s="9">
+        <v>0.73149509996953055</v>
+      </c>
+      <c r="C41" s="9">
+        <v>-2.8586423182114341E-2</v>
+      </c>
+      <c r="D41" s="9">
+        <v>0.52255892204669263</v>
+      </c>
+      <c r="E41" s="9">
+        <v>0.82320125797833932</v>
+      </c>
+      <c r="F41" s="9">
+        <v>0.72122640791496284</v>
+      </c>
+      <c r="G41" s="9">
+        <v>0.8558440209459891</v>
+      </c>
+      <c r="H41" s="9">
+        <v>7.5927219566325532E-2</v>
+      </c>
+      <c r="I41" s="9">
+        <v>3.766670982291765E-2</v>
+      </c>
+      <c r="J41" s="9">
+        <v>-7.2006954760897954E-2</v>
+      </c>
+      <c r="K41" s="9">
+        <v>-0.12393476061016166</v>
+      </c>
+      <c r="L41" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A42" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="B42" s="9">
+        <v>0.73149509996953055</v>
+      </c>
+      <c r="C42" s="9">
+        <v>-2.8586423182114341E-2</v>
+      </c>
+      <c r="D42" s="9">
+        <v>0.52255892204669263</v>
+      </c>
+      <c r="E42" s="9">
+        <v>0.82320125797833932</v>
+      </c>
+      <c r="F42" s="9">
+        <v>0.72122640791496284</v>
+      </c>
+      <c r="G42" s="9">
+        <v>0.8558440209459891</v>
+      </c>
+      <c r="H42" s="9">
+        <v>7.5927219566325532E-2</v>
+      </c>
+      <c r="I42" s="9">
+        <v>3.766670982291765E-2</v>
+      </c>
+      <c r="J42" s="9">
+        <v>-7.2006954760897954E-2</v>
+      </c>
+      <c r="K42" s="9">
+        <v>-0.12393476061016166</v>
+      </c>
+      <c r="L42" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A43" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="B43" s="9">
+        <v>0.77850018207787042</v>
+      </c>
+      <c r="C43" s="9">
+        <v>-1.3145736324044107E-2</v>
+      </c>
+      <c r="D43" s="9">
+        <v>0.61794826431333727</v>
+      </c>
+      <c r="E43" s="9">
+        <v>0.88283288161365192</v>
+      </c>
+      <c r="F43" s="9">
+        <v>0.72351423035443763</v>
+      </c>
+      <c r="G43" s="9">
+        <v>0.86283125682774919</v>
+      </c>
+      <c r="H43" s="9">
+        <v>-0.43669012473840579</v>
+      </c>
+      <c r="I43" s="9">
+        <v>0.24120257571902134</v>
+      </c>
+      <c r="J43" s="9">
+        <v>0.22612451565972078</v>
+      </c>
+      <c r="K43" s="9">
+        <v>-6.0582072659633411E-2</v>
+      </c>
+      <c r="L43" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A44" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="B44" s="9">
+        <v>0.77850018207787042</v>
+      </c>
+      <c r="C44" s="9">
+        <v>-1.3145736324044107E-2</v>
+      </c>
+      <c r="D44" s="9">
+        <v>0.61794826431333727</v>
+      </c>
+      <c r="E44" s="9">
+        <v>0.88283288161365192</v>
+      </c>
+      <c r="F44" s="9">
+        <v>0.72351423035443763</v>
+      </c>
+      <c r="G44" s="9">
+        <v>0.86283125682774919</v>
+      </c>
+      <c r="H44" s="9">
+        <v>-0.43669012473840579</v>
+      </c>
+      <c r="I44" s="9">
+        <v>0.24120257571902134</v>
+      </c>
+      <c r="J44" s="9">
+        <v>0.22612451565972078</v>
+      </c>
+      <c r="K44" s="9">
+        <v>-6.0582072659633411E-2</v>
+      </c>
+      <c r="L44" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A45" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B45" s="9">
+        <v>0.75613362183755173</v>
+      </c>
+      <c r="C45" s="9">
+        <v>-9.7176188239614977E-2</v>
+      </c>
+      <c r="D45" s="9">
+        <v>0.6696598228763615</v>
+      </c>
+      <c r="E45" s="9">
+        <v>0.87612473347389841</v>
+      </c>
+      <c r="F45" s="9">
+        <v>0.74350830904792964</v>
+      </c>
+      <c r="G45" s="9">
+        <v>0.80470206510809461</v>
+      </c>
+      <c r="H45" s="9">
+        <v>-0.23870858198575715</v>
+      </c>
+      <c r="I45" s="9">
+        <v>0.31735826477875656</v>
+      </c>
+      <c r="J45" s="9">
+        <v>0.27942577414939918</v>
+      </c>
+      <c r="K45" s="9">
+        <v>-0.32933327641170074</v>
+      </c>
+      <c r="L45" s="9">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A46" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B46" s="9">
+        <v>0.7536399090977578</v>
+      </c>
+      <c r="C46" s="9">
+        <v>-0.24726427831233375</v>
+      </c>
+      <c r="D46" s="9">
+        <v>0.70221452214844893</v>
+      </c>
+      <c r="E46" s="9">
+        <v>0.85892770409869035</v>
+      </c>
+      <c r="F46" s="9">
+        <v>0.73221991076598691</v>
+      </c>
+      <c r="G46" s="9">
+        <v>0.76700556984874346</v>
+      </c>
+      <c r="H46" s="9">
+        <v>-0.44328190876545043</v>
+      </c>
+      <c r="I46" s="9">
+        <v>0.25396316828080889</v>
+      </c>
+      <c r="J46" s="9">
+        <v>0.22576187319871766</v>
+      </c>
+      <c r="K46" s="9">
+        <v>-0.40601788305720882</v>
+      </c>
+      <c r="L46" s="9">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A47" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="B47" s="9">
+        <v>0.84418831267468697</v>
+      </c>
+      <c r="C47" s="9">
+        <v>-0.98928012875441951</v>
+      </c>
+      <c r="D47" s="9">
+        <v>0.88766983293904234</v>
+      </c>
+      <c r="E47" s="9">
+        <v>0.88908502337218565</v>
+      </c>
+      <c r="F47" s="9">
+        <v>0.76904052415305191</v>
+      </c>
+      <c r="G47" s="9">
+        <v>0.8351531315824966</v>
+      </c>
+      <c r="H47" s="9">
+        <v>-1.7336709085962372</v>
+      </c>
+      <c r="I47" s="9">
+        <v>0.56000994841475915</v>
+      </c>
+      <c r="J47" s="9">
+        <v>0.47570200274960556</v>
+      </c>
+      <c r="K47" s="9">
+        <v>-1.1814644095181581</v>
+      </c>
+      <c r="L47" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A48" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="B48" s="9">
+        <v>0.78080432727161619</v>
+      </c>
+      <c r="C48" s="9">
+        <v>0.12331756212205791</v>
+      </c>
+      <c r="D48" s="9">
+        <v>0.73191045657243492</v>
+      </c>
+      <c r="E48" s="9">
+        <v>0.88730455851755796</v>
+      </c>
+      <c r="F48" s="9">
+        <v>0.77520481488547233</v>
+      </c>
+      <c r="G48" s="9">
+        <v>0.79118414822180938</v>
+      </c>
+      <c r="H48" s="9">
+        <v>0.12491851781939363</v>
+      </c>
+      <c r="I48" s="9">
+        <v>0.27137939560030622</v>
+      </c>
+      <c r="J48" s="9">
+        <v>0.2082691310338621</v>
+      </c>
+      <c r="K48" s="9">
+        <v>8.5201340042552351E-2</v>
+      </c>
+      <c r="L48" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A49" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="B49" s="9">
+        <v>0.72296968447116239</v>
+      </c>
+      <c r="C49" s="9">
+        <v>-0.21274331483584544</v>
+      </c>
+      <c r="D49" s="9">
+        <v>0.70622315004840208</v>
+      </c>
+      <c r="E49" s="9">
+        <v>0.82263817965584984</v>
+      </c>
+      <c r="F49" s="9">
+        <v>0.68217882702790256</v>
+      </c>
+      <c r="G49" s="9">
+        <v>0.77337754359623201</v>
+      </c>
+      <c r="H49" s="9">
+        <v>-0.13582572781821278</v>
+      </c>
+      <c r="I49" s="9">
+        <v>-7.0542367600500575E-2</v>
+      </c>
+      <c r="J49" s="9">
+        <v>-4.958466065450795E-2</v>
+      </c>
+      <c r="K49" s="9">
+        <v>-0.43177132716531447</v>
+      </c>
+      <c r="L49" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A50" s="8">
+        <v>5</v>
+      </c>
+      <c r="B50" s="9">
+        <v>0.66659731197356553</v>
+      </c>
+      <c r="C50" s="9">
+        <v>8.9648768218872188E-2</v>
+      </c>
+      <c r="D50" s="9">
+        <v>0.48305464903391676</v>
+      </c>
+      <c r="E50" s="9">
+        <v>0.83668305484916772</v>
+      </c>
+      <c r="F50" s="9">
+        <v>0.70245547699752076</v>
+      </c>
+      <c r="G50" s="9">
+        <v>0.66830745599443586</v>
+      </c>
+      <c r="H50" s="9">
+        <v>-2.854951646674515E-2</v>
+      </c>
+      <c r="I50" s="9">
+        <v>0.25500569670867074</v>
+      </c>
+      <c r="J50" s="9">
+        <v>0.26866101966591088</v>
+      </c>
+      <c r="K50" s="9">
+        <v>-9.6037135587915004E-2</v>
+      </c>
+      <c r="L50" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A51" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B51" s="9">
+        <v>0.75812859202938665</v>
+      </c>
+      <c r="C51" s="9">
+        <v>2.2894283818560068E-2</v>
+      </c>
+      <c r="D51" s="9">
+        <v>0.64361606345869171</v>
+      </c>
+      <c r="E51" s="9">
+        <v>0.88988235697406459</v>
+      </c>
+      <c r="F51" s="9">
+        <v>0.7525390276734838</v>
+      </c>
+      <c r="G51" s="9">
+        <v>0.83485926131557564</v>
+      </c>
+      <c r="H51" s="9">
+        <v>-7.5049920562002631E-2</v>
+      </c>
+      <c r="I51" s="9">
+        <v>0.36807434197711481</v>
+      </c>
+      <c r="J51" s="9">
+        <v>0.32235689490994418</v>
+      </c>
+      <c r="K51" s="9">
+        <v>-0.26798559109529424</v>
+      </c>
+      <c r="L51" s="9">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A52" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="B52" s="9">
+        <v>0.75812859202938665</v>
+      </c>
+      <c r="C52" s="9">
+        <v>2.2894283818560068E-2</v>
+      </c>
+      <c r="D52" s="9">
+        <v>0.64361606345869171</v>
+      </c>
+      <c r="E52" s="9">
+        <v>0.88988235697406459</v>
+      </c>
+      <c r="F52" s="9">
+        <v>0.7525390276734838</v>
+      </c>
+      <c r="G52" s="9">
+        <v>0.83485926131557564</v>
+      </c>
+      <c r="H52" s="9">
+        <v>-7.5049920562002631E-2</v>
+      </c>
+      <c r="I52" s="9">
+        <v>0.36807434197711481</v>
+      </c>
+      <c r="J52" s="9">
+        <v>0.32235689490994418</v>
+      </c>
+      <c r="K52" s="9">
+        <v>-0.26798559109529424</v>
+      </c>
+      <c r="L52" s="9">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A53" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B53" s="9">
+        <v>0.77290972674060299</v>
+      </c>
+      <c r="C53" s="9">
+        <v>-0.57463744375341264</v>
+      </c>
+      <c r="D53" s="9">
+        <v>0.65988570056503359</v>
+      </c>
+      <c r="E53" s="9">
+        <v>0.89133259338526638</v>
+      </c>
+      <c r="F53" s="9">
+        <v>0.79228051745805061</v>
+      </c>
+      <c r="G53" s="9">
+        <v>0.79594498610437314</v>
+      </c>
+      <c r="H53" s="9">
+        <v>-0.37165937093573492</v>
+      </c>
+      <c r="I53" s="9">
+        <v>-0.33602683282219598</v>
+      </c>
+      <c r="J53" s="9">
+        <v>-8.226343472344666E-2</v>
+      </c>
+      <c r="K53" s="9">
+        <v>-0.58440263585059204</v>
+      </c>
+      <c r="L53" s="9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A54" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B54" s="9">
+        <v>0.77290972674060299</v>
+      </c>
+      <c r="C54" s="9">
+        <v>-0.57463744375341264</v>
+      </c>
+      <c r="D54" s="9">
+        <v>0.65988570056503359</v>
+      </c>
+      <c r="E54" s="9">
+        <v>0.89133259338526638</v>
+      </c>
+      <c r="F54" s="9">
+        <v>0.79228051745805061</v>
+      </c>
+      <c r="G54" s="9">
+        <v>0.79594498610437314</v>
+      </c>
+      <c r="H54" s="9">
+        <v>-0.37165937093573492</v>
+      </c>
+      <c r="I54" s="9">
+        <v>-0.33602683282219598</v>
+      </c>
+      <c r="J54" s="9">
+        <v>-8.226343472344666E-2</v>
+      </c>
+      <c r="K54" s="9">
+        <v>-0.58440263585059204</v>
+      </c>
+      <c r="L54" s="9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A55" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="B55" s="9">
+        <v>0.80931506626641969</v>
+      </c>
+      <c r="C55" s="9">
+        <v>-0.64915569865115053</v>
+      </c>
+      <c r="D55" s="9">
+        <v>0.75813851603485183</v>
+      </c>
+      <c r="E55" s="9">
+        <v>0.90650875160174349</v>
+      </c>
+      <c r="F55" s="9">
+        <v>0.8322243475299923</v>
+      </c>
+      <c r="G55" s="9">
+        <v>0.80944090108791833</v>
+      </c>
+      <c r="H55" s="9">
+        <v>-0.809589803684994</v>
+      </c>
+      <c r="I55" s="9">
+        <v>-0.4443799481502933</v>
+      </c>
+      <c r="J55" s="9">
+        <v>-1.5470004649048352E-2</v>
+      </c>
+      <c r="K55" s="9">
+        <v>-1.0184116845780429</v>
+      </c>
+      <c r="L55" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A56" s="8">
+        <v>5</v>
+      </c>
+      <c r="B56" s="9">
+        <v>0.73650438721478639</v>
+      </c>
+      <c r="C56" s="9">
+        <v>-0.50011918885567475</v>
+      </c>
+      <c r="D56" s="9">
+        <v>0.56163288509521536</v>
+      </c>
+      <c r="E56" s="9">
+        <v>0.87615643516878927</v>
+      </c>
+      <c r="F56" s="9">
+        <v>0.75233668738610904</v>
+      </c>
+      <c r="G56" s="9">
+        <v>0.78244907112082795</v>
+      </c>
+      <c r="H56" s="9">
+        <v>6.627106181352431E-2</v>
+      </c>
+      <c r="I56" s="9">
+        <v>-0.22767371749409857</v>
+      </c>
+      <c r="J56" s="9">
+        <v>-0.14905686479784497</v>
+      </c>
+      <c r="K56" s="9">
+        <v>-0.15039358712314113</v>
+      </c>
+      <c r="L56" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A57" s="3">
+        <v>4</v>
+      </c>
+      <c r="B57" s="9">
+        <v>0.75718351490092817</v>
+      </c>
+      <c r="C57" s="9">
+        <v>9.0357583941765449E-2</v>
+      </c>
+      <c r="D57" s="9">
+        <v>0.68237250738338795</v>
+      </c>
+      <c r="E57" s="9">
+        <v>0.75559966964583858</v>
+      </c>
+      <c r="F57" s="9">
+        <v>0.7691136920645919</v>
+      </c>
+      <c r="G57" s="9">
+        <v>0.74813842536074693</v>
+      </c>
+      <c r="H57" s="9">
+        <v>0.1345855381242079</v>
+      </c>
+      <c r="I57" s="9">
+        <v>8.8923566883683441E-2</v>
+      </c>
+      <c r="J57" s="9">
+        <v>0.3307414800923682</v>
+      </c>
+      <c r="K57" s="9">
+        <v>-0.15751719749678442</v>
+      </c>
+      <c r="L57" s="9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A58" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B58" s="9">
+        <v>0.75006921883984434</v>
+      </c>
+      <c r="C58" s="9">
+        <v>8.5252735780993461E-2</v>
+      </c>
+      <c r="D58" s="9">
+        <v>0.65459800415176828</v>
+      </c>
+      <c r="E58" s="9">
+        <v>0.75646033846208527</v>
+      </c>
+      <c r="F58" s="9">
+        <v>0.76634003439806053</v>
+      </c>
+      <c r="G58" s="9">
+        <v>0.73693717965629801</v>
+      </c>
+      <c r="H58" s="9">
+        <v>6.087008648466289E-2</v>
+      </c>
+      <c r="I58" s="9">
+        <v>8.8817569045262626E-2</v>
+      </c>
+      <c r="J58" s="9">
+        <v>0.30537556650815739</v>
+      </c>
+      <c r="K58" s="9">
+        <v>-5.0729734535457448E-2</v>
+      </c>
+      <c r="L58" s="9">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A59" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B59" s="9">
+        <v>0.75006921883984434</v>
+      </c>
+      <c r="C59" s="9">
+        <v>8.5252735780993461E-2</v>
+      </c>
+      <c r="D59" s="9">
+        <v>0.65459800415176828</v>
+      </c>
+      <c r="E59" s="9">
+        <v>0.75646033846208527</v>
+      </c>
+      <c r="F59" s="9">
+        <v>0.76634003439806053</v>
+      </c>
+      <c r="G59" s="9">
+        <v>0.73693717965629801</v>
+      </c>
+      <c r="H59" s="9">
+        <v>6.087008648466289E-2</v>
+      </c>
+      <c r="I59" s="9">
+        <v>8.8817569045262626E-2</v>
+      </c>
+      <c r="J59" s="9">
+        <v>0.30537556650815739</v>
+      </c>
+      <c r="K59" s="9">
+        <v>-5.0729734535457448E-2</v>
+      </c>
+      <c r="L59" s="9">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A60" s="8">
+        <v>3</v>
+      </c>
+      <c r="B60" s="9">
+        <v>0.77524258853677475</v>
+      </c>
+      <c r="C60" s="9">
+        <v>3.7976877322300019E-2</v>
+      </c>
+      <c r="D60" s="9">
+        <v>0.77304646220539042</v>
+      </c>
+      <c r="E60" s="9">
+        <v>0.83177234289534863</v>
+      </c>
+      <c r="F60" s="9">
+        <v>0.74282838012189456</v>
+      </c>
+      <c r="G60" s="9">
+        <v>0.75810211585266796</v>
+      </c>
+      <c r="H60" s="9">
+        <v>-9.7437493651897841E-2</v>
+      </c>
+      <c r="I60" s="9">
+        <v>0.3747397838373574</v>
+      </c>
+      <c r="J60" s="9">
+        <v>0.16805161558230722</v>
+      </c>
+      <c r="K60" s="9">
+        <v>-8.4463535577716645E-2</v>
+      </c>
+      <c r="L60" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A61" s="8">
+        <v>5</v>
+      </c>
+      <c r="B61" s="9">
+        <v>0.74512525706482646</v>
+      </c>
+      <c r="C61" s="9">
+        <v>0.16261700879737989</v>
+      </c>
+      <c r="D61" s="9">
+        <v>0.67087482805852294</v>
+      </c>
+      <c r="E61" s="9">
+        <v>0.72737613112787558</v>
+      </c>
+      <c r="F61" s="9">
+        <v>0.74416452627284846</v>
+      </c>
+      <c r="G61" s="9">
+        <v>0.72533037757646479</v>
+      </c>
+      <c r="H61" s="9">
+        <v>0.19510051965839367</v>
+      </c>
+      <c r="I61" s="9">
+        <v>0.19404735033338219</v>
+      </c>
+      <c r="J61" s="9">
+        <v>0.32301046130768984</v>
+      </c>
+      <c r="K61" s="9">
+        <v>-5.7590260174745785E-2</v>
+      </c>
+      <c r="L61" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A62" s="8">
+        <v>2</v>
+      </c>
+      <c r="B62" s="9">
+        <v>0.76411536818040482</v>
+      </c>
+      <c r="C62" s="9">
+        <v>0.11354503967076053</v>
+      </c>
+      <c r="D62" s="9">
+        <v>0.58110006489703736</v>
+      </c>
+      <c r="E62" s="9">
+        <v>0.84297227909773664</v>
+      </c>
+      <c r="F62" s="9">
+        <v>0.81321685060025128</v>
+      </c>
+      <c r="G62" s="9">
+        <v>0.83941846687770683</v>
+      </c>
+      <c r="H62" s="9">
+        <v>-3.2580287222685356E-2</v>
+      </c>
+      <c r="I62" s="9">
+        <v>-0.14749592269400455</v>
+      </c>
+      <c r="J62" s="9">
+        <v>0.58746193494830778</v>
+      </c>
+      <c r="K62" s="9">
+        <v>0.20230466481130646</v>
+      </c>
+      <c r="L62" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A63" s="8">
+        <v>8</v>
+      </c>
+      <c r="B63" s="9">
+        <v>0.7157936615773709</v>
+      </c>
+      <c r="C63" s="9">
+        <v>2.6872017333533376E-2</v>
+      </c>
+      <c r="D63" s="9">
+        <v>0.59337066144612249</v>
+      </c>
+      <c r="E63" s="9">
+        <v>0.62372060072738023</v>
+      </c>
+      <c r="F63" s="9">
+        <v>0.76515038059724771</v>
+      </c>
+      <c r="G63" s="9">
+        <v>0.62489775831835237</v>
+      </c>
+      <c r="H63" s="9">
+        <v>0.1783976071548411</v>
+      </c>
+      <c r="I63" s="9">
+        <v>-6.6020935295684549E-2</v>
+      </c>
+      <c r="J63" s="9">
+        <v>0.14297825419432486</v>
+      </c>
+      <c r="K63" s="9">
+        <v>-0.26316980720067379</v>
+      </c>
+      <c r="L63" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A64" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B64" s="9">
+        <v>0.79986929126743034</v>
+      </c>
+      <c r="C64" s="9">
+        <v>0.12098667290639745</v>
+      </c>
+      <c r="D64" s="9">
+        <v>0.84901952677310621</v>
+      </c>
+      <c r="E64" s="9">
+        <v>0.75043565674835844</v>
+      </c>
+      <c r="F64" s="9">
+        <v>0.78575563806377979</v>
+      </c>
+      <c r="G64" s="9">
+        <v>0.8153458995874403</v>
+      </c>
+      <c r="H64" s="9">
+        <v>0.57687824796147791</v>
+      </c>
+      <c r="I64" s="9">
+        <v>8.955955391420839E-2</v>
+      </c>
+      <c r="J64" s="9">
+        <v>0.48293696159763283</v>
+      </c>
+      <c r="K64" s="9">
+        <v>-0.79824197526474627</v>
+      </c>
+      <c r="L64" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A65" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B65" s="9">
+        <v>0.79986929126743034</v>
+      </c>
+      <c r="C65" s="9">
+        <v>0.12098667290639745</v>
+      </c>
+      <c r="D65" s="9">
+        <v>0.84901952677310621</v>
+      </c>
+      <c r="E65" s="9">
+        <v>0.75043565674835844</v>
+      </c>
+      <c r="F65" s="9">
+        <v>0.78575563806377979</v>
+      </c>
+      <c r="G65" s="9">
+        <v>0.8153458995874403</v>
+      </c>
+      <c r="H65" s="9">
+        <v>0.57687824796147791</v>
+      </c>
+      <c r="I65" s="9">
+        <v>8.955955391420839E-2</v>
+      </c>
+      <c r="J65" s="9">
+        <v>0.48293696159763283</v>
+      </c>
+      <c r="K65" s="9">
+        <v>-0.79824197526474627</v>
+      </c>
+      <c r="L65" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A66" s="8">
+        <v>2</v>
+      </c>
+      <c r="B66" s="9">
+        <v>0.79986929126743034</v>
+      </c>
+      <c r="C66" s="9">
+        <v>0.12098667290639745</v>
+      </c>
+      <c r="D66" s="9">
+        <v>0.84901952677310621</v>
+      </c>
+      <c r="E66" s="9">
+        <v>0.75043565674835844</v>
+      </c>
+      <c r="F66" s="9">
+        <v>0.78575563806377979</v>
+      </c>
+      <c r="G66" s="9">
+        <v>0.8153458995874403</v>
+      </c>
+      <c r="H66" s="9">
+        <v>0.57687824796147791</v>
+      </c>
+      <c r="I66" s="9">
+        <v>8.955955391420839E-2</v>
+      </c>
+      <c r="J66" s="9">
+        <v>0.48293696159763283</v>
+      </c>
+      <c r="K66" s="9">
+        <v>-0.79824197526474627</v>
+      </c>
+      <c r="L66" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A67" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="B67" s="9">
+        <v>0.6000573113155343</v>
+      </c>
+      <c r="C67" s="9">
+        <v>-7.3687783208431154E-2</v>
+      </c>
+      <c r="D67" s="9">
+        <v>0.43954667678608356</v>
+      </c>
+      <c r="E67" s="9">
+        <v>0.63567473010720454</v>
+      </c>
+      <c r="F67" s="9">
+        <v>0.52406824138797692</v>
+      </c>
+      <c r="G67" s="9">
+        <v>0.70166207335070352</v>
+      </c>
+      <c r="H67" s="9">
+        <v>-0.10978850568749605</v>
+      </c>
+      <c r="I67" s="9">
+        <v>7.5616782188577758E-2</v>
+      </c>
+      <c r="J67" s="9">
+        <v>0.14440727588182414</v>
+      </c>
+      <c r="K67" s="9">
+        <v>-0.21806963769529558</v>
+      </c>
+      <c r="L67" s="9">
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/logs/massive_topology_search/massive_topology_search.xlsx
+++ b/logs/massive_topology_search/massive_topology_search.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgep-my.sharepoint.com/personal/uxue_ballarin_alumni_mondragon_edu/Documents/Semestre 8-Erasmus/Simula/ship_qnn/logs/massive_topology_search/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="219" documentId="11_AD4D2F04E46CFB4ACB3E20D455D6CCDA693EDF1F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EC38DEB0-993A-4CB1-89CD-BFFD4B9E3197}"/>
+  <xr:revisionPtr revIDLastSave="232" documentId="11_AD4D2F04E46CFB4ACB3E20D455D6CCDA693EDF1F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{006836B1-E337-4C38-8D4B-52908CCEF2AD}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2370" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2446" uniqueCount="272">
   <si>
     <t>date</t>
   </si>
@@ -831,6 +831,21 @@
   <si>
     <t>03-03_07-18-06_multihead_spsa_compact_f5_w5_h5_effsu2_lin_r2.pkl</t>
   </si>
+  <si>
+    <t>03-03_13-50-32_multihead_spsa_compact_f5_w5_h5_effsu2_lin_r2.pkl</t>
+  </si>
+  <si>
+    <t>03-03_21-45-50_multihead_spsa_compact_f5_w5_h5_effsu2_lin_r3.pkl</t>
+  </si>
+  <si>
+    <t>[{'features': ['wv', 'rarad'], 'output_dim': 1, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1]}, {'features': ['sv', 'rarad'], 'output_dim': 1, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1]}, {'features': ['yr', 'rarad'], 'output_dim': 1, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1]}]</t>
+  </si>
+  <si>
+    <t>03-04_05-20-44_multihead_spsa_compact_f5_w5_h5_effsu2_lin_r3.pkl</t>
+  </si>
+  <si>
+    <t>03-04_13-32-28_multihead_spsa_compact_f5_w5_h5_effsu2_lin_r3.pkl</t>
+  </si>
 </sst>
 </file>
 
@@ -973,13 +988,13 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Uxue Ballarin" refreshedDate="46084.590416203704" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="116" xr:uid="{74ED0919-17AD-467A-B408-AADD8AC7697B}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Uxue Ballarin" refreshedDate="46086.568596759258" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="120" xr:uid="{74ED0919-17AD-467A-B408-AADD8AC7697B}">
   <cacheSource type="worksheet">
     <worksheetSource name="Tabla1"/>
   </cacheSource>
   <cacheFields count="75">
     <cacheField name="date" numFmtId="164">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-02-17T13:56:47" maxDate="2026-03-03T07:18:06"/>
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-02-17T13:56:47" maxDate="2026-03-04T13:32:28"/>
     </cacheField>
     <cacheField name="model_id" numFmtId="0">
       <sharedItems/>
@@ -1190,25 +1205,25 @@
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-1.9508774442032091" maxValue="0.759048124160834"/>
     </cacheField>
     <cacheField name="Yaw Rate Step MSE" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="3.7365891845960029E-2" maxValue="0.2321027489969984"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="2.8422902017742321E-2" maxValue="0.2321027489969984"/>
     </cacheField>
     <cacheField name="Yaw Rate Step R2" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="6.8180877318678279E-2" maxValue="0.84998776314123747"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="6.8180877318678279E-2" maxValue="0.88589103861681395"/>
     </cacheField>
     <cacheField name="Yaw Rate Local MSE" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="3.7365891845960029E-2" maxValue="0.2321027489969984"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="2.8422902017742321E-2" maxValue="0.2321027489969984"/>
     </cacheField>
     <cacheField name="Yaw Rate Global open MSE" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="3.7365891845960029E-2" maxValue="0.2321027489969984"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="2.8422902017742321E-2" maxValue="0.2321027489969984"/>
     </cacheField>
     <cacheField name="Yaw Rate Global open R2" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="6.8180877318678279E-2" maxValue="0.84998776314123747"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="6.8180877318678279E-2" maxValue="0.88589103861681395"/>
     </cacheField>
     <cacheField name="Yaw Rate Global closed MSE" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="7.6995679521455779E-2" maxValue="0.47455718790751072"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="7.2238055104180895E-2" maxValue="0.80870605181118038"/>
     </cacheField>
     <cacheField name="Yaw Rate Global closed R2" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-0.90519700610616405" maxValue="0.69088670060145219"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-2.2466990027572451" maxValue="0.70998705779114513"/>
     </cacheField>
     <cacheField name="Yaw Angle Step MSE" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="20.09951675360124" maxValue="205.0599827949176"/>
@@ -1241,7 +1256,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="116">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="120">
   <r>
     <d v="2026-02-22T09:16:08"/>
     <s v="02-22_09-16-08_multihead_spsa_compact_f5_w5_h5_effsu2_effsu2_realamplitudes_lin_r1_3_1.pkl"/>
@@ -10174,12 +10189,320 @@
     <n v="350.38007034092919"/>
     <n v="2.75655493797955E-3"/>
   </r>
+  <r>
+    <d v="2026-03-03T13:50:32"/>
+    <s v="03-03_13-50-32_multihead_spsa_compact_f5_w5_h5_effsu2_lin_r2.pkl"/>
+    <x v="2"/>
+    <s v="Final (Last Iteration)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <s v="[['wv', 'rarad'], ['sv', 'rarad'], ['yr', 'rarad'], ['ya', 'yr']]"/>
+    <s v="['Surge Velocity', 'Sway Velocity', 'Yaw Rate', 'Yaw Angle']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="motion"/>
+    <s v="true"/>
+    <s v="false"/>
+    <s v="false"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['wv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1]}, {'features': ['sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1]}, {'features': ['yr', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1]}]"/>
+    <x v="1"/>
+    <s v="compact"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="5"/>
+    <s v="[0, 1, -1]"/>
+    <s v="false"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="512"/>
+    <s v="[0.05, 0.001]"/>
+    <n v="0.1"/>
+    <n v="200"/>
+    <n v="80"/>
+    <n v="120"/>
+    <n v="8.1052205736362792E-2"/>
+    <n v="14.22849995965816"/>
+    <n v="0.77746501612623886"/>
+    <n v="-0.3388975246539947"/>
+    <n v="15.862007738386041"/>
+    <n v="0.78442861878483838"/>
+    <n v="15.862007738386041"/>
+    <n v="15.862007738386041"/>
+    <n v="0.78442861878483838"/>
+    <n v="121.20113997537661"/>
+    <n v="-8.1210961546633792E-2"/>
+    <n v="0.8"/>
+    <s v="identity"/>
+    <n v="2.8301968546252301E-2"/>
+    <n v="0.79449111508239822"/>
+    <n v="2.8301968546252301E-2"/>
+    <n v="2.8301968546252301E-2"/>
+    <n v="0.79449111508239822"/>
+    <n v="8.7375441623793029E-2"/>
+    <n v="0.36554132098820119"/>
+    <n v="8.5353100083140371E-2"/>
+    <n v="0.70426973809866467"/>
+    <n v="8.5353100083140371E-2"/>
+    <n v="8.5353100083140371E-2"/>
+    <n v="0.70426973809866467"/>
+    <n v="0.25345929775810411"/>
+    <n v="0.12181766761464741"/>
+    <n v="4.5063036259409023E-2"/>
+    <n v="0.81908616294267955"/>
+    <n v="4.5063036259409023E-2"/>
+    <n v="4.5063036259409023E-2"/>
+    <n v="0.81908616294267955"/>
+    <n v="0.35727610205897897"/>
+    <n v="-0.43435054265516498"/>
+    <n v="63.289312848655371"/>
+    <n v="0.81986745901560942"/>
+    <n v="63.289312848655371"/>
+    <n v="63.289312848655371"/>
+    <n v="0.81986745901560942"/>
+    <n v="484.10644906006519"/>
+    <n v="-0.37785229213422711"/>
+  </r>
+  <r>
+    <d v="2026-03-03T21:45:50"/>
+    <s v="03-03_21-45-50_multihead_spsa_compact_f5_w5_h5_effsu2_lin_r3.pkl"/>
+    <x v="1"/>
+    <s v="Final (Last Iteration)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <s v="[['wv', 'rarad'], ['sv', 'rarad'], ['yr', 'rarad'], ['ya', 'yr']]"/>
+    <s v="['Surge Velocity', 'Sway Velocity', 'Yaw Rate', 'Yaw Angle']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="motion"/>
+    <s v="true"/>
+    <s v="false"/>
+    <s v="false"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['wv', 'rarad'], 'output_dim': 1, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1]}, {'features': ['sv', 'rarad'], 'output_dim': 1, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1]}, {'features': ['yr', 'rarad'], 'output_dim': 1, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1]}]"/>
+    <x v="1"/>
+    <s v="compact"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="[0, 1, -1]"/>
+    <s v="false"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="512"/>
+    <s v="[0.05, 0.001]"/>
+    <n v="0.1"/>
+    <n v="240"/>
+    <n v="120"/>
+    <n v="120"/>
+    <n v="0.106008494446163"/>
+    <n v="33.838931129888543"/>
+    <n v="0.66621549860948348"/>
+    <n v="5.3792376803492359E-2"/>
+    <n v="35.082387455197612"/>
+    <n v="0.68480606442805336"/>
+    <n v="35.082387455197612"/>
+    <n v="35.082387455197612"/>
+    <n v="0.68480606442805336"/>
+    <n v="114.439596298278"/>
+    <n v="-0.61720424299988363"/>
+    <n v="0.8"/>
+    <s v="identity"/>
+    <n v="3.8320129051456348E-2"/>
+    <n v="0.72174631674847922"/>
+    <n v="3.8320129051456348E-2"/>
+    <n v="3.8320129051456348E-2"/>
+    <n v="0.72174631674847922"/>
+    <n v="0.1118626898969249"/>
+    <n v="0.1877322375285925"/>
+    <n v="8.0002391425953584E-2"/>
+    <n v="0.72280880078070253"/>
+    <n v="8.0002391425953584E-2"/>
+    <n v="8.0002391425953584E-2"/>
+    <n v="0.72280880078070253"/>
+    <n v="0.3205165810134426"/>
+    <n v="-0.1105214966357024"/>
+    <n v="7.6340327560767682E-2"/>
+    <n v="0.69351773143454143"/>
+    <n v="7.6340327560767682E-2"/>
+    <n v="7.6340327560767682E-2"/>
+    <n v="0.69351773143454143"/>
+    <n v="0.80870605181118038"/>
+    <n v="-2.2466990027572451"/>
+    <n v="140.13488697275301"/>
+    <n v="0.6011514087484886"/>
+    <n v="140.13488697275301"/>
+    <n v="140.13488697275301"/>
+    <n v="0.6011514087484886"/>
+    <n v="456.51729987039209"/>
+    <n v="-0.29932871013520312"/>
+  </r>
+  <r>
+    <d v="2026-03-04T05:20:44"/>
+    <s v="03-04_05-20-44_multihead_spsa_compact_f5_w5_h5_effsu2_lin_r3.pkl"/>
+    <x v="0"/>
+    <s v="Final (Last Iteration)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <s v="[['wv', 'rarad'], ['sv', 'rarad'], ['yr', 'rarad'], ['ya', 'yr']]"/>
+    <s v="['Surge Velocity', 'Sway Velocity', 'Yaw Rate', 'Yaw Angle']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="motion"/>
+    <s v="true"/>
+    <s v="false"/>
+    <s v="false"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['wv', 'rarad'], 'output_dim': 1, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1]}, {'features': ['sv', 'rarad'], 'output_dim': 1, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1]}, {'features': ['yr', 'rarad'], 'output_dim': 1, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1]}]"/>
+    <x v="1"/>
+    <s v="compact"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="[0, 1, -1]"/>
+    <s v="false"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="512"/>
+    <s v="[0.05, 0.001]"/>
+    <n v="0.1"/>
+    <n v="240"/>
+    <n v="120"/>
+    <n v="120"/>
+    <n v="8.6326044526204557E-2"/>
+    <n v="14.146799722733681"/>
+    <n v="0.72262530601792541"/>
+    <n v="7.581434566459494E-2"/>
+    <n v="25.026228384313718"/>
+    <n v="0.73291761438861314"/>
+    <n v="25.026228384313718"/>
+    <n v="25.026228384313718"/>
+    <n v="0.73291761438861314"/>
+    <n v="120.5007286916416"/>
+    <n v="4.6809187335239033E-2"/>
+    <n v="0.8"/>
+    <s v="identity"/>
+    <n v="4.3604468438270379E-2"/>
+    <n v="0.68337518036849354"/>
+    <n v="4.3604468438270379E-2"/>
+    <n v="4.3604468438270379E-2"/>
+    <n v="0.68337518036849354"/>
+    <n v="0.15250768795884201"/>
+    <n v="-0.10740300069810479"/>
+    <n v="0.10193258953106291"/>
+    <n v="0.64682534824230808"/>
+    <n v="0.10193258953106291"/>
+    <n v="0.10193258953106291"/>
+    <n v="0.64682534824230808"/>
+    <n v="0.30160015428650921"/>
+    <n v="-4.4980118235335993E-2"/>
+    <n v="2.8422902017742321E-2"/>
+    <n v="0.88589103861681395"/>
+    <n v="2.8422902017742321E-2"/>
+    <n v="2.8422902017742321E-2"/>
+    <n v="0.88589103861681395"/>
+    <n v="7.2238055104180895E-2"/>
+    <n v="0.70998705779114513"/>
+    <n v="99.930953577267957"/>
+    <n v="0.7155788903268383"/>
+    <n v="99.930953577267957"/>
+    <n v="99.930953577267957"/>
+    <n v="0.7155788903268383"/>
+    <n v="481.47656886921482"/>
+    <n v="-0.37036718951674041"/>
+  </r>
+  <r>
+    <d v="2026-03-04T13:32:28"/>
+    <s v="03-04_13-32-28_multihead_spsa_compact_f5_w5_h5_effsu2_lin_r3.pkl"/>
+    <x v="2"/>
+    <s v="Best (Lowest Val Loss)"/>
+    <s v="data/reduce_row_number_absolutes"/>
+    <n v="16590"/>
+    <n v="4.5"/>
+    <s v="[['wv', 'rarad'], ['sv', 'rarad'], ['yr', 'rarad'], ['ya', 'yr']]"/>
+    <s v="['Surge Velocity', 'Sway Velocity', 'Yaw Rate', 'Yaw Angle']"/>
+    <n v="5"/>
+    <n v="5"/>
+    <s v="motion"/>
+    <s v="true"/>
+    <s v="false"/>
+    <s v="false"/>
+    <s v="multihead"/>
+    <s v="[{'features': ['wv', 'rarad'], 'output_dim': 1, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1]}, {'features': ['sv', 'rarad'], 'output_dim': 1, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1]}, {'features': ['yr', 'rarad'], 'output_dim': 1, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1]}]"/>
+    <x v="1"/>
+    <s v="compact"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="2"/>
+    <s v="[0, 1, -1]"/>
+    <s v="false"/>
+    <s v="spsa"/>
+    <n v="4000"/>
+    <n v="4000"/>
+    <m/>
+    <n v="512"/>
+    <s v="[0.05, 0.001]"/>
+    <n v="0.1"/>
+    <n v="240"/>
+    <n v="120"/>
+    <n v="120"/>
+    <n v="0.10290996228240711"/>
+    <n v="26.931966029656579"/>
+    <n v="0.68443970848741087"/>
+    <n v="8.6293657915927025E-2"/>
+    <n v="28.812146797667111"/>
+    <n v="0.67734594458609443"/>
+    <n v="28.812146797667111"/>
+    <n v="28.812146797667111"/>
+    <n v="0.67734594458609443"/>
+    <n v="112.7319246644321"/>
+    <n v="1.2595647239736749E-2"/>
+    <n v="0.8"/>
+    <s v="identity"/>
+    <n v="3.4941550989431677E-2"/>
+    <n v="0.74627916184012233"/>
+    <n v="3.4941550989431677E-2"/>
+    <n v="3.4941550989431677E-2"/>
+    <n v="0.74627916184012233"/>
+    <n v="0.1223043357798201"/>
+    <n v="0.1119123878036022"/>
+    <n v="0.1088797158354875"/>
+    <n v="0.62275503937868226"/>
+    <n v="0.1088797158354875"/>
+    <n v="0.1088797158354875"/>
+    <n v="0.62275503937868226"/>
+    <n v="0.26707186033242392"/>
+    <n v="7.465304569311626E-2"/>
+    <n v="8.2765557334563297E-2"/>
+    <n v="0.66772246620516862"/>
+    <n v="8.2765557334563297E-2"/>
+    <n v="8.2765557334563297E-2"/>
+    <n v="0.66772246620516862"/>
+    <n v="0.21283797098879029"/>
+    <n v="0.14552286753565319"/>
+    <n v="115.0220003665092"/>
+    <n v="0.6726271109204025"/>
+    <n v="115.0220003665092"/>
+    <n v="115.0220003665092"/>
+    <n v="0.6726271109204025"/>
+    <n v="450.32548449062648"/>
+    <n v="-0.28170571207342049"/>
+  </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2D21AEEF-8491-4048-847C-B48B541C6815}" name="TablaDinámica1" cacheId="24" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A2:L67" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <location ref="A2:L68" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="75">
     <pivotField numFmtId="164" showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
@@ -10307,7 +10630,7 @@
     <field x="21"/>
     <field x="2"/>
   </rowFields>
-  <rowItems count="65">
+  <rowItems count="66">
     <i>
       <x/>
     </i>
@@ -10498,6 +10821,9 @@
       <x v="1"/>
     </i>
     <i r="3">
+      <x/>
+    </i>
+    <i r="3">
       <x v="6"/>
     </i>
     <i t="grand">
@@ -10568,8 +10894,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3111F1FF-B489-4444-B033-EAAA6A990F8A}" name="Tabla1" displayName="Tabla1" ref="A1:BW117" totalsRowShown="0" headerRowDxfId="3" headerRowBorderDxfId="2" tableBorderDxfId="1">
-  <autoFilter ref="A1:BW117" xr:uid="{3111F1FF-B489-4444-B033-EAAA6A990F8A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3111F1FF-B489-4444-B033-EAAA6A990F8A}" name="Tabla1" displayName="Tabla1" ref="A1:BW121" totalsRowShown="0" headerRowDxfId="3" headerRowBorderDxfId="2" tableBorderDxfId="1">
+  <autoFilter ref="A1:BW121" xr:uid="{3111F1FF-B489-4444-B033-EAAA6A990F8A}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:BW100">
     <sortCondition descending="1" ref="AK1:AK100"/>
   </sortState>
@@ -10917,7 +11243,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BW117"/>
+  <dimension ref="A1:BW121"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:75" x14ac:dyDescent="0.3">
@@ -37093,6 +37419,902 @@
       </c>
       <c r="BW117">
         <v>2.75655493797955E-3</v>
+      </c>
+    </row>
+    <row r="118" spans="1:75" x14ac:dyDescent="0.3">
+      <c r="A118" s="2">
+        <v>46084.57675925926</v>
+      </c>
+      <c r="B118" t="s">
+        <v>267</v>
+      </c>
+      <c r="C118">
+        <v>3</v>
+      </c>
+      <c r="D118" t="s">
+        <v>76</v>
+      </c>
+      <c r="E118" t="s">
+        <v>77</v>
+      </c>
+      <c r="F118">
+        <v>16590</v>
+      </c>
+      <c r="G118">
+        <v>4.5</v>
+      </c>
+      <c r="H118" t="s">
+        <v>171</v>
+      </c>
+      <c r="I118" t="s">
+        <v>79</v>
+      </c>
+      <c r="J118">
+        <v>5</v>
+      </c>
+      <c r="K118">
+        <v>5</v>
+      </c>
+      <c r="L118" t="s">
+        <v>80</v>
+      </c>
+      <c r="M118" t="s">
+        <v>81</v>
+      </c>
+      <c r="N118" t="s">
+        <v>82</v>
+      </c>
+      <c r="O118" t="s">
+        <v>82</v>
+      </c>
+      <c r="P118" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q118" t="s">
+        <v>265</v>
+      </c>
+      <c r="R118">
+        <v>4</v>
+      </c>
+      <c r="S118" t="s">
+        <v>85</v>
+      </c>
+      <c r="T118" t="s">
+        <v>86</v>
+      </c>
+      <c r="U118" t="s">
+        <v>108</v>
+      </c>
+      <c r="V118">
+        <v>2</v>
+      </c>
+      <c r="W118" t="s">
+        <v>173</v>
+      </c>
+      <c r="X118" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y118" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z118">
+        <v>4000</v>
+      </c>
+      <c r="AA118">
+        <v>4000</v>
+      </c>
+      <c r="AC118">
+        <v>512</v>
+      </c>
+      <c r="AD118" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE118">
+        <v>0.1</v>
+      </c>
+      <c r="AF118">
+        <v>200</v>
+      </c>
+      <c r="AG118">
+        <v>80</v>
+      </c>
+      <c r="AH118">
+        <v>120</v>
+      </c>
+      <c r="AI118">
+        <v>8.1052205736362792E-2</v>
+      </c>
+      <c r="AJ118">
+        <v>14.22849995965816</v>
+      </c>
+      <c r="AK118">
+        <v>0.77746501612623886</v>
+      </c>
+      <c r="AL118">
+        <v>-0.3388975246539947</v>
+      </c>
+      <c r="AM118">
+        <v>15.862007738386041</v>
+      </c>
+      <c r="AN118">
+        <v>0.78442861878483838</v>
+      </c>
+      <c r="AO118">
+        <v>15.862007738386041</v>
+      </c>
+      <c r="AP118">
+        <v>15.862007738386041</v>
+      </c>
+      <c r="AQ118">
+        <v>0.78442861878483838</v>
+      </c>
+      <c r="AR118">
+        <v>121.20113997537661</v>
+      </c>
+      <c r="AS118">
+        <v>-8.1210961546633792E-2</v>
+      </c>
+      <c r="AT118">
+        <v>0.8</v>
+      </c>
+      <c r="AU118" t="s">
+        <v>91</v>
+      </c>
+      <c r="AV118">
+        <v>2.8301968546252301E-2</v>
+      </c>
+      <c r="AW118">
+        <v>0.79449111508239822</v>
+      </c>
+      <c r="AX118">
+        <v>2.8301968546252301E-2</v>
+      </c>
+      <c r="AY118">
+        <v>2.8301968546252301E-2</v>
+      </c>
+      <c r="AZ118">
+        <v>0.79449111508239822</v>
+      </c>
+      <c r="BA118">
+        <v>8.7375441623793029E-2</v>
+      </c>
+      <c r="BB118">
+        <v>0.36554132098820119</v>
+      </c>
+      <c r="BC118">
+        <v>8.5353100083140371E-2</v>
+      </c>
+      <c r="BD118">
+        <v>0.70426973809866467</v>
+      </c>
+      <c r="BE118">
+        <v>8.5353100083140371E-2</v>
+      </c>
+      <c r="BF118">
+        <v>8.5353100083140371E-2</v>
+      </c>
+      <c r="BG118">
+        <v>0.70426973809866467</v>
+      </c>
+      <c r="BH118">
+        <v>0.25345929775810411</v>
+      </c>
+      <c r="BI118">
+        <v>0.12181766761464741</v>
+      </c>
+      <c r="BJ118">
+        <v>4.5063036259409023E-2</v>
+      </c>
+      <c r="BK118">
+        <v>0.81908616294267955</v>
+      </c>
+      <c r="BL118">
+        <v>4.5063036259409023E-2</v>
+      </c>
+      <c r="BM118">
+        <v>4.5063036259409023E-2</v>
+      </c>
+      <c r="BN118">
+        <v>0.81908616294267955</v>
+      </c>
+      <c r="BO118">
+        <v>0.35727610205897897</v>
+      </c>
+      <c r="BP118">
+        <v>-0.43435054265516498</v>
+      </c>
+      <c r="BQ118">
+        <v>63.289312848655371</v>
+      </c>
+      <c r="BR118">
+        <v>0.81986745901560942</v>
+      </c>
+      <c r="BS118">
+        <v>63.289312848655371</v>
+      </c>
+      <c r="BT118">
+        <v>63.289312848655371</v>
+      </c>
+      <c r="BU118">
+        <v>0.81986745901560942</v>
+      </c>
+      <c r="BV118">
+        <v>484.10644906006519</v>
+      </c>
+      <c r="BW118">
+        <v>-0.37785229213422711</v>
+      </c>
+    </row>
+    <row r="119" spans="1:75" x14ac:dyDescent="0.3">
+      <c r="A119" s="2">
+        <v>46084.906828703701</v>
+      </c>
+      <c r="B119" t="s">
+        <v>268</v>
+      </c>
+      <c r="C119">
+        <v>1</v>
+      </c>
+      <c r="D119" t="s">
+        <v>76</v>
+      </c>
+      <c r="E119" t="s">
+        <v>77</v>
+      </c>
+      <c r="F119">
+        <v>16590</v>
+      </c>
+      <c r="G119">
+        <v>4.5</v>
+      </c>
+      <c r="H119" t="s">
+        <v>171</v>
+      </c>
+      <c r="I119" t="s">
+        <v>79</v>
+      </c>
+      <c r="J119">
+        <v>5</v>
+      </c>
+      <c r="K119">
+        <v>5</v>
+      </c>
+      <c r="L119" t="s">
+        <v>80</v>
+      </c>
+      <c r="M119" t="s">
+        <v>81</v>
+      </c>
+      <c r="N119" t="s">
+        <v>82</v>
+      </c>
+      <c r="O119" t="s">
+        <v>82</v>
+      </c>
+      <c r="P119" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q119" t="s">
+        <v>269</v>
+      </c>
+      <c r="R119">
+        <v>4</v>
+      </c>
+      <c r="S119" t="s">
+        <v>85</v>
+      </c>
+      <c r="T119" t="s">
+        <v>86</v>
+      </c>
+      <c r="U119" t="s">
+        <v>108</v>
+      </c>
+      <c r="V119">
+        <v>3</v>
+      </c>
+      <c r="W119" t="s">
+        <v>173</v>
+      </c>
+      <c r="X119" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y119" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z119">
+        <v>4000</v>
+      </c>
+      <c r="AA119">
+        <v>4000</v>
+      </c>
+      <c r="AC119">
+        <v>512</v>
+      </c>
+      <c r="AD119" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE119">
+        <v>0.1</v>
+      </c>
+      <c r="AF119">
+        <v>240</v>
+      </c>
+      <c r="AG119">
+        <v>120</v>
+      </c>
+      <c r="AH119">
+        <v>120</v>
+      </c>
+      <c r="AI119">
+        <v>0.106008494446163</v>
+      </c>
+      <c r="AJ119">
+        <v>33.838931129888543</v>
+      </c>
+      <c r="AK119">
+        <v>0.66621549860948348</v>
+      </c>
+      <c r="AL119">
+        <v>5.3792376803492359E-2</v>
+      </c>
+      <c r="AM119">
+        <v>35.082387455197612</v>
+      </c>
+      <c r="AN119">
+        <v>0.68480606442805336</v>
+      </c>
+      <c r="AO119">
+        <v>35.082387455197612</v>
+      </c>
+      <c r="AP119">
+        <v>35.082387455197612</v>
+      </c>
+      <c r="AQ119">
+        <v>0.68480606442805336</v>
+      </c>
+      <c r="AR119">
+        <v>114.439596298278</v>
+      </c>
+      <c r="AS119">
+        <v>-0.61720424299988363</v>
+      </c>
+      <c r="AT119">
+        <v>0.8</v>
+      </c>
+      <c r="AU119" t="s">
+        <v>91</v>
+      </c>
+      <c r="AV119">
+        <v>3.8320129051456348E-2</v>
+      </c>
+      <c r="AW119">
+        <v>0.72174631674847922</v>
+      </c>
+      <c r="AX119">
+        <v>3.8320129051456348E-2</v>
+      </c>
+      <c r="AY119">
+        <v>3.8320129051456348E-2</v>
+      </c>
+      <c r="AZ119">
+        <v>0.72174631674847922</v>
+      </c>
+      <c r="BA119">
+        <v>0.1118626898969249</v>
+      </c>
+      <c r="BB119">
+        <v>0.1877322375285925</v>
+      </c>
+      <c r="BC119">
+        <v>8.0002391425953584E-2</v>
+      </c>
+      <c r="BD119">
+        <v>0.72280880078070253</v>
+      </c>
+      <c r="BE119">
+        <v>8.0002391425953584E-2</v>
+      </c>
+      <c r="BF119">
+        <v>8.0002391425953584E-2</v>
+      </c>
+      <c r="BG119">
+        <v>0.72280880078070253</v>
+      </c>
+      <c r="BH119">
+        <v>0.3205165810134426</v>
+      </c>
+      <c r="BI119">
+        <v>-0.1105214966357024</v>
+      </c>
+      <c r="BJ119">
+        <v>7.6340327560767682E-2</v>
+      </c>
+      <c r="BK119">
+        <v>0.69351773143454143</v>
+      </c>
+      <c r="BL119">
+        <v>7.6340327560767682E-2</v>
+      </c>
+      <c r="BM119">
+        <v>7.6340327560767682E-2</v>
+      </c>
+      <c r="BN119">
+        <v>0.69351773143454143</v>
+      </c>
+      <c r="BO119">
+        <v>0.80870605181118038</v>
+      </c>
+      <c r="BP119">
+        <v>-2.2466990027572451</v>
+      </c>
+      <c r="BQ119">
+        <v>140.13488697275301</v>
+      </c>
+      <c r="BR119">
+        <v>0.6011514087484886</v>
+      </c>
+      <c r="BS119">
+        <v>140.13488697275301</v>
+      </c>
+      <c r="BT119">
+        <v>140.13488697275301</v>
+      </c>
+      <c r="BU119">
+        <v>0.6011514087484886</v>
+      </c>
+      <c r="BV119">
+        <v>456.51729987039209</v>
+      </c>
+      <c r="BW119">
+        <v>-0.29932871013520312</v>
+      </c>
+    </row>
+    <row r="120" spans="1:75" x14ac:dyDescent="0.3">
+      <c r="A120" s="2">
+        <v>46085.222731481481</v>
+      </c>
+      <c r="B120" t="s">
+        <v>270</v>
+      </c>
+      <c r="C120">
+        <v>2</v>
+      </c>
+      <c r="D120" t="s">
+        <v>76</v>
+      </c>
+      <c r="E120" t="s">
+        <v>77</v>
+      </c>
+      <c r="F120">
+        <v>16590</v>
+      </c>
+      <c r="G120">
+        <v>4.5</v>
+      </c>
+      <c r="H120" t="s">
+        <v>171</v>
+      </c>
+      <c r="I120" t="s">
+        <v>79</v>
+      </c>
+      <c r="J120">
+        <v>5</v>
+      </c>
+      <c r="K120">
+        <v>5</v>
+      </c>
+      <c r="L120" t="s">
+        <v>80</v>
+      </c>
+      <c r="M120" t="s">
+        <v>81</v>
+      </c>
+      <c r="N120" t="s">
+        <v>82</v>
+      </c>
+      <c r="O120" t="s">
+        <v>82</v>
+      </c>
+      <c r="P120" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q120" t="s">
+        <v>269</v>
+      </c>
+      <c r="R120">
+        <v>4</v>
+      </c>
+      <c r="S120" t="s">
+        <v>85</v>
+      </c>
+      <c r="T120" t="s">
+        <v>86</v>
+      </c>
+      <c r="U120" t="s">
+        <v>108</v>
+      </c>
+      <c r="V120">
+        <v>3</v>
+      </c>
+      <c r="W120" t="s">
+        <v>173</v>
+      </c>
+      <c r="X120" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y120" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z120">
+        <v>4000</v>
+      </c>
+      <c r="AA120">
+        <v>4000</v>
+      </c>
+      <c r="AC120">
+        <v>512</v>
+      </c>
+      <c r="AD120" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE120">
+        <v>0.1</v>
+      </c>
+      <c r="AF120">
+        <v>240</v>
+      </c>
+      <c r="AG120">
+        <v>120</v>
+      </c>
+      <c r="AH120">
+        <v>120</v>
+      </c>
+      <c r="AI120">
+        <v>8.6326044526204557E-2</v>
+      </c>
+      <c r="AJ120">
+        <v>14.146799722733681</v>
+      </c>
+      <c r="AK120">
+        <v>0.72262530601792541</v>
+      </c>
+      <c r="AL120">
+        <v>7.581434566459494E-2</v>
+      </c>
+      <c r="AM120">
+        <v>25.026228384313718</v>
+      </c>
+      <c r="AN120">
+        <v>0.73291761438861314</v>
+      </c>
+      <c r="AO120">
+        <v>25.026228384313718</v>
+      </c>
+      <c r="AP120">
+        <v>25.026228384313718</v>
+      </c>
+      <c r="AQ120">
+        <v>0.73291761438861314</v>
+      </c>
+      <c r="AR120">
+        <v>120.5007286916416</v>
+      </c>
+      <c r="AS120">
+        <v>4.6809187335239033E-2</v>
+      </c>
+      <c r="AT120">
+        <v>0.8</v>
+      </c>
+      <c r="AU120" t="s">
+        <v>91</v>
+      </c>
+      <c r="AV120">
+        <v>4.3604468438270379E-2</v>
+      </c>
+      <c r="AW120">
+        <v>0.68337518036849354</v>
+      </c>
+      <c r="AX120">
+        <v>4.3604468438270379E-2</v>
+      </c>
+      <c r="AY120">
+        <v>4.3604468438270379E-2</v>
+      </c>
+      <c r="AZ120">
+        <v>0.68337518036849354</v>
+      </c>
+      <c r="BA120">
+        <v>0.15250768795884201</v>
+      </c>
+      <c r="BB120">
+        <v>-0.10740300069810479</v>
+      </c>
+      <c r="BC120">
+        <v>0.10193258953106291</v>
+      </c>
+      <c r="BD120">
+        <v>0.64682534824230808</v>
+      </c>
+      <c r="BE120">
+        <v>0.10193258953106291</v>
+      </c>
+      <c r="BF120">
+        <v>0.10193258953106291</v>
+      </c>
+      <c r="BG120">
+        <v>0.64682534824230808</v>
+      </c>
+      <c r="BH120">
+        <v>0.30160015428650921</v>
+      </c>
+      <c r="BI120">
+        <v>-4.4980118235335993E-2</v>
+      </c>
+      <c r="BJ120">
+        <v>2.8422902017742321E-2</v>
+      </c>
+      <c r="BK120">
+        <v>0.88589103861681395</v>
+      </c>
+      <c r="BL120">
+        <v>2.8422902017742321E-2</v>
+      </c>
+      <c r="BM120">
+        <v>2.8422902017742321E-2</v>
+      </c>
+      <c r="BN120">
+        <v>0.88589103861681395</v>
+      </c>
+      <c r="BO120">
+        <v>7.2238055104180895E-2</v>
+      </c>
+      <c r="BP120">
+        <v>0.70998705779114513</v>
+      </c>
+      <c r="BQ120">
+        <v>99.930953577267957</v>
+      </c>
+      <c r="BR120">
+        <v>0.7155788903268383</v>
+      </c>
+      <c r="BS120">
+        <v>99.930953577267957</v>
+      </c>
+      <c r="BT120">
+        <v>99.930953577267957</v>
+      </c>
+      <c r="BU120">
+        <v>0.7155788903268383</v>
+      </c>
+      <c r="BV120">
+        <v>481.47656886921482</v>
+      </c>
+      <c r="BW120">
+        <v>-0.37036718951674041</v>
+      </c>
+    </row>
+    <row r="121" spans="1:75" x14ac:dyDescent="0.3">
+      <c r="A121" s="2">
+        <v>46085.564212962963</v>
+      </c>
+      <c r="B121" t="s">
+        <v>271</v>
+      </c>
+      <c r="C121">
+        <v>3</v>
+      </c>
+      <c r="D121" t="s">
+        <v>101</v>
+      </c>
+      <c r="E121" t="s">
+        <v>77</v>
+      </c>
+      <c r="F121">
+        <v>16590</v>
+      </c>
+      <c r="G121">
+        <v>4.5</v>
+      </c>
+      <c r="H121" t="s">
+        <v>171</v>
+      </c>
+      <c r="I121" t="s">
+        <v>79</v>
+      </c>
+      <c r="J121">
+        <v>5</v>
+      </c>
+      <c r="K121">
+        <v>5</v>
+      </c>
+      <c r="L121" t="s">
+        <v>80</v>
+      </c>
+      <c r="M121" t="s">
+        <v>81</v>
+      </c>
+      <c r="N121" t="s">
+        <v>82</v>
+      </c>
+      <c r="O121" t="s">
+        <v>82</v>
+      </c>
+      <c r="P121" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q121" t="s">
+        <v>269</v>
+      </c>
+      <c r="R121">
+        <v>4</v>
+      </c>
+      <c r="S121" t="s">
+        <v>85</v>
+      </c>
+      <c r="T121" t="s">
+        <v>86</v>
+      </c>
+      <c r="U121" t="s">
+        <v>108</v>
+      </c>
+      <c r="V121">
+        <v>3</v>
+      </c>
+      <c r="W121" t="s">
+        <v>173</v>
+      </c>
+      <c r="X121" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y121" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z121">
+        <v>4000</v>
+      </c>
+      <c r="AA121">
+        <v>4000</v>
+      </c>
+      <c r="AC121">
+        <v>512</v>
+      </c>
+      <c r="AD121" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE121">
+        <v>0.1</v>
+      </c>
+      <c r="AF121">
+        <v>240</v>
+      </c>
+      <c r="AG121">
+        <v>120</v>
+      </c>
+      <c r="AH121">
+        <v>120</v>
+      </c>
+      <c r="AI121">
+        <v>0.10290996228240711</v>
+      </c>
+      <c r="AJ121">
+        <v>26.931966029656579</v>
+      </c>
+      <c r="AK121">
+        <v>0.68443970848741087</v>
+      </c>
+      <c r="AL121">
+        <v>8.6293657915927025E-2</v>
+      </c>
+      <c r="AM121">
+        <v>28.812146797667111</v>
+      </c>
+      <c r="AN121">
+        <v>0.67734594458609443</v>
+      </c>
+      <c r="AO121">
+        <v>28.812146797667111</v>
+      </c>
+      <c r="AP121">
+        <v>28.812146797667111</v>
+      </c>
+      <c r="AQ121">
+        <v>0.67734594458609443</v>
+      </c>
+      <c r="AR121">
+        <v>112.7319246644321</v>
+      </c>
+      <c r="AS121">
+        <v>1.2595647239736749E-2</v>
+      </c>
+      <c r="AT121">
+        <v>0.8</v>
+      </c>
+      <c r="AU121" t="s">
+        <v>91</v>
+      </c>
+      <c r="AV121">
+        <v>3.4941550989431677E-2</v>
+      </c>
+      <c r="AW121">
+        <v>0.74627916184012233</v>
+      </c>
+      <c r="AX121">
+        <v>3.4941550989431677E-2</v>
+      </c>
+      <c r="AY121">
+        <v>3.4941550989431677E-2</v>
+      </c>
+      <c r="AZ121">
+        <v>0.74627916184012233</v>
+      </c>
+      <c r="BA121">
+        <v>0.1223043357798201</v>
+      </c>
+      <c r="BB121">
+        <v>0.1119123878036022</v>
+      </c>
+      <c r="BC121">
+        <v>0.1088797158354875</v>
+      </c>
+      <c r="BD121">
+        <v>0.62275503937868226</v>
+      </c>
+      <c r="BE121">
+        <v>0.1088797158354875</v>
+      </c>
+      <c r="BF121">
+        <v>0.1088797158354875</v>
+      </c>
+      <c r="BG121">
+        <v>0.62275503937868226</v>
+      </c>
+      <c r="BH121">
+        <v>0.26707186033242392</v>
+      </c>
+      <c r="BI121">
+        <v>7.465304569311626E-2</v>
+      </c>
+      <c r="BJ121">
+        <v>8.2765557334563297E-2</v>
+      </c>
+      <c r="BK121">
+        <v>0.66772246620516862</v>
+      </c>
+      <c r="BL121">
+        <v>8.2765557334563297E-2</v>
+      </c>
+      <c r="BM121">
+        <v>8.2765557334563297E-2</v>
+      </c>
+      <c r="BN121">
+        <v>0.66772246620516862</v>
+      </c>
+      <c r="BO121">
+        <v>0.21283797098879029</v>
+      </c>
+      <c r="BP121">
+        <v>0.14552286753565319</v>
+      </c>
+      <c r="BQ121">
+        <v>115.0220003665092</v>
+      </c>
+      <c r="BR121">
+        <v>0.6726271109204025</v>
+      </c>
+      <c r="BS121">
+        <v>115.0220003665092</v>
+      </c>
+      <c r="BT121">
+        <v>115.0220003665092</v>
+      </c>
+      <c r="BU121">
+        <v>0.6726271109204025</v>
+      </c>
+      <c r="BV121">
+        <v>450.32548449062648</v>
+      </c>
+      <c r="BW121">
+        <v>-0.28170571207342049</v>
       </c>
     </row>
   </sheetData>
@@ -37105,7 +38327,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC2417C5-69B1-40A5-8AFE-A835A2C478FA}">
-  <dimension ref="A2:L67"/>
+  <dimension ref="A2:L68"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="41.21875" bestFit="1" customWidth="1"/>
@@ -39217,37 +40439,37 @@
         <v>4</v>
       </c>
       <c r="B57" s="9">
-        <v>0.75718351490092817</v>
+        <v>0.74729526321411399</v>
       </c>
       <c r="C57" s="9">
-        <v>9.0357583941765449E-2</v>
+        <v>6.3444946161929791E-2</v>
       </c>
       <c r="D57" s="9">
-        <v>0.68237250738338795</v>
+        <v>0.69439482652260698</v>
       </c>
       <c r="E57" s="9">
-        <v>0.75559966964583858</v>
+        <v>0.73750301675233876</v>
       </c>
       <c r="F57" s="9">
-        <v>0.7691136920645919</v>
+        <v>0.76854494933908279</v>
       </c>
       <c r="G57" s="9">
-        <v>0.74813842536074693</v>
+        <v>0.73795349022565537</v>
       </c>
       <c r="H57" s="9">
-        <v>0.1345855381242079</v>
+        <v>0.13566558218673344</v>
       </c>
       <c r="I57" s="9">
-        <v>8.8923566883683441E-2</v>
+        <v>7.143883526712741E-2</v>
       </c>
       <c r="J57" s="9">
-        <v>0.3307414800923682</v>
+        <v>0.15582450562264127</v>
       </c>
       <c r="K57" s="9">
-        <v>-0.15751719749678442</v>
+        <v>-0.19636081493414295</v>
       </c>
       <c r="L57" s="9">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.3">
@@ -39483,37 +40705,37 @@
         <v>108</v>
       </c>
       <c r="B64" s="9">
-        <v>0.79986929126743034</v>
+        <v>0.74174735196265329</v>
       </c>
       <c r="C64" s="9">
-        <v>0.12098667290639745</v>
+        <v>1.9829366923802421E-2</v>
       </c>
       <c r="D64" s="9">
-        <v>0.84901952677310621</v>
+        <v>0.77398847126428427</v>
       </c>
       <c r="E64" s="9">
-        <v>0.75043565674835844</v>
+        <v>0.69958837333284574</v>
       </c>
       <c r="F64" s="9">
-        <v>0.78575563806377979</v>
+        <v>0.77295477922112721</v>
       </c>
       <c r="G64" s="9">
-        <v>0.8153458995874403</v>
+        <v>0.73998611136436987</v>
       </c>
       <c r="H64" s="9">
-        <v>0.57687824796147791</v>
+        <v>0.28525657359087447</v>
       </c>
       <c r="I64" s="9">
-        <v>8.955955391420839E-2</v>
+        <v>3.6681367710857005E-2</v>
       </c>
       <c r="J64" s="9">
-        <v>0.48293696159763283</v>
+        <v>-0.14327761614839099</v>
       </c>
       <c r="K64" s="9">
-        <v>-0.79824197526474627</v>
+        <v>-0.48762297573151397</v>
       </c>
       <c r="L64" s="9">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.3">
@@ -39521,113 +40743,151 @@
         <v>86</v>
       </c>
       <c r="B65" s="9">
-        <v>0.79986929126743034</v>
+        <v>0.74174735196265329</v>
       </c>
       <c r="C65" s="9">
-        <v>0.12098667290639745</v>
+        <v>1.9829366923802421E-2</v>
       </c>
       <c r="D65" s="9">
-        <v>0.84901952677310621</v>
+        <v>0.77398847126428427</v>
       </c>
       <c r="E65" s="9">
-        <v>0.75043565674835844</v>
+        <v>0.69958837333284574</v>
       </c>
       <c r="F65" s="9">
-        <v>0.78575563806377979</v>
+        <v>0.77295477922112721</v>
       </c>
       <c r="G65" s="9">
-        <v>0.8153458995874403</v>
+        <v>0.73998611136436987</v>
       </c>
       <c r="H65" s="9">
-        <v>0.57687824796147791</v>
+        <v>0.28525657359087447</v>
       </c>
       <c r="I65" s="9">
-        <v>8.955955391420839E-2</v>
+        <v>3.6681367710857005E-2</v>
       </c>
       <c r="J65" s="9">
-        <v>0.48293696159763283</v>
+        <v>-0.14327761614839099</v>
       </c>
       <c r="K65" s="9">
-        <v>-0.79824197526474627</v>
+        <v>-0.48762297573151397</v>
       </c>
       <c r="L65" s="9">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B66" s="9">
-        <v>0.79986929126743034</v>
+        <v>0.69109350437160655</v>
       </c>
       <c r="C66" s="9">
-        <v>0.12098667290639745</v>
+        <v>7.1966793461338108E-2</v>
       </c>
       <c r="D66" s="9">
-        <v>0.84901952677310621</v>
+        <v>0.71713355298569825</v>
       </c>
       <c r="E66" s="9">
-        <v>0.75043565674835844</v>
+        <v>0.66412972946723092</v>
       </c>
       <c r="F66" s="9">
-        <v>0.78575563806377979</v>
+        <v>0.74904374541884133</v>
       </c>
       <c r="G66" s="9">
-        <v>0.8153458995874403</v>
+        <v>0.66311913666524314</v>
       </c>
       <c r="H66" s="9">
-        <v>0.57687824796147791</v>
+        <v>6.4080541544696626E-2</v>
       </c>
       <c r="I66" s="9">
-        <v>8.955955391420839E-2</v>
+        <v>-2.6949523059307378E-2</v>
       </c>
       <c r="J66" s="9">
-        <v>0.48293696159763283</v>
+        <v>-0.46372969247681556</v>
       </c>
       <c r="K66" s="9">
-        <v>-0.79824197526474627</v>
+        <v>-0.31713387057512138</v>
       </c>
       <c r="L66" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A67" s="3" t="s">
+      <c r="A67" s="8">
+        <v>2</v>
+      </c>
+      <c r="B67" s="9">
+        <v>0.79240119955369981</v>
+      </c>
+      <c r="C67" s="9">
+        <v>-3.2308059613733266E-2</v>
+      </c>
+      <c r="D67" s="9">
+        <v>0.83084338954287018</v>
+      </c>
+      <c r="E67" s="9">
+        <v>0.73504701719846055</v>
+      </c>
+      <c r="F67" s="9">
+        <v>0.79686581302341308</v>
+      </c>
+      <c r="G67" s="9">
+        <v>0.81685308606349671</v>
+      </c>
+      <c r="H67" s="9">
+        <v>0.50643260563705239</v>
+      </c>
+      <c r="I67" s="9">
+        <v>0.10031225848102139</v>
+      </c>
+      <c r="J67" s="9">
+        <v>0.17717446018003358</v>
+      </c>
+      <c r="K67" s="9">
+        <v>-0.65811208088790651</v>
+      </c>
+      <c r="L67" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A68" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="B67" s="9">
-        <v>0.6000573113155343</v>
-      </c>
-      <c r="C67" s="9">
-        <v>-7.3687783208431154E-2</v>
-      </c>
-      <c r="D67" s="9">
-        <v>0.43954667678608356</v>
-      </c>
-      <c r="E67" s="9">
-        <v>0.63567473010720454</v>
-      </c>
-      <c r="F67" s="9">
-        <v>0.52406824138797692</v>
-      </c>
-      <c r="G67" s="9">
-        <v>0.70166207335070352</v>
-      </c>
-      <c r="H67" s="9">
-        <v>-0.10978850568749605</v>
-      </c>
-      <c r="I67" s="9">
-        <v>7.5616782188577758E-2</v>
-      </c>
-      <c r="J67" s="9">
-        <v>0.14440727588182414</v>
-      </c>
-      <c r="K67" s="9">
-        <v>-0.21806963769529558</v>
-      </c>
-      <c r="L67" s="9">
-        <v>116</v>
+      <c r="B68" s="9">
+        <v>0.60381161368202541</v>
+      </c>
+      <c r="C68" s="9">
+        <v>-7.2256499970399929E-2</v>
+      </c>
+      <c r="D68" s="9">
+        <v>0.44944421901020987</v>
+      </c>
+      <c r="E68" s="9">
+        <v>0.63695773015780055</v>
+      </c>
+      <c r="F68" s="9">
+        <v>0.53215111166837104</v>
+      </c>
+      <c r="G68" s="9">
+        <v>0.70168354481410788</v>
+      </c>
+      <c r="H68" s="9">
+        <v>-0.10148069761772709</v>
+      </c>
+      <c r="I68" s="9">
+        <v>7.3437631935931211E-2</v>
+      </c>
+      <c r="J68" s="9">
+        <v>0.12438086985171655</v>
+      </c>
+      <c r="K68" s="9">
+        <v>-0.22187776563761569</v>
+      </c>
+      <c r="L68" s="9">
+        <v>120</v>
       </c>
     </row>
   </sheetData>
